--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -11,189 +11,186 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="116">
   <si>
     <t>📚 مرحلة كي جي (KG):</t>
   </si>
   <si>
-    <t>• المعاصر إنجليزي كي جي 1 ⬅️ 125 (قبل الخصم)</t>
-  </si>
-  <si>
-    <t>• المعاصر ماس كي جي 1 ⬅️ 205 (قبل الخصم)</t>
-  </si>
-  <si>
-    <t>• المعاصر إنجليزي كي جي 2 ⬅️ 125 (قبل الخصم)</t>
-  </si>
-  <si>
-    <t>• المعاصر ماس كي جي 2 ⬅️ 210 (قبل الخصم)</t>
+    <t>• المعاصر إنجليزي كي جي 1 ⬅️ 125</t>
+  </si>
+  <si>
+    <t>• المعاصر ماس كي جي 1 ⬅️ 205</t>
+  </si>
+  <si>
+    <t>• المعاصر إنجليزي كي جي 2 ⬅️ 125</t>
+  </si>
+  <si>
+    <t>• المعاصر ماس كي جي 2 ⬅️ 210</t>
   </si>
   <si>
     <t>🎒 الصف الأول الابتدائي:</t>
   </si>
   <si>
-    <t>• أضواء رياضيات ⬅️ 149 | بعد الخصم: 126.65</t>
-  </si>
-  <si>
-    <t>• أضواء عربي ⬅️ 159 | بعد الخصم: 135.15</t>
-  </si>
-  <si>
-    <t>• أضواء دين ⬅️ 129 | بعد الخصم: 109.65</t>
-  </si>
-  <si>
-    <t>• أضواء جيم إنجليزي ⬅️ 165 | بعد الخصم: 140.25</t>
-  </si>
-  <si>
-    <t>• ستيب أهيد إنجليزي ⬅️ 165 | بعد الخصم: 140.25</t>
-  </si>
-  <si>
-    <t>• بيت باي بيت إنجليزي ⬅️ 135 | بعد الخصم: 114.75</t>
-  </si>
-  <si>
-    <t>• المعاصر إنجليزي ⬅️ 175 | بعد الخصم: 148.75</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ عربي ⬅️ 180 | بعد الخصم: 153.00</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ رياضيات ⬅️ 170 | بعد الخصم: 144.50</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ دين ⬅️ 130 | بعد الخصم: 110.50</t>
-  </si>
-  <si>
-    <t>• تأسيس سليم عربي ⬅️ 175 | بعد الخصم: 148.75</t>
-  </si>
-  <si>
-    <t>• تأسيس سليم رياضيات ⬅️ 169 | بعد الخصم: 143.65</t>
-  </si>
-  <si>
-    <t>• المعاصر ماث لغات ⬅️ 255| بعد الخصم: 216.75</t>
-  </si>
-  <si>
-    <t>• المعاصر رياضه بالعربي ⬅️ 165| بعد الخصم: 140.25</t>
+    <t xml:space="preserve">• أضواء رياضيات ⬅️ 149 </t>
+  </si>
+  <si>
+    <t>• أضواء عربي ⬅️ 159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• أضواء دين ⬅️ 129 </t>
+  </si>
+  <si>
+    <t>• أضواء جيم إنجليزي ⬅️ 165</t>
+  </si>
+  <si>
+    <t>• ستيب أهيد إنجليزي ⬅️ 165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• بيت باي بيت إنجليزي ⬅️ 135 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">• المعاصر إنجليزي ⬅️ 175 </t>
+  </si>
+  <si>
+    <t>• سلاح التلميذ عربي ⬅️ 180</t>
+  </si>
+  <si>
+    <t>• سلاح التلميذ رياضيات ⬅️ 170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• سلاح التلميذ دين ⬅️ 130 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">• تأسيس سليم عربي ⬅️ 175 </t>
+  </si>
+  <si>
+    <t>• تأسيس سليم رياضيات ⬅️ 169</t>
+  </si>
+  <si>
+    <t>• المعاصر ماث لغات ⬅️ 255</t>
+  </si>
+  <si>
+    <t>• المعاصر رياضه بالعربي ⬅️ 165</t>
   </si>
   <si>
     <t>🎒 الصف الثاني الابتدائي:</t>
   </si>
   <si>
-    <t>• أضواء رياضيات ⬅️ 159 | بعد الخصم: 135.15</t>
-  </si>
-  <si>
-    <t>• أضواء دين ⬅️ 139 | بعد الخصم: 118.15</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ دين ⬅️ 140 | بعد الخصم: 119.00</t>
+    <t>• أضواء رياضيات ⬅️ 159</t>
+  </si>
+  <si>
+    <t>• أضواء دين ⬅️ 139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• سلاح التلميذ دين ⬅️ 140 </t>
   </si>
   <si>
     <t>🎒 الصف الثالث الابتدائي:</t>
   </si>
   <si>
-    <t>• أضواء عربي ⬅️ 169 | بعد الخصم: 143.65</t>
-  </si>
-  <si>
-    <t>• ستيب أهيد إنجليزي ⬅️ 185 | بعد الخصم: 157.25</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ عربي ⬅️ 190 | بعد الخصم: 161.50</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ رياضيات ⬅️ 175 | بعد الخصم: 148.75</t>
-  </si>
-  <si>
-    <t>• بيت باي بيت  ⬅️ 140 | بعد الخصم: 119.00</t>
-  </si>
-  <si>
-    <t>• التأسيس السيلم عربي  ⬅️ 179 | بعد الخصم: 152.15</t>
-  </si>
-  <si>
-    <t>• التأسيس السليم حساب  ⬅️ 179 | بعد الخصم: 152.15</t>
-  </si>
-  <si>
-    <t>• المعاصر انجليزي ⬅️ 189 | بعد الخصم: 160.65</t>
+    <t>• أضواء عربي ⬅️ 169</t>
+  </si>
+  <si>
+    <t>• ستيب أهيد إنجليزي ⬅️ 185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• سلاح التلميذ عربي ⬅️ 190 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">• سلاح التلميذ رياضيات ⬅️ 175 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">• بيت باي بيت  ⬅️ 140 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">• التأسيس السيلم عربي  ⬅️ 179 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">• التأسيس السليم حساب  ⬅️ 179 </t>
+  </si>
+  <si>
+    <t>• المعاصر انجليزي ⬅️ 189</t>
   </si>
   <si>
     <t>🎒 الصف الرابع الابتدائي:</t>
   </si>
   <si>
-    <t>• أضواء عربي ⬅️ 195 | بعد الخصم: 165.75</t>
-  </si>
-  <si>
-    <t>• أضواء رياضيات ⬅️ 165 | بعد الخصم: 140.25</t>
-  </si>
-  <si>
-    <t>• أضواء دراسات ⬅️ 159 | بعد الخصم: 135.15</t>
-  </si>
-  <si>
-    <t>• المعاصر إنجليزي ⬅️ 189 | بعد الخصم: 160.65</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ عربي ⬅️ 215 | بعد الخصم: 182.75</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ دراسات ⬅️ 185 | بعد الخصم: 157.25</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ رياضيات ⬅️ 190 | بعد الخصم: 161.50</t>
-  </si>
-  <si>
-    <t>• الإمتحان دراسات ⬅️ 169 | بعد الخصم: 143.65</t>
-  </si>
-  <si>
-    <t>• الإمتحان عربي ⬅️ 205 | بعد الخصم: 174.25</t>
-  </si>
-  <si>
-    <t>• تأسيس سليم عربي ⬅️ 189 | بعد الخصم: 160.65</t>
-  </si>
-  <si>
-    <t>• جيم الاضواء انجليزي ⬅️ 169 | بعد الخصم: 143.65</t>
-  </si>
-  <si>
-    <t>• المعاصر ماث لغات ⬅️ 315| بعد الخصم: 268</t>
+    <t xml:space="preserve">• أضواء عربي ⬅️ 195 </t>
+  </si>
+  <si>
+    <t>• أضواء رياضيات ⬅️ 165</t>
+  </si>
+  <si>
+    <t>• أضواء دراسات ⬅️ 159</t>
+  </si>
+  <si>
+    <t>• المعاصر إنجليزي ⬅️ 189</t>
+  </si>
+  <si>
+    <t>• سلاح التلميذ عربي ⬅️ 215</t>
+  </si>
+  <si>
+    <t>• سلاح التلميذ دراسات ⬅️ 185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• سلاح التلميذ رياضيات ⬅️ 190 </t>
+  </si>
+  <si>
+    <t>• الإمتحان دراسات ⬅️ 169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• الإمتحان عربي ⬅️ 205 </t>
+  </si>
+  <si>
+    <t>• تأسيس سليم عربي ⬅️ 189</t>
+  </si>
+  <si>
+    <t>• جيم الاضواء انجليزي ⬅️ 169</t>
+  </si>
+  <si>
+    <t>• المعاصر ماث لغات ⬅️ 315</t>
   </si>
   <si>
     <t>🎒 الصف الخامس الابتدائي:</t>
   </si>
   <si>
-    <t>• أضواء رياضيات ⬅️ 169 | بعد الخصم: 143.65</t>
-  </si>
-  <si>
-    <t>• ستيب أهيد إنجليزي ⬅️ 187 | بعد الخصم: 158.95</t>
-  </si>
-  <si>
-    <t>• بيت باي بيت إنجليزي ⬅️ 155 | بعد الخصم: 131.75</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ عربي⬅️ 215 | بعد الخصم: 182.75</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ دراسات ⬅️ 185| بعد الخصم: 157.25</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ رياضه⬅️ 190 بعد الخصم 161.5</t>
-  </si>
-  <si>
-    <t>• جيم الاضواء انجليزي ⬅️ 179 | بعد الخصم: 152.15</t>
+    <t>• أضواء رياضيات ⬅️ 169</t>
+  </si>
+  <si>
+    <t>• ستيب أهيد إنجليزي ⬅️ 187</t>
+  </si>
+  <si>
+    <t>• بيت باي بيت إنجليزي ⬅️ 155</t>
+  </si>
+  <si>
+    <t>• سلاح التلميذ عربي⬅️ 215</t>
+  </si>
+  <si>
+    <t>• سلاح التلميذ رياضه⬅️ 190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• جيم الاضواء انجليزي ⬅️ 179 </t>
   </si>
   <si>
     <t>🎒 الصف السادس الابتدائي:</t>
   </si>
   <si>
-    <t>• أضواء عربي ⬅️ 199 | بعد الخصم: 169.15</t>
-  </si>
-  <si>
-    <t>• أضواء جيم إنجليزي ⬅️ 179 | بعد الخصم: 152.15</t>
-  </si>
-  <si>
-    <t>• ستيب أهيد إنجليزي ⬅️ 195 | بعد الخصم: 165.75</t>
-  </si>
-  <si>
-    <t>• سلاح عربي ⬅️ 220| بعد الخصم: 187</t>
-  </si>
-  <si>
-    <t>• سلاح رياضه ⬅️ 190| بعد الخصم: 161.5</t>
-  </si>
-  <si>
-    <t>• سلاح دراسات ⬅️ 185| بعد الخصم: 157.25</t>
+    <t>• أضواء عربي ⬅️ 199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• أضواء جيم إنجليزي ⬅️ 179 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">• ستيب أهيد إنجليزي ⬅️ 195 </t>
+  </si>
+  <si>
+    <t>• سلاح عربي ⬅️ 220</t>
+  </si>
+  <si>
+    <t>• سلاح رياضه ⬅️ 190</t>
+  </si>
+  <si>
+    <t>• سلاح دراسات ⬅️ 185</t>
   </si>
   <si>
     <t>• سلاح دين ⬅️ 145 | بعد الخصم: 123.25</t>
@@ -202,64 +199,78 @@
     <t>🎒 الصف الأول الإعدادي:</t>
   </si>
   <si>
-    <t>• أضواء عربي أولى إعدادي ⬅️ 199 | بعد الخصم: 169.15</t>
-  </si>
-  <si>
-    <t>• أضواء دين أولى إعدادي ⬅️ 139 | بعد الخصم: 118.15</t>
-  </si>
-  <si>
-    <t>• أضواء علوم أولى إعدادي ⬅️ 185 | بعد الخصم: 157.25</t>
-  </si>
-  <si>
-    <t>• أضواء دراسات أولى إعدادي ⬅️ 175 | بعد الخصم: 148.75</t>
-  </si>
-  <si>
-    <t>• أضواء جيم إنجليزي أولى إعدادي ⬅️ 199 | بعد الخصم: 169.15</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ دين أولى إعدادي ⬅️ 145 | بعد الخصم: 123.25</t>
-  </si>
-  <si>
-    <t>• إمتحان عربي أولى إعدادي ⬅️ 220 | بعد الخصم: 187.00</t>
-  </si>
-  <si>
-    <t>• إمتحان دراسات أولى إعدادي ⬅️ 187 | بعد الخصم: 158.95</t>
+    <t>• أضواء عربي أولى إعدادي ⬅️ 199</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>• أضواء دين أولى إعدادي ⬅️</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <strike/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> 139</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">• أضواء علوم أولى إعدادي ⬅️ 185 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">• أضواء دراسات أولى إعدادي ⬅️ 175 </t>
+  </si>
+  <si>
+    <t>• أضواء جيم إنجليزي أولى إعدادي ⬅️ 199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• سلاح التلميذ دين أولى إعدادي ⬅️ 145 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">• إمتحان عربي أولى إعدادي ⬅️ 220 </t>
+  </si>
+  <si>
+    <t>• إمتحان دراسات أولى إعدادي ⬅️ 187</t>
   </si>
   <si>
     <t>• إمتحان علوم أولى إعدادي ⬅️ ما نزلش</t>
   </si>
   <si>
-    <t>• المعاصر رياضيات أولى إعدادي ⬅️ 185 | بعد الخصم: 157.25</t>
-  </si>
-  <si>
-    <t>• المعاصر انجليزي ⬅️ 199 | بعد الخصم: 170</t>
+    <t xml:space="preserve">• المعاصر رياضيات أولى إعدادي ⬅️ 185 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">• المعاصر انجليزي ⬅️ 199 </t>
   </si>
   <si>
     <t>🎒 الصف الثاني الإعدادي:</t>
   </si>
   <si>
-    <t>• أضواء دراسات تانية إعدادي ⬅️ 179 | بعد الخصم: 152.15</t>
-  </si>
-  <si>
-    <t>• أضواء علوم تانية إعدادي ⬅️ 185 | بعد الخصم: 157.25</t>
-  </si>
-  <si>
-    <t>• بيت باي بيت إنجليزي تانية إعدادي ⬅️ 150 | بعد الخصم: 127.50</t>
-  </si>
-  <si>
-    <t>• إمتحان عربي تانية إعدادي ⬅️ 220 | بعد الخصم: 187.00</t>
-  </si>
-  <si>
-    <t>• إمتحان دراسات تانية إعدادي ⬅️ 189 | بعد الخصم: 160.65</t>
-  </si>
-  <si>
-    <t>• إمتحان علوم تانية إعدادي ⬅️ 189 | بعد الخصم: 160.65</t>
-  </si>
-  <si>
-    <t>• المعاصر رياضيات تانية إعدادي ⬅️ 185 | بعد الخصم: 157.25</t>
-  </si>
-  <si>
-    <t>• الاضواء عربي ⬅️ 199 | بعد الخصم: 170</t>
+    <t xml:space="preserve">• أضواء دراسات تانية إعدادي ⬅️ 179 </t>
+  </si>
+  <si>
+    <t>• أضواء علوم تانية إعدادي ⬅️ 185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• بيت باي بيت إنجليزي تانية إعدادي ⬅️ 150 </t>
+  </si>
+  <si>
+    <t>• إمتحان عربي تانية إعدادي ⬅️ 220 .00</t>
+  </si>
+  <si>
+    <t>• إمتحان دراسات تانية إعدادي ⬅️ 189</t>
+  </si>
+  <si>
+    <t>• إمتحان علوم تانية إعدادي ⬅️ 189</t>
+  </si>
+  <si>
+    <t>• المعاصر رياضيات تانية إعدادي ⬅️ 185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• الاضواء عربي ⬅️ 199 </t>
   </si>
   <si>
     <t>• الاضواء دين ⬅️ 149 | بعد الخصم: 127</t>
@@ -268,28 +279,28 @@
     <t>🎒 الصف الثالث الإعدادي:</t>
   </si>
   <si>
-    <t>• أضواء عربي تالتة إعدادي ⬅️ 215 | بعد الخصم: 182.75</t>
-  </si>
-  <si>
-    <t>• بيت باي بيت إنجليزي تالتة إعدادي ⬅️ 150 | بعد الخصم: 127.50</t>
-  </si>
-  <si>
-    <t>• جيم الاضواء انجليزي ⬅️ 199 | بعد الخصم: 170</t>
+    <t>• أضواء عربي تالتة إعدادي ⬅️ 215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• بيت باي بيت إنجليزي تالتة إعدادي ⬅️ 150 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">• جيم الاضواء انجليزي ⬅️ 199 </t>
   </si>
   <si>
     <t>🎓 الثانوية العامة (أولى ثانوي):</t>
   </si>
   <si>
-    <t>• انجليزي جيم الاضواء  ⬅️ 275 | بعد الخصم 233.75</t>
+    <t xml:space="preserve">• انجليزي جيم الاضواء  ⬅️ 275 </t>
   </si>
   <si>
     <t>• عربي الأضواء ⬅️ 239 | بعدالخصم 203.1</t>
   </si>
   <si>
-    <t>- امتحان تاريخ اولى ثانوني ⬅️ 174 | بعدالخصم 148</t>
-  </si>
-  <si>
-    <t>- امتحان فلسفه اولى ثانوي ⬅️ 185 | بعدالخصم 157.25</t>
+    <t xml:space="preserve">- امتحان تاريخ اولى ثانوني ⬅️ 174 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- امتحان فلسفه اولى ثانوي ⬅️ 185 </t>
   </si>
   <si>
     <t>🎓 الثانوية العامة (تانية ثانوي):</t>
@@ -623,7 +634,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="40.13"/>
+    <col customWidth="1" min="1" max="1" width="18.75"/>
     <col customWidth="1" min="2" max="2" width="38.63"/>
   </cols>
   <sheetData>
@@ -1517,7 +1528,7 @@
         <v>46</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C60" s="2">
         <v>185.0</v>
@@ -1532,7 +1543,7 @@
         <v>46</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C61" s="2">
         <v>190.0</v>
@@ -1547,7 +1558,7 @@
         <v>46</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C62" s="2">
         <v>179.0</v>
@@ -1559,10 +1570,10 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="C63" s="2">
         <v>199.0</v>
@@ -1574,7 +1585,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>47</v>
@@ -1589,10 +1600,10 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C65" s="2">
         <v>179.0</v>
@@ -1604,10 +1615,10 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C66" s="2">
         <v>195.0</v>
@@ -1619,7 +1630,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>49</v>
@@ -1634,7 +1645,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>37</v>
@@ -1649,10 +1660,10 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C69" s="2">
         <v>220.0</v>
@@ -1664,10 +1675,10 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C70" s="2">
         <v>190.0</v>
@@ -1679,10 +1690,10 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C71" s="2">
         <v>185.0</v>
@@ -1694,10 +1705,10 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C72" s="2">
         <v>145.0</v>
@@ -1709,10 +1720,10 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C73" s="2">
         <v>199.0</v>
@@ -1724,10 +1735,10 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C74" s="2">
         <v>139.0</v>
@@ -1739,10 +1750,10 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C75" s="2">
         <v>185.0</v>
@@ -1754,10 +1765,10 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C76" s="2">
         <v>175.0</v>
@@ -1769,10 +1780,10 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C77" s="2">
         <v>199.0</v>
@@ -1784,10 +1795,10 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C78" s="2">
         <v>145.0</v>
@@ -1799,10 +1810,10 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C79" s="2">
         <v>220.0</v>
@@ -1814,10 +1825,10 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C80" s="2">
         <v>187.0</v>
@@ -1829,10 +1840,10 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C81" s="2">
         <v>0.0</v>
@@ -1844,10 +1855,10 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C82" s="2">
         <v>185.0</v>
@@ -1859,10 +1870,10 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C83" s="2">
         <v>199.0</v>
@@ -1874,10 +1885,10 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="C84" s="2">
         <v>179.0</v>
@@ -1889,10 +1900,10 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C85" s="2">
         <v>185.0</v>
@@ -1904,10 +1915,10 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C86" s="2">
         <v>150.0</v>
@@ -1919,10 +1930,10 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C87" s="2">
         <v>220.0</v>
@@ -1934,10 +1945,10 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C88" s="2">
         <v>189.0</v>
@@ -1949,10 +1960,10 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C89" s="2">
         <v>189.0</v>
@@ -1964,10 +1975,10 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C90" s="2">
         <v>185.0</v>
@@ -1979,10 +1990,10 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C91" s="2">
         <v>199.0</v>
@@ -1994,10 +2005,10 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C92" s="2">
         <v>199.0</v>
@@ -2009,10 +2020,10 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C93" s="2">
         <v>149.0</v>
@@ -2024,10 +2035,10 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C94" s="2">
         <v>215.0</v>
@@ -2039,10 +2050,10 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C95" s="2">
         <v>150.0</v>
@@ -2054,10 +2065,10 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C96" s="2">
         <v>199.0</v>
@@ -2069,10 +2080,10 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="C97" s="2">
         <v>275.0</v>
@@ -2084,10 +2095,10 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C98" s="2">
         <v>239.0</v>
@@ -2099,10 +2110,10 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C99" s="2">
         <v>174.0</v>
@@ -2114,10 +2125,10 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C100" s="2">
         <v>185.0</v>
@@ -2129,10 +2140,10 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C101" s="2">
         <v>0.0</v>
@@ -2144,90 +2155,90 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C102" s="2">
         <v>0.0</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D107" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B108" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D109" s="2">
         <v>340.0</v>
@@ -2235,32 +2246,32 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D110" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B111" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D111" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C112" s="2">
         <v>278.0</v>
@@ -2271,10 +2282,10 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C113" s="2">
         <v>405.0</v>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD31485-EB55-4E6F-A1EB-D46E0C4BD34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA237097-6C75-4332-B821-FE01A670E66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="116">
   <si>
     <t>📚 مرحلة كي جي (KG):</t>
   </si>
@@ -674,14 +674,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="38.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -692,11 +692,11 @@
         <v>125</v>
       </c>
       <c r="D1" s="1">
-        <f t="shared" ref="D1:D106" si="0">C1-C1*15/100</f>
+        <f t="shared" ref="D1:D107" si="0">C1-C1*15/100</f>
         <v>106.25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>174.25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -726,7 +726,7 @@
         <v>106.25</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -741,7 +741,7 @@
         <v>178.5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -756,7 +756,7 @@
         <v>126.65</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -771,7 +771,7 @@
         <v>135.15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -786,7 +786,7 @@
         <v>109.65</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -801,7 +801,7 @@
         <v>140.25</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,7 +816,7 @@
         <v>140.25</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -831,7 +831,7 @@
         <v>114.75</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -846,7 +846,7 @@
         <v>148.75</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -861,7 +861,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
@@ -876,7 +876,7 @@
         <v>144.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -891,7 +891,7 @@
         <v>110.5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -906,7 +906,7 @@
         <v>148.75</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
@@ -921,7 +921,7 @@
         <v>143.65</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -936,7 +936,7 @@
         <v>216.75</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -951,7 +951,7 @@
         <v>140.25</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -966,7 +966,7 @@
         <v>135.15</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
@@ -981,7 +981,7 @@
         <v>135.15</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -996,7 +996,7 @@
         <v>118.15</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>140.25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>20</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>140.25</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>20</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>114.75</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>148.75</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>20</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>20</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>144.5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>20</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>20</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>148.75</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>143.65</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>24</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>140.25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>24</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>118.15</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>24</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>157.25</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>24</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>161.5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>24</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>148.75</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>24</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>24</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>24</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>143.65</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>24</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>152.15</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>24</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>152.15</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>160.65</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>33</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>165.75</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>33</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>140.25</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>33</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>135.15</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>33</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>157.25</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>33</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>160.65</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>33</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>182.75</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>33</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>157.25</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>33</v>
       </c>
@@ -1416,7 +1416,7 @@
         <v>161.5</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>33</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>143.65</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>33</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>174.25</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>33</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>160.65</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>33</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>143.65</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>33</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>267.75</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>33</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>144.5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>46</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>165.75</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>46</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>135.15</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>46</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>143.65</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>46</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>158.94999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>46</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>131.75</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>46</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>160.65</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>46</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>182.75</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>46</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>157.25</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>46</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>161.5</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>46</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>152.15</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>46</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>250.75</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>53</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>169.15</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>53</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>143.65</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>53</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>152.15</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>53</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>165.75</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>53</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>131.75</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>53</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>160.65</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>53</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>53</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>161.5</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>53</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>157.25</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>53</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>123.25</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>61</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>169.15</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>61</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>118.15</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>61</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>157.25</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>61</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>148.75</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>61</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>169.15</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>61</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>123.25</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>61</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>61</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>158.94999999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>61</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>61</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>157.25</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>61</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>169.15</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>61</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>73</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>152.15</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>73</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>157.25</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>73</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>73</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>73</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>160.65</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>73</v>
       </c>
@@ -2091,42 +2091,42 @@
         <v>160.65</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C95" s="1">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D95" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+        <f t="shared" ref="D95" si="1">C95-C95*15/100</f>
+        <v>169.15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C96" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D96" s="1">
         <f t="shared" si="0"/>
-        <v>169.15</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+        <v>157.25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C97" s="1">
         <v>199</v>
@@ -2136,349 +2136,349 @@
         <v>169.15</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C98" s="1">
+        <v>199</v>
+      </c>
+      <c r="D98" s="1">
+        <f t="shared" si="0"/>
+        <v>169.15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C98" s="1">
+      <c r="C99" s="1">
         <v>149</v>
       </c>
-      <c r="D98" s="1">
+      <c r="D99" s="1">
         <f t="shared" si="0"/>
         <v>126.65</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C99" s="1">
-        <v>215</v>
-      </c>
-      <c r="D99" s="1">
-        <f t="shared" si="0"/>
-        <v>182.75</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C100" s="1">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="D100" s="1">
         <f t="shared" si="0"/>
-        <v>127.5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+        <v>182.75</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B101" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C101" s="1">
+        <v>150</v>
+      </c>
+      <c r="D101" s="1">
+        <f t="shared" si="0"/>
+        <v>127.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C101" s="1">
+      <c r="C102" s="1">
         <v>199</v>
       </c>
-      <c r="D101" s="1">
+      <c r="D102" s="1">
         <f t="shared" si="0"/>
         <v>169.15</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C102" s="1">
-        <v>275</v>
-      </c>
-      <c r="D102" s="1">
-        <f t="shared" si="0"/>
-        <v>233.75</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="C103" s="1">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="D103" s="1">
         <f t="shared" si="0"/>
-        <v>203.15</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+        <v>233.75</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>89</v>
+      <c r="B104" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C104" s="1">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="D104" s="1">
         <f t="shared" si="0"/>
-        <v>147.9</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+        <v>203.15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C105" s="1">
+        <v>174</v>
+      </c>
+      <c r="D105" s="1">
+        <f t="shared" si="0"/>
+        <v>147.9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C105" s="1">
+      <c r="C106" s="1">
         <v>185</v>
       </c>
-      <c r="D105" s="1">
+      <c r="D106" s="1">
         <f t="shared" si="0"/>
         <v>157.25</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" s="1" t="s">
+    <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B107" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C106" s="1">
+      <c r="C107" s="1">
         <v>249</v>
       </c>
-      <c r="D106" s="1">
+      <c r="D107" s="1">
         <f t="shared" si="0"/>
         <v>211.65</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C107" s="1">
-        <v>218</v>
-      </c>
-      <c r="D107" s="1">
-        <f t="shared" ref="D107:D123" si="1">C107-C107*15/100</f>
-        <v>185.3</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C108" s="1">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="D108" s="1">
-        <f t="shared" si="1"/>
-        <v>225.25</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+        <f t="shared" ref="D108:D124" si="2">C108-C108*15/100</f>
+        <v>185.3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C109" s="1">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" si="1"/>
-        <v>242.25</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+        <f t="shared" si="2"/>
+        <v>225.25</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C110" s="1">
-        <v>340</v>
+        <v>285</v>
       </c>
       <c r="D110" s="1">
-        <f t="shared" si="1"/>
-        <v>289</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+        <f t="shared" si="2"/>
+        <v>242.25</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C111" s="1">
-        <v>215</v>
+        <v>340</v>
       </c>
       <c r="D111" s="1">
-        <f t="shared" si="1"/>
-        <v>182.75</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+        <f t="shared" si="2"/>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C112">
-        <v>230</v>
+        <v>108</v>
+      </c>
+      <c r="C112" s="1">
+        <v>215</v>
       </c>
       <c r="D112" s="1">
-        <f t="shared" si="1"/>
-        <v>195.5</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+        <f t="shared" si="2"/>
+        <v>182.75</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C113">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="D113" s="1">
-        <f t="shared" si="1"/>
-        <v>169.15</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+        <f t="shared" si="2"/>
+        <v>195.5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C114">
-        <v>445</v>
+        <v>199</v>
       </c>
       <c r="D114" s="1">
-        <f t="shared" si="1"/>
-        <v>378.25</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+        <f t="shared" si="2"/>
+        <v>169.15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C115">
-        <v>400</v>
+        <v>445</v>
       </c>
       <c r="D115" s="1">
-        <f t="shared" si="1"/>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+        <f t="shared" si="2"/>
+        <v>378.25</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C116">
-        <v>299</v>
+        <v>400</v>
       </c>
       <c r="D116" s="1">
-        <f t="shared" si="1"/>
-        <v>254.15</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+        <f t="shared" si="2"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C117">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="D117" s="1">
-        <f t="shared" si="1"/>
-        <v>276.25</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+        <f t="shared" si="2"/>
+        <v>254.15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C118" s="1">
-        <v>278</v>
+        <v>114</v>
+      </c>
+      <c r="C118">
+        <v>325</v>
       </c>
       <c r="D118" s="1">
-        <f t="shared" si="1"/>
-        <v>236.3</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+        <f t="shared" si="2"/>
+        <v>276.25</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C119" s="1">
-        <v>405</v>
+        <v>278</v>
       </c>
       <c r="D119" s="1">
-        <f t="shared" si="1"/>
-        <v>344.25</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="2"/>
+        <v>236.3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C120">
-        <v>360</v>
+        <v>94</v>
+      </c>
+      <c r="C120" s="1">
+        <v>405</v>
       </c>
       <c r="D120" s="1">
-        <f t="shared" si="1"/>
-        <v>306</v>
+        <f t="shared" si="2"/>
+        <v>344.25</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2486,14 +2486,14 @@
         <v>92</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C121">
-        <v>249</v>
+        <v>360</v>
       </c>
       <c r="D121" s="1">
-        <f t="shared" si="1"/>
-        <v>211.65</v>
+        <f t="shared" si="2"/>
+        <v>306</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2501,14 +2501,14 @@
         <v>92</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C122">
-        <v>329</v>
+        <v>249</v>
       </c>
       <c r="D122" s="1">
-        <f t="shared" si="1"/>
-        <v>279.64999999999998</v>
+        <f t="shared" si="2"/>
+        <v>211.65</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2516,13 +2516,28 @@
         <v>92</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C123">
+        <v>329</v>
+      </c>
+      <c r="D123" s="1">
+        <f t="shared" si="2"/>
+        <v>279.64999999999998</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C123">
+      <c r="C124">
         <v>275</v>
       </c>
-      <c r="D123" s="1">
-        <f t="shared" si="1"/>
+      <c r="D124" s="1">
+        <f t="shared" si="2"/>
         <v>233.75</v>
       </c>
     </row>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA237097-6C75-4332-B821-FE01A670E66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E05650F-5B2C-4F60-8807-2BF688919A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="117">
   <si>
     <t>📚 مرحلة كي جي (KG):</t>
   </si>
@@ -395,6 +395,9 @@
   </si>
   <si>
     <t>• عربي الأضواء ⬅️ 239</t>
+  </si>
+  <si>
+    <t>• أضواء دراسات ⬅️ 165</t>
   </si>
 </sst>
 </file>
@@ -674,7 +677,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D125"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -692,7 +695,7 @@
         <v>125</v>
       </c>
       <c r="D1" s="1">
-        <f t="shared" ref="D1:D107" si="0">C1-C1*15/100</f>
+        <f t="shared" ref="D1:D108" si="0">C1-C1*15/100</f>
         <v>106.25</v>
       </c>
     </row>
@@ -1706,14 +1709,14 @@
         <v>53</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="C69" s="1">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f t="shared" ref="D69" si="1">C69-C69*15/100</f>
+        <v>140.25</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1721,14 +1724,14 @@
         <v>53</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C70" s="1">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D70" s="1">
         <f t="shared" si="0"/>
-        <v>165.75</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1736,14 +1739,14 @@
         <v>53</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C71" s="1">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="D71" s="1">
         <f t="shared" si="0"/>
-        <v>131.75</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1751,14 +1754,14 @@
         <v>53</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C72" s="1">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="D72" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1766,14 +1769,14 @@
         <v>53</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C73" s="1">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="D73" s="1">
         <f t="shared" si="0"/>
-        <v>187</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1781,14 +1784,14 @@
         <v>53</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C74" s="1">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="D74" s="1">
         <f t="shared" si="0"/>
-        <v>161.5</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1796,14 +1799,14 @@
         <v>53</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C75" s="1">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D75" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1811,29 +1814,29 @@
         <v>53</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C76" s="1">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="D76" s="1">
         <f t="shared" si="0"/>
-        <v>123.25</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C77" s="1">
-        <v>199</v>
+        <v>145</v>
       </c>
       <c r="D77" s="1">
         <f t="shared" si="0"/>
-        <v>169.15</v>
+        <v>123.25</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1841,14 +1844,14 @@
         <v>61</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C78" s="1">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="D78" s="1">
         <f t="shared" si="0"/>
-        <v>118.15</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1856,14 +1859,14 @@
         <v>61</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C79" s="1">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="D79" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>118.15</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1871,14 +1874,14 @@
         <v>61</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C80" s="1">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D80" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1886,14 +1889,14 @@
         <v>61</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C81" s="1">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="D81" s="1">
         <f t="shared" si="0"/>
-        <v>169.15</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1901,14 +1904,14 @@
         <v>61</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C82" s="1">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="D82" s="1">
         <f t="shared" si="0"/>
-        <v>123.25</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1916,14 +1919,14 @@
         <v>61</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C83" s="1">
-        <v>220</v>
+        <v>145</v>
       </c>
       <c r="D83" s="1">
         <f t="shared" si="0"/>
-        <v>187</v>
+        <v>123.25</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1931,14 +1934,14 @@
         <v>61</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C84" s="1">
+        <v>220</v>
+      </c>
+      <c r="D84" s="1">
+        <f t="shared" si="0"/>
         <v>187</v>
-      </c>
-      <c r="D84" s="1">
-        <f t="shared" si="0"/>
-        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1946,14 +1949,14 @@
         <v>61</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C85" s="1">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="D85" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1961,14 +1964,14 @@
         <v>61</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C86" s="1">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="D86" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1976,14 +1979,14 @@
         <v>61</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C87" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D87" s="1">
         <f t="shared" si="0"/>
-        <v>169.15</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1991,29 +1994,29 @@
         <v>61</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C88" s="1">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="D88" s="1">
         <f t="shared" si="0"/>
-        <v>127.5</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C89" s="1">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="D89" s="1">
         <f t="shared" si="0"/>
-        <v>152.15</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2021,14 +2024,14 @@
         <v>73</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C90" s="1">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D90" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2036,14 +2039,14 @@
         <v>73</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C91" s="1">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="D91" s="1">
         <f t="shared" si="0"/>
-        <v>127.5</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2051,14 +2054,14 @@
         <v>73</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C92" s="1">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="D92" s="1">
         <f t="shared" si="0"/>
-        <v>187</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2066,14 +2069,14 @@
         <v>73</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C93" s="1">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="D93" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2081,7 +2084,7 @@
         <v>73</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C94" s="1">
         <v>189</v>
@@ -2096,14 +2099,14 @@
         <v>73</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C95" s="1">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D95" s="1">
-        <f t="shared" ref="D95" si="1">C95-C95*15/100</f>
-        <v>169.15</v>
+        <f t="shared" si="0"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2111,14 +2114,14 @@
         <v>73</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C96" s="1">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D96" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f t="shared" ref="D96" si="2">C96-C96*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2126,14 +2129,14 @@
         <v>73</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C97" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D97" s="1">
         <f t="shared" si="0"/>
-        <v>169.15</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2141,7 +2144,7 @@
         <v>73</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C98" s="1">
         <v>199</v>
@@ -2156,29 +2159,29 @@
         <v>73</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C99" s="1">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="D99" s="1">
         <f t="shared" si="0"/>
-        <v>126.65</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C100" s="1">
-        <v>215</v>
+        <v>149</v>
       </c>
       <c r="D100" s="1">
         <f t="shared" si="0"/>
-        <v>182.75</v>
+        <v>126.65</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2186,14 +2189,14 @@
         <v>83</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C101" s="1">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="D101" s="1">
         <f t="shared" si="0"/>
-        <v>127.5</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2201,29 +2204,29 @@
         <v>83</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C102" s="1">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="D102" s="1">
         <f t="shared" si="0"/>
-        <v>169.15</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C103" s="1">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="D103" s="1">
         <f t="shared" si="0"/>
-        <v>233.75</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2231,29 +2234,29 @@
         <v>87</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="C104" s="1">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="D104" s="1">
         <f t="shared" si="0"/>
-        <v>203.15</v>
+        <v>233.75</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>89</v>
+      <c r="B105" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C105" s="1">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="D105" s="1">
         <f t="shared" si="0"/>
-        <v>147.9</v>
+        <v>203.15</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2261,44 +2264,44 @@
         <v>87</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C106" s="1">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="D106" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>100</v>
+        <v>87</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C107" s="1">
-        <v>249</v>
+        <v>185</v>
       </c>
       <c r="D107" s="1">
         <f t="shared" si="0"/>
-        <v>211.65</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C108" s="1">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="D108" s="1">
-        <f t="shared" ref="D108:D124" si="2">C108-C108*15/100</f>
-        <v>185.3</v>
+        <f t="shared" si="0"/>
+        <v>211.65</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2306,14 +2309,14 @@
         <v>92</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C109" s="1">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" si="2"/>
-        <v>225.25</v>
+        <f t="shared" ref="D109:D125" si="3">C109-C109*15/100</f>
+        <v>185.3</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2321,14 +2324,14 @@
         <v>92</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C110" s="1">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="D110" s="1">
-        <f t="shared" si="2"/>
-        <v>242.25</v>
+        <f t="shared" si="3"/>
+        <v>225.25</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2336,14 +2339,14 @@
         <v>92</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C111" s="1">
-        <v>340</v>
+        <v>285</v>
       </c>
       <c r="D111" s="1">
-        <f t="shared" si="2"/>
-        <v>289</v>
+        <f t="shared" si="3"/>
+        <v>242.25</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2351,14 +2354,14 @@
         <v>92</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C112" s="1">
-        <v>215</v>
+        <v>340</v>
       </c>
       <c r="D112" s="1">
-        <f t="shared" si="2"/>
-        <v>182.75</v>
+        <f t="shared" si="3"/>
+        <v>289</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2366,14 +2369,14 @@
         <v>92</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C113">
-        <v>230</v>
+        <v>108</v>
+      </c>
+      <c r="C113" s="1">
+        <v>215</v>
       </c>
       <c r="D113" s="1">
-        <f t="shared" si="2"/>
-        <v>195.5</v>
+        <f t="shared" si="3"/>
+        <v>182.75</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2381,14 +2384,14 @@
         <v>92</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C114">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="D114" s="1">
-        <f t="shared" si="2"/>
-        <v>169.15</v>
+        <f t="shared" si="3"/>
+        <v>195.5</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2396,14 +2399,14 @@
         <v>92</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C115">
-        <v>445</v>
+        <v>199</v>
       </c>
       <c r="D115" s="1">
-        <f t="shared" si="2"/>
-        <v>378.25</v>
+        <f t="shared" si="3"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2411,14 +2414,14 @@
         <v>92</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C116">
-        <v>400</v>
+        <v>445</v>
       </c>
       <c r="D116" s="1">
-        <f t="shared" si="2"/>
-        <v>340</v>
+        <f t="shared" si="3"/>
+        <v>378.25</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2426,14 +2429,14 @@
         <v>92</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C117">
-        <v>299</v>
+        <v>400</v>
       </c>
       <c r="D117" s="1">
-        <f t="shared" si="2"/>
-        <v>254.15</v>
+        <f t="shared" si="3"/>
+        <v>340</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2441,14 +2444,14 @@
         <v>92</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C118">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="D118" s="1">
-        <f t="shared" si="2"/>
-        <v>276.25</v>
+        <f t="shared" si="3"/>
+        <v>254.15</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2456,14 +2459,14 @@
         <v>92</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C119" s="1">
-        <v>278</v>
+        <v>114</v>
+      </c>
+      <c r="C119">
+        <v>325</v>
       </c>
       <c r="D119" s="1">
-        <f t="shared" si="2"/>
-        <v>236.3</v>
+        <f t="shared" si="3"/>
+        <v>276.25</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2471,29 +2474,29 @@
         <v>92</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C120" s="1">
-        <v>405</v>
+        <v>278</v>
       </c>
       <c r="D120" s="1">
-        <f t="shared" si="2"/>
-        <v>344.25</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>236.3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C121">
-        <v>360</v>
+        <v>94</v>
+      </c>
+      <c r="C121" s="1">
+        <v>405</v>
       </c>
       <c r="D121" s="1">
-        <f t="shared" si="2"/>
-        <v>306</v>
+        <f t="shared" si="3"/>
+        <v>344.25</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2501,14 +2504,14 @@
         <v>92</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C122">
-        <v>249</v>
+        <v>360</v>
       </c>
       <c r="D122" s="1">
-        <f t="shared" si="2"/>
-        <v>211.65</v>
+        <f t="shared" si="3"/>
+        <v>306</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2516,14 +2519,14 @@
         <v>92</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C123">
-        <v>329</v>
+        <v>249</v>
       </c>
       <c r="D123" s="1">
-        <f t="shared" si="2"/>
-        <v>279.64999999999998</v>
+        <f t="shared" si="3"/>
+        <v>211.65</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2531,13 +2534,28 @@
         <v>92</v>
       </c>
       <c r="B124" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C124">
+        <v>329</v>
+      </c>
+      <c r="D124" s="1">
+        <f t="shared" si="3"/>
+        <v>279.64999999999998</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C124">
+      <c r="C125">
         <v>275</v>
       </c>
-      <c r="D124" s="1">
-        <f t="shared" si="2"/>
+      <c r="D125" s="1">
+        <f t="shared" si="3"/>
         <v>233.75</v>
       </c>
     </row>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E05650F-5B2C-4F60-8807-2BF688919A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA21006-E404-4C2D-8A38-418BB5403B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,373 +31,378 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="117">
-  <si>
-    <t>📚 مرحلة كي جي (KG):</t>
-  </si>
-  <si>
-    <t>• المعاصر إنجليزي كي جي 1 ⬅️ 125</t>
-  </si>
-  <si>
-    <t>• المعاصر ماس كي جي 1 ⬅️ 205</t>
-  </si>
-  <si>
-    <t>• المعاصر إنجليزي كي جي 2 ⬅️ 125</t>
-  </si>
-  <si>
-    <t>• المعاصر ماس كي جي 2 ⬅️ 210</t>
-  </si>
-  <si>
-    <t>🎒 الصف الأول الابتدائي:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• أضواء رياضيات ⬅️ 149 </t>
-  </si>
-  <si>
-    <t>• أضواء عربي ⬅️ 159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• أضواء دين ⬅️ 129 </t>
-  </si>
-  <si>
-    <t>• أضواء جيم إنجليزي ⬅️ 165</t>
-  </si>
-  <si>
-    <t>• ستيب أهيد إنجليزي ⬅️ 165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• بيت باي بيت إنجليزي ⬅️ 135 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">• المعاصر إنجليزي ⬅️ 175 </t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ عربي ⬅️ 180</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ رياضيات ⬅️ 170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• سلاح التلميذ دين ⬅️ 130 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">• تأسيس سليم عربي ⬅️ 175 </t>
-  </si>
-  <si>
-    <t>• تأسيس سليم رياضيات ⬅️ 169</t>
-  </si>
-  <si>
-    <t>• المعاصر ماث لغات ⬅️ 255</t>
-  </si>
-  <si>
-    <t>• المعاصر رياضه بالعربي ⬅️ 165</t>
-  </si>
-  <si>
-    <t>🎒 الصف الثاني الابتدائي:</t>
-  </si>
-  <si>
-    <t>• أضواء رياضيات ⬅️ 159</t>
-  </si>
-  <si>
-    <t>• أضواء دين ⬅️ 139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• سلاح التلميذ دين ⬅️ 140 </t>
-  </si>
-  <si>
-    <t>🎒 الصف الثالث الابتدائي:</t>
-  </si>
-  <si>
-    <t>• أضواء عربي ⬅️ 169</t>
-  </si>
-  <si>
-    <t>• ستيب أهيد إنجليزي ⬅️ 185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• سلاح التلميذ عربي ⬅️ 190 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">• سلاح التلميذ رياضيات ⬅️ 175 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">• بيت باي بيت  ⬅️ 140 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">• التأسيس السيلم عربي  ⬅️ 179 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">• التأسيس السليم حساب  ⬅️ 179 </t>
-  </si>
-  <si>
-    <t>• المعاصر انجليزي ⬅️ 189</t>
-  </si>
-  <si>
-    <t>🎒 الصف الرابع الابتدائي:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• أضواء عربي ⬅️ 195 </t>
-  </si>
-  <si>
-    <t>• أضواء رياضيات ⬅️ 165</t>
-  </si>
-  <si>
-    <t>• أضواء دراسات ⬅️ 159</t>
-  </si>
-  <si>
-    <t>• المعاصر إنجليزي ⬅️ 189</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ عربي ⬅️ 215</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ دراسات ⬅️ 185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• سلاح التلميذ رياضيات ⬅️ 190 </t>
-  </si>
-  <si>
-    <t>• الإمتحان دراسات ⬅️ 169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• الإمتحان عربي ⬅️ 205 </t>
-  </si>
-  <si>
-    <t>• تأسيس سليم عربي ⬅️ 189</t>
-  </si>
-  <si>
-    <t>• جيم الاضواء انجليزي ⬅️ 169</t>
-  </si>
-  <si>
-    <t>• المعاصر ماث لغات ⬅️ 315</t>
-  </si>
-  <si>
-    <t>🎒 الصف الخامس الابتدائي:</t>
-  </si>
-  <si>
-    <t>• أضواء رياضيات ⬅️ 169</t>
-  </si>
-  <si>
-    <t>• ستيب أهيد إنجليزي ⬅️ 187</t>
-  </si>
-  <si>
-    <t>• بيت باي بيت إنجليزي ⬅️ 155</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ عربي⬅️ 215</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ رياضه⬅️ 190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• جيم الاضواء انجليزي ⬅️ 179 </t>
-  </si>
-  <si>
-    <t>🎒 الصف السادس الابتدائي:</t>
-  </si>
-  <si>
-    <t>• أضواء عربي ⬅️ 199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• أضواء جيم إنجليزي ⬅️ 179 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">• ستيب أهيد إنجليزي ⬅️ 195 </t>
-  </si>
-  <si>
-    <t>• سلاح عربي ⬅️ 220</t>
-  </si>
-  <si>
-    <t>• سلاح رياضه ⬅️ 190</t>
-  </si>
-  <si>
-    <t>• سلاح دراسات ⬅️ 185</t>
-  </si>
-  <si>
-    <t>• سلاح دين ⬅️ 145 | بعد الخصم: 123.25</t>
-  </si>
-  <si>
-    <t>🎒 الصف الأول الإعدادي:</t>
-  </si>
-  <si>
-    <t>• أضواء عربي أولى إعدادي ⬅️ 199</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>• أضواء دين أولى إعدادي ⬅️</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> 139</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">• أضواء علوم أولى إعدادي ⬅️ 185 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">• أضواء دراسات أولى إعدادي ⬅️ 175 </t>
-  </si>
-  <si>
-    <t>• أضواء جيم إنجليزي أولى إعدادي ⬅️ 199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• سلاح التلميذ دين أولى إعدادي ⬅️ 145 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">• إمتحان عربي أولى إعدادي ⬅️ 220 </t>
-  </si>
-  <si>
-    <t>• إمتحان دراسات أولى إعدادي ⬅️ 187</t>
-  </si>
-  <si>
-    <t>• إمتحان علوم أولى إعدادي ⬅️ ما نزلش</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• المعاصر رياضيات أولى إعدادي ⬅️ 185 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">• المعاصر انجليزي ⬅️ 199 </t>
-  </si>
-  <si>
-    <t>🎒 الصف الثاني الإعدادي:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• أضواء دراسات تانية إعدادي ⬅️ 179 </t>
-  </si>
-  <si>
-    <t>• أضواء علوم تانية إعدادي ⬅️ 185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• بيت باي بيت إنجليزي تانية إعدادي ⬅️ 150 </t>
-  </si>
-  <si>
-    <t>• إمتحان عربي تانية إعدادي ⬅️ 220 .00</t>
-  </si>
-  <si>
-    <t>• إمتحان دراسات تانية إعدادي ⬅️ 189</t>
-  </si>
-  <si>
-    <t>• إمتحان علوم تانية إعدادي ⬅️ 189</t>
-  </si>
-  <si>
-    <t>• المعاصر رياضيات تانية إعدادي ⬅️ 185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• الاضواء عربي ⬅️ 199 </t>
-  </si>
-  <si>
-    <t>• الاضواء دين ⬅️ 149 | بعد الخصم: 127</t>
-  </si>
-  <si>
-    <t>🎒 الصف الثالث الإعدادي:</t>
-  </si>
-  <si>
-    <t>• أضواء عربي تالتة إعدادي ⬅️ 215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• بيت باي بيت إنجليزي تالتة إعدادي ⬅️ 150 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">• جيم الاضواء انجليزي ⬅️ 199 </t>
-  </si>
-  <si>
-    <t>🎓 الثانوية العامة (أولى ثانوي):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• انجليزي جيم الاضواء  ⬅️ 275 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">- امتحان تاريخ اولى ثانوني ⬅️ 174 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">- امتحان فلسفه اولى ثانوي ⬅️ 185 </t>
-  </si>
-  <si>
-    <t>🎓 الثانوية العامة (تانية ثانوي):</t>
-  </si>
-  <si>
-    <t>🎓 الثانوية العامة (تالتة ثانوي):</t>
-  </si>
-  <si>
-    <t>• سلاح التلميذ علوم ⬅️ 170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• إمتحان عربي (أسئلة) ⬅️ 405 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">• إمتحان عربي (شرح) ⬅️ 278 </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="124">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
   <si>
-    <t>• المعاصر ماث ⬅️ 295</t>
-  </si>
-  <si>
-    <t>• إمتحان كيمياء (اسئلة) ⬅️ 340</t>
-  </si>
-  <si>
     <t>الأضواء عربي (شرح) ⬅️ 249</t>
   </si>
   <si>
-    <t>• عربي الأضواء ⬅️ 249</t>
-  </si>
-  <si>
     <t>جيم الأضواء انجليزي (جزء اول)  ⬅️ 275</t>
   </si>
   <si>
-    <t>• أضواء حساب ⬅️ 165</t>
-  </si>
-  <si>
     <t>جيم الأضواء انجليزي  ⬅️ 169</t>
   </si>
   <si>
     <t>الأضواء عربي (اسئلة) ⬅️ 329</t>
   </si>
   <si>
-    <t>• إمتحان جغرافيا (شرح) ⬅️ 218</t>
-  </si>
-  <si>
-    <t>• إمتحان تاريخ (شرح) ⬅️ 265</t>
-  </si>
-  <si>
-    <t>• إمتحان كيمياء (شرح) ⬅️ 285</t>
-  </si>
-  <si>
-    <t>• إمتحان أحياء (شرح) ⬅️ 215</t>
-  </si>
-  <si>
-    <t>• الإمتحان فيزياء (شرح) ⬅️ 230</t>
-  </si>
-  <si>
-    <t>• المعاصر إحصاء (أدبي) ⬅️ 199</t>
-  </si>
-  <si>
-    <t>• المعاصر رياضة بحتة (جبر وهندسة وتفاضل) ⬅️ 445</t>
-  </si>
-  <si>
-    <t>• المعاصر رياضة تطبيقية (استاتيكا وديناميكا) ⬅️ 400</t>
-  </si>
-  <si>
-    <t>• إمتحان أحياء (أسئلة) ⬅️ 299</t>
-  </si>
-  <si>
-    <t>• إمتحان فيزياء (أسئلة) ⬅️ 325</t>
-  </si>
-  <si>
-    <t>• عربي الأضواء ⬅️ 239</t>
-  </si>
-  <si>
-    <t>• أضواء دراسات ⬅️ 165</t>
+    <t xml:space="preserve">  سلاح دين ⬅️ 145</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر إنجليزي كي جي 1 ⬅️ 125</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر ماس كي جي 1 ⬅️ 205</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر إنجليزي كي جي 2 ⬅️ 125</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر ماس كي جي 2 ⬅️ 210</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ عربي ⬅️ 180</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ رياضيات ⬅️ 170</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ دين ⬅️ 130 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء رياضيات ⬅️ 149 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء عربي ⬅️ 159</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء دين ⬅️ 129 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء جيم إنجليزي ⬅️ 165</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ستيب أهيد إنجليزي ⬅️ 165</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> بيت باي بيت إنجليزي ⬅️ 135 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر إنجليزي ⬅️ 175 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر ماث لغات ⬅️ 255</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر رياضه بالعربي ⬅️ 165</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تأسيس سليم عربي ⬅️ 175 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تأسيس سليم رياضيات ⬅️ 169</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ دين ⬅️ 140 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء رياضيات ⬅️ 159</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء دين ⬅️ 139</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ عربي ⬅️ 190 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ رياضيات ⬅️ 175 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء عربي ⬅️ 169</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء حساب ⬅️ 165</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ستيب أهيد إنجليزي ⬅️ 185</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> بيت باي بيت  ⬅️ 140 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر انجليزي ⬅️ 189</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> التأسيس السيلم عربي  ⬅️ 179 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> التأسيس السليم حساب  ⬅️ 179 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ عربي ⬅️ 215</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ دراسات ⬅️ 185</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ رياضيات ⬅️ 190 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ علوم ⬅️ 170</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ دين ⬅️ 145 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء عربي ⬅️ 195 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء رياضيات ⬅️ 165</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء دراسات ⬅️ 159</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> جيم الاضواء انجليزي ⬅️ 169</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر إنجليزي ⬅️ 189</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر ماث لغات ⬅️ 315</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> الإمتحان دراسات ⬅️ 169</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> الإمتحان عربي ⬅️ 205 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تأسيس سليم عربي ⬅️ 189</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ عربي⬅️ 215</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ رياضه⬅️ 190</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء رياضيات ⬅️ 169</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> جيم الاضواء انجليزي ⬅️ 179 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ستيب أهيد إنجليزي ⬅️ 187</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> بيت باي بيت إنجليزي ⬅️ 155</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر ماث ⬅️ 295</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح عربي ⬅️ 220</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح رياضه ⬅️ 190</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح دراسات ⬅️ 185</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء عربي ⬅️ 199</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء دراسات ⬅️ 165</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء جيم إنجليزي ⬅️ 179 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ستيب أهيد إنجليزي ⬅️ 195 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر انجليزي ⬅️ 199 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> الاضواء عربي ⬅️ 199 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> جيم الاضواء انجليزي ⬅️ 199 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> انجليزي جيم الاضواء  ⬅️ 275 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> عربي الأضواء ⬅️ 239</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> عربي الأضواء ⬅️ 249</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان جغرافيا (شرح) ⬅️ 218</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان تاريخ (شرح) ⬅️ 265</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان كيمياء (شرح) ⬅️ 285</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان كيمياء (اسئلة) ⬅️ 340</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان أحياء (شرح) ⬅️ 215</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان أحياء (أسئلة) ⬅️ 299</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> الإمتحان فيزياء (شرح) ⬅️ 230</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان فيزياء (أسئلة) ⬅️ 325</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر إحصاء (أدبي) ⬅️ 199</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر رياضة بحتة (جبر وهندسة وتفاضل) ⬅️ 445</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر رياضة تطبيقية (استاتيكا وديناميكا) ⬅️ 400</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان عربي (شرح) ⬅️ 278 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان عربي (أسئلة) ⬅️ 405 </t>
+  </si>
+  <si>
+    <t>📚 مرحلة كي جي (KG)</t>
+  </si>
+  <si>
+    <t>🎒 الصف الأول الابتدائي</t>
+  </si>
+  <si>
+    <t>🎒 الصف الثاني الابتدائي</t>
+  </si>
+  <si>
+    <t>🎒 الصف الثالث الابتدائي</t>
+  </si>
+  <si>
+    <t>🎒 الصف الرابع الابتدائي</t>
+  </si>
+  <si>
+    <t>🎒 الصف الخامس الابتدائي</t>
+  </si>
+  <si>
+    <t>🎒 الصف السادس الابتدائي</t>
+  </si>
+  <si>
+    <t>🎒 الصف الأول الإعدادي</t>
+  </si>
+  <si>
+    <t>🎒 الصف الثاني الإعدادي</t>
+  </si>
+  <si>
+    <t>🎒 الصف الثالث الإعدادي</t>
+  </si>
+  <si>
+    <t>🎓 الثانوية العامة (أولى ثانوي)</t>
+  </si>
+  <si>
+    <t>🎓 الثانوية العامة (تانية ثانوي)</t>
+  </si>
+  <si>
+    <t>🎓 الثانوية العامة (تالتة ثانوي)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ دين ⬅️ 0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ علوم ⬅️ 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء علوم ⬅️ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان عربي  ⬅️ 220 .00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان دراسات  ⬅️ 189</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان علوم  ⬅️ 189</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان عربي  ⬅️ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان دراسات  ⬅️ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان علوم  ⬅️ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر رياضيات  ⬅️ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر انجليزي ⬅️  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> الاضواء دين ⬅️ 149 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء دراسات  ⬅️ 179 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء علوم  ⬅️ 185</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> بيت باي بيت إنجليزي  ⬅️ 150 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء جيم إنجليزي  ⬅️ 199</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر رياضيات  ⬅️ 185</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان عربي  ⬅️ 220 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان دراسات  ⬅️ 187</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر رياضيات  ⬅️ 185 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء عربي  ⬅️ 199</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء علوم  ⬅️ 185 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء دراسات  ⬅️ 175 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء دين  ⬅️ 139</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ دين  ⬅️ 145 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء عربي  ⬅️ 215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">امتحان فلسفه ⬅️ 185 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">امتحان تاريخ  ⬅️ 174 </t>
   </si>
 </sst>
 </file>
@@ -421,12 +426,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <strike/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -449,10 +456,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -677,7 +686,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -686,25 +695,25 @@
   <sheetData>
     <row r="1" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>83</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="C1" s="1">
         <v>125</v>
       </c>
       <c r="D1" s="1">
-        <f t="shared" ref="D1:D108" si="0">C1-C1*15/100</f>
+        <f t="shared" ref="D1:D120" si="0">C1-C1*15/100</f>
         <v>106.25</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1">
         <v>205</v>
@@ -716,10 +725,10 @@
     </row>
     <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1">
         <v>125</v>
@@ -731,10 +740,10 @@
     </row>
     <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1">
         <v>210</v>
@@ -746,370 +755,370 @@
     </row>
     <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="D5" s="1">
-        <f t="shared" si="0"/>
-        <v>126.65</v>
+        <f>C5-C5*15/100</f>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D6" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f>C6-C6*15/100</f>
+        <v>144.5</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" si="0"/>
-        <v>109.65</v>
+        <f>C7-C7*15/100</f>
+        <v>110.5</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>126.65</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>114.75</v>
+        <v>109.65</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>153</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C13" s="1">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>144.5</v>
+        <v>114.75</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C14" s="1">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>110.5</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C15" s="1">
-        <v>175</v>
+        <v>255</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" si="0"/>
-        <v>148.75</v>
+        <f>C15-C15*15/100</f>
+        <v>216.75</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C16" s="1">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f>C16-C16*15/100</f>
+        <v>140.25</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C17" s="1">
-        <v>255</v>
+        <v>175</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="0"/>
-        <v>216.75</v>
+        <f>C17-C17*15/100</f>
+        <v>148.75</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
+        <f>C18-C18*15/100</f>
+        <v>143.65</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C19" s="1">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f>C19-C19*15/100</f>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C20" s="1">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f>C20-C20*15/100</f>
+        <v>144.5</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C21" s="1">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" si="0"/>
-        <v>118.15</v>
+        <f>C21-C21*15/100</f>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C22" s="1">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D22" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D23" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C24" s="1">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D24" s="1">
         <f t="shared" si="0"/>
-        <v>114.75</v>
+        <v>118.15</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C25" s="1">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D25" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C26" s="1">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D26" s="1">
         <f t="shared" si="0"/>
-        <v>153</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C27" s="1">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="D27" s="1">
         <f t="shared" si="0"/>
-        <v>144.5</v>
+        <v>114.75</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C28" s="1">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="D28" s="1">
         <f t="shared" si="0"/>
-        <v>119</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C29" s="1">
         <v>175</v>
@@ -1121,160 +1130,160 @@
     </row>
     <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C30" s="1">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="D30" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f>C30-C30*15/100</f>
+        <v>161.5</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="C31" s="1">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
+        <f>C31-C31*15/100</f>
+        <v>148.75</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C32" s="1">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D32" s="1">
-        <f t="shared" si="0"/>
-        <v>118.15</v>
+        <f>C32-C32*15/100</f>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C33" s="1">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D33" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C34" s="1">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="D34" s="1">
         <f t="shared" si="0"/>
-        <v>161.5</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C35" s="1">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="D35" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>118.15</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C36" s="1">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D36" s="1">
-        <f t="shared" si="0"/>
-        <v>119</v>
+        <f>C36-C36*15/100</f>
+        <v>143.65</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C37" s="1">
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="D37" s="1">
         <f t="shared" si="0"/>
-        <v>119</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="C38" s="1">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="D38" s="1">
         <f t="shared" si="0"/>
-        <v>143.65</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C39" s="1">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f>C39-C39*15/100</f>
+        <v>160.65</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C40" s="1">
         <v>179</v>
@@ -1286,1000 +1295,1000 @@
     </row>
     <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C41" s="1">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D41" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C42" s="1">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="D42" s="1">
-        <f t="shared" si="0"/>
-        <v>165.75</v>
+        <f>C42-C42*15/100</f>
+        <v>182.75</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C43" s="1">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="D43" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
+        <f>C43-C43*15/100</f>
+        <v>157.25</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C44" s="1">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="D44" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f>C44-C44*15/100</f>
+        <v>161.5</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C45" s="1">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="D45" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f>C45-C45*15/100</f>
+        <v>144.5</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>37</v>
+        <v>87</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="C46" s="1">
-        <v>189</v>
+        <v>145</v>
       </c>
       <c r="D46" s="1">
-        <f t="shared" si="0"/>
-        <v>160.65</v>
+        <f t="shared" ref="D46" si="1">C46-C46*15/100</f>
+        <v>123.25</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C47" s="1">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="D47" s="1">
         <f t="shared" si="0"/>
-        <v>182.75</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C48" s="1">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="D48" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C49" s="1">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D49" s="1">
         <f t="shared" si="0"/>
-        <v>161.5</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>41</v>
+        <v>87</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="C50" s="1">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="D50" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f t="shared" ref="D50" si="2">C50-C50*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C51" s="1">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D51" s="1">
-        <f t="shared" si="0"/>
-        <v>174.25</v>
+        <f>C51-C51*15/100</f>
+        <v>143.65</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C52" s="1">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D52" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C53" s="1">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D53" s="1">
         <f t="shared" si="0"/>
-        <v>143.65</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C54" s="1">
         <v>315</v>
       </c>
       <c r="D54" s="1">
-        <f t="shared" si="0"/>
+        <f>C54-C54*15/100</f>
         <v>267.75</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="C55" s="1">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D55" s="1">
         <f t="shared" si="0"/>
-        <v>144.5</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C56" s="1">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D56" s="1">
         <f t="shared" si="0"/>
-        <v>165.75</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C57" s="1">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="D57" s="1">
         <f t="shared" si="0"/>
-        <v>135.15</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C58" s="1">
-        <v>169</v>
+        <v>215</v>
       </c>
       <c r="D58" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f>C58-C58*15/100</f>
+        <v>182.75</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C59" s="1">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D59" s="1">
-        <f t="shared" si="0"/>
-        <v>158.94999999999999</v>
+        <f>C59-C59*15/100</f>
+        <v>157.25</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C60" s="1">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="D60" s="1">
-        <f t="shared" si="0"/>
-        <v>131.75</v>
+        <f>C60-C60*15/100</f>
+        <v>161.5</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C61" s="1">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="D61" s="1">
-        <f t="shared" si="0"/>
-        <v>160.65</v>
+        <f>C61-C61*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>50</v>
+        <v>88</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C62" s="1">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="D62" s="1">
-        <f t="shared" si="0"/>
-        <v>182.75</v>
+        <f t="shared" ref="D62" si="3">C62-C62*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C63" s="1">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D63" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C64" s="1">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D64" s="1">
         <f t="shared" si="0"/>
-        <v>161.5</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C65" s="1">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D65" s="1">
         <f t="shared" si="0"/>
-        <v>152.15</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="C66" s="1">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="D66" s="1">
         <f t="shared" si="0"/>
-        <v>250.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C67" s="1">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="D67" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f>C67-C67*15/100</f>
+        <v>152.15</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C68" s="1">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="D68" s="1">
         <f t="shared" si="0"/>
-        <v>143.65</v>
+        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="C69" s="1">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" ref="D69" si="1">C69-C69*15/100</f>
-        <v>140.25</v>
+        <f t="shared" si="0"/>
+        <v>131.75</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C70" s="1">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D70" s="1">
         <f t="shared" si="0"/>
-        <v>152.15</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C71" s="1">
-        <v>195</v>
+        <v>295</v>
       </c>
       <c r="D71" s="1">
-        <f t="shared" si="0"/>
-        <v>165.75</v>
+        <f>C71-C71*15/100</f>
+        <v>250.75</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C72" s="1">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="D72" s="1">
-        <f t="shared" si="0"/>
-        <v>131.75</v>
+        <f>C72-C72*15/100</f>
+        <v>187</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C73" s="1">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D73" s="1">
-        <f t="shared" si="0"/>
-        <v>160.65</v>
+        <f>C73-C73*15/100</f>
+        <v>161.5</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C74" s="1">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="D74" s="1">
-        <f t="shared" si="0"/>
-        <v>187</v>
+        <f>C74-C74*15/100</f>
+        <v>157.25</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>58</v>
+        <v>89</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C75" s="1">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="D75" s="1">
-        <f t="shared" si="0"/>
-        <v>161.5</v>
+        <f>C75-C75*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>59</v>
+        <v>89</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C76" s="1">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="D76" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f>C76-C76*15/100</f>
+        <v>123.25</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C77" s="1">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="D77" s="1">
         <f t="shared" si="0"/>
-        <v>123.25</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C78" s="1">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="D78" s="1">
         <f t="shared" si="0"/>
-        <v>169.15</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="C79" s="1">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="D79" s="1">
-        <f t="shared" si="0"/>
-        <v>118.15</v>
+        <f t="shared" ref="D79:D80" si="4">C79-C79*15/100</f>
+        <v>140.25</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>64</v>
+        <v>88</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="C80" s="1">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C81" s="1">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D81" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C82" s="1">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D82" s="1">
         <f t="shared" si="0"/>
-        <v>169.15</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C83" s="1">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="D83" s="1">
         <f t="shared" si="0"/>
-        <v>123.25</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="C84" s="1">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="D84" s="1">
         <f t="shared" si="0"/>
-        <v>187</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="C85" s="1">
+        <v>220</v>
+      </c>
+      <c r="D85" s="1">
+        <f>C85-C85*15/100</f>
         <v>187</v>
-      </c>
-      <c r="D85" s="1">
-        <f t="shared" si="0"/>
-        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="C86" s="1">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="D86" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>C86-C86*15/100</f>
+        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="C87" s="1">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="D87" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f>C87-C87*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="C88" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D88" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f>C88-C88*15/100</f>
+        <v>157.25</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C89" s="1">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="D89" s="1">
-        <f t="shared" si="0"/>
-        <v>127.5</v>
+        <f>C89-C89*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="C90" s="1">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="D90" s="1">
         <f t="shared" si="0"/>
-        <v>152.15</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="C91" s="1">
         <v>185</v>
       </c>
       <c r="D91" s="1">
-        <f t="shared" si="0"/>
+        <f>C91-C91*15/100</f>
         <v>157.25</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="C92" s="1">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="D92" s="1">
-        <f t="shared" si="0"/>
-        <v>127.5</v>
+        <f>C92-C92*15/100</f>
+        <v>148.75</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="C93" s="1">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="D93" s="1">
-        <f t="shared" si="0"/>
-        <v>187</v>
+        <f>C93-C93*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>78</v>
+        <v>90</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="C94" s="1">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="D94" s="1">
-        <f t="shared" si="0"/>
-        <v>160.65</v>
+        <f>C94-C94*15/100</f>
+        <v>127.5</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="C95" s="1">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="D95" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>118.15</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>66</v>
+        <v>90</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="C96" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D96" s="1">
-        <f t="shared" ref="D96" si="2">C96-C96*15/100</f>
-        <v>169.15</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="C97" s="1">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="D97" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f>C97-C97*15/100</f>
+        <v>187</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C98" s="1">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D98" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f>C98-C98*15/100</f>
+        <v>160.65</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="C99" s="1">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D99" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f>C99-C99*15/100</f>
+        <v>160.65</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="C100" s="1">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="D100" s="1">
-        <f t="shared" si="0"/>
-        <v>126.65</v>
+        <f>C100-C100*15/100</f>
+        <v>157.25</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C101" s="1">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="D101" s="1">
-        <f t="shared" si="0"/>
-        <v>182.75</v>
+        <f>C101-C101*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="C102" s="1">
         <v>150</v>
       </c>
       <c r="D102" s="1">
-        <f t="shared" si="0"/>
+        <f>C102-C102*15/100</f>
         <v>127.5</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="C103" s="1">
         <v>199</v>
       </c>
       <c r="D103" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D103" si="5">C103-C103*15/100</f>
         <v>169.15</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="C104" s="1">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="D104" s="1">
-        <f t="shared" si="0"/>
-        <v>233.75</v>
+        <f>C104-C104*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>115</v>
+        <v>91</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="C105" s="1">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="D105" s="1">
-        <f t="shared" si="0"/>
-        <v>203.15</v>
+        <f>C105-C105*15/100</f>
+        <v>126.65</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C106" s="1">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D106" s="1">
         <f t="shared" si="0"/>
-        <v>147.9</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C107" s="1">
         <v>185</v>
@@ -2291,77 +2300,77 @@
     </row>
     <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>100</v>
+        <v>92</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="C108" s="1">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="D108" s="1">
-        <f t="shared" si="0"/>
-        <v>211.65</v>
+        <f>C108-C108*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>105</v>
+      <c r="B109" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="C109" s="1">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" ref="D109:D125" si="3">C109-C109*15/100</f>
-        <v>185.3</v>
+        <f>C109-C109*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>106</v>
+      <c r="B110" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="C110" s="1">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="D110" s="1">
-        <f t="shared" si="3"/>
-        <v>225.25</v>
+        <f>C110-C110*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>107</v>
+      <c r="B111" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="C111" s="1">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="D111" s="1">
-        <f t="shared" si="3"/>
-        <v>242.25</v>
+        <f>C111-C111*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>98</v>
+      <c r="B112" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="C112" s="1">
-        <v>340</v>
+        <v>199</v>
       </c>
       <c r="D112" s="1">
-        <f t="shared" si="3"/>
-        <v>289</v>
+        <f>C112-C112*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2369,14 +2378,14 @@
         <v>92</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C113" s="1">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="D113" s="1">
-        <f t="shared" si="3"/>
-        <v>182.75</v>
+        <f t="shared" si="0"/>
+        <v>127.5</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2384,14 +2393,14 @@
         <v>92</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C114">
-        <v>230</v>
+        <v>66</v>
+      </c>
+      <c r="C114" s="1">
+        <v>199</v>
       </c>
       <c r="D114" s="1">
-        <f t="shared" si="3"/>
-        <v>195.5</v>
+        <f t="shared" si="0"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2399,163 +2408,343 @@
         <v>92</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C115">
-        <v>199</v>
+        <v>121</v>
+      </c>
+      <c r="C115" s="1">
+        <v>215</v>
       </c>
       <c r="D115" s="1">
-        <f t="shared" si="3"/>
-        <v>169.15</v>
+        <f>C115-C115*15/100</f>
+        <v>182.75</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C116">
-        <v>445</v>
+        <v>67</v>
+      </c>
+      <c r="C116" s="1">
+        <v>275</v>
       </c>
       <c r="D116" s="1">
-        <f t="shared" si="3"/>
-        <v>378.25</v>
+        <f t="shared" si="0"/>
+        <v>233.75</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C117">
-        <v>400</v>
+        <v>68</v>
+      </c>
+      <c r="C117" s="1">
+        <v>239</v>
       </c>
       <c r="D117" s="1">
-        <f t="shared" si="3"/>
-        <v>340</v>
+        <f t="shared" si="0"/>
+        <v>203.15</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C118">
-        <v>299</v>
+        <v>93</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C118" s="1">
+        <v>174</v>
       </c>
       <c r="D118" s="1">
-        <f t="shared" si="3"/>
-        <v>254.15</v>
+        <f t="shared" si="0"/>
+        <v>147.9</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C119">
-        <v>325</v>
+        <v>93</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C119" s="1">
+        <v>185</v>
       </c>
       <c r="D119" s="1">
-        <f t="shared" si="3"/>
-        <v>276.25</v>
+        <f t="shared" si="0"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="C120" s="1">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="D120" s="1">
-        <f t="shared" si="3"/>
-        <v>236.3</v>
+        <f t="shared" si="0"/>
+        <v>211.65</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="C121" s="1">
+        <v>218</v>
+      </c>
+      <c r="D121" s="1">
+        <f t="shared" ref="D121:D137" si="6">C121-C121*15/100</f>
+        <v>185.3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A122" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C122" s="1">
+        <v>265</v>
+      </c>
+      <c r="D122" s="1">
+        <f t="shared" si="6"/>
+        <v>225.25</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A123" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C123" s="1">
+        <v>285</v>
+      </c>
+      <c r="D123" s="1">
+        <f t="shared" si="6"/>
+        <v>242.25</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C124" s="1">
+        <v>340</v>
+      </c>
+      <c r="D124" s="1">
+        <f t="shared" si="6"/>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C125" s="1">
+        <v>215</v>
+      </c>
+      <c r="D125" s="1">
+        <f t="shared" si="6"/>
+        <v>182.75</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A126" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C126">
+        <v>299</v>
+      </c>
+      <c r="D126" s="1">
+        <f>C126-C126*15/100</f>
+        <v>254.15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A127" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C127">
+        <v>230</v>
+      </c>
+      <c r="D127" s="1">
+        <f t="shared" si="6"/>
+        <v>195.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A128" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C128">
+        <v>325</v>
+      </c>
+      <c r="D128" s="1">
+        <f>C128-C128*15/100</f>
+        <v>276.25</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A129" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C129">
+        <v>199</v>
+      </c>
+      <c r="D129" s="1">
+        <f t="shared" si="6"/>
+        <v>169.15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A130" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C130">
+        <v>445</v>
+      </c>
+      <c r="D130" s="1">
+        <f t="shared" si="6"/>
+        <v>378.25</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A131" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C131">
+        <v>400</v>
+      </c>
+      <c r="D131" s="1">
+        <f t="shared" si="6"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A132" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C132" s="1">
+        <v>278</v>
+      </c>
+      <c r="D132" s="1">
+        <f t="shared" si="6"/>
+        <v>236.3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A133" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C133" s="1">
         <v>405</v>
       </c>
-      <c r="D121" s="1">
-        <f t="shared" si="3"/>
+      <c r="D133" s="1">
+        <f t="shared" si="6"/>
         <v>344.25</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C122">
+    <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C134">
         <v>360</v>
       </c>
-      <c r="D122" s="1">
-        <f t="shared" si="3"/>
+      <c r="D134" s="1">
+        <f t="shared" si="6"/>
         <v>306</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C123">
+    <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C135">
         <v>249</v>
       </c>
-      <c r="D123" s="1">
-        <f t="shared" si="3"/>
+      <c r="D135" s="1">
+        <f t="shared" si="6"/>
         <v>211.65</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C124">
+    <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C136">
         <v>329</v>
       </c>
-      <c r="D124" s="1">
-        <f t="shared" si="3"/>
+      <c r="D136" s="1">
+        <f t="shared" si="6"/>
         <v>279.64999999999998</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C125">
+    <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C137">
         <v>275</v>
       </c>
-      <c r="D125" s="1">
-        <f t="shared" si="3"/>
+      <c r="D137" s="1">
+        <f t="shared" si="6"/>
         <v>233.75</v>
       </c>
     </row>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA21006-E404-4C2D-8A38-418BB5403B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A403C1E-0E78-4793-8568-1C184B4826E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="127">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -403,6 +403,15 @@
   </si>
   <si>
     <t xml:space="preserve">امتحان تاريخ  ⬅️ 174 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر ماث لغات ⬅️ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر ساينس لغات ⬅️ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر بلس ⬅️  </t>
   </si>
 </sst>
 </file>
@@ -686,7 +695,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D158"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -704,7 +713,7 @@
         <v>125</v>
       </c>
       <c r="D1" s="1">
-        <f t="shared" ref="D1:D120" si="0">C1-C1*15/100</f>
+        <f t="shared" ref="D1:D141" si="0">C1-C1*15/100</f>
         <v>106.25</v>
       </c>
     </row>
@@ -908,14 +917,14 @@
         <v>84</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="C15" s="1">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1">
-        <f>C15-C15*15/100</f>
-        <v>216.75</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -923,14 +932,14 @@
         <v>84</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" s="1">
-        <v>165</v>
+        <v>255</v>
       </c>
       <c r="D16" s="1">
-        <f>C16-C16*15/100</f>
-        <v>140.25</v>
+        <f t="shared" ref="D16:D22" si="1">C16-C16*15/100</f>
+        <v>216.75</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -938,14 +947,14 @@
         <v>84</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="1">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D17" s="1">
-        <f>C17-C17*15/100</f>
-        <v>148.75</v>
+        <f t="shared" si="1"/>
+        <v>140.25</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -953,29 +962,29 @@
         <v>84</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" s="1">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D18" s="1">
-        <f>C18-C18*15/100</f>
-        <v>143.65</v>
+        <f t="shared" si="1"/>
+        <v>148.75</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C19" s="1">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="D19" s="1">
-        <f>C19-C19*15/100</f>
-        <v>153</v>
+        <f t="shared" si="1"/>
+        <v>143.65</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -983,14 +992,14 @@
         <v>85</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D20" s="1">
-        <f>C20-C20*15/100</f>
-        <v>144.5</v>
+        <f t="shared" si="1"/>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -998,14 +1007,14 @@
         <v>85</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C21" s="1">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="D21" s="1">
-        <f>C21-C21*15/100</f>
-        <v>119</v>
+        <f t="shared" si="1"/>
+        <v>144.5</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1013,14 +1022,14 @@
         <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22" s="1">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f t="shared" si="1"/>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1028,7 +1037,7 @@
         <v>85</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C23" s="1">
         <v>159</v>
@@ -1043,14 +1052,14 @@
         <v>85</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D24" s="1">
         <f t="shared" si="0"/>
-        <v>118.15</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1058,14 +1067,14 @@
         <v>85</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C25" s="1">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="D25" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>118.15</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1073,7 +1082,7 @@
         <v>85</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26" s="1">
         <v>165</v>
@@ -1088,14 +1097,14 @@
         <v>85</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="1">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="D27" s="1">
         <f t="shared" si="0"/>
-        <v>114.75</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1103,14 +1112,14 @@
         <v>85</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28" s="1">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D28" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>114.75</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1118,7 +1127,7 @@
         <v>85</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C29" s="1">
         <v>175</v>
@@ -1130,47 +1139,47 @@
     </row>
     <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="C30" s="1">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="D30" s="1">
-        <f>C30-C30*15/100</f>
-        <v>161.5</v>
+        <f t="shared" ref="D30" si="2">C30-C30*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>28</v>
+        <v>124</v>
       </c>
       <c r="C31" s="1">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="D31" s="1">
-        <f>C31-C31*15/100</f>
-        <v>148.75</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C32" s="1">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="D32" s="1">
-        <f>C32-C32*15/100</f>
-        <v>119</v>
+        <f t="shared" si="0"/>
+        <v>148.75</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1178,14 +1187,14 @@
         <v>86</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C33" s="1">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="D33" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f>C33-C33*15/100</f>
+        <v>161.5</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1193,14 +1202,14 @@
         <v>86</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C34" s="1">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D34" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
+        <f>C34-C34*15/100</f>
+        <v>148.75</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1208,14 +1217,14 @@
         <v>86</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C35" s="1">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" si="0"/>
-        <v>118.15</v>
+        <f>C35-C35*15/100</f>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1223,13 +1232,13 @@
         <v>86</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C36" s="1">
         <v>169</v>
       </c>
       <c r="D36" s="1">
-        <f>C36-C36*15/100</f>
+        <f t="shared" si="0"/>
         <v>143.65</v>
       </c>
     </row>
@@ -1238,14 +1247,14 @@
         <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C37" s="1">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="D37" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1253,14 +1262,14 @@
         <v>86</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C38" s="1">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D38" s="1">
         <f t="shared" si="0"/>
-        <v>119</v>
+        <v>118.15</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1268,14 +1277,14 @@
         <v>86</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="C39" s="1">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D39" s="1">
         <f>C39-C39*15/100</f>
-        <v>160.65</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1283,14 +1292,14 @@
         <v>86</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C40" s="1">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D40" s="1">
         <f t="shared" si="0"/>
-        <v>152.15</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1298,89 +1307,89 @@
         <v>86</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C41" s="1">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="D41" s="1">
         <f t="shared" si="0"/>
-        <v>152.15</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C42" s="1">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="D42" s="1">
         <f>C42-C42*15/100</f>
-        <v>182.75</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="C43" s="1">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="D43" s="1">
-        <f>C43-C43*15/100</f>
-        <v>157.25</v>
+        <f t="shared" ref="D43" si="3">C43-C43*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="C44" s="1">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="D44" s="1">
-        <f>C44-C44*15/100</f>
-        <v>161.5</v>
+        <f t="shared" ref="D44" si="4">C44-C44*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C45" s="1">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D45" s="1">
-        <f>C45-C45*15/100</f>
-        <v>144.5</v>
+        <f t="shared" si="0"/>
+        <v>152.15</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>40</v>
+        <v>86</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="C46" s="1">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="D46" s="1">
-        <f t="shared" ref="D46" si="1">C46-C46*15/100</f>
-        <v>123.25</v>
+        <f t="shared" si="0"/>
+        <v>152.15</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1388,14 +1397,14 @@
         <v>87</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C47" s="1">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="D47" s="1">
-        <f t="shared" si="0"/>
-        <v>165.75</v>
+        <f>C47-C47*15/100</f>
+        <v>182.75</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1403,14 +1412,14 @@
         <v>87</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C48" s="1">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="D48" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
+        <f>C48-C48*15/100</f>
+        <v>157.25</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1418,44 +1427,44 @@
         <v>87</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C49" s="1">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="D49" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f>C49-C49*15/100</f>
+        <v>161.5</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>98</v>
+      <c r="B50" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="C50" s="1">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="D50" s="1">
-        <f t="shared" ref="D50" si="2">C50-C50*15/100</f>
-        <v>0</v>
+        <f>C50-C50*15/100</f>
+        <v>144.5</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>44</v>
+      <c r="B51" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="C51" s="1">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="D51" s="1">
-        <f>C51-C51*15/100</f>
-        <v>143.65</v>
+        <f t="shared" ref="D51" si="5">C51-C51*15/100</f>
+        <v>123.25</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1463,14 +1472,14 @@
         <v>87</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C52" s="1">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D52" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1478,14 +1487,14 @@
         <v>87</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C53" s="1">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="D53" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1493,29 +1502,29 @@
         <v>87</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C54" s="1">
-        <v>315</v>
+        <v>159</v>
       </c>
       <c r="D54" s="1">
-        <f>C54-C54*15/100</f>
-        <v>267.75</v>
+        <f t="shared" si="0"/>
+        <v>135.15</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>47</v>
+      <c r="B55" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="C55" s="1">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="D55" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f t="shared" ref="D55" si="6">C55-C55*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1523,14 +1532,14 @@
         <v>87</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C56" s="1">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D56" s="1">
-        <f t="shared" si="0"/>
-        <v>174.25</v>
+        <f>C56-C56*15/100</f>
+        <v>143.65</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1538,119 +1547,119 @@
         <v>87</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C57" s="1">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D57" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C58" s="1">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="D58" s="1">
-        <f>C58-C58*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="0"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="C59" s="1">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="D59" s="1">
-        <f>C59-C59*15/100</f>
-        <v>157.25</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C60" s="1">
-        <v>190</v>
+        <v>315</v>
       </c>
       <c r="D60" s="1">
         <f>C60-C60*15/100</f>
-        <v>161.5</v>
+        <v>267.75</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C61" s="1">
         <v>0</v>
       </c>
       <c r="D61" s="1">
-        <f>C61-C61*15/100</f>
+        <f t="shared" ref="D61" si="7">C61-C61*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C62" s="1">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D62" s="1">
-        <f t="shared" ref="D62" si="3">C62-C62*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>143.65</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C63" s="1">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D63" s="1">
         <f t="shared" si="0"/>
-        <v>165.75</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C64" s="1">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="D64" s="1">
         <f t="shared" si="0"/>
-        <v>135.15</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1658,29 +1667,29 @@
         <v>88</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C65" s="1">
-        <v>169</v>
+        <v>215</v>
       </c>
       <c r="D65" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f>C65-C65*15/100</f>
+        <v>182.75</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>98</v>
+      <c r="B66" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="C66" s="1">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D66" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>C66-C66*15/100</f>
+        <v>157.25</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1688,44 +1697,44 @@
         <v>88</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C67" s="1">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D67" s="1">
         <f>C67-C67*15/100</f>
-        <v>152.15</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>54</v>
+      <c r="B68" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C68" s="1">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="D68" s="1">
-        <f t="shared" si="0"/>
-        <v>158.94999999999999</v>
+        <f>C68-C68*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>55</v>
+      <c r="B69" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C69" s="1">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" si="0"/>
-        <v>131.75</v>
+        <f t="shared" ref="D69" si="8">C69-C69*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1733,14 +1742,14 @@
         <v>88</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C70" s="1">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D70" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1748,148 +1757,148 @@
         <v>88</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C71" s="1">
-        <v>295</v>
+        <v>159</v>
       </c>
       <c r="D71" s="1">
-        <f>C71-C71*15/100</f>
-        <v>250.75</v>
+        <f t="shared" si="0"/>
+        <v>135.15</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C72" s="1">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="D72" s="1">
-        <f>C72-C72*15/100</f>
-        <v>187</v>
+        <f t="shared" si="0"/>
+        <v>143.65</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>58</v>
+        <v>88</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="C73" s="1">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="D73" s="1">
-        <f>C73-C73*15/100</f>
-        <v>161.5</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C74" s="1">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D74" s="1">
         <f>C74-C74*15/100</f>
-        <v>157.25</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="C75" s="1">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="D75" s="1">
-        <f>C75-C75*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>5</v>
+        <v>88</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="C76" s="1">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="D76" s="1">
-        <f>C76-C76*15/100</f>
-        <v>123.25</v>
+        <f t="shared" si="0"/>
+        <v>131.75</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C77" s="1">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D77" s="1">
         <f t="shared" si="0"/>
-        <v>169.15</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="C78" s="1">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="D78" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f t="shared" ref="D78" si="9">C78-C78*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C79" s="1">
-        <v>165</v>
+        <v>295</v>
       </c>
       <c r="D79" s="1">
-        <f t="shared" ref="D79:D80" si="4">C79-C79*15/100</f>
-        <v>140.25</v>
+        <f t="shared" ref="D79:D85" si="10">C79-C79*15/100</f>
+        <v>250.75</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>98</v>
+      <c r="B80" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C80" s="1">
         <v>0</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -1898,14 +1907,14 @@
         <v>89</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C81" s="1">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="D81" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f t="shared" si="10"/>
+        <v>187</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1913,14 +1922,14 @@
         <v>89</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C82" s="1">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D82" s="1">
-        <f t="shared" si="0"/>
-        <v>165.75</v>
+        <f t="shared" si="10"/>
+        <v>161.5</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1928,217 +1937,217 @@
         <v>89</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C83" s="1">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="D83" s="1">
-        <f t="shared" si="0"/>
-        <v>131.75</v>
+        <f t="shared" si="10"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>45</v>
+      <c r="B84" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C84" s="1">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="D84" s="1">
-        <f t="shared" si="0"/>
-        <v>160.65</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>113</v>
+        <v>89</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C85" s="1">
-        <v>220</v>
+        <v>145</v>
       </c>
       <c r="D85" s="1">
-        <f>C85-C85*15/100</f>
-        <v>187</v>
+        <f t="shared" si="10"/>
+        <v>123.25</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="C86" s="1">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="D86" s="1">
-        <f>C86-C86*15/100</f>
-        <v>158.94999999999999</v>
+        <f t="shared" si="0"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>104</v>
+        <v>89</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="C87" s="1">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D87" s="1">
-        <f>C87-C87*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>143.65</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="C88" s="1">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="D88" s="1">
-        <f>C88-C88*15/100</f>
-        <v>157.25</v>
+        <f t="shared" ref="D88:D89" si="11">C88-C88*15/100</f>
+        <v>140.25</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>64</v>
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="C89" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D89" s="1">
-        <f>C89-C89*15/100</f>
-        <v>169.15</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="C90" s="1">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="D90" s="1">
         <f t="shared" si="0"/>
-        <v>169.15</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="C91" s="1">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D91" s="1">
-        <f>C91-C91*15/100</f>
-        <v>157.25</v>
+        <f t="shared" si="0"/>
+        <v>165.75</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="C92" s="1">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="D92" s="1">
-        <f>C92-C92*15/100</f>
-        <v>148.75</v>
+        <f t="shared" si="0"/>
+        <v>131.75</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="C93" s="1">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D93" s="1">
-        <f>C93-C93*15/100</f>
-        <v>169.15</v>
+        <f t="shared" si="0"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>110</v>
+        <v>89</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C94" s="1">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D94" s="1">
-        <f>C94-C94*15/100</f>
-        <v>127.5</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C95" s="1">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="D95" s="1">
         <f t="shared" si="0"/>
-        <v>118.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>120</v>
+        <v>89</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
       </c>
       <c r="D96" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D96" si="12">C96-C96*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C97" s="1">
         <v>220</v>
@@ -2150,40 +2159,40 @@
     </row>
     <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C98" s="1">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D98" s="1">
         <f>C98-C98*15/100</f>
-        <v>160.65</v>
+        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C99" s="1">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="D99" s="1">
         <f>C99-C99*15/100</f>
-        <v>160.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C100" s="1">
         <v>185</v>
@@ -2195,7 +2204,7 @@
     </row>
     <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>64</v>
@@ -2210,541 +2219,856 @@
     </row>
     <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>110</v>
+        <v>90</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C102" s="1">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D102" s="1">
-        <f>C102-C102*15/100</f>
-        <v>127.5</v>
+        <f t="shared" ref="D102:D104" si="13">C102-C102*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>111</v>
+        <v>90</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C103" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D103" s="1">
-        <f t="shared" ref="D103" si="5">C103-C103*15/100</f>
-        <v>169.15</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="C104" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D104" s="1">
-        <f>C104-C104*15/100</f>
-        <v>169.15</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>107</v>
+        <v>90</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C105" s="1">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="D105" s="1">
-        <f>C105-C105*15/100</f>
-        <v>126.65</v>
+        <f t="shared" si="0"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>108</v>
+        <v>90</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="C106" s="1">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D106" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f>C106-C106*15/100</f>
+        <v>157.25</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>109</v>
+        <v>90</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C107" s="1">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D107" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f>C107-C107*15/100</f>
+        <v>148.75</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C108" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D108" s="1">
         <f>C108-C108*15/100</f>
-        <v>0</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C109" s="1">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D109" s="1">
         <f>C109-C109*15/100</f>
-        <v>0</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>104</v>
+        <v>90</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="C110" s="1">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D110" s="1">
-        <f>C110-C110*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>118.15</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
       </c>
       <c r="D111" s="1">
-        <f>C111-C111*15/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C112" s="1">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="D112" s="1">
-        <f>C112-C112*15/100</f>
-        <v>169.15</v>
+        <f t="shared" ref="D112:D120" si="14">C112-C112*15/100</f>
+        <v>187</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>110</v>
+        <v>91</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C113" s="1">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="D113" s="1">
-        <f t="shared" si="0"/>
-        <v>127.5</v>
+        <f t="shared" si="14"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>66</v>
+        <v>91</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="C114" s="1">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D114" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f t="shared" si="14"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>121</v>
+        <v>91</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="C115" s="1">
-        <v>215</v>
+        <v>185</v>
       </c>
       <c r="D115" s="1">
-        <f>C115-C115*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="14"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C116" s="1">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="D116" s="1">
-        <f t="shared" si="0"/>
-        <v>233.75</v>
+        <f t="shared" si="14"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="C117" s="1">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="D117" s="1">
-        <f t="shared" si="0"/>
-        <v>203.15</v>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>123</v>
+        <v>91</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C118" s="1">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="D118" s="1">
-        <f t="shared" si="0"/>
-        <v>147.9</v>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>122</v>
+        <v>91</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C119" s="1">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="D119" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="C120" s="1">
-        <v>249</v>
+        <v>150</v>
       </c>
       <c r="D120" s="1">
-        <f t="shared" si="0"/>
-        <v>211.65</v>
+        <f t="shared" si="14"/>
+        <v>127.5</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>70</v>
+        <v>91</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="C121" s="1">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="D121" s="1">
-        <f t="shared" ref="D121:D137" si="6">C121-C121*15/100</f>
-        <v>185.3</v>
+        <f t="shared" ref="D121" si="15">C121-C121*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C122" s="1">
-        <v>265</v>
+        <v>199</v>
       </c>
       <c r="D122" s="1">
-        <f t="shared" si="6"/>
-        <v>225.25</v>
+        <f>C122-C122*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="C123" s="1">
-        <v>285</v>
+        <v>149</v>
       </c>
       <c r="D123" s="1">
-        <f t="shared" si="6"/>
-        <v>242.25</v>
+        <f>C123-C123*15/100</f>
+        <v>126.65</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="C124" s="1">
-        <v>340</v>
+        <v>179</v>
       </c>
       <c r="D124" s="1">
-        <f t="shared" si="6"/>
-        <v>289</v>
+        <f t="shared" si="0"/>
+        <v>152.15</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>74</v>
+        <v>91</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="C125" s="1">
-        <v>215</v>
+        <v>185</v>
       </c>
       <c r="D125" s="1">
-        <f t="shared" si="6"/>
-        <v>182.75</v>
+        <f t="shared" si="0"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C126">
-        <v>299</v>
+        <v>92</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C126" s="1">
+        <v>0</v>
       </c>
       <c r="D126" s="1">
         <f>C126-C126*15/100</f>
-        <v>254.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C127">
-        <v>230</v>
+        <v>92</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C127" s="1">
+        <v>0</v>
       </c>
       <c r="D127" s="1">
-        <f t="shared" si="6"/>
-        <v>195.5</v>
+        <f>C127-C127*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C128">
-        <v>325</v>
+        <v>92</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C128" s="1">
+        <v>0</v>
       </c>
       <c r="D128" s="1">
         <f>C128-C128*15/100</f>
-        <v>276.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C129">
-        <v>199</v>
+        <v>92</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C129" s="1">
+        <v>0</v>
       </c>
       <c r="D129" s="1">
-        <f t="shared" si="6"/>
-        <v>169.15</v>
+        <f>C129-C129*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C130">
-        <v>445</v>
+        <v>92</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C130" s="1">
+        <v>199</v>
       </c>
       <c r="D130" s="1">
-        <f t="shared" si="6"/>
-        <v>378.25</v>
+        <f>C130-C130*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C131">
-        <v>400</v>
+        <v>126</v>
+      </c>
+      <c r="C131" s="1">
+        <v>0</v>
       </c>
       <c r="D131" s="1">
-        <f t="shared" si="6"/>
-        <v>340</v>
+        <f t="shared" ref="D131:D133" si="16">C131-C131*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="C132" s="1">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="D132" s="1">
-        <f t="shared" si="6"/>
-        <v>236.3</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C133" s="1">
+        <v>0</v>
+      </c>
+      <c r="D133" s="1">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A134" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C134" s="1">
+        <v>150</v>
+      </c>
+      <c r="D134" s="1">
+        <f t="shared" si="0"/>
+        <v>127.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A135" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C135" s="1">
+        <v>199</v>
+      </c>
+      <c r="D135" s="1">
+        <f t="shared" si="0"/>
+        <v>169.15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A136" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C136" s="1">
+        <v>215</v>
+      </c>
+      <c r="D136" s="1">
+        <f>C136-C136*15/100</f>
+        <v>182.75</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A137" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C137" s="1">
+        <v>275</v>
+      </c>
+      <c r="D137" s="1">
+        <f t="shared" si="0"/>
+        <v>233.75</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A138" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C138" s="1">
+        <v>239</v>
+      </c>
+      <c r="D138" s="1">
+        <f t="shared" si="0"/>
+        <v>203.15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A139" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C139" s="1">
+        <v>174</v>
+      </c>
+      <c r="D139" s="1">
+        <f t="shared" si="0"/>
+        <v>147.9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A140" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C140" s="1">
+        <v>185</v>
+      </c>
+      <c r="D140" s="1">
+        <f t="shared" si="0"/>
+        <v>157.25</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A141" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C141" s="1">
+        <v>249</v>
+      </c>
+      <c r="D141" s="1">
+        <f t="shared" si="0"/>
+        <v>211.65</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B142" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C142" s="1">
+        <v>218</v>
+      </c>
+      <c r="D142" s="1">
+        <f t="shared" ref="D142:D158" si="17">C142-C142*15/100</f>
+        <v>185.3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A143" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C143" s="1">
+        <v>265</v>
+      </c>
+      <c r="D143" s="1">
+        <f t="shared" si="17"/>
+        <v>225.25</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C144" s="1">
+        <v>285</v>
+      </c>
+      <c r="D144" s="1">
+        <f t="shared" si="17"/>
+        <v>242.25</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A145" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C145" s="1">
+        <v>340</v>
+      </c>
+      <c r="D145" s="1">
+        <f t="shared" si="17"/>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C146" s="1">
+        <v>215</v>
+      </c>
+      <c r="D146" s="1">
+        <f t="shared" si="17"/>
+        <v>182.75</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A147" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C147">
+        <v>299</v>
+      </c>
+      <c r="D147" s="1">
+        <f>C147-C147*15/100</f>
+        <v>254.15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A148" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C148">
+        <v>230</v>
+      </c>
+      <c r="D148" s="1">
+        <f t="shared" si="17"/>
+        <v>195.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C149">
+        <v>325</v>
+      </c>
+      <c r="D149" s="1">
+        <f>C149-C149*15/100</f>
+        <v>276.25</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C150">
+        <v>199</v>
+      </c>
+      <c r="D150" s="1">
+        <f t="shared" si="17"/>
+        <v>169.15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C151">
+        <v>445</v>
+      </c>
+      <c r="D151" s="1">
+        <f t="shared" si="17"/>
+        <v>378.25</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A152" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C152">
+        <v>400</v>
+      </c>
+      <c r="D152" s="1">
+        <f t="shared" si="17"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A153" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C153" s="1">
+        <v>278</v>
+      </c>
+      <c r="D153" s="1">
+        <f t="shared" si="17"/>
+        <v>236.3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A154" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C133" s="1">
+      <c r="C154" s="1">
         <v>405</v>
       </c>
-      <c r="D133" s="1">
-        <f t="shared" si="6"/>
+      <c r="D154" s="1">
+        <f t="shared" si="17"/>
         <v>344.25</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="1" t="s">
+    <row r="155" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C134">
+      <c r="B155" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C155">
         <v>360</v>
       </c>
-      <c r="D134" s="1">
-        <f t="shared" si="6"/>
+      <c r="D155" s="1">
+        <f t="shared" si="17"/>
         <v>306</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="1" t="s">
+    <row r="156" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B156" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C135">
+      <c r="C156">
         <v>249</v>
       </c>
-      <c r="D135" s="1">
-        <f t="shared" si="6"/>
+      <c r="D156" s="1">
+        <f t="shared" si="17"/>
         <v>211.65</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="1" t="s">
+    <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="B157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C136">
+      <c r="C157">
         <v>329</v>
       </c>
-      <c r="D136" s="1">
-        <f t="shared" si="6"/>
+      <c r="D157" s="1">
+        <f t="shared" si="17"/>
         <v>279.64999999999998</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="1" t="s">
+    <row r="158" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B158" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C137">
+      <c r="C158">
         <v>275</v>
       </c>
-      <c r="D137" s="1">
-        <f t="shared" si="6"/>
+      <c r="D158" s="1">
+        <f t="shared" si="17"/>
         <v>233.75</v>
       </c>
     </row>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A403C1E-0E78-4793-8568-1C184B4826E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F4A7A0-3AD7-4121-BD27-B439F1063B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2024,7 +2024,7 @@
     </row>
     <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>98</v>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F4A7A0-3AD7-4121-BD27-B439F1063B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF0E0E3-661D-4ADA-8C88-655AEF062E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2180,11 +2180,11 @@
         <v>104</v>
       </c>
       <c r="C99" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D99" s="1">
         <f>C99-C99*15/100</f>
-        <v>0</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2585,11 +2585,11 @@
         <v>102</v>
       </c>
       <c r="C126" s="1">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="D126" s="1">
         <f>C126-C126*15/100</f>
-        <v>0</v>
+        <v>191.25</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF0E0E3-661D-4ADA-8C88-655AEF062E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0682BF53-7E48-4851-8297-316201569724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="132">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -339,9 +339,6 @@
     <t xml:space="preserve"> إمتحان علوم  ⬅️ 189</t>
   </si>
   <si>
-    <t xml:space="preserve"> إمتحان عربي  ⬅️ </t>
-  </si>
-  <si>
     <t xml:space="preserve"> إمتحان دراسات  ⬅️ </t>
   </si>
   <si>
@@ -412,6 +409,24 @@
   </si>
   <si>
     <t xml:space="preserve"> المعاصر بلس ⬅️  </t>
+  </si>
+  <si>
+    <t>كتب التأسيس</t>
+  </si>
+  <si>
+    <t>(نحو تأسيس سليم او سندباد أجزاء 1و2و3) ( نور البيان) ) ذا بيست ستارت) ( توب)  ( اوكسفورد</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان علوم  ⬅️ 199</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان عربي  ⬅️ 225</t>
   </si>
 </sst>
 </file>
@@ -477,7 +492,93 @@
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -492,6 +593,21 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D159" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:D159" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="كتب التأسيس" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="(نحو تأسيس سليم او سندباد أجزاء 1و2و3) ( نور البيان) ) ذا بيست ستارت) ( توب)  ( اوكسفورد" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{18281C2B-AE74-4493-8A8B-816AFDD52349}" name="1)"/>
+    <tableColumn id="4" xr3:uid="{0BC2C3D8-7FE3-4D02-BC47-E5D5B75D5119}" name="1" dataDxfId="2">
+      <calculatedColumnFormula>C2-C2*15/100</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -695,7 +811,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D158"/>
+  <dimension ref="A1:D159"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -704,32 +820,31 @@
   <sheetData>
     <row r="1" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="1">
-        <v>125</v>
-      </c>
-      <c r="D1" s="1">
-        <f t="shared" ref="D1:D141" si="0">C1-C1*15/100</f>
-        <v>106.25</v>
+        <v>127</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="C2" s="1">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="D2" s="1">
-        <f t="shared" si="0"/>
-        <v>174.25</v>
+        <f t="shared" ref="D2:D142" si="0">C2-C2*15/100</f>
+        <v>106.25</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -737,14 +852,14 @@
         <v>83</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="D3" s="1">
         <f t="shared" si="0"/>
-        <v>106.25</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -752,29 +867,29 @@
         <v>83</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" si="0"/>
-        <v>178.5</v>
+        <v>106.25</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="D5" s="1">
-        <f>C5-C5*15/100</f>
-        <v>153</v>
+        <f t="shared" si="0"/>
+        <v>178.5</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -782,14 +897,14 @@
         <v>84</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D6" s="1">
         <f>C6-C6*15/100</f>
-        <v>144.5</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -797,14 +912,14 @@
         <v>84</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="D7" s="1">
         <f>C7-C7*15/100</f>
-        <v>110.5</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -812,14 +927,14 @@
         <v>84</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="D8" s="1">
-        <f t="shared" si="0"/>
-        <v>126.65</v>
+        <f>C8-C8*15/100</f>
+        <v>110.5</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -827,14 +942,14 @@
         <v>84</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>135.15</v>
+        <v>126.65</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -842,14 +957,14 @@
         <v>84</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>109.65</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -857,14 +972,14 @@
         <v>84</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" s="1">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>109.65</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -872,7 +987,7 @@
         <v>84</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1">
         <v>165</v>
@@ -887,14 +1002,14 @@
         <v>84</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>114.75</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -902,14 +1017,14 @@
         <v>84</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="1">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>114.75</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -917,14 +1032,14 @@
         <v>84</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>126</v>
+        <v>19</v>
       </c>
       <c r="C15" s="1">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -932,14 +1047,14 @@
         <v>84</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="C16" s="1">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" ref="D16:D22" si="1">C16-C16*15/100</f>
-        <v>216.75</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -947,14 +1062,14 @@
         <v>84</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="1">
-        <v>165</v>
+        <v>255</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="1"/>
-        <v>140.25</v>
+        <f t="shared" ref="D17:D23" si="1">C17-C17*15/100</f>
+        <v>216.75</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -962,14 +1077,14 @@
         <v>84</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="1">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D18" s="1">
         <f t="shared" si="1"/>
-        <v>148.75</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -977,29 +1092,29 @@
         <v>84</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="1">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D19" s="1">
         <f t="shared" si="1"/>
-        <v>143.65</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C20" s="1">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" si="1"/>
-        <v>153</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1007,14 +1122,14 @@
         <v>85</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D21" s="1">
         <f t="shared" si="1"/>
-        <v>144.5</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1022,14 +1137,14 @@
         <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C22" s="1">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="D22" s="1">
         <f t="shared" si="1"/>
-        <v>119</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1037,14 +1152,14 @@
         <v>85</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23" s="1">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f t="shared" si="1"/>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1052,7 +1167,7 @@
         <v>85</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C24" s="1">
         <v>159</v>
@@ -1067,14 +1182,14 @@
         <v>85</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C25" s="1">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D25" s="1">
         <f t="shared" si="0"/>
-        <v>118.15</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1082,14 +1197,14 @@
         <v>85</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C26" s="1">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="D26" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>118.15</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1097,7 +1212,7 @@
         <v>85</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1">
         <v>165</v>
@@ -1112,14 +1227,14 @@
         <v>85</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="D28" s="1">
         <f t="shared" si="0"/>
-        <v>114.75</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1127,14 +1242,14 @@
         <v>85</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C29" s="1">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D29" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>114.75</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1142,14 +1257,14 @@
         <v>85</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>126</v>
+        <v>19</v>
       </c>
       <c r="C30" s="1">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D30" s="1">
-        <f t="shared" ref="D30" si="2">C30-C30*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>148.75</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1157,13 +1272,13 @@
         <v>85</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C31" s="1">
         <v>0</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D31" si="2">C31-C31*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -1172,29 +1287,29 @@
         <v>85</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="C32" s="1">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="D32" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C33" s="1">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="D33" s="1">
-        <f>C33-C33*15/100</f>
-        <v>161.5</v>
+        <f t="shared" si="0"/>
+        <v>148.75</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1202,14 +1317,14 @@
         <v>86</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C34" s="1">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="D34" s="1">
         <f>C34-C34*15/100</f>
-        <v>148.75</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1217,14 +1332,14 @@
         <v>86</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C35" s="1">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="D35" s="1">
         <f>C35-C35*15/100</f>
-        <v>119</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1232,14 +1347,14 @@
         <v>86</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C36" s="1">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="D36" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f>C36-C36*15/100</f>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1247,14 +1362,14 @@
         <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C37" s="1">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D37" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1262,14 +1377,14 @@
         <v>86</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C38" s="1">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="D38" s="1">
         <f t="shared" si="0"/>
-        <v>118.15</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1277,14 +1392,14 @@
         <v>86</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C39" s="1">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="D39" s="1">
-        <f>C39-C39*15/100</f>
-        <v>143.65</v>
+        <f t="shared" si="0"/>
+        <v>118.15</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1292,14 +1407,14 @@
         <v>86</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C40" s="1">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D40" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f>C40-C40*15/100</f>
+        <v>143.65</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1307,14 +1422,14 @@
         <v>86</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C41" s="1">
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="D41" s="1">
         <f t="shared" si="0"/>
-        <v>119</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1322,14 +1437,14 @@
         <v>86</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C42" s="1">
-        <v>189</v>
+        <v>140</v>
       </c>
       <c r="D42" s="1">
-        <f>C42-C42*15/100</f>
-        <v>160.65</v>
+        <f t="shared" si="0"/>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1337,14 +1452,14 @@
         <v>86</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>126</v>
+        <v>33</v>
       </c>
       <c r="C43" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D43" s="1">
-        <f t="shared" ref="D43" si="3">C43-C43*15/100</f>
-        <v>0</v>
+        <f>C43-C43*15/100</f>
+        <v>160.65</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1352,13 +1467,13 @@
         <v>86</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C44" s="1">
         <v>0</v>
       </c>
       <c r="D44" s="1">
-        <f t="shared" ref="D44" si="4">C44-C44*15/100</f>
+        <f t="shared" ref="D44" si="3">C44-C44*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -1367,14 +1482,14 @@
         <v>86</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="C45" s="1">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D45" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f t="shared" ref="D45" si="4">C45-C45*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1382,7 +1497,7 @@
         <v>86</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C46" s="1">
         <v>179</v>
@@ -1394,17 +1509,17 @@
     </row>
     <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C47" s="1">
-        <v>215</v>
+        <v>179</v>
       </c>
       <c r="D47" s="1">
-        <f>C47-C47*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="0"/>
+        <v>152.15</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1412,14 +1527,14 @@
         <v>87</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C48" s="1">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="D48" s="1">
         <f>C48-C48*15/100</f>
-        <v>157.25</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1427,14 +1542,14 @@
         <v>87</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C49" s="1">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D49" s="1">
         <f>C49-C49*15/100</f>
-        <v>161.5</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1442,44 +1557,44 @@
         <v>87</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C50" s="1">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D50" s="1">
         <f>C50-C50*15/100</f>
-        <v>144.5</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>40</v>
+      <c r="B51" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="C51" s="1">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="D51" s="1">
-        <f t="shared" ref="D51" si="5">C51-C51*15/100</f>
-        <v>123.25</v>
+        <f>C51-C51*15/100</f>
+        <v>144.5</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>41</v>
+      <c r="B52" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="C52" s="1">
-        <v>195</v>
+        <v>145</v>
       </c>
       <c r="D52" s="1">
-        <f t="shared" si="0"/>
-        <v>165.75</v>
+        <f t="shared" ref="D52" si="5">C52-C52*15/100</f>
+        <v>123.25</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1487,14 +1602,14 @@
         <v>87</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53" s="1">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="D53" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1502,44 +1617,44 @@
         <v>87</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C54" s="1">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D54" s="1">
         <f t="shared" si="0"/>
-        <v>135.15</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>98</v>
+      <c r="B55" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="C55" s="1">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="D55" s="1">
-        <f t="shared" ref="D55" si="6">C55-C55*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>135.15</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>44</v>
+      <c r="B56" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="C56" s="1">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="D56" s="1">
-        <f>C56-C56*15/100</f>
-        <v>143.65</v>
+        <f t="shared" ref="D56" si="6">C56-C56*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1547,14 +1662,14 @@
         <v>87</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C57" s="1">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D57" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f>C57-C57*15/100</f>
+        <v>143.65</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1562,14 +1677,14 @@
         <v>87</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C58" s="1">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D58" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1577,14 +1692,14 @@
         <v>87</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="C59" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D59" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1592,14 +1707,14 @@
         <v>87</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="C60" s="1">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="D60" s="1">
-        <f>C60-C60*15/100</f>
-        <v>267.75</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1607,14 +1722,14 @@
         <v>87</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>125</v>
+        <v>46</v>
       </c>
       <c r="C61" s="1">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="D61" s="1">
-        <f t="shared" ref="D61" si="7">C61-C61*15/100</f>
-        <v>0</v>
+        <f>C61-C61*15/100</f>
+        <v>267.75</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1622,14 +1737,14 @@
         <v>87</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>47</v>
+        <v>124</v>
       </c>
       <c r="C62" s="1">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="D62" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f t="shared" ref="D62" si="7">C62-C62*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1637,14 +1752,14 @@
         <v>87</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C63" s="1">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D63" s="1">
         <f t="shared" si="0"/>
-        <v>174.25</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1652,29 +1767,29 @@
         <v>87</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C64" s="1">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="D64" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C65" s="1">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="D65" s="1">
-        <f>C65-C65*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="0"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1682,14 +1797,14 @@
         <v>88</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C66" s="1">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="D66" s="1">
         <f>C66-C66*15/100</f>
-        <v>157.25</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1697,29 +1812,29 @@
         <v>88</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C67" s="1">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D67" s="1">
         <f>C67-C67*15/100</f>
-        <v>161.5</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>97</v>
+      <c r="B68" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="C68" s="1">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="D68" s="1">
         <f>C68-C68*15/100</f>
-        <v>0</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1727,13 +1842,13 @@
         <v>88</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C69" s="1">
         <v>0</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" ref="D69" si="8">C69-C69*15/100</f>
+        <f>C69-C69*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -1741,15 +1856,15 @@
       <c r="A70" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>41</v>
+      <c r="B70" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C70" s="1">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="D70" s="1">
-        <f t="shared" si="0"/>
-        <v>165.75</v>
+        <f t="shared" ref="D70" si="8">C70-C70*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1757,14 +1872,14 @@
         <v>88</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C71" s="1">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="D71" s="1">
         <f t="shared" si="0"/>
-        <v>135.15</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1772,44 +1887,44 @@
         <v>88</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C72" s="1">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D72" s="1">
         <f t="shared" si="0"/>
-        <v>143.65</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>98</v>
+      <c r="B73" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="C73" s="1">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D73" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>53</v>
+      <c r="B74" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="C74" s="1">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D74" s="1">
-        <f>C74-C74*15/100</f>
-        <v>152.15</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1817,14 +1932,14 @@
         <v>88</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C75" s="1">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D75" s="1">
-        <f t="shared" si="0"/>
-        <v>158.94999999999999</v>
+        <f>C75-C75*15/100</f>
+        <v>152.15</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1832,14 +1947,14 @@
         <v>88</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C76" s="1">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="D76" s="1">
         <f t="shared" si="0"/>
-        <v>131.75</v>
+        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1847,14 +1962,14 @@
         <v>88</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C77" s="1">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="D77" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1862,14 +1977,14 @@
         <v>88</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="C78" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D78" s="1">
-        <f t="shared" ref="D78" si="9">C78-C78*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1877,14 +1992,14 @@
         <v>88</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="C79" s="1">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="D79" s="1">
-        <f t="shared" ref="D79:D85" si="10">C79-C79*15/100</f>
-        <v>250.75</v>
+        <f t="shared" ref="D79" si="9">C79-C79*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1892,29 +2007,29 @@
         <v>88</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="C80" s="1">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" ref="D80:D86" si="10">C80-C80*15/100</f>
+        <v>250.75</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>57</v>
+        <v>124</v>
       </c>
       <c r="C81" s="1">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D81" s="1">
         <f t="shared" si="10"/>
-        <v>187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1922,14 +2037,14 @@
         <v>89</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C82" s="1">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="D82" s="1">
         <f t="shared" si="10"/>
-        <v>161.5</v>
+        <v>187</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1937,29 +2052,29 @@
         <v>89</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C83" s="1">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D83" s="1">
         <f t="shared" si="10"/>
-        <v>157.25</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>97</v>
+      <c r="B84" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="C84" s="1">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D84" s="1">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1967,29 +2082,29 @@
         <v>89</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="C85" s="1">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="D85" s="1">
         <f t="shared" si="10"/>
-        <v>123.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>60</v>
+      <c r="B86" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C86" s="1">
-        <v>199</v>
+        <v>145</v>
       </c>
       <c r="D86" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f t="shared" si="10"/>
+        <v>123.25</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1997,14 +2112,14 @@
         <v>89</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C87" s="1">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="D87" s="1">
         <f t="shared" si="0"/>
-        <v>143.65</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2012,44 +2127,44 @@
         <v>89</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C88" s="1">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D88" s="1">
-        <f t="shared" ref="D88:D89" si="11">C88-C88*15/100</f>
-        <v>140.25</v>
+        <f t="shared" si="0"/>
+        <v>143.65</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>98</v>
+      <c r="B89" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C89" s="1">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="D89" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" ref="D89:D90" si="11">C89-C89*15/100</f>
+        <v>140.25</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>62</v>
+      <c r="B90" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="C90" s="1">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D90" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2057,14 +2172,14 @@
         <v>89</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C91" s="1">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D91" s="1">
         <f t="shared" si="0"/>
-        <v>165.75</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2072,14 +2187,14 @@
         <v>89</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C92" s="1">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="D92" s="1">
         <f t="shared" si="0"/>
-        <v>131.75</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2087,14 +2202,14 @@
         <v>89</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C93" s="1">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="D93" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2102,14 +2217,14 @@
         <v>89</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="C94" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D94" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2117,7 +2232,7 @@
         <v>89</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C95" s="1">
         <v>0</v>
@@ -2132,29 +2247,29 @@
         <v>89</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
       </c>
       <c r="D96" s="1">
-        <f t="shared" ref="D96" si="12">C96-C96*15/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C97" s="1">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D97" s="1">
-        <f>C97-C97*15/100</f>
-        <v>187</v>
+        <f t="shared" ref="D97" si="12">C97-C97*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2162,44 +2277,44 @@
         <v>90</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C98" s="1">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="D98" s="1">
         <f>C98-C98*15/100</f>
-        <v>158.94999999999999</v>
+        <v>187</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>104</v>
+      <c r="B99" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C99" s="1">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D99" s="1">
         <f>C99-C99*15/100</f>
-        <v>169.15</v>
+        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>115</v>
+      <c r="B100" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="C100" s="1">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D100" s="1">
         <f>C100-C100*15/100</f>
-        <v>157.25</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2207,14 +2322,14 @@
         <v>90</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="C101" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D101" s="1">
         <f>C101-C101*15/100</f>
-        <v>169.15</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2222,14 +2337,14 @@
         <v>90</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="C102" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D102" s="1">
-        <f t="shared" ref="D102:D104" si="13">C102-C102*15/100</f>
-        <v>0</v>
+        <f>C102-C102*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2237,13 +2352,13 @@
         <v>90</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
       </c>
       <c r="D103" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="D103:D105" si="13">C103-C103*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -2252,7 +2367,7 @@
         <v>90</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C104" s="1">
         <v>0</v>
@@ -2267,14 +2382,14 @@
         <v>90</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C105" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D105" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2282,14 +2397,14 @@
         <v>90</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C106" s="1">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D106" s="1">
-        <f>C106-C106*15/100</f>
-        <v>157.25</v>
+        <f t="shared" si="0"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2297,14 +2412,14 @@
         <v>90</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C107" s="1">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D107" s="1">
         <f>C107-C107*15/100</f>
-        <v>148.75</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2312,74 +2427,74 @@
         <v>90</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C108" s="1">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="D108" s="1">
         <f>C108-C108*15/100</f>
-        <v>169.15</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C109" s="1">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="D109" s="1">
         <f>C109-C109*15/100</f>
-        <v>127.5</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>119</v>
+      <c r="B110" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="C110" s="1">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D110" s="1">
-        <f t="shared" si="0"/>
-        <v>118.15</v>
+        <f>C110-C110*15/100</f>
+        <v>127.5</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>120</v>
+      <c r="B111" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="C111" s="1">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D111" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>118.15</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="C112" s="1">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D112" s="1">
-        <f t="shared" ref="D112:D120" si="14">C112-C112*15/100</f>
-        <v>187</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2387,14 +2502,14 @@
         <v>91</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C113" s="1">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="D113" s="1">
-        <f t="shared" si="14"/>
-        <v>160.65</v>
+        <f t="shared" ref="D113:D121" si="14">C113-C113*15/100</f>
+        <v>187</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2402,7 +2517,7 @@
         <v>91</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C114" s="1">
         <v>189</v>
@@ -2417,29 +2532,29 @@
         <v>91</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C115" s="1">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D115" s="1">
         <f t="shared" si="14"/>
-        <v>157.25</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>64</v>
+      <c r="B116" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="C116" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D116" s="1">
         <f t="shared" si="14"/>
-        <v>169.15</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2447,14 +2562,14 @@
         <v>91</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="C117" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D117" s="1">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2462,7 +2577,7 @@
         <v>91</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C118" s="1">
         <v>0</v>
@@ -2477,7 +2592,7 @@
         <v>91</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C119" s="1">
         <v>0</v>
@@ -2491,15 +2606,15 @@
       <c r="A120" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>110</v>
+      <c r="B120" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C120" s="1">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D120" s="1">
         <f t="shared" si="14"/>
-        <v>127.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2507,28 +2622,28 @@
         <v>91</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C121" s="1">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="D121" s="1">
-        <f t="shared" ref="D121" si="15">C121-C121*15/100</f>
-        <v>169.15</v>
+        <f t="shared" si="14"/>
+        <v>127.5</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>65</v>
+      <c r="B122" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="C122" s="1">
         <v>199</v>
       </c>
       <c r="D122" s="1">
-        <f>C122-C122*15/100</f>
+        <f t="shared" ref="D122" si="15">C122-C122*15/100</f>
         <v>169.15</v>
       </c>
     </row>
@@ -2536,15 +2651,15 @@
       <c r="A123" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>107</v>
+      <c r="B123" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C123" s="1">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="D123" s="1">
         <f>C123-C123*15/100</f>
-        <v>126.65</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2552,14 +2667,14 @@
         <v>91</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C124" s="1">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D124" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f>C124-C124*15/100</f>
+        <v>126.65</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2567,29 +2682,29 @@
         <v>91</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C125" s="1">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D125" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C126" s="1">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="D126" s="1">
-        <f>C126-C126*15/100</f>
-        <v>191.25</v>
+        <f t="shared" si="0"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2597,14 +2712,14 @@
         <v>92</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="C127" s="1">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="D127" s="1">
         <f>C127-C127*15/100</f>
-        <v>0</v>
+        <v>191.25</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2612,7 +2727,7 @@
         <v>92</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C128" s="1">
         <v>0</v>
@@ -2627,7 +2742,7 @@
         <v>92</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C129" s="1">
         <v>0</v>
@@ -2642,29 +2757,29 @@
         <v>92</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C130" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D130" s="1">
         <f>C130-C130*15/100</f>
-        <v>169.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>126</v>
+      <c r="B131" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="C131" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D131" s="1">
-        <f t="shared" ref="D131:D133" si="16">C131-C131*15/100</f>
-        <v>0</v>
+        <f>C131-C131*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2672,13 +2787,13 @@
         <v>92</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C132" s="1">
         <v>0</v>
       </c>
       <c r="D132" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="D132:D134" si="16">C132-C132*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -2687,7 +2802,7 @@
         <v>92</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C133" s="1">
         <v>0</v>
@@ -2702,14 +2817,14 @@
         <v>92</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="C134" s="1">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D134" s="1">
-        <f t="shared" si="0"/>
-        <v>127.5</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2717,14 +2832,14 @@
         <v>92</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="C135" s="1">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="D135" s="1">
         <f t="shared" si="0"/>
-        <v>169.15</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2732,29 +2847,29 @@
         <v>92</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="C136" s="1">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="D136" s="1">
-        <f>C136-C136*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="0"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="C137" s="1">
-        <v>275</v>
+        <v>215</v>
       </c>
       <c r="D137" s="1">
-        <f t="shared" si="0"/>
-        <v>233.75</v>
+        <f>C137-C137*15/100</f>
+        <v>182.75</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2762,29 +2877,29 @@
         <v>93</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C138" s="1">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="D138" s="1">
         <f t="shared" si="0"/>
-        <v>203.15</v>
+        <v>233.75</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B139" s="4" t="s">
-        <v>123</v>
+      <c r="B139" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="C139" s="1">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="D139" s="1">
         <f t="shared" si="0"/>
-        <v>147.9</v>
+        <v>203.15</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2795,41 +2910,41 @@
         <v>122</v>
       </c>
       <c r="C140" s="1">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="D140" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>69</v>
+        <v>93</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="C141" s="1">
-        <v>249</v>
+        <v>185</v>
       </c>
       <c r="D141" s="1">
         <f t="shared" si="0"/>
-        <v>211.65</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C142" s="1">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="D142" s="1">
-        <f t="shared" ref="D142:D158" si="17">C142-C142*15/100</f>
-        <v>185.3</v>
+        <f t="shared" si="0"/>
+        <v>211.65</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2837,14 +2952,14 @@
         <v>95</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C143" s="1">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="D143" s="1">
-        <f t="shared" si="17"/>
-        <v>225.25</v>
+        <f t="shared" ref="D143:D159" si="17">C143-C143*15/100</f>
+        <v>185.3</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2852,14 +2967,14 @@
         <v>95</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C144" s="1">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="D144" s="1">
         <f t="shared" si="17"/>
-        <v>242.25</v>
+        <v>225.25</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2867,14 +2982,14 @@
         <v>95</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C145" s="1">
-        <v>340</v>
+        <v>285</v>
       </c>
       <c r="D145" s="1">
         <f t="shared" si="17"/>
-        <v>289</v>
+        <v>242.25</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2882,14 +2997,14 @@
         <v>95</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C146" s="1">
-        <v>215</v>
+        <v>340</v>
       </c>
       <c r="D146" s="1">
         <f t="shared" si="17"/>
-        <v>182.75</v>
+        <v>289</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2897,14 +3012,14 @@
         <v>95</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C147">
-        <v>299</v>
+        <v>74</v>
+      </c>
+      <c r="C147" s="1">
+        <v>215</v>
       </c>
       <c r="D147" s="1">
-        <f>C147-C147*15/100</f>
-        <v>254.15</v>
+        <f t="shared" si="17"/>
+        <v>182.75</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2912,14 +3027,14 @@
         <v>95</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C148">
-        <v>230</v>
+        <v>299</v>
       </c>
       <c r="D148" s="1">
-        <f t="shared" si="17"/>
-        <v>195.5</v>
+        <f>C148-C148*15/100</f>
+        <v>254.15</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2927,14 +3042,14 @@
         <v>95</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C149">
-        <v>325</v>
+        <v>230</v>
       </c>
       <c r="D149" s="1">
-        <f>C149-C149*15/100</f>
-        <v>276.25</v>
+        <f t="shared" si="17"/>
+        <v>195.5</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2942,14 +3057,14 @@
         <v>95</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C150">
-        <v>199</v>
+        <v>325</v>
       </c>
       <c r="D150" s="1">
-        <f t="shared" si="17"/>
-        <v>169.15</v>
+        <f>C150-C150*15/100</f>
+        <v>276.25</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2957,14 +3072,14 @@
         <v>95</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C151">
-        <v>445</v>
+        <v>199</v>
       </c>
       <c r="D151" s="1">
         <f t="shared" si="17"/>
-        <v>378.25</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2972,14 +3087,14 @@
         <v>95</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C152">
-        <v>400</v>
+        <v>445</v>
       </c>
       <c r="D152" s="1">
         <f t="shared" si="17"/>
-        <v>340</v>
+        <v>378.25</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2987,14 +3102,14 @@
         <v>95</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C153" s="1">
-        <v>278</v>
+        <v>80</v>
+      </c>
+      <c r="C153">
+        <v>400</v>
       </c>
       <c r="D153" s="1">
         <f t="shared" si="17"/>
-        <v>236.3</v>
+        <v>340</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3002,14 +3117,14 @@
         <v>95</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C154" s="1">
-        <v>405</v>
+        <v>278</v>
       </c>
       <c r="D154" s="1">
         <f t="shared" si="17"/>
-        <v>344.25</v>
+        <v>236.3</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3017,14 +3132,14 @@
         <v>95</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C155">
-        <v>360</v>
+        <v>82</v>
+      </c>
+      <c r="C155" s="1">
+        <v>405</v>
       </c>
       <c r="D155" s="1">
         <f t="shared" si="17"/>
-        <v>306</v>
+        <v>344.25</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3032,14 +3147,14 @@
         <v>95</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C156">
-        <v>249</v>
+        <v>360</v>
       </c>
       <c r="D156" s="1">
         <f t="shared" si="17"/>
-        <v>211.65</v>
+        <v>306</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3047,14 +3162,14 @@
         <v>95</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C157">
-        <v>329</v>
+        <v>249</v>
       </c>
       <c r="D157" s="1">
         <f t="shared" si="17"/>
-        <v>279.64999999999998</v>
+        <v>211.65</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3062,17 +3177,35 @@
         <v>95</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C158">
-        <v>275</v>
+        <v>329</v>
       </c>
       <c r="D158" s="1">
         <f t="shared" si="17"/>
+        <v>279.64999999999998</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C159">
+        <v>275</v>
+      </c>
+      <c r="D159" s="1">
+        <f t="shared" si="17"/>
         <v>233.75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0682BF53-7E48-4851-8297-316201569724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A3780E-5040-46F2-8DE0-B0A0F726374F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="131">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -39,12 +39,6 @@
     <t>الأضواء عربي (شرح) ⬅️ 249</t>
   </si>
   <si>
-    <t>جيم الأضواء انجليزي (جزء اول)  ⬅️ 275</t>
-  </si>
-  <si>
-    <t>جيم الأضواء انجليزي  ⬅️ 169</t>
-  </si>
-  <si>
     <t>الأضواء عربي (اسئلة) ⬅️ 329</t>
   </si>
   <si>
@@ -165,9 +159,6 @@
     <t xml:space="preserve"> أضواء دراسات ⬅️ 159</t>
   </si>
   <si>
-    <t xml:space="preserve"> جيم الاضواء انجليزي ⬅️ 169</t>
-  </si>
-  <si>
     <t xml:space="preserve"> المعاصر إنجليزي ⬅️ 189</t>
   </si>
   <si>
@@ -192,9 +183,6 @@
     <t xml:space="preserve"> أضواء رياضيات ⬅️ 169</t>
   </si>
   <si>
-    <t xml:space="preserve"> جيم الاضواء انجليزي ⬅️ 179 </t>
-  </si>
-  <si>
     <t xml:space="preserve"> ستيب أهيد إنجليزي ⬅️ 187</t>
   </si>
   <si>
@@ -231,18 +219,6 @@
     <t xml:space="preserve"> الاضواء عربي ⬅️ 199 </t>
   </si>
   <si>
-    <t xml:space="preserve"> جيم الاضواء انجليزي ⬅️ 199 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> انجليزي جيم الاضواء  ⬅️ 275 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> عربي الأضواء ⬅️ 239</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> عربي الأضواء ⬅️ 249</t>
-  </si>
-  <si>
     <t xml:space="preserve"> إمتحان جغرافيا (شرح) ⬅️ 218</t>
   </si>
   <si>
@@ -414,9 +390,6 @@
     <t>كتب التأسيس</t>
   </si>
   <si>
-    <t>(نحو تأسيس سليم او سندباد أجزاء 1و2و3) ( نور البيان) ) ذا بيست ستارت) ( توب)  ( اوكسفورد</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -426,7 +399,38 @@
     <t xml:space="preserve"> إمتحان علوم  ⬅️ 199</t>
   </si>
   <si>
-    <t xml:space="preserve"> إمتحان عربي  ⬅️ 225</t>
+    <t xml:space="preserve"> أضواء جيم إنجليزي ⬅️ 169</t>
+  </si>
+  <si>
+    <t>أضواء جيم إنجليزي  ⬅️ 169</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء جيم إنجليزي ⬅️ 199 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء جيم إنجليزي  ⬅️ 275 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> الأضواء عربي ⬅️ 239</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> الأضواء عربي ⬅️ 249</t>
+  </si>
+  <si>
+    <t>أضواء جيم انجليزي (جزء اول)  ⬅️ 275</t>
+  </si>
+  <si>
+    <t>(نحو تأسيس سليم  أجزاء 1و2و3) 
+(نحو  سندباد أجزاء 1و2و3) 
+( نور البيان انجليزي جزئين - عربي) 
+( ذا بيست ستارت بوك 1و2) 
+( توب فونكس1و2 - جرامر 1و2و3)  
+( اوكسفورد 5أجزاء)
+(معلم القراءة)
+(نون والقلم)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان عربي  ⬅️ 235</t>
   </si>
 </sst>
 </file>
@@ -480,13 +484,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -596,13 +606,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D159" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D159" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="A1:D159" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="كتب التأسيس" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="(نحو تأسيس سليم او سندباد أجزاء 1و2و3) ( نور البيان) ) ذا بيست ستارت) ( توب)  ( اوكسفورد" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="كتب التأسيس" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="(نحو تأسيس سليم  أجزاء 1و2و3) _x000a_(نحو  سندباد أجزاء 1و2و3) _x000a_( نور البيان انجليزي جزئين - عربي) _x000a_( ذا بيست ستارت بوك 1و2) _x000a_( توب فونكس1و2 - جرامر 1و2و3)  _x000a_( اوكسفورد 5أجزاء)_x000a_(معلم القراءة)_x000a_(نون والقلم)" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{18281C2B-AE74-4493-8A8B-816AFDD52349}" name="1)"/>
-    <tableColumn id="4" xr3:uid="{0BC2C3D8-7FE3-4D02-BC47-E5D5B75D5119}" name="1" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{0BC2C3D8-7FE3-4D02-BC47-E5D5B75D5119}" name="1" dataDxfId="0">
       <calculatedColumnFormula>C2-C2*15/100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -818,26 +828,26 @@
     <col min="2" max="2" width="38.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>127</v>
+    <row r="1" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1">
         <v>125</v>
@@ -849,10 +859,10 @@
     </row>
     <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1">
         <v>205</v>
@@ -864,10 +874,10 @@
     </row>
     <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1">
         <v>125</v>
@@ -879,10 +889,10 @@
     </row>
     <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1">
         <v>210</v>
@@ -894,10 +904,10 @@
     </row>
     <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1">
         <v>180</v>
@@ -909,10 +919,10 @@
     </row>
     <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1">
         <v>170</v>
@@ -924,10 +934,10 @@
     </row>
     <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1">
         <v>130</v>
@@ -939,10 +949,10 @@
     </row>
     <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1">
         <v>149</v>
@@ -954,10 +964,10 @@
     </row>
     <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>159</v>
@@ -969,10 +979,10 @@
     </row>
     <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1">
         <v>129</v>
@@ -984,10 +994,10 @@
     </row>
     <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C12" s="1">
         <v>165</v>
@@ -999,10 +1009,10 @@
     </row>
     <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C13" s="1">
         <v>165</v>
@@ -1014,10 +1024,10 @@
     </row>
     <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C14" s="1">
         <v>135</v>
@@ -1029,10 +1039,10 @@
     </row>
     <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1">
         <v>175</v>
@@ -1044,10 +1054,10 @@
     </row>
     <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C16" s="1">
         <v>0</v>
@@ -1059,10 +1069,10 @@
     </row>
     <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1">
         <v>255</v>
@@ -1074,10 +1084,10 @@
     </row>
     <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1">
         <v>165</v>
@@ -1089,10 +1099,10 @@
     </row>
     <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19" s="1">
         <v>175</v>
@@ -1104,10 +1114,10 @@
     </row>
     <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" s="1">
         <v>169</v>
@@ -1119,10 +1129,10 @@
     </row>
     <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C21" s="1">
         <v>180</v>
@@ -1134,10 +1144,10 @@
     </row>
     <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C22" s="1">
         <v>170</v>
@@ -1149,10 +1159,10 @@
     </row>
     <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C23" s="1">
         <v>140</v>
@@ -1164,10 +1174,10 @@
     </row>
     <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C24" s="1">
         <v>159</v>
@@ -1179,10 +1189,10 @@
     </row>
     <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C25" s="1">
         <v>159</v>
@@ -1194,10 +1204,10 @@
     </row>
     <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C26" s="1">
         <v>139</v>
@@ -1209,10 +1219,10 @@
     </row>
     <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C27" s="1">
         <v>165</v>
@@ -1224,10 +1234,10 @@
     </row>
     <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>165</v>
@@ -1239,10 +1249,10 @@
     </row>
     <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1">
         <v>135</v>
@@ -1254,10 +1264,10 @@
     </row>
     <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1">
         <v>175</v>
@@ -1269,10 +1279,10 @@
     </row>
     <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C31" s="1">
         <v>0</v>
@@ -1284,10 +1294,10 @@
     </row>
     <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C32" s="1">
         <v>0</v>
@@ -1299,10 +1309,10 @@
     </row>
     <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C33" s="1">
         <v>175</v>
@@ -1314,10 +1324,10 @@
     </row>
     <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C34" s="1">
         <v>190</v>
@@ -1329,10 +1339,10 @@
     </row>
     <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C35" s="1">
         <v>175</v>
@@ -1344,10 +1354,10 @@
     </row>
     <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C36" s="1">
         <v>140</v>
@@ -1359,10 +1369,10 @@
     </row>
     <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C37" s="1">
         <v>169</v>
@@ -1374,10 +1384,10 @@
     </row>
     <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C38" s="1">
         <v>165</v>
@@ -1389,10 +1399,10 @@
     </row>
     <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C39" s="1">
         <v>139</v>
@@ -1404,10 +1414,10 @@
     </row>
     <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="C40" s="1">
         <v>169</v>
@@ -1419,10 +1429,10 @@
     </row>
     <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C41" s="1">
         <v>185</v>
@@ -1434,10 +1444,10 @@
     </row>
     <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C42" s="1">
         <v>140</v>
@@ -1449,10 +1459,10 @@
     </row>
     <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C43" s="1">
         <v>189</v>
@@ -1464,10 +1474,10 @@
     </row>
     <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C44" s="1">
         <v>0</v>
@@ -1479,10 +1489,10 @@
     </row>
     <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C45" s="1">
         <v>0</v>
@@ -1494,10 +1504,10 @@
     </row>
     <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C46" s="1">
         <v>179</v>
@@ -1509,10 +1519,10 @@
     </row>
     <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C47" s="1">
         <v>179</v>
@@ -1524,10 +1534,10 @@
     </row>
     <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C48" s="1">
         <v>215</v>
@@ -1539,10 +1549,10 @@
     </row>
     <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C49" s="1">
         <v>185</v>
@@ -1554,10 +1564,10 @@
     </row>
     <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C50" s="1">
         <v>190</v>
@@ -1569,10 +1579,10 @@
     </row>
     <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" s="1">
         <v>170</v>
@@ -1584,10 +1594,10 @@
     </row>
     <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C52" s="1">
         <v>145</v>
@@ -1599,10 +1609,10 @@
     </row>
     <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C53" s="1">
         <v>195</v>
@@ -1614,10 +1624,10 @@
     </row>
     <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C54" s="1">
         <v>165</v>
@@ -1629,10 +1639,10 @@
     </row>
     <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C55" s="1">
         <v>159</v>
@@ -1644,10 +1654,10 @@
     </row>
     <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C56" s="1">
         <v>0</v>
@@ -1659,10 +1669,10 @@
     </row>
     <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="C57" s="1">
         <v>169</v>
@@ -1674,10 +1684,10 @@
     </row>
     <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C58" s="1">
         <v>185</v>
@@ -1689,10 +1699,10 @@
     </row>
     <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C59" s="1">
         <v>189</v>
@@ -1704,10 +1714,10 @@
     </row>
     <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C60" s="1">
         <v>0</v>
@@ -1719,10 +1729,10 @@
     </row>
     <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C61" s="1">
         <v>315</v>
@@ -1734,10 +1744,10 @@
     </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C62" s="1">
         <v>0</v>
@@ -1749,10 +1759,10 @@
     </row>
     <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C63" s="1">
         <v>169</v>
@@ -1764,10 +1774,10 @@
     </row>
     <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C64" s="1">
         <v>205</v>
@@ -1779,10 +1789,10 @@
     </row>
     <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C65" s="1">
         <v>189</v>
@@ -1794,10 +1804,10 @@
     </row>
     <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C66" s="1">
         <v>215</v>
@@ -1809,10 +1819,10 @@
     </row>
     <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C67" s="1">
         <v>185</v>
@@ -1824,10 +1834,10 @@
     </row>
     <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C68" s="1">
         <v>190</v>
@@ -1839,10 +1849,10 @@
     </row>
     <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C69" s="1">
         <v>0</v>
@@ -1854,10 +1864,10 @@
     </row>
     <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="C70" s="1">
         <v>0</v>
@@ -1869,10 +1879,10 @@
     </row>
     <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C71" s="1">
         <v>195</v>
@@ -1884,10 +1894,10 @@
     </row>
     <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C72" s="1">
         <v>159</v>
@@ -1899,10 +1909,10 @@
     </row>
     <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C73" s="1">
         <v>169</v>
@@ -1914,10 +1924,10 @@
     </row>
     <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C74" s="1">
         <v>0</v>
@@ -1929,10 +1939,10 @@
     </row>
     <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C75" s="1">
         <v>179</v>
@@ -1944,10 +1954,10 @@
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C76" s="1">
         <v>187</v>
@@ -1959,10 +1969,10 @@
     </row>
     <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C77" s="1">
         <v>155</v>
@@ -1974,10 +1984,10 @@
     </row>
     <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C78" s="1">
         <v>189</v>
@@ -1989,10 +1999,10 @@
     </row>
     <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C79" s="1">
         <v>0</v>
@@ -2004,10 +2014,10 @@
     </row>
     <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C80" s="1">
         <v>295</v>
@@ -2019,10 +2029,10 @@
     </row>
     <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C81" s="1">
         <v>0</v>
@@ -2034,10 +2044,10 @@
     </row>
     <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C82" s="1">
         <v>220</v>
@@ -2049,10 +2059,10 @@
     </row>
     <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C83" s="1">
         <v>190</v>
@@ -2064,10 +2074,10 @@
     </row>
     <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C84" s="1">
         <v>185</v>
@@ -2079,10 +2089,10 @@
     </row>
     <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="C85" s="1">
         <v>0</v>
@@ -2094,10 +2104,10 @@
     </row>
     <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C86" s="1">
         <v>145</v>
@@ -2109,10 +2119,10 @@
     </row>
     <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C87" s="1">
         <v>199</v>
@@ -2124,10 +2134,10 @@
     </row>
     <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C88" s="1">
         <v>169</v>
@@ -2139,10 +2149,10 @@
     </row>
     <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C89" s="1">
         <v>165</v>
@@ -2154,10 +2164,10 @@
     </row>
     <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C90" s="1">
         <v>0</v>
@@ -2169,10 +2179,10 @@
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C91" s="1">
         <v>179</v>
@@ -2184,10 +2194,10 @@
     </row>
     <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C92" s="1">
         <v>195</v>
@@ -2199,10 +2209,10 @@
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C93" s="1">
         <v>155</v>
@@ -2214,10 +2224,10 @@
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C94" s="1">
         <v>189</v>
@@ -2229,10 +2239,10 @@
     </row>
     <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C95" s="1">
         <v>0</v>
@@ -2244,10 +2254,10 @@
     </row>
     <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
@@ -2259,10 +2269,10 @@
     </row>
     <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C97" s="1">
         <v>0</v>
@@ -2274,10 +2284,10 @@
     </row>
     <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C98" s="1">
         <v>220</v>
@@ -2289,10 +2299,10 @@
     </row>
     <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C99" s="1">
         <v>187</v>
@@ -2304,10 +2314,10 @@
     </row>
     <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C100" s="1">
         <v>199</v>
@@ -2319,10 +2329,10 @@
     </row>
     <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C101" s="1">
         <v>185</v>
@@ -2334,10 +2344,10 @@
     </row>
     <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C102" s="1">
         <v>199</v>
@@ -2349,10 +2359,10 @@
     </row>
     <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
@@ -2364,10 +2374,10 @@
     </row>
     <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C104" s="1">
         <v>0</v>
@@ -2379,10 +2389,10 @@
     </row>
     <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C105" s="1">
         <v>0</v>
@@ -2394,10 +2404,10 @@
     </row>
     <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C106" s="1">
         <v>199</v>
@@ -2409,10 +2419,10 @@
     </row>
     <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C107" s="1">
         <v>185</v>
@@ -2424,10 +2434,10 @@
     </row>
     <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C108" s="1">
         <v>175</v>
@@ -2439,10 +2449,10 @@
     </row>
     <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C109" s="1">
         <v>199</v>
@@ -2454,10 +2464,10 @@
     </row>
     <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C110" s="1">
         <v>150</v>
@@ -2469,10 +2479,10 @@
     </row>
     <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C111" s="1">
         <v>139</v>
@@ -2484,10 +2494,10 @@
     </row>
     <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C112" s="1">
         <v>0</v>
@@ -2499,10 +2509,10 @@
     </row>
     <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="C113" s="1">
         <v>220</v>
@@ -2514,10 +2524,10 @@
     </row>
     <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C114" s="1">
         <v>189</v>
@@ -2529,10 +2539,10 @@
     </row>
     <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C115" s="1">
         <v>189</v>
@@ -2544,10 +2554,10 @@
     </row>
     <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C116" s="1">
         <v>185</v>
@@ -2559,10 +2569,10 @@
     </row>
     <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C117" s="1">
         <v>199</v>
@@ -2574,10 +2584,10 @@
     </row>
     <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C118" s="1">
         <v>0</v>
@@ -2589,10 +2599,10 @@
     </row>
     <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C119" s="1">
         <v>0</v>
@@ -2604,10 +2614,10 @@
     </row>
     <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C120" s="1">
         <v>0</v>
@@ -2619,10 +2629,10 @@
     </row>
     <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C121" s="1">
         <v>150</v>
@@ -2634,10 +2644,10 @@
     </row>
     <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C122" s="1">
         <v>199</v>
@@ -2649,10 +2659,10 @@
     </row>
     <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C123" s="1">
         <v>199</v>
@@ -2664,10 +2674,10 @@
     </row>
     <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C124" s="1">
         <v>149</v>
@@ -2679,10 +2689,10 @@
     </row>
     <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C125" s="1">
         <v>179</v>
@@ -2694,10 +2704,10 @@
     </row>
     <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C126" s="1">
         <v>185</v>
@@ -2709,25 +2719,25 @@
     </row>
     <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C127" s="1">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D127" s="1">
         <f>C127-C127*15/100</f>
-        <v>191.25</v>
+        <v>199.75</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C128" s="1">
         <v>0</v>
@@ -2739,10 +2749,10 @@
     </row>
     <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C129" s="1">
         <v>0</v>
@@ -2754,10 +2764,10 @@
     </row>
     <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C130" s="1">
         <v>0</v>
@@ -2769,10 +2779,10 @@
     </row>
     <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C131" s="1">
         <v>199</v>
@@ -2784,10 +2794,10 @@
     </row>
     <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C132" s="1">
         <v>0</v>
@@ -2799,10 +2809,10 @@
     </row>
     <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C133" s="1">
         <v>0</v>
@@ -2814,10 +2824,10 @@
     </row>
     <row r="134" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C134" s="1">
         <v>0</v>
@@ -2829,10 +2839,10 @@
     </row>
     <row r="135" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C135" s="1">
         <v>150</v>
@@ -2844,10 +2854,10 @@
     </row>
     <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="C136" s="1">
         <v>199</v>
@@ -2859,10 +2869,10 @@
     </row>
     <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C137" s="1">
         <v>215</v>
@@ -2874,10 +2884,10 @@
     </row>
     <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="C138" s="1">
         <v>275</v>
@@ -2889,10 +2899,10 @@
     </row>
     <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="C139" s="1">
         <v>239</v>
@@ -2904,10 +2914,10 @@
     </row>
     <row r="140" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C140" s="1">
         <v>174</v>
@@ -2919,10 +2929,10 @@
     </row>
     <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C141" s="1">
         <v>185</v>
@@ -2934,10 +2944,10 @@
     </row>
     <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="C142" s="1">
         <v>249</v>
@@ -2949,10 +2959,10 @@
     </row>
     <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C143" s="1">
         <v>218</v>
@@ -2964,10 +2974,10 @@
     </row>
     <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C144" s="1">
         <v>265</v>
@@ -2979,10 +2989,10 @@
     </row>
     <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C145" s="1">
         <v>285</v>
@@ -2994,10 +3004,10 @@
     </row>
     <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C146" s="1">
         <v>340</v>
@@ -3009,10 +3019,10 @@
     </row>
     <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C147" s="1">
         <v>215</v>
@@ -3024,10 +3034,10 @@
     </row>
     <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C148">
         <v>299</v>
@@ -3039,10 +3049,10 @@
     </row>
     <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C149">
         <v>230</v>
@@ -3054,10 +3064,10 @@
     </row>
     <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C150">
         <v>325</v>
@@ -3069,10 +3079,10 @@
     </row>
     <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C151">
         <v>199</v>
@@ -3084,10 +3094,10 @@
     </row>
     <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C152">
         <v>445</v>
@@ -3099,10 +3109,10 @@
     </row>
     <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C153">
         <v>400</v>
@@ -3114,10 +3124,10 @@
     </row>
     <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C154" s="1">
         <v>278</v>
@@ -3129,10 +3139,10 @@
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C155" s="1">
         <v>405</v>
@@ -3144,7 +3154,7 @@
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>0</v>
@@ -3159,7 +3169,7 @@
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>1</v>
@@ -3174,10 +3184,10 @@
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C158">
         <v>329</v>
@@ -3189,10 +3199,10 @@
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="C159">
         <v>275</v>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A3780E-5040-46F2-8DE0-B0A0F726374F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A25053-5C5E-4D06-980A-794B89768412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="131">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -606,8 +606,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D159" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:D159" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D160" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:D160" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="كتب التأسيس" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="(نحو تأسيس سليم  أجزاء 1و2و3) _x000a_(نحو  سندباد أجزاء 1و2و3) _x000a_( نور البيان انجليزي جزئين - عربي) _x000a_( ذا بيست ستارت بوك 1و2) _x000a_( توب فونكس1و2 - جرامر 1و2و3)  _x000a_( اوكسفورد 5أجزاء)_x000a_(معلم القراءة)_x000a_(نون والقلم)" dataDxfId="1"/>
@@ -821,7 +821,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D159"/>
+  <dimension ref="A1:D160"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -853,7 +853,7 @@
         <v>125</v>
       </c>
       <c r="D2" s="1">
-        <f t="shared" ref="D2:D142" si="0">C2-C2*15/100</f>
+        <f t="shared" ref="D2:D143" si="0">C2-C2*15/100</f>
         <v>106.25</v>
       </c>
     </row>
@@ -1702,14 +1702,14 @@
         <v>79</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C59" s="1">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="D59" s="1">
-        <f t="shared" si="0"/>
-        <v>160.65</v>
+        <f>C59-C59*15/100</f>
+        <v>127.5</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1717,14 +1717,14 @@
         <v>79</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="C60" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D60" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1732,14 +1732,14 @@
         <v>79</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="C61" s="1">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="D61" s="1">
-        <f>C61-C61*15/100</f>
-        <v>267.75</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1747,14 +1747,14 @@
         <v>79</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="C62" s="1">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="D62" s="1">
-        <f t="shared" ref="D62" si="7">C62-C62*15/100</f>
-        <v>0</v>
+        <f>C62-C62*15/100</f>
+        <v>267.75</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1762,14 +1762,14 @@
         <v>79</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="C63" s="1">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="D63" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f t="shared" ref="D63" si="7">C63-C63*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1777,14 +1777,14 @@
         <v>79</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C64" s="1">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D64" s="1">
         <f t="shared" si="0"/>
-        <v>174.25</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1792,29 +1792,29 @@
         <v>79</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C65" s="1">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="D65" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C66" s="1">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="D66" s="1">
-        <f>C66-C66*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="0"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1822,14 +1822,14 @@
         <v>80</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C67" s="1">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="D67" s="1">
         <f>C67-C67*15/100</f>
-        <v>157.25</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1837,29 +1837,29 @@
         <v>80</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C68" s="1">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D68" s="1">
         <f>C68-C68*15/100</f>
-        <v>161.5</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>89</v>
+      <c r="B69" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="C69" s="1">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="D69" s="1">
         <f>C69-C69*15/100</f>
-        <v>0</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1867,13 +1867,13 @@
         <v>80</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C70" s="1">
         <v>0</v>
       </c>
       <c r="D70" s="1">
-        <f t="shared" ref="D70" si="8">C70-C70*15/100</f>
+        <f>C70-C70*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -1881,15 +1881,15 @@
       <c r="A71" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>39</v>
+      <c r="B71" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="C71" s="1">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="D71" s="1">
-        <f t="shared" si="0"/>
-        <v>165.75</v>
+        <f t="shared" ref="D71" si="8">C71-C71*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1897,14 +1897,14 @@
         <v>80</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C72" s="1">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="D72" s="1">
         <f t="shared" si="0"/>
-        <v>135.15</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1912,44 +1912,44 @@
         <v>80</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C73" s="1">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D73" s="1">
         <f t="shared" si="0"/>
-        <v>143.65</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>90</v>
+      <c r="B74" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="C74" s="1">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D74" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>58</v>
+      <c r="B75" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C75" s="1">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D75" s="1">
-        <f>C75-C75*15/100</f>
-        <v>152.15</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1957,14 +1957,14 @@
         <v>80</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C76" s="1">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D76" s="1">
-        <f t="shared" si="0"/>
-        <v>158.94999999999999</v>
+        <f>C76-C76*15/100</f>
+        <v>152.15</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1972,14 +1972,14 @@
         <v>80</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C77" s="1">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="D77" s="1">
         <f t="shared" si="0"/>
-        <v>131.75</v>
+        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1987,14 +1987,14 @@
         <v>80</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C78" s="1">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="D78" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2002,14 +2002,14 @@
         <v>80</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="C79" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D79" s="1">
-        <f t="shared" ref="D79" si="9">C79-C79*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2017,14 +2017,14 @@
         <v>80</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="C80" s="1">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" ref="D80:D86" si="10">C80-C80*15/100</f>
-        <v>250.75</v>
+        <f t="shared" ref="D80" si="9">C80-C80*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2032,29 +2032,29 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="C81" s="1">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="D81" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" ref="D81:D87" si="10">C81-C81*15/100</f>
+        <v>250.75</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="C82" s="1">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D82" s="1">
         <f t="shared" si="10"/>
-        <v>187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2062,14 +2062,14 @@
         <v>81</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C83" s="1">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="D83" s="1">
         <f t="shared" si="10"/>
-        <v>161.5</v>
+        <v>187</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2077,29 +2077,29 @@
         <v>81</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C84" s="1">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D84" s="1">
         <f t="shared" si="10"/>
-        <v>157.25</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>89</v>
+      <c r="B85" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="C85" s="1">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D85" s="1">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2107,29 +2107,29 @@
         <v>81</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="C86" s="1">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="D86" s="1">
         <f t="shared" si="10"/>
-        <v>123.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>56</v>
+      <c r="B87" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="C87" s="1">
-        <v>199</v>
+        <v>145</v>
       </c>
       <c r="D87" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f t="shared" si="10"/>
+        <v>123.25</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2137,14 +2137,14 @@
         <v>81</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C88" s="1">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="D88" s="1">
         <f t="shared" si="0"/>
-        <v>143.65</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2152,44 +2152,44 @@
         <v>81</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C89" s="1">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D89" s="1">
-        <f t="shared" ref="D89:D90" si="11">C89-C89*15/100</f>
-        <v>140.25</v>
+        <f t="shared" si="0"/>
+        <v>143.65</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>90</v>
+      <c r="B90" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="C90" s="1">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="D90" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" ref="D90:D91" si="11">C90-C90*15/100</f>
+        <v>140.25</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>58</v>
+      <c r="B91" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C91" s="1">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D91" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2197,14 +2197,14 @@
         <v>81</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C92" s="1">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D92" s="1">
         <f t="shared" si="0"/>
-        <v>165.75</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2212,14 +2212,14 @@
         <v>81</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C93" s="1">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="D93" s="1">
         <f t="shared" si="0"/>
-        <v>131.75</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2227,14 +2227,14 @@
         <v>81</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C94" s="1">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="D94" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2242,14 +2242,14 @@
         <v>81</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="C95" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D95" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2257,7 +2257,7 @@
         <v>81</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
@@ -2272,29 +2272,29 @@
         <v>81</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C97" s="1">
         <v>0</v>
       </c>
       <c r="D97" s="1">
-        <f t="shared" ref="D97" si="12">C97-C97*15/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C98" s="1">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D98" s="1">
-        <f>C98-C98*15/100</f>
-        <v>187</v>
+        <f t="shared" ref="D98" si="12">C98-C98*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2302,44 +2302,44 @@
         <v>82</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C99" s="1">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="D99" s="1">
         <f>C99-C99*15/100</f>
-        <v>158.94999999999999</v>
+        <v>187</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>121</v>
+      <c r="B100" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="C100" s="1">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D100" s="1">
         <f>C100-C100*15/100</f>
-        <v>169.15</v>
+        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>106</v>
+      <c r="B101" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="C101" s="1">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D101" s="1">
         <f>C101-C101*15/100</f>
-        <v>157.25</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2347,14 +2347,14 @@
         <v>82</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="C102" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D102" s="1">
         <f>C102-C102*15/100</f>
-        <v>169.15</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2362,14 +2362,14 @@
         <v>82</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="C103" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D103" s="1">
-        <f t="shared" ref="D103:D105" si="13">C103-C103*15/100</f>
-        <v>0</v>
+        <f>C103-C103*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2377,13 +2377,13 @@
         <v>82</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C104" s="1">
         <v>0</v>
       </c>
       <c r="D104" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="D104:D106" si="13">C104-C104*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
         <v>82</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C105" s="1">
         <v>0</v>
@@ -2407,14 +2407,14 @@
         <v>82</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C106" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D106" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2422,14 +2422,14 @@
         <v>82</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C107" s="1">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D107" s="1">
-        <f>C107-C107*15/100</f>
-        <v>157.25</v>
+        <f t="shared" si="0"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2437,14 +2437,14 @@
         <v>82</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C108" s="1">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D108" s="1">
         <f>C108-C108*15/100</f>
-        <v>148.75</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2452,74 +2452,74 @@
         <v>82</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C109" s="1">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="D109" s="1">
         <f>C109-C109*15/100</f>
-        <v>169.15</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>101</v>
+      <c r="B110" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="C110" s="1">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="D110" s="1">
         <f>C110-C110*15/100</f>
-        <v>127.5</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B111" s="3" t="s">
-        <v>110</v>
+      <c r="B111" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="C111" s="1">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D111" s="1">
-        <f t="shared" si="0"/>
-        <v>118.15</v>
+        <f>C111-C111*15/100</f>
+        <v>127.5</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>111</v>
+      <c r="B112" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="C112" s="1">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D112" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>118.15</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C113" s="1">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D113" s="1">
-        <f t="shared" ref="D113:D121" si="14">C113-C113*15/100</f>
-        <v>187</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2527,14 +2527,14 @@
         <v>83</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C114" s="1">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="D114" s="1">
-        <f t="shared" si="14"/>
-        <v>160.65</v>
+        <f t="shared" ref="D114:D122" si="14">C114-C114*15/100</f>
+        <v>187</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2542,7 +2542,7 @@
         <v>83</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C115" s="1">
         <v>189</v>
@@ -2557,29 +2557,29 @@
         <v>83</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C116" s="1">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D116" s="1">
         <f t="shared" si="14"/>
-        <v>157.25</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>60</v>
+      <c r="B117" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="C117" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D117" s="1">
         <f t="shared" si="14"/>
-        <v>169.15</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2587,14 +2587,14 @@
         <v>83</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="C118" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D118" s="1">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2602,7 +2602,7 @@
         <v>83</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C119" s="1">
         <v>0</v>
@@ -2617,7 +2617,7 @@
         <v>83</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C120" s="1">
         <v>0</v>
@@ -2631,15 +2631,15 @@
       <c r="A121" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>101</v>
+      <c r="B121" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C121" s="1">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D121" s="1">
         <f t="shared" si="14"/>
-        <v>127.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2647,28 +2647,28 @@
         <v>83</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C122" s="1">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="D122" s="1">
-        <f t="shared" ref="D122" si="15">C122-C122*15/100</f>
-        <v>169.15</v>
+        <f t="shared" si="14"/>
+        <v>127.5</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>61</v>
+      <c r="B123" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="C123" s="1">
         <v>199</v>
       </c>
       <c r="D123" s="1">
-        <f>C123-C123*15/100</f>
+        <f t="shared" ref="D123" si="15">C123-C123*15/100</f>
         <v>169.15</v>
       </c>
     </row>
@@ -2676,15 +2676,15 @@
       <c r="A124" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>98</v>
+      <c r="B124" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C124" s="1">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="D124" s="1">
         <f>C124-C124*15/100</f>
-        <v>126.65</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2692,14 +2692,14 @@
         <v>83</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C125" s="1">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D125" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f>C125-C125*15/100</f>
+        <v>126.65</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2707,29 +2707,29 @@
         <v>83</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C126" s="1">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D126" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C127" s="1">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="D127" s="1">
-        <f>C127-C127*15/100</f>
-        <v>199.75</v>
+        <f t="shared" si="0"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2737,14 +2737,14 @@
         <v>84</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="C128" s="1">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="D128" s="1">
         <f>C128-C128*15/100</f>
-        <v>0</v>
+        <v>199.75</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2752,7 +2752,7 @@
         <v>84</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C129" s="1">
         <v>0</v>
@@ -2767,7 +2767,7 @@
         <v>84</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C130" s="1">
         <v>0</v>
@@ -2782,29 +2782,29 @@
         <v>84</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C131" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D131" s="1">
         <f>C131-C131*15/100</f>
-        <v>169.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>117</v>
+      <c r="B132" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C132" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D132" s="1">
-        <f t="shared" ref="D132:D134" si="16">C132-C132*15/100</f>
-        <v>0</v>
+        <f>C132-C132*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2812,13 +2812,13 @@
         <v>84</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C133" s="1">
         <v>0</v>
       </c>
       <c r="D133" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="D133:D135" si="16">C133-C133*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
         <v>84</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C134" s="1">
         <v>0</v>
@@ -2842,14 +2842,14 @@
         <v>84</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C135" s="1">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D135" s="1">
-        <f t="shared" si="0"/>
-        <v>127.5</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2857,14 +2857,14 @@
         <v>84</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C136" s="1">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="D136" s="1">
         <f t="shared" si="0"/>
-        <v>169.15</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2872,29 +2872,29 @@
         <v>84</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C137" s="1">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="D137" s="1">
-        <f>C137-C137*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="0"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C138" s="1">
-        <v>275</v>
+        <v>215</v>
       </c>
       <c r="D138" s="1">
-        <f t="shared" si="0"/>
-        <v>233.75</v>
+        <f>C138-C138*15/100</f>
+        <v>182.75</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2902,29 +2902,29 @@
         <v>85</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C139" s="1">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="D139" s="1">
         <f t="shared" si="0"/>
-        <v>203.15</v>
+        <v>233.75</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B140" s="4" t="s">
-        <v>114</v>
+      <c r="B140" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C140" s="1">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="D140" s="1">
         <f t="shared" si="0"/>
-        <v>147.9</v>
+        <v>203.15</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2932,44 +2932,44 @@
         <v>85</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C141" s="1">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="D141" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>127</v>
+        <v>85</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="C142" s="1">
-        <v>249</v>
+        <v>185</v>
       </c>
       <c r="D142" s="1">
         <f t="shared" si="0"/>
-        <v>211.65</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="C143" s="1">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="D143" s="1">
-        <f t="shared" ref="D143:D159" si="17">C143-C143*15/100</f>
-        <v>185.3</v>
+        <f t="shared" si="0"/>
+        <v>211.65</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2977,14 +2977,14 @@
         <v>87</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C144" s="1">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="D144" s="1">
-        <f t="shared" si="17"/>
-        <v>225.25</v>
+        <f t="shared" ref="D144:D160" si="17">C144-C144*15/100</f>
+        <v>185.3</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2992,14 +2992,14 @@
         <v>87</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C145" s="1">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="D145" s="1">
         <f t="shared" si="17"/>
-        <v>242.25</v>
+        <v>225.25</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3007,14 +3007,14 @@
         <v>87</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C146" s="1">
-        <v>340</v>
+        <v>285</v>
       </c>
       <c r="D146" s="1">
         <f t="shared" si="17"/>
-        <v>289</v>
+        <v>242.25</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3022,14 +3022,14 @@
         <v>87</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C147" s="1">
-        <v>215</v>
+        <v>340</v>
       </c>
       <c r="D147" s="1">
         <f t="shared" si="17"/>
-        <v>182.75</v>
+        <v>289</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3037,14 +3037,14 @@
         <v>87</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C148">
-        <v>299</v>
+        <v>66</v>
+      </c>
+      <c r="C148" s="1">
+        <v>215</v>
       </c>
       <c r="D148" s="1">
-        <f>C148-C148*15/100</f>
-        <v>254.15</v>
+        <f t="shared" si="17"/>
+        <v>182.75</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3052,14 +3052,14 @@
         <v>87</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C149">
-        <v>230</v>
+        <v>299</v>
       </c>
       <c r="D149" s="1">
-        <f t="shared" si="17"/>
-        <v>195.5</v>
+        <f>C149-C149*15/100</f>
+        <v>254.15</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3067,14 +3067,14 @@
         <v>87</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C150">
-        <v>325</v>
+        <v>230</v>
       </c>
       <c r="D150" s="1">
-        <f>C150-C150*15/100</f>
-        <v>276.25</v>
+        <f t="shared" si="17"/>
+        <v>195.5</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3082,14 +3082,14 @@
         <v>87</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C151">
-        <v>199</v>
+        <v>325</v>
       </c>
       <c r="D151" s="1">
-        <f t="shared" si="17"/>
-        <v>169.15</v>
+        <f>C151-C151*15/100</f>
+        <v>276.25</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3097,14 +3097,14 @@
         <v>87</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C152">
-        <v>445</v>
+        <v>199</v>
       </c>
       <c r="D152" s="1">
         <f t="shared" si="17"/>
-        <v>378.25</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3112,14 +3112,14 @@
         <v>87</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C153">
-        <v>400</v>
+        <v>445</v>
       </c>
       <c r="D153" s="1">
         <f t="shared" si="17"/>
-        <v>340</v>
+        <v>378.25</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3127,29 +3127,29 @@
         <v>87</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C154" s="1">
-        <v>278</v>
+        <v>72</v>
+      </c>
+      <c r="C154">
+        <v>400</v>
       </c>
       <c r="D154" s="1">
         <f t="shared" si="17"/>
-        <v>236.3</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C155" s="1">
-        <v>405</v>
+        <v>278</v>
       </c>
       <c r="D155" s="1">
         <f t="shared" si="17"/>
-        <v>344.25</v>
+        <v>236.3</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3157,14 +3157,14 @@
         <v>87</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C156">
-        <v>360</v>
+        <v>74</v>
+      </c>
+      <c r="C156" s="1">
+        <v>405</v>
       </c>
       <c r="D156" s="1">
         <f t="shared" si="17"/>
-        <v>306</v>
+        <v>344.25</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3172,14 +3172,14 @@
         <v>87</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C157">
-        <v>249</v>
+        <v>360</v>
       </c>
       <c r="D157" s="1">
         <f t="shared" si="17"/>
-        <v>211.65</v>
+        <v>306</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3187,14 +3187,14 @@
         <v>87</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C158">
-        <v>329</v>
+        <v>249</v>
       </c>
       <c r="D158" s="1">
         <f t="shared" si="17"/>
-        <v>279.64999999999998</v>
+        <v>211.65</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3202,12 +3202,27 @@
         <v>87</v>
       </c>
       <c r="B159" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C159">
+        <v>329</v>
+      </c>
+      <c r="D159" s="1">
+        <f t="shared" si="17"/>
+        <v>279.64999999999998</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C159">
+      <c r="C160">
         <v>275</v>
       </c>
-      <c r="D159" s="1">
+      <c r="D160" s="1">
         <f t="shared" si="17"/>
         <v>233.75</v>
       </c>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A25053-5C5E-4D06-980A-794B89768412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2A8704-514F-4308-AF13-28D5DDE391A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="132">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -431,6 +431,9 @@
   </si>
   <si>
     <t xml:space="preserve"> إمتحان عربي  ⬅️ 235</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> بيت باي بيت  ⬅️ 150 </t>
   </si>
 </sst>
 </file>
@@ -1702,7 +1705,7 @@
         <v>79</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="C59" s="1">
         <v>150</v>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2A8704-514F-4308-AF13-28D5DDE391A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAC951C-DFA3-43B8-96D1-4740A49012D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="136">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -256,9 +256,6 @@
   </si>
   <si>
     <t xml:space="preserve"> إمتحان عربي (أسئلة) ⬅️ 405 </t>
-  </si>
-  <si>
-    <t>📚 مرحلة كي جي (KG)</t>
   </si>
   <si>
     <t>🎒 الصف الأول الابتدائي</t>
@@ -434,6 +431,21 @@
   </si>
   <si>
     <t xml:space="preserve"> بيت باي بيت  ⬅️ 150 </t>
+  </si>
+  <si>
+    <t>📚 مرحلة لغات (KG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ عربي ⬅️ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر بلس كي جي 2 ⬅️ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> الأضواء عربي ⬅️ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ستيب اهيد إنجليزي كي جي 2 ⬅️ 145</t>
   </si>
 </sst>
 </file>
@@ -609,8 +621,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D160" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:D160" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D164" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:D164" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="كتب التأسيس" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="(نحو تأسيس سليم  أجزاء 1و2و3) _x000a_(نحو  سندباد أجزاء 1و2و3) _x000a_( نور البيان انجليزي جزئين - عربي) _x000a_( ذا بيست ستارت بوك 1و2) _x000a_( توب فونكس1و2 - جرامر 1و2و3)  _x000a_( اوكسفورد 5أجزاء)_x000a_(معلم القراءة)_x000a_(نون والقلم)" dataDxfId="1"/>
@@ -824,7 +836,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D164"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -833,21 +845,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -856,13 +868,13 @@
         <v>125</v>
       </c>
       <c r="D2" s="1">
-        <f t="shared" ref="D2:D143" si="0">C2-C2*15/100</f>
+        <f t="shared" ref="D2:D147" si="0">C2-C2*15/100</f>
         <v>106.25</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -877,7 +889,7 @@
     </row>
     <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
@@ -892,7 +904,7 @@
     </row>
     <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
@@ -907,2325 +919,2385 @@
     </row>
     <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="C6" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="D6" s="1">
         <f>C6-C6*15/100</f>
-        <v>153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>135</v>
       </c>
       <c r="C7" s="1">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="D7" s="1">
         <f>C7-C7*15/100</f>
-        <v>144.5</v>
+        <v>123.25</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="C8" s="1">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
         <f>C8-C8*15/100</f>
-        <v>110.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>132</v>
       </c>
       <c r="C9" s="1">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1">
-        <f t="shared" si="0"/>
-        <v>126.65</v>
+        <f>C9-C9*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D10" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f>C10-C10*15/100</f>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="D11" s="1">
-        <f t="shared" si="0"/>
-        <v>109.65</v>
+        <f>C11-C11*15/100</f>
+        <v>144.5</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="D12" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
+        <f>C12-C12*15/100</f>
+        <v>110.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>126.65</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>114.75</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>109.65</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="C16" s="1">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1">
-        <v>255</v>
+        <v>165</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" ref="D17:D23" si="1">C17-C17*15/100</f>
-        <v>216.75</v>
+        <f t="shared" si="0"/>
+        <v>140.25</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1">
+        <v>135</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="0"/>
+        <v>114.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="1">
+        <v>175</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="0"/>
+        <v>148.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="1">
+        <v>255</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" ref="D21:D27" si="1">C21-C21*15/100</f>
+        <v>216.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C22" s="1">
         <v>165</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D22" s="1">
         <f t="shared" si="1"/>
         <v>140.25</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="1" t="s">
+    <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C23" s="1">
         <v>175</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D23" s="1">
         <f t="shared" si="1"/>
         <v>148.75</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="1" t="s">
+    <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C24" s="1">
         <v>169</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D24" s="1">
         <f t="shared" si="1"/>
         <v>143.65</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" s="1" t="s">
+    <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C25" s="1">
         <v>180</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D25" s="1">
         <f t="shared" si="1"/>
         <v>153</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="1" t="s">
+    <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C26" s="1">
         <v>170</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D26" s="1">
         <f t="shared" si="1"/>
         <v>144.5</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="1" t="s">
+    <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C27" s="1">
         <v>140</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D27" s="1">
         <f t="shared" si="1"/>
         <v>119</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="1">
-        <v>159</v>
-      </c>
-      <c r="D24" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="1">
-        <v>159</v>
-      </c>
-      <c r="D25" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="1">
-        <v>139</v>
-      </c>
-      <c r="D26" s="1">
-        <f t="shared" si="0"/>
-        <v>118.15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="1">
-        <v>165</v>
-      </c>
-      <c r="D27" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
-      </c>
-    </row>
     <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C28" s="1">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D28" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C29" s="1">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="D29" s="1">
         <f t="shared" si="0"/>
-        <v>114.75</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C30" s="1">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="D30" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>118.15</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="C31" s="1">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" ref="D31" si="2">C31-C31*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>140.25</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="C32" s="1">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="D32" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D33" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>114.75</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="D34" s="1">
-        <f>C34-C34*15/100</f>
-        <v>161.5</v>
+        <f t="shared" si="0"/>
+        <v>148.75</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="C35" s="1">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="D35" s="1">
-        <f>C35-C35*15/100</f>
-        <v>148.75</v>
+        <f t="shared" ref="D35" si="2">C35-C35*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>22</v>
+        <v>114</v>
       </c>
       <c r="C36" s="1">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="D36" s="1">
-        <f>C36-C36*15/100</f>
-        <v>119</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C37" s="1">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D37" s="1">
         <f t="shared" si="0"/>
-        <v>143.65</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C38" s="1">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
+        <f>C38-C38*15/100</f>
+        <v>161.5</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C39" s="1">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" si="0"/>
-        <v>118.15</v>
+        <f>C39-C39*15/100</f>
+        <v>148.75</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="C40" s="1">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="D40" s="1">
         <f>C40-C40*15/100</f>
-        <v>143.65</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C41" s="1">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D41" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C42" s="1">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="D42" s="1">
         <f t="shared" si="0"/>
-        <v>119</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C43" s="1">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="D43" s="1">
-        <f>C43-C43*15/100</f>
-        <v>160.65</v>
+        <f t="shared" si="0"/>
+        <v>118.15</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C44" s="1">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D44" s="1">
-        <f t="shared" ref="D44" si="3">C44-C44*15/100</f>
-        <v>0</v>
+        <f>C44-C44*15/100</f>
+        <v>143.65</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="C45" s="1">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D45" s="1">
-        <f t="shared" ref="D45" si="4">C45-C45*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C46" s="1">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="D46" s="1">
         <f t="shared" si="0"/>
-        <v>152.15</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C47" s="1">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D47" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f>C47-C47*15/100</f>
+        <v>160.65</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="C48" s="1">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="D48" s="1">
-        <f>C48-C48*15/100</f>
-        <v>182.75</v>
+        <f t="shared" ref="D48" si="3">C48-C48*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="C49" s="1">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="D49" s="1">
-        <f>C49-C49*15/100</f>
-        <v>157.25</v>
+        <f t="shared" ref="D49" si="4">C49-C49*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C50" s="1">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D50" s="1">
-        <f>C50-C50*15/100</f>
-        <v>161.5</v>
+        <f t="shared" si="0"/>
+        <v>152.15</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C51" s="1">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D51" s="1">
-        <f>C51-C51*15/100</f>
-        <v>144.5</v>
+        <f t="shared" si="0"/>
+        <v>152.15</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>38</v>
+        <v>78</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="C52" s="1">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="D52" s="1">
-        <f t="shared" ref="D52" si="5">C52-C52*15/100</f>
-        <v>123.25</v>
+        <f>C52-C52*15/100</f>
+        <v>182.75</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C53" s="1">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D53" s="1">
-        <f t="shared" si="0"/>
-        <v>165.75</v>
+        <f>C53-C53*15/100</f>
+        <v>157.25</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C54" s="1">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="D54" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
+        <f>C54-C54*15/100</f>
+        <v>161.5</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C55" s="1">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D55" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f>C55-C55*15/100</f>
+        <v>144.5</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="C56" s="1">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="D56" s="1">
-        <f t="shared" ref="D56" si="6">C56-C56*15/100</f>
-        <v>0</v>
+        <f t="shared" ref="D56" si="5">C56-C56*15/100</f>
+        <v>123.25</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="C57" s="1">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="D57" s="1">
-        <f>C57-C57*15/100</f>
-        <v>143.65</v>
+        <f t="shared" si="0"/>
+        <v>165.75</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C58" s="1">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="D58" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="C59" s="1">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D59" s="1">
-        <f>C59-C59*15/100</f>
-        <v>127.5</v>
+        <f t="shared" si="0"/>
+        <v>135.15</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>42</v>
+        <v>78</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="C60" s="1">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="D60" s="1">
-        <f t="shared" si="0"/>
-        <v>160.65</v>
+        <f t="shared" ref="D60" si="6">C60-C60*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C61" s="1">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D61" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>C61-C61*15/100</f>
+        <v>143.65</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C62" s="1">
-        <v>315</v>
+        <v>185</v>
       </c>
       <c r="D62" s="1">
-        <f>C62-C62*15/100</f>
-        <v>267.75</v>
+        <f t="shared" si="0"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C63" s="1">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D63" s="1">
-        <f t="shared" ref="D63" si="7">C63-C63*15/100</f>
-        <v>0</v>
+        <f>C63-C63*15/100</f>
+        <v>127.5</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C64" s="1">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D64" s="1">
         <f t="shared" si="0"/>
-        <v>143.65</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="C65" s="1">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="D65" s="1">
         <f t="shared" si="0"/>
-        <v>174.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C66" s="1">
-        <v>189</v>
+        <v>315</v>
       </c>
       <c r="D66" s="1">
-        <f t="shared" si="0"/>
-        <v>160.65</v>
+        <f>C66-C66*15/100</f>
+        <v>267.75</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="C67" s="1">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="D67" s="1">
-        <f>C67-C67*15/100</f>
-        <v>182.75</v>
+        <f t="shared" ref="D67" si="7">C67-C67*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C68" s="1">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D68" s="1">
-        <f>C68-C68*15/100</f>
-        <v>157.25</v>
+        <f t="shared" si="0"/>
+        <v>143.65</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C69" s="1">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="D69" s="1">
-        <f>C69-C69*15/100</f>
-        <v>161.5</v>
+        <f t="shared" si="0"/>
+        <v>174.25</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="C70" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D70" s="1">
-        <f>C70-C70*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C71" s="1">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="D71" s="1">
-        <f t="shared" ref="D71" si="8">C71-C71*15/100</f>
-        <v>0</v>
+        <f>C71-C71*15/100</f>
+        <v>182.75</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C72" s="1">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D72" s="1">
-        <f t="shared" si="0"/>
-        <v>165.75</v>
+        <f>C72-C72*15/100</f>
+        <v>157.25</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C73" s="1">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="D73" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f>C73-C73*15/100</f>
+        <v>161.5</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>49</v>
+        <v>79</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="C74" s="1">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="D74" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f>C74-C74*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C75" s="1">
         <v>0</v>
       </c>
       <c r="D75" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D75" si="8">C75-C75*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C76" s="1">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="D76" s="1">
-        <f>C76-C76*15/100</f>
-        <v>152.15</v>
+        <f t="shared" si="0"/>
+        <v>165.75</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C77" s="1">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="D77" s="1">
         <f t="shared" si="0"/>
-        <v>158.94999999999999</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C78" s="1">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="D78" s="1">
         <f t="shared" si="0"/>
-        <v>131.75</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>42</v>
+        <v>79</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="C79" s="1">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="D79" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="C80" s="1">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" ref="D80" si="9">C80-C80*15/100</f>
-        <v>0</v>
+        <f>C80-C80*15/100</f>
+        <v>152.15</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C81" s="1">
-        <v>295</v>
+        <v>187</v>
       </c>
       <c r="D81" s="1">
-        <f t="shared" ref="D81:D87" si="10">C81-C81*15/100</f>
-        <v>250.75</v>
+        <f t="shared" si="0"/>
+        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="C82" s="1">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="D82" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>131.75</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C83" s="1">
+        <v>189</v>
+      </c>
+      <c r="D83" s="1">
+        <f t="shared" si="0"/>
+        <v>160.65</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C84" s="1">
+        <v>0</v>
+      </c>
+      <c r="D84" s="1">
+        <f t="shared" ref="D84" si="9">C84-C84*15/100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C85" s="1">
+        <v>295</v>
+      </c>
+      <c r="D85" s="1">
+        <f t="shared" ref="D85:D91" si="10">C85-C85*15/100</f>
+        <v>250.75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C86" s="1">
+        <v>0</v>
+      </c>
+      <c r="D86" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C83" s="1">
+      <c r="C87" s="1">
         <v>220</v>
       </c>
-      <c r="D83" s="1">
+      <c r="D87" s="1">
         <f t="shared" si="10"/>
         <v>187</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B84" s="1" t="s">
+    <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C84" s="1">
+      <c r="C88" s="1">
         <v>190</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D88" s="1">
         <f t="shared" si="10"/>
         <v>161.5</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B85" s="1" t="s">
+    <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C85" s="1">
+      <c r="C89" s="1">
         <v>185</v>
       </c>
-      <c r="D85" s="1">
+      <c r="D89" s="1">
         <f t="shared" si="10"/>
         <v>157.25</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C86" s="1">
-        <v>0</v>
-      </c>
-      <c r="D86" s="1">
+    <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C90" s="1">
+        <v>0</v>
+      </c>
+      <c r="D90" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B87" s="2" t="s">
+    <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C87" s="1">
+      <c r="C91" s="1">
         <v>145</v>
       </c>
-      <c r="D87" s="1">
+      <c r="D91" s="1">
         <f t="shared" si="10"/>
         <v>123.25</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C88" s="1">
-        <v>199</v>
-      </c>
-      <c r="D88" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A89" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C89" s="1">
-        <v>169</v>
-      </c>
-      <c r="D89" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A90" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C90" s="1">
-        <v>165</v>
-      </c>
-      <c r="D90" s="1">
-        <f t="shared" ref="D90:D91" si="11">C90-C90*15/100</f>
-        <v>140.25</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C91" s="1">
-        <v>0</v>
-      </c>
-      <c r="D91" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
     <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C92" s="1">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="D92" s="1">
         <f t="shared" si="0"/>
-        <v>152.15</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C93" s="1">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="D93" s="1">
         <f t="shared" si="0"/>
-        <v>165.75</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C94" s="1">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D94" s="1">
-        <f t="shared" si="0"/>
-        <v>131.75</v>
+        <f t="shared" ref="D94:D95" si="11">C94-C94*15/100</f>
+        <v>140.25</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>42</v>
+        <v>80</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="C95" s="1">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="D95" s="1">
-        <f t="shared" si="0"/>
-        <v>160.65</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="C96" s="1">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="D96" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="C97" s="1">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="D97" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="C98" s="1">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="D98" s="1">
-        <f t="shared" ref="D98" si="12">C98-C98*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>131.75</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="C99" s="1">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="D99" s="1">
-        <f>C99-C99*15/100</f>
-        <v>187</v>
+        <f t="shared" si="0"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C100" s="1">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="D100" s="1">
-        <f>C100-C100*15/100</f>
-        <v>158.94999999999999</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>121</v>
+        <v>80</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C101" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D101" s="1">
-        <f>C101-C101*15/100</f>
-        <v>169.15</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C102" s="1">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="D102" s="1">
-        <f>C102-C102*15/100</f>
-        <v>157.25</v>
+        <f t="shared" ref="D102" si="12">C102-C102*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="C103" s="1">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="D103" s="1">
         <f>C103-C103*15/100</f>
-        <v>169.15</v>
+        <v>187</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C104" s="1">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="D104" s="1">
-        <f t="shared" ref="D104:D106" si="13">C104-C104*15/100</f>
-        <v>0</v>
+        <f>C104-C104*15/100</f>
+        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>115</v>
+        <v>81</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="C105" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D105" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f>C105-C105*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C106" s="1">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D106" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f>C106-C106*15/100</f>
+        <v>157.25</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="C107" s="1">
         <v>199</v>
       </c>
       <c r="D107" s="1">
-        <f t="shared" si="0"/>
+        <f>C107-C107*15/100</f>
         <v>169.15</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C108" s="1">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="D108" s="1">
-        <f>C108-C108*15/100</f>
-        <v>157.25</v>
+        <f t="shared" ref="D108:D110" si="13">C108-C108*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C109" s="1">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="D109" s="1">
-        <f>C109-C109*15/100</f>
-        <v>148.75</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C110" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D110" s="1">
-        <f>C110-C110*15/100</f>
-        <v>169.15</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>101</v>
+        <v>81</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C111" s="1">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="D111" s="1">
-        <f>C111-C111*15/100</f>
-        <v>127.5</v>
+        <f t="shared" si="0"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>110</v>
+        <v>81</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C112" s="1">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="D112" s="1">
-        <f t="shared" si="0"/>
-        <v>118.15</v>
+        <f>C112-C112*15/100</f>
+        <v>157.25</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>111</v>
+        <v>81</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="C113" s="1">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D113" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>C113-C113*15/100</f>
+        <v>148.75</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="C114" s="1">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="D114" s="1">
-        <f t="shared" ref="D114:D122" si="14">C114-C114*15/100</f>
-        <v>187</v>
+        <f>C114-C114*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C115" s="1">
+        <v>150</v>
+      </c>
+      <c r="D115" s="1">
+        <f>C115-C115*15/100</f>
+        <v>127.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C116" s="1">
+        <v>139</v>
+      </c>
+      <c r="D116" s="1">
+        <f t="shared" si="0"/>
+        <v>118.15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A117" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C117" s="1">
+        <v>0</v>
+      </c>
+      <c r="D117" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C118" s="1">
+        <v>220</v>
+      </c>
+      <c r="D118" s="1">
+        <f t="shared" ref="D118:D126" si="14">C118-C118*15/100</f>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C119" s="1">
         <v>189</v>
       </c>
-      <c r="D115" s="1">
+      <c r="D119" s="1">
         <f t="shared" si="14"/>
         <v>160.65</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A116" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C116" s="1">
+    <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C120" s="1">
         <v>189</v>
       </c>
-      <c r="D116" s="1">
+      <c r="D120" s="1">
         <f t="shared" si="14"/>
         <v>160.65</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A117" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C117" s="1">
+    <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A121" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C121" s="1">
         <v>185</v>
       </c>
-      <c r="D117" s="1">
+      <c r="D121" s="1">
         <f t="shared" si="14"/>
         <v>157.25</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A118" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B118" s="1" t="s">
+    <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A122" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C118" s="1">
+      <c r="C122" s="1">
         <v>199</v>
       </c>
-      <c r="D118" s="1">
+      <c r="D122" s="1">
         <f t="shared" si="14"/>
         <v>169.15</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A119" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C119" s="1">
-        <v>0</v>
-      </c>
-      <c r="D119" s="1">
+    <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A123" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C123" s="1">
+        <v>0</v>
+      </c>
+      <c r="D123" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A120" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B120" s="1" t="s">
+    <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C124" s="1">
+        <v>0</v>
+      </c>
+      <c r="D124" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C120" s="1">
-        <v>0</v>
-      </c>
-      <c r="D120" s="1">
+      <c r="C125" s="1">
+        <v>0</v>
+      </c>
+      <c r="D125" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A121" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C121" s="1">
-        <v>0</v>
-      </c>
-      <c r="D121" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A122" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C122" s="1">
+    <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A126" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C126" s="1">
         <v>150</v>
       </c>
-      <c r="D122" s="1">
+      <c r="D126" s="1">
         <f t="shared" si="14"/>
         <v>127.5</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A123" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C123" s="1">
-        <v>199</v>
-      </c>
-      <c r="D123" s="1">
-        <f t="shared" ref="D123" si="15">C123-C123*15/100</f>
-        <v>169.15</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A124" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C124" s="1">
-        <v>199</v>
-      </c>
-      <c r="D124" s="1">
-        <f>C124-C124*15/100</f>
-        <v>169.15</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A125" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C125" s="1">
-        <v>149</v>
-      </c>
-      <c r="D125" s="1">
-        <f>C125-C125*15/100</f>
-        <v>126.65</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A126" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C126" s="1">
-        <v>179</v>
-      </c>
-      <c r="D126" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
-      </c>
-    </row>
     <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C127" s="1">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D127" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f t="shared" ref="D127" si="15">C127-C127*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>130</v>
+        <v>82</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C128" s="1">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D128" s="1">
         <f>C128-C128*15/100</f>
-        <v>199.75</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C129" s="1">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="D129" s="1">
         <f>C129-C129*15/100</f>
-        <v>0</v>
+        <v>126.65</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C130" s="1">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="D130" s="1">
-        <f>C130-C130*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>152.15</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C131" s="1">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D131" s="1">
-        <f>C131-C131*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="C132" s="1">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="D132" s="1">
         <f>C132-C132*15/100</f>
-        <v>169.15</v>
+        <v>199.75</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>117</v>
+        <v>83</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="C133" s="1">
         <v>0</v>
       </c>
       <c r="D133" s="1">
-        <f t="shared" ref="D133:D135" si="16">C133-C133*15/100</f>
+        <f>C133-C133*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>115</v>
+        <v>83</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="C134" s="1">
         <v>0</v>
       </c>
       <c r="D134" s="1">
-        <f t="shared" si="16"/>
+        <f>C134-C134*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>116</v>
+        <v>83</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="C135" s="1">
         <v>0</v>
       </c>
       <c r="D135" s="1">
-        <f t="shared" si="16"/>
+        <f>C135-C135*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>101</v>
+        <v>83</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C136" s="1">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="D136" s="1">
-        <f t="shared" si="0"/>
-        <v>127.5</v>
+        <f>C136-C136*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C137" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D137" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f t="shared" ref="D137:D139" si="16">C137-C137*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C138" s="1">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="D138" s="1">
-        <f>C138-C138*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C139" s="1">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="D139" s="1">
-        <f t="shared" si="0"/>
-        <v>233.75</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C140" s="1">
-        <v>239</v>
+        <v>150</v>
       </c>
       <c r="D140" s="1">
         <f t="shared" si="0"/>
-        <v>203.15</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>114</v>
+        <v>83</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="C141" s="1">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="D141" s="1">
         <f t="shared" si="0"/>
-        <v>147.9</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>113</v>
+        <v>83</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C142" s="1">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="D142" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f>C142-C142*15/100</f>
+        <v>182.75</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C143" s="1">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="D143" s="1">
         <f t="shared" si="0"/>
-        <v>211.65</v>
+        <v>233.75</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="C144" s="1">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="D144" s="1">
-        <f t="shared" ref="D144:D160" si="17">C144-C144*15/100</f>
-        <v>185.3</v>
+        <f t="shared" si="0"/>
+        <v>203.15</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B145" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C145" s="1">
+        <v>174</v>
+      </c>
+      <c r="D145" s="1">
+        <f t="shared" si="0"/>
+        <v>147.9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C146" s="1">
+        <v>185</v>
+      </c>
+      <c r="D146" s="1">
+        <f t="shared" si="0"/>
+        <v>157.25</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A147" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C147" s="1">
+        <v>249</v>
+      </c>
+      <c r="D147" s="1">
+        <f t="shared" si="0"/>
+        <v>211.65</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A148" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C148" s="1">
+        <v>218</v>
+      </c>
+      <c r="D148" s="1">
+        <f t="shared" ref="D148:D164" si="17">C148-C148*15/100</f>
+        <v>185.3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C145" s="1">
+      <c r="C149" s="1">
         <v>265</v>
       </c>
-      <c r="D145" s="1">
+      <c r="D149" s="1">
         <f t="shared" si="17"/>
         <v>225.25</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A146" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B146" s="1" t="s">
+    <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C146" s="1">
+      <c r="C150" s="1">
         <v>285</v>
       </c>
-      <c r="D146" s="1">
+      <c r="D150" s="1">
         <f t="shared" si="17"/>
         <v>242.25</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A147" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B147" s="1" t="s">
+    <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C147" s="1">
+      <c r="C151" s="1">
         <v>340</v>
       </c>
-      <c r="D147" s="1">
+      <c r="D151" s="1">
         <f t="shared" si="17"/>
         <v>289</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A148" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B148" s="1" t="s">
+    <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A152" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C148" s="1">
+      <c r="C152" s="1">
         <v>215</v>
       </c>
-      <c r="D148" s="1">
+      <c r="D152" s="1">
         <f t="shared" si="17"/>
         <v>182.75</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A149" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B149" s="1" t="s">
+    <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A153" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C149">
+      <c r="C153">
         <v>299</v>
       </c>
-      <c r="D149" s="1">
-        <f>C149-C149*15/100</f>
+      <c r="D153" s="1">
+        <f>C153-C153*15/100</f>
         <v>254.15</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A150" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B150" s="1" t="s">
+    <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A154" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C150">
+      <c r="C154">
         <v>230</v>
       </c>
-      <c r="D150" s="1">
+      <c r="D154" s="1">
         <f t="shared" si="17"/>
         <v>195.5</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A151" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B151" s="1" t="s">
+    <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A155" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C151">
+      <c r="C155">
         <v>325</v>
       </c>
-      <c r="D151" s="1">
-        <f>C151-C151*15/100</f>
+      <c r="D155" s="1">
+        <f>C155-C155*15/100</f>
         <v>276.25</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A152" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B152" s="1" t="s">
+    <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A156" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C152">
+      <c r="C156">
         <v>199</v>
       </c>
-      <c r="D152" s="1">
+      <c r="D156" s="1">
         <f t="shared" si="17"/>
         <v>169.15</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A153" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B153" s="1" t="s">
+    <row r="157" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A157" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C153">
+      <c r="C157">
         <v>445</v>
       </c>
-      <c r="D153" s="1">
+      <c r="D157" s="1">
         <f t="shared" si="17"/>
         <v>378.25</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A154" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B154" s="1" t="s">
+    <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A158" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C154">
+      <c r="C158">
         <v>400</v>
       </c>
-      <c r="D154" s="1">
+      <c r="D158" s="1">
         <f t="shared" si="17"/>
         <v>340</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A155" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B155" s="1" t="s">
+    <row r="159" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A159" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C155" s="1">
+      <c r="C159" s="1">
         <v>278</v>
       </c>
-      <c r="D155" s="1">
+      <c r="D159" s="1">
         <f t="shared" si="17"/>
         <v>236.3</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B156" s="1" t="s">
+    <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C156" s="1">
+      <c r="C160" s="1">
         <v>405</v>
       </c>
-      <c r="D156" s="1">
+      <c r="D160" s="1">
         <f t="shared" si="17"/>
         <v>344.25</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C157">
+    <row r="161" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C161">
         <v>360</v>
       </c>
-      <c r="D157" s="1">
+      <c r="D161" s="1">
         <f t="shared" si="17"/>
         <v>306</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B158" s="1" t="s">
+    <row r="162" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C158">
+      <c r="C162">
         <v>249</v>
       </c>
-      <c r="D158" s="1">
+      <c r="D162" s="1">
         <f t="shared" si="17"/>
         <v>211.65</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B159" s="1" t="s">
+    <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C159">
+      <c r="C163">
         <v>329</v>
       </c>
-      <c r="D159" s="1">
+      <c r="D163" s="1">
         <f t="shared" si="17"/>
         <v>279.64999999999998</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C160">
+    <row r="164" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C164">
         <v>275</v>
       </c>
-      <c r="D160" s="1">
+      <c r="D164" s="1">
         <f t="shared" si="17"/>
         <v>233.75</v>
       </c>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAC951C-DFA3-43B8-96D1-4740A49012D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FBF9E8-5690-4495-97E2-EB676034D5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="135">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -295,9 +295,6 @@
   </si>
   <si>
     <t xml:space="preserve"> سلاح التلميذ دين ⬅️ 0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> سلاح التلميذ علوم ⬅️ 0</t>
   </si>
   <si>
     <t xml:space="preserve"> أضواء علوم ⬅️ </t>
@@ -845,21 +842,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -874,7 +871,7 @@
     </row>
     <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -889,7 +886,7 @@
     </row>
     <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
@@ -904,7 +901,7 @@
     </row>
     <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
@@ -919,61 +916,61 @@
     </row>
     <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
       </c>
       <c r="D6" s="1">
-        <f>C6-C6*15/100</f>
+        <f t="shared" ref="D6:D12" si="1">C6-C6*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C7" s="1">
         <v>145</v>
       </c>
       <c r="D7" s="1">
-        <f>C7-C7*15/100</f>
+        <f t="shared" si="1"/>
         <v>123.25</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>
       </c>
       <c r="D8" s="1">
-        <f>C8-C8*15/100</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="C9" s="1">
         <v>0</v>
       </c>
       <c r="D9" s="1">
-        <f>C9-C9*15/100</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -988,7 +985,7 @@
         <v>180</v>
       </c>
       <c r="D10" s="1">
-        <f>C10-C10*15/100</f>
+        <f t="shared" si="1"/>
         <v>153</v>
       </c>
     </row>
@@ -1003,7 +1000,7 @@
         <v>170</v>
       </c>
       <c r="D11" s="1">
-        <f>C11-C11*15/100</f>
+        <f t="shared" si="1"/>
         <v>144.5</v>
       </c>
     </row>
@@ -1018,7 +1015,7 @@
         <v>130</v>
       </c>
       <c r="D12" s="1">
-        <f>C12-C12*15/100</f>
+        <f t="shared" si="1"/>
         <v>110.5</v>
       </c>
     </row>
@@ -1132,7 +1129,7 @@
         <v>75</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C20" s="1">
         <v>0</v>
@@ -1153,7 +1150,7 @@
         <v>255</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" ref="D21:D27" si="1">C21-C21*15/100</f>
+        <f t="shared" ref="D21:D27" si="2">C21-C21*15/100</f>
         <v>216.75</v>
       </c>
     </row>
@@ -1168,7 +1165,7 @@
         <v>165</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>140.25</v>
       </c>
     </row>
@@ -1183,7 +1180,7 @@
         <v>175</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>148.75</v>
       </c>
     </row>
@@ -1198,7 +1195,7 @@
         <v>169</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>143.65</v>
       </c>
     </row>
@@ -1213,7 +1210,7 @@
         <v>180</v>
       </c>
       <c r="D25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>153</v>
       </c>
     </row>
@@ -1228,7 +1225,7 @@
         <v>170</v>
       </c>
       <c r="D26" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>144.5</v>
       </c>
     </row>
@@ -1243,7 +1240,7 @@
         <v>140</v>
       </c>
       <c r="D27" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>119</v>
       </c>
     </row>
@@ -1357,13 +1354,13 @@
         <v>76</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C35" s="1">
         <v>0</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" ref="D35" si="2">C35-C35*15/100</f>
+        <f t="shared" ref="D35" si="3">C35-C35*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -1372,7 +1369,7 @@
         <v>76</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C36" s="1">
         <v>0</v>
@@ -1492,7 +1489,7 @@
         <v>77</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C44" s="1">
         <v>169</v>
@@ -1552,13 +1549,13 @@
         <v>77</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C48" s="1">
         <v>0</v>
       </c>
       <c r="D48" s="1">
-        <f t="shared" ref="D48" si="3">C48-C48*15/100</f>
+        <f t="shared" ref="D48" si="4">C48-C48*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -1567,13 +1564,13 @@
         <v>77</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C49" s="1">
         <v>0</v>
       </c>
       <c r="D49" s="1">
-        <f t="shared" ref="D49" si="4">C49-C49*15/100</f>
+        <f t="shared" ref="D49" si="5">C49-C49*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -1678,7 +1675,7 @@
         <v>145</v>
       </c>
       <c r="D56" s="1">
-        <f t="shared" ref="D56" si="5">C56-C56*15/100</f>
+        <f t="shared" ref="D56" si="6">C56-C56*15/100</f>
         <v>123.25</v>
       </c>
     </row>
@@ -1732,13 +1729,13 @@
         <v>78</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C60" s="1">
         <v>0</v>
       </c>
       <c r="D60" s="1">
-        <f t="shared" ref="D60" si="6">C60-C60*15/100</f>
+        <f t="shared" ref="D60" si="7">C60-C60*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -1747,7 +1744,7 @@
         <v>78</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C61" s="1">
         <v>169</v>
@@ -1777,7 +1774,7 @@
         <v>78</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C63" s="1">
         <v>150</v>
@@ -1807,7 +1804,7 @@
         <v>78</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C65" s="1">
         <v>0</v>
@@ -1837,13 +1834,13 @@
         <v>78</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C67" s="1">
         <v>0</v>
       </c>
       <c r="D67" s="1">
-        <f t="shared" ref="D67" si="7">C67-C67*15/100</f>
+        <f t="shared" ref="D67" si="8">C67-C67*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -1942,14 +1939,14 @@
         <v>79</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="C74" s="1">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="D74" s="1">
         <f>C74-C74*15/100</f>
-        <v>0</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1963,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="1">
-        <f t="shared" ref="D75" si="8">C75-C75*15/100</f>
+        <f t="shared" ref="D75" si="9">C75-C75*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -2017,7 +2014,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C79" s="1">
         <v>0</v>
@@ -2092,13 +2089,13 @@
         <v>79</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C84" s="1">
         <v>0</v>
       </c>
       <c r="D84" s="1">
-        <f t="shared" ref="D84" si="9">C84-C84*15/100</f>
+        <f t="shared" ref="D84" si="10">C84-C84*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -2113,7 +2110,7 @@
         <v>295</v>
       </c>
       <c r="D85" s="1">
-        <f t="shared" ref="D85:D91" si="10">C85-C85*15/100</f>
+        <f t="shared" ref="D85:D91" si="11">C85-C85*15/100</f>
         <v>250.75</v>
       </c>
     </row>
@@ -2122,13 +2119,13 @@
         <v>79</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C86" s="1">
         <v>0</v>
       </c>
       <c r="D86" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -2143,7 +2140,7 @@
         <v>220</v>
       </c>
       <c r="D87" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>187</v>
       </c>
     </row>
@@ -2158,7 +2155,7 @@
         <v>190</v>
       </c>
       <c r="D88" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>161.5</v>
       </c>
     </row>
@@ -2173,7 +2170,7 @@
         <v>185</v>
       </c>
       <c r="D89" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>157.25</v>
       </c>
     </row>
@@ -2182,14 +2179,14 @@
         <v>80</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="C90" s="1">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="D90" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>144.5</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2203,7 +2200,7 @@
         <v>145</v>
       </c>
       <c r="D91" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>123.25</v>
       </c>
     </row>
@@ -2248,7 +2245,7 @@
         <v>165</v>
       </c>
       <c r="D94" s="1">
-        <f t="shared" ref="D94:D95" si="11">C94-C94*15/100</f>
+        <f t="shared" ref="D94:D95" si="12">C94-C94*15/100</f>
         <v>140.25</v>
       </c>
     </row>
@@ -2257,13 +2254,13 @@
         <v>80</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C95" s="1">
         <v>0</v>
       </c>
       <c r="D95" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -2332,7 +2329,7 @@
         <v>80</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C100" s="1">
         <v>0</v>
@@ -2347,7 +2344,7 @@
         <v>80</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C101" s="1">
         <v>0</v>
@@ -2362,13 +2359,13 @@
         <v>80</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C102" s="1">
         <v>0</v>
       </c>
       <c r="D102" s="1">
-        <f t="shared" ref="D102" si="12">C102-C102*15/100</f>
+        <f t="shared" ref="D102" si="13">C102-C102*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -2377,7 +2374,7 @@
         <v>81</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C103" s="1">
         <v>220</v>
@@ -2392,7 +2389,7 @@
         <v>81</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C104" s="1">
         <v>187</v>
@@ -2407,7 +2404,7 @@
         <v>81</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C105" s="1">
         <v>199</v>
@@ -2422,7 +2419,7 @@
         <v>81</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C106" s="1">
         <v>185</v>
@@ -2452,13 +2449,13 @@
         <v>81</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C108" s="1">
         <v>0</v>
       </c>
       <c r="D108" s="1">
-        <f t="shared" ref="D108:D110" si="13">C108-C108*15/100</f>
+        <f t="shared" ref="D108:D110" si="14">C108-C108*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -2467,13 +2464,13 @@
         <v>81</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C109" s="1">
         <v>0</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -2482,13 +2479,13 @@
         <v>81</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
       </c>
       <c r="D110" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -2497,7 +2494,7 @@
         <v>81</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C111" s="1">
         <v>199</v>
@@ -2512,7 +2509,7 @@
         <v>81</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C112" s="1">
         <v>185</v>
@@ -2527,7 +2524,7 @@
         <v>81</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C113" s="1">
         <v>175</v>
@@ -2542,7 +2539,7 @@
         <v>81</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C114" s="1">
         <v>199</v>
@@ -2557,7 +2554,7 @@
         <v>81</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C115" s="1">
         <v>150</v>
@@ -2572,7 +2569,7 @@
         <v>81</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C116" s="1">
         <v>139</v>
@@ -2587,7 +2584,7 @@
         <v>81</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C117" s="1">
         <v>0</v>
@@ -2602,13 +2599,13 @@
         <v>82</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C118" s="1">
         <v>220</v>
       </c>
       <c r="D118" s="1">
-        <f t="shared" ref="D118:D126" si="14">C118-C118*15/100</f>
+        <f t="shared" ref="D118:D126" si="15">C118-C118*15/100</f>
         <v>187</v>
       </c>
     </row>
@@ -2617,13 +2614,13 @@
         <v>82</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C119" s="1">
         <v>189</v>
       </c>
       <c r="D119" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>160.65</v>
       </c>
     </row>
@@ -2632,13 +2629,13 @@
         <v>82</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C120" s="1">
         <v>189</v>
       </c>
       <c r="D120" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>160.65</v>
       </c>
     </row>
@@ -2647,13 +2644,13 @@
         <v>82</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C121" s="1">
         <v>185</v>
       </c>
       <c r="D121" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>157.25</v>
       </c>
     </row>
@@ -2668,7 +2665,7 @@
         <v>199</v>
       </c>
       <c r="D122" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>169.15</v>
       </c>
     </row>
@@ -2677,13 +2674,13 @@
         <v>82</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C123" s="1">
         <v>0</v>
       </c>
       <c r="D123" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -2692,13 +2689,13 @@
         <v>82</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C124" s="1">
         <v>0</v>
       </c>
       <c r="D124" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -2707,13 +2704,13 @@
         <v>82</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C125" s="1">
         <v>0</v>
       </c>
       <c r="D125" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -2722,13 +2719,13 @@
         <v>82</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C126" s="1">
         <v>150</v>
       </c>
       <c r="D126" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>127.5</v>
       </c>
     </row>
@@ -2737,13 +2734,13 @@
         <v>82</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C127" s="1">
         <v>199</v>
       </c>
       <c r="D127" s="1">
-        <f t="shared" ref="D127" si="15">C127-C127*15/100</f>
+        <f t="shared" ref="D127" si="16">C127-C127*15/100</f>
         <v>169.15</v>
       </c>
     </row>
@@ -2767,7 +2764,7 @@
         <v>82</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C129" s="1">
         <v>149</v>
@@ -2782,7 +2779,7 @@
         <v>82</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C130" s="1">
         <v>179</v>
@@ -2797,7 +2794,7 @@
         <v>82</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C131" s="1">
         <v>185</v>
@@ -2812,7 +2809,7 @@
         <v>83</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C132" s="1">
         <v>235</v>
@@ -2827,7 +2824,7 @@
         <v>83</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C133" s="1">
         <v>0</v>
@@ -2842,7 +2839,7 @@
         <v>83</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C134" s="1">
         <v>0</v>
@@ -2857,7 +2854,7 @@
         <v>83</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C135" s="1">
         <v>0</v>
@@ -2872,7 +2869,7 @@
         <v>83</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C136" s="1">
         <v>199</v>
@@ -2887,13 +2884,13 @@
         <v>83</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C137" s="1">
         <v>0</v>
       </c>
       <c r="D137" s="1">
-        <f t="shared" ref="D137:D139" si="16">C137-C137*15/100</f>
+        <f t="shared" ref="D137:D139" si="17">C137-C137*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -2902,13 +2899,13 @@
         <v>83</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C138" s="1">
         <v>0</v>
       </c>
       <c r="D138" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -2917,13 +2914,13 @@
         <v>83</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C139" s="1">
         <v>0</v>
       </c>
       <c r="D139" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -2932,7 +2929,7 @@
         <v>83</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C140" s="1">
         <v>150</v>
@@ -2947,7 +2944,7 @@
         <v>83</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C141" s="1">
         <v>199</v>
@@ -2962,7 +2959,7 @@
         <v>83</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C142" s="1">
         <v>215</v>
@@ -2977,7 +2974,7 @@
         <v>84</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C143" s="1">
         <v>275</v>
@@ -2992,7 +2989,7 @@
         <v>84</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C144" s="1">
         <v>239</v>
@@ -3007,7 +3004,7 @@
         <v>84</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C145" s="1">
         <v>174</v>
@@ -3022,7 +3019,7 @@
         <v>84</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C146" s="1">
         <v>185</v>
@@ -3037,7 +3034,7 @@
         <v>85</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C147" s="1">
         <v>249</v>
@@ -3058,7 +3055,7 @@
         <v>218</v>
       </c>
       <c r="D148" s="1">
-        <f t="shared" ref="D148:D164" si="17">C148-C148*15/100</f>
+        <f t="shared" ref="D148:D164" si="18">C148-C148*15/100</f>
         <v>185.3</v>
       </c>
     </row>
@@ -3073,7 +3070,7 @@
         <v>265</v>
       </c>
       <c r="D149" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>225.25</v>
       </c>
     </row>
@@ -3088,7 +3085,7 @@
         <v>285</v>
       </c>
       <c r="D150" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>242.25</v>
       </c>
     </row>
@@ -3103,7 +3100,7 @@
         <v>340</v>
       </c>
       <c r="D151" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>289</v>
       </c>
     </row>
@@ -3118,7 +3115,7 @@
         <v>215</v>
       </c>
       <c r="D152" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>182.75</v>
       </c>
     </row>
@@ -3148,7 +3145,7 @@
         <v>230</v>
       </c>
       <c r="D154" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>195.5</v>
       </c>
     </row>
@@ -3178,7 +3175,7 @@
         <v>199</v>
       </c>
       <c r="D156" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>169.15</v>
       </c>
     </row>
@@ -3193,7 +3190,7 @@
         <v>445</v>
       </c>
       <c r="D157" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>378.25</v>
       </c>
     </row>
@@ -3208,7 +3205,7 @@
         <v>400</v>
       </c>
       <c r="D158" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>340</v>
       </c>
     </row>
@@ -3223,7 +3220,7 @@
         <v>278</v>
       </c>
       <c r="D159" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>236.3</v>
       </c>
     </row>
@@ -3238,7 +3235,7 @@
         <v>405</v>
       </c>
       <c r="D160" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>344.25</v>
       </c>
     </row>
@@ -3253,7 +3250,7 @@
         <v>360</v>
       </c>
       <c r="D161" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>306</v>
       </c>
     </row>
@@ -3268,7 +3265,7 @@
         <v>249</v>
       </c>
       <c r="D162" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>211.65</v>
       </c>
     </row>
@@ -3283,7 +3280,7 @@
         <v>329</v>
       </c>
       <c r="D163" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>279.64999999999998</v>
       </c>
     </row>
@@ -3292,13 +3289,13 @@
         <v>86</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C164">
         <v>275</v>
       </c>
       <c r="D164" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>233.75</v>
       </c>
     </row>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FBF9E8-5690-4495-97E2-EB676034D5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1230BC72-B085-4D1A-9D60-946BE2C570EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الورقة1" sheetId="1" r:id="rId1"/>
@@ -294,9 +294,6 @@
     <t>🎓 الثانوية العامة (تالتة ثانوي)</t>
   </si>
   <si>
-    <t xml:space="preserve"> سلاح التلميذ دين ⬅️ 0 </t>
-  </si>
-  <si>
     <t xml:space="preserve"> أضواء علوم ⬅️ </t>
   </si>
   <si>
@@ -443,6 +440,9 @@
   </si>
   <si>
     <t xml:space="preserve"> ستيب اهيد إنجليزي كي جي 2 ⬅️ 145</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ دين ⬅️145</t>
   </si>
 </sst>
 </file>
@@ -512,7 +512,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="عادي" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -611,10 +611,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -842,21 +838,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -871,7 +867,7 @@
     </row>
     <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -886,7 +882,7 @@
     </row>
     <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
@@ -901,7 +897,7 @@
     </row>
     <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
@@ -916,10 +912,10 @@
     </row>
     <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -931,10 +927,10 @@
     </row>
     <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C7" s="1">
         <v>145</v>
@@ -946,10 +942,10 @@
     </row>
     <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>
@@ -961,10 +957,10 @@
     </row>
     <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="C9" s="1">
         <v>0</v>
@@ -1129,7 +1125,7 @@
         <v>75</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C20" s="1">
         <v>0</v>
@@ -1354,7 +1350,7 @@
         <v>76</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C35" s="1">
         <v>0</v>
@@ -1369,7 +1365,7 @@
         <v>76</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C36" s="1">
         <v>0</v>
@@ -1489,7 +1485,7 @@
         <v>77</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C44" s="1">
         <v>169</v>
@@ -1549,7 +1545,7 @@
         <v>77</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" s="1">
         <v>0</v>
@@ -1564,7 +1560,7 @@
         <v>77</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C49" s="1">
         <v>0</v>
@@ -1729,7 +1725,7 @@
         <v>78</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C60" s="1">
         <v>0</v>
@@ -1744,7 +1740,7 @@
         <v>78</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C61" s="1">
         <v>169</v>
@@ -1774,7 +1770,7 @@
         <v>78</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C63" s="1">
         <v>150</v>
@@ -1804,7 +1800,7 @@
         <v>78</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C65" s="1">
         <v>0</v>
@@ -1834,7 +1830,7 @@
         <v>78</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C67" s="1">
         <v>0</v>
@@ -1954,14 +1950,14 @@
         <v>79</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="C75" s="1">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="D75" s="1">
         <f t="shared" ref="D75" si="9">C75-C75*15/100</f>
-        <v>0</v>
+        <v>123.25</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2014,7 +2010,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C79" s="1">
         <v>0</v>
@@ -2089,7 +2085,7 @@
         <v>79</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C84" s="1">
         <v>0</v>
@@ -2119,7 +2115,7 @@
         <v>79</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C86" s="1">
         <v>0</v>
@@ -2254,7 +2250,7 @@
         <v>80</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C95" s="1">
         <v>0</v>
@@ -2329,7 +2325,7 @@
         <v>80</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C100" s="1">
         <v>0</v>
@@ -2344,7 +2340,7 @@
         <v>80</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C101" s="1">
         <v>0</v>
@@ -2359,7 +2355,7 @@
         <v>80</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C102" s="1">
         <v>0</v>
@@ -2374,7 +2370,7 @@
         <v>81</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C103" s="1">
         <v>220</v>
@@ -2389,7 +2385,7 @@
         <v>81</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C104" s="1">
         <v>187</v>
@@ -2404,7 +2400,7 @@
         <v>81</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C105" s="1">
         <v>199</v>
@@ -2419,7 +2415,7 @@
         <v>81</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C106" s="1">
         <v>185</v>
@@ -2449,7 +2445,7 @@
         <v>81</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C108" s="1">
         <v>0</v>
@@ -2464,7 +2460,7 @@
         <v>81</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C109" s="1">
         <v>0</v>
@@ -2479,7 +2475,7 @@
         <v>81</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
@@ -2494,7 +2490,7 @@
         <v>81</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C111" s="1">
         <v>199</v>
@@ -2509,7 +2505,7 @@
         <v>81</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C112" s="1">
         <v>185</v>
@@ -2524,7 +2520,7 @@
         <v>81</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C113" s="1">
         <v>175</v>
@@ -2539,7 +2535,7 @@
         <v>81</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C114" s="1">
         <v>199</v>
@@ -2554,7 +2550,7 @@
         <v>81</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C115" s="1">
         <v>150</v>
@@ -2569,7 +2565,7 @@
         <v>81</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C116" s="1">
         <v>139</v>
@@ -2584,7 +2580,7 @@
         <v>81</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C117" s="1">
         <v>0</v>
@@ -2599,7 +2595,7 @@
         <v>82</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C118" s="1">
         <v>220</v>
@@ -2614,7 +2610,7 @@
         <v>82</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C119" s="1">
         <v>189</v>
@@ -2629,7 +2625,7 @@
         <v>82</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C120" s="1">
         <v>189</v>
@@ -2644,7 +2640,7 @@
         <v>82</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C121" s="1">
         <v>185</v>
@@ -2674,7 +2670,7 @@
         <v>82</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C123" s="1">
         <v>0</v>
@@ -2689,7 +2685,7 @@
         <v>82</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C124" s="1">
         <v>0</v>
@@ -2704,7 +2700,7 @@
         <v>82</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C125" s="1">
         <v>0</v>
@@ -2719,7 +2715,7 @@
         <v>82</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C126" s="1">
         <v>150</v>
@@ -2734,7 +2730,7 @@
         <v>82</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C127" s="1">
         <v>199</v>
@@ -2764,7 +2760,7 @@
         <v>82</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C129" s="1">
         <v>149</v>
@@ -2779,7 +2775,7 @@
         <v>82</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C130" s="1">
         <v>179</v>
@@ -2794,7 +2790,7 @@
         <v>82</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C131" s="1">
         <v>185</v>
@@ -2809,7 +2805,7 @@
         <v>83</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C132" s="1">
         <v>235</v>
@@ -2824,7 +2820,7 @@
         <v>83</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C133" s="1">
         <v>0</v>
@@ -2839,7 +2835,7 @@
         <v>83</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C134" s="1">
         <v>0</v>
@@ -2854,7 +2850,7 @@
         <v>83</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C135" s="1">
         <v>0</v>
@@ -2869,7 +2865,7 @@
         <v>83</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C136" s="1">
         <v>199</v>
@@ -2884,7 +2880,7 @@
         <v>83</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C137" s="1">
         <v>0</v>
@@ -2899,7 +2895,7 @@
         <v>83</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C138" s="1">
         <v>0</v>
@@ -2914,7 +2910,7 @@
         <v>83</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C139" s="1">
         <v>0</v>
@@ -2929,7 +2925,7 @@
         <v>83</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C140" s="1">
         <v>150</v>
@@ -2944,7 +2940,7 @@
         <v>83</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C141" s="1">
         <v>199</v>
@@ -2959,7 +2955,7 @@
         <v>83</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C142" s="1">
         <v>215</v>
@@ -2974,7 +2970,7 @@
         <v>84</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C143" s="1">
         <v>275</v>
@@ -2989,7 +2985,7 @@
         <v>84</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C144" s="1">
         <v>239</v>
@@ -3004,7 +3000,7 @@
         <v>84</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C145" s="1">
         <v>174</v>
@@ -3019,7 +3015,7 @@
         <v>84</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C146" s="1">
         <v>185</v>
@@ -3034,7 +3030,7 @@
         <v>85</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C147" s="1">
         <v>249</v>
@@ -3289,7 +3285,7 @@
         <v>86</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C164">
         <v>275</v>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1230BC72-B085-4D1A-9D60-946BE2C570EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5952F4C3-DDCF-41ED-80EE-48189ECEC2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الورقة1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="138">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -430,9 +430,6 @@
     <t>📚 مرحلة لغات (KG)</t>
   </si>
   <si>
-    <t xml:space="preserve"> سلاح التلميذ عربي ⬅️ </t>
-  </si>
-  <si>
     <t xml:space="preserve"> المعاصر بلس كي جي 2 ⬅️ </t>
   </si>
   <si>
@@ -443,6 +440,18 @@
   </si>
   <si>
     <t xml:space="preserve"> سلاح التلميذ دين ⬅️145</t>
+  </si>
+  <si>
+    <t>المعاصر انجليزي (جزء اول)  ⬅️ 285</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ عربي كي جي 2 ⬅️ 120</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ عربي كي جي 1 ⬅️ 120</t>
+  </si>
+  <si>
+    <t>المعاصر انجليزي   ⬅️ 285</t>
   </si>
 </sst>
 </file>
@@ -512,7 +521,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -614,8 +623,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D164" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:D164" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D167" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:D167" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="كتب التأسيس" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="(نحو تأسيس سليم  أجزاء 1و2و3) _x000a_(نحو  سندباد أجزاء 1و2و3) _x000a_( نور البيان انجليزي جزئين - عربي) _x000a_( ذا بيست ستارت بوك 1و2) _x000a_( توب فونكس1و2 - جرامر 1و2و3)  _x000a_( اوكسفورد 5أجزاء)_x000a_(معلم القراءة)_x000a_(نون والقلم)" dataDxfId="1"/>
@@ -829,7 +838,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D164"/>
+  <dimension ref="A1:D167"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -861,7 +870,7 @@
         <v>125</v>
       </c>
       <c r="D2" s="1">
-        <f t="shared" ref="D2:D147" si="0">C2-C2*15/100</f>
+        <f t="shared" ref="D2:D149" si="0">C2-C2*15/100</f>
         <v>106.25</v>
       </c>
     </row>
@@ -885,14 +894,14 @@
         <v>129</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C4" s="1">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D4" s="1">
-        <f t="shared" si="0"/>
-        <v>106.25</v>
+        <f>C4-C4*15/100</f>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -900,14 +909,14 @@
         <v>129</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>178.5</v>
+        <v>106.25</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -915,14 +924,14 @@
         <v>129</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>131</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="D6" s="1">
-        <f t="shared" ref="D6:D12" si="1">C6-C6*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>178.5</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -930,14 +939,14 @@
         <v>129</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C7" s="1">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" si="1"/>
-        <v>123.25</v>
+        <f t="shared" ref="D7:D13" si="1">C7-C7*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -948,11 +957,11 @@
         <v>132</v>
       </c>
       <c r="C8" s="1">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>123.25</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -960,7 +969,7 @@
         <v>129</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C9" s="1">
         <v>0</v>
@@ -972,17 +981,17 @@
     </row>
     <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>135</v>
       </c>
       <c r="C10" s="1">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="1"/>
-        <v>153</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -990,14 +999,14 @@
         <v>75</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="1">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="1"/>
-        <v>144.5</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1005,14 +1014,14 @@
         <v>75</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="1"/>
-        <v>110.5</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1020,14 +1029,14 @@
         <v>75</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="D13" s="1">
-        <f t="shared" si="0"/>
-        <v>126.65</v>
+        <f t="shared" si="1"/>
+        <v>110.5</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1035,14 +1044,14 @@
         <v>75</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>135.15</v>
+        <v>126.65</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1050,14 +1059,14 @@
         <v>75</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>109.65</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1065,14 +1074,14 @@
         <v>75</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>109.65</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1080,7 +1089,7 @@
         <v>75</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" s="1">
         <v>165</v>
@@ -1095,14 +1104,14 @@
         <v>75</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" s="1">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="D18" s="1">
         <f t="shared" si="0"/>
-        <v>114.75</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1110,14 +1119,14 @@
         <v>75</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" s="1">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D19" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>114.75</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1125,14 +1134,14 @@
         <v>75</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="C20" s="1">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1140,14 +1149,14 @@
         <v>75</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="C21" s="1">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" ref="D21:D27" si="2">C21-C21*15/100</f>
-        <v>216.75</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1155,14 +1164,14 @@
         <v>75</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C22" s="1">
-        <v>165</v>
+        <v>255</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" si="2"/>
-        <v>140.25</v>
+        <f t="shared" ref="D22:D28" si="2">C22-C22*15/100</f>
+        <v>216.75</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1170,14 +1179,14 @@
         <v>75</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23" s="1">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D23" s="1">
         <f t="shared" si="2"/>
-        <v>148.75</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1185,29 +1194,29 @@
         <v>75</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" s="1">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D24" s="1">
         <f t="shared" si="2"/>
-        <v>143.65</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C25" s="1">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="D25" s="1">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1215,14 +1224,14 @@
         <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="1">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D26" s="1">
         <f t="shared" si="2"/>
-        <v>144.5</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1230,14 +1239,14 @@
         <v>76</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C27" s="1">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="D27" s="1">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1245,14 +1254,14 @@
         <v>76</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28" s="1">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D28" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f t="shared" si="2"/>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1260,7 +1269,7 @@
         <v>76</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C29" s="1">
         <v>159</v>
@@ -1275,14 +1284,14 @@
         <v>76</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C30" s="1">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D30" s="1">
         <f t="shared" si="0"/>
-        <v>118.15</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1290,14 +1299,14 @@
         <v>76</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C31" s="1">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="D31" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>118.15</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1305,7 +1314,7 @@
         <v>76</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C32" s="1">
         <v>165</v>
@@ -1320,14 +1329,14 @@
         <v>76</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C33" s="1">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="D33" s="1">
         <f t="shared" si="0"/>
-        <v>114.75</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1335,14 +1344,14 @@
         <v>76</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C34" s="1">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D34" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>114.75</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1350,14 +1359,14 @@
         <v>76</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="C35" s="1">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" ref="D35" si="3">C35-C35*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>148.75</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1365,13 +1374,13 @@
         <v>76</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C36" s="1">
         <v>0</v>
       </c>
       <c r="D36" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D36" si="3">C36-C36*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -1380,29 +1389,29 @@
         <v>76</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="C37" s="1">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="D37" s="1">
         <f t="shared" si="0"/>
-        <v>148.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C38" s="1">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="D38" s="1">
-        <f>C38-C38*15/100</f>
-        <v>161.5</v>
+        <f t="shared" si="0"/>
+        <v>148.75</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1410,14 +1419,14 @@
         <v>77</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C39" s="1">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="D39" s="1">
         <f>C39-C39*15/100</f>
-        <v>148.75</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1425,14 +1434,14 @@
         <v>77</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C40" s="1">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="D40" s="1">
         <f>C40-C40*15/100</f>
-        <v>119</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1440,14 +1449,14 @@
         <v>77</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C41" s="1">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="D41" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f>C41-C41*15/100</f>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1455,14 +1464,14 @@
         <v>77</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C42" s="1">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D42" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1470,14 +1479,14 @@
         <v>77</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C43" s="1">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="D43" s="1">
         <f t="shared" si="0"/>
-        <v>118.15</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1485,14 +1494,14 @@
         <v>77</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="C44" s="1">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="D44" s="1">
-        <f>C44-C44*15/100</f>
-        <v>143.65</v>
+        <f t="shared" si="0"/>
+        <v>118.15</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1500,14 +1509,14 @@
         <v>77</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="C45" s="1">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D45" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f>C45-C45*15/100</f>
+        <v>143.65</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1515,14 +1524,14 @@
         <v>77</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C46" s="1">
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="D46" s="1">
         <f t="shared" si="0"/>
-        <v>119</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1530,14 +1539,14 @@
         <v>77</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C47" s="1">
-        <v>189</v>
+        <v>140</v>
       </c>
       <c r="D47" s="1">
-        <f>C47-C47*15/100</f>
-        <v>160.65</v>
+        <f t="shared" si="0"/>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1545,14 +1554,14 @@
         <v>77</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="C48" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D48" s="1">
-        <f t="shared" ref="D48" si="4">C48-C48*15/100</f>
-        <v>0</v>
+        <f>C48-C48*15/100</f>
+        <v>160.65</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1560,13 +1569,13 @@
         <v>77</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C49" s="1">
         <v>0</v>
       </c>
       <c r="D49" s="1">
-        <f t="shared" ref="D49" si="5">C49-C49*15/100</f>
+        <f t="shared" ref="D49" si="4">C49-C49*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -1575,14 +1584,14 @@
         <v>77</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C50" s="1">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D50" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f t="shared" ref="D50" si="5">C50-C50*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1590,7 +1599,7 @@
         <v>77</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C51" s="1">
         <v>179</v>
@@ -1602,17 +1611,17 @@
     </row>
     <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C52" s="1">
-        <v>215</v>
+        <v>179</v>
       </c>
       <c r="D52" s="1">
-        <f>C52-C52*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="0"/>
+        <v>152.15</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1620,14 +1629,14 @@
         <v>78</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C53" s="1">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="D53" s="1">
         <f>C53-C53*15/100</f>
-        <v>157.25</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1635,14 +1644,14 @@
         <v>78</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C54" s="1">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D54" s="1">
         <f>C54-C54*15/100</f>
-        <v>161.5</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1650,44 +1659,44 @@
         <v>78</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C55" s="1">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D55" s="1">
         <f>C55-C55*15/100</f>
-        <v>144.5</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>38</v>
+      <c r="B56" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="C56" s="1">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="D56" s="1">
-        <f t="shared" ref="D56" si="6">C56-C56*15/100</f>
-        <v>123.25</v>
+        <f>C56-C56*15/100</f>
+        <v>144.5</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>39</v>
+      <c r="B57" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C57" s="1">
-        <v>195</v>
+        <v>145</v>
       </c>
       <c r="D57" s="1">
-        <f t="shared" si="0"/>
-        <v>165.75</v>
+        <f t="shared" ref="D57" si="6">C57-C57*15/100</f>
+        <v>123.25</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1695,14 +1704,14 @@
         <v>78</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C58" s="1">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="D58" s="1">
         <f t="shared" si="0"/>
-        <v>140.25</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1710,44 +1719,44 @@
         <v>78</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C59" s="1">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D59" s="1">
         <f t="shared" si="0"/>
-        <v>135.15</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>87</v>
+      <c r="B60" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="C60" s="1">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="D60" s="1">
-        <f t="shared" ref="D60" si="7">C60-C60*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>135.15</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>119</v>
+      <c r="B61" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C61" s="1">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="D61" s="1">
-        <f>C61-C61*15/100</f>
-        <v>143.65</v>
+        <f t="shared" ref="D61" si="7">C61-C61*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1755,14 +1764,14 @@
         <v>78</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="C62" s="1">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D62" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f>C62-C62*15/100</f>
+        <v>143.65</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1770,14 +1779,14 @@
         <v>78</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="C63" s="1">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="D63" s="1">
-        <f>C63-C63*15/100</f>
-        <v>127.5</v>
+        <f t="shared" si="0"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1785,14 +1794,14 @@
         <v>78</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C64" s="1">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="D64" s="1">
-        <f t="shared" si="0"/>
-        <v>160.65</v>
+        <f>C64-C64*15/100</f>
+        <v>127.5</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1800,14 +1809,14 @@
         <v>78</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="C65" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D65" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1815,14 +1824,14 @@
         <v>78</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="C66" s="1">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="D66" s="1">
-        <f>C66-C66*15/100</f>
-        <v>267.75</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1830,14 +1839,14 @@
         <v>78</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="C67" s="1">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="D67" s="1">
-        <f t="shared" ref="D67" si="8">C67-C67*15/100</f>
-        <v>0</v>
+        <f>C67-C67*15/100</f>
+        <v>267.75</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1845,14 +1854,14 @@
         <v>78</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="C68" s="1">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="D68" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f t="shared" ref="D68" si="8">C68-C68*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1860,14 +1869,14 @@
         <v>78</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C69" s="1">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D69" s="1">
         <f t="shared" si="0"/>
-        <v>174.25</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1875,29 +1884,29 @@
         <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C70" s="1">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="D70" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C71" s="1">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="D71" s="1">
-        <f>C71-C71*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="0"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1905,14 +1914,14 @@
         <v>79</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C72" s="1">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="D72" s="1">
         <f>C72-C72*15/100</f>
-        <v>157.25</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1920,29 +1929,29 @@
         <v>79</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C73" s="1">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D73" s="1">
         <f>C73-C73*15/100</f>
-        <v>161.5</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>37</v>
+      <c r="B74" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="C74" s="1">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D74" s="1">
         <f>C74-C74*15/100</f>
-        <v>144.5</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1950,29 +1959,29 @@
         <v>79</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="C75" s="1">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="D75" s="1">
-        <f t="shared" ref="D75" si="9">C75-C75*15/100</f>
-        <v>123.25</v>
+        <f>C75-C75*15/100</f>
+        <v>144.5</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>39</v>
+      <c r="B76" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="C76" s="1">
-        <v>195</v>
+        <v>145</v>
       </c>
       <c r="D76" s="1">
-        <f t="shared" si="0"/>
-        <v>165.75</v>
+        <f t="shared" ref="D76" si="9">C76-C76*15/100</f>
+        <v>123.25</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1980,14 +1989,14 @@
         <v>79</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C77" s="1">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="D77" s="1">
         <f t="shared" si="0"/>
-        <v>135.15</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1995,44 +2004,44 @@
         <v>79</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C78" s="1">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D78" s="1">
         <f t="shared" si="0"/>
-        <v>143.65</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>87</v>
+      <c r="B79" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="C79" s="1">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D79" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>58</v>
+      <c r="B80" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C80" s="1">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D80" s="1">
-        <f>C80-C80*15/100</f>
-        <v>152.15</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2040,14 +2049,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C81" s="1">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D81" s="1">
-        <f t="shared" si="0"/>
-        <v>158.94999999999999</v>
+        <f>C81-C81*15/100</f>
+        <v>152.15</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2055,14 +2064,14 @@
         <v>79</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C82" s="1">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="D82" s="1">
         <f t="shared" si="0"/>
-        <v>131.75</v>
+        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2070,14 +2079,14 @@
         <v>79</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C83" s="1">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="D83" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2085,14 +2094,14 @@
         <v>79</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="C84" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D84" s="1">
-        <f t="shared" ref="D84" si="10">C84-C84*15/100</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2100,14 +2109,14 @@
         <v>79</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="C85" s="1">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="D85" s="1">
-        <f t="shared" ref="D85:D91" si="11">C85-C85*15/100</f>
-        <v>250.75</v>
+        <f t="shared" ref="D85" si="10">C85-C85*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2115,29 +2124,29 @@
         <v>79</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="C86" s="1">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="D86" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" ref="D86:D92" si="11">C86-C86*15/100</f>
+        <v>250.75</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="C87" s="1">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D87" s="1">
         <f t="shared" si="11"/>
-        <v>187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2145,14 +2154,14 @@
         <v>80</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C88" s="1">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="D88" s="1">
         <f t="shared" si="11"/>
-        <v>161.5</v>
+        <v>187</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2160,29 +2169,29 @@
         <v>80</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C89" s="1">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D89" s="1">
         <f t="shared" si="11"/>
-        <v>157.25</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>37</v>
+      <c r="B90" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="C90" s="1">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="D90" s="1">
         <f t="shared" si="11"/>
-        <v>144.5</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2190,29 +2199,29 @@
         <v>80</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="C91" s="1">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="D91" s="1">
         <f t="shared" si="11"/>
-        <v>123.25</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>56</v>
+      <c r="B92" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="C92" s="1">
-        <v>199</v>
+        <v>145</v>
       </c>
       <c r="D92" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f t="shared" si="11"/>
+        <v>123.25</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2220,14 +2229,14 @@
         <v>80</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C93" s="1">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="D93" s="1">
         <f t="shared" si="0"/>
-        <v>143.65</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2235,44 +2244,44 @@
         <v>80</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C94" s="1">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D94" s="1">
-        <f t="shared" ref="D94:D95" si="12">C94-C94*15/100</f>
-        <v>140.25</v>
+        <f t="shared" si="0"/>
+        <v>143.65</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>87</v>
+      <c r="B95" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="C95" s="1">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="D95" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" ref="D95:D96" si="12">C95-C95*15/100</f>
+        <v>140.25</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>58</v>
+      <c r="B96" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C96" s="1">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D96" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2280,14 +2289,14 @@
         <v>80</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C97" s="1">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D97" s="1">
         <f t="shared" si="0"/>
-        <v>165.75</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2295,14 +2304,14 @@
         <v>80</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C98" s="1">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="D98" s="1">
         <f t="shared" si="0"/>
-        <v>131.75</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2310,14 +2319,14 @@
         <v>80</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C99" s="1">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="D99" s="1">
         <f t="shared" si="0"/>
-        <v>160.65</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2325,14 +2334,14 @@
         <v>80</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="C100" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D100" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2340,7 +2349,7 @@
         <v>80</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C101" s="1">
         <v>0</v>
@@ -2355,29 +2364,29 @@
         <v>80</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C102" s="1">
         <v>0</v>
       </c>
       <c r="D102" s="1">
-        <f t="shared" ref="D102" si="13">C102-C102*15/100</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C103" s="1">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D103" s="1">
-        <f>C103-C103*15/100</f>
-        <v>187</v>
+        <f t="shared" ref="D103" si="13">C103-C103*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2385,44 +2394,44 @@
         <v>81</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C104" s="1">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="D104" s="1">
         <f>C104-C104*15/100</f>
-        <v>158.94999999999999</v>
+        <v>187</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>118</v>
+      <c r="B105" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="C105" s="1">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D105" s="1">
         <f>C105-C105*15/100</f>
-        <v>169.15</v>
+        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>103</v>
+      <c r="B106" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="C106" s="1">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D106" s="1">
         <f>C106-C106*15/100</f>
-        <v>157.25</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2430,14 +2439,14 @@
         <v>81</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="C107" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D107" s="1">
         <f>C107-C107*15/100</f>
-        <v>169.15</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2445,14 +2454,14 @@
         <v>81</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="C108" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D108" s="1">
-        <f t="shared" ref="D108:D110" si="14">C108-C108*15/100</f>
-        <v>0</v>
+        <f>C108-C108*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2460,13 +2469,13 @@
         <v>81</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C109" s="1">
         <v>0</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="D109:D111" si="14">C109-C109*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -2475,7 +2484,7 @@
         <v>81</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
@@ -2490,14 +2499,14 @@
         <v>81</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C111" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D111" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2505,14 +2514,14 @@
         <v>81</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C112" s="1">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D112" s="1">
-        <f>C112-C112*15/100</f>
-        <v>157.25</v>
+        <f t="shared" si="0"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2520,14 +2529,14 @@
         <v>81</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C113" s="1">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D113" s="1">
         <f>C113-C113*15/100</f>
-        <v>148.75</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2535,74 +2544,74 @@
         <v>81</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C114" s="1">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="D114" s="1">
         <f>C114-C114*15/100</f>
-        <v>169.15</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>98</v>
+      <c r="B115" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="C115" s="1">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="D115" s="1">
         <f>C115-C115*15/100</f>
-        <v>127.5</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B116" s="3" t="s">
-        <v>107</v>
+      <c r="B116" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="C116" s="1">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D116" s="1">
-        <f t="shared" si="0"/>
-        <v>118.15</v>
+        <f>C116-C116*15/100</f>
+        <v>127.5</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>108</v>
+      <c r="B117" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="C117" s="1">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D117" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>118.15</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C118" s="1">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D118" s="1">
-        <f t="shared" ref="D118:D126" si="15">C118-C118*15/100</f>
-        <v>187</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2610,14 +2619,14 @@
         <v>82</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C119" s="1">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="D119" s="1">
-        <f t="shared" si="15"/>
-        <v>160.65</v>
+        <f t="shared" ref="D119:D127" si="15">C119-C119*15/100</f>
+        <v>187</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2625,7 +2634,7 @@
         <v>82</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C120" s="1">
         <v>189</v>
@@ -2640,29 +2649,29 @@
         <v>82</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C121" s="1">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D121" s="1">
         <f t="shared" si="15"/>
-        <v>157.25</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>60</v>
+      <c r="B122" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C122" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D122" s="1">
         <f t="shared" si="15"/>
-        <v>169.15</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2670,14 +2679,14 @@
         <v>82</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="C123" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D123" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2685,7 +2694,7 @@
         <v>82</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C124" s="1">
         <v>0</v>
@@ -2700,7 +2709,7 @@
         <v>82</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C125" s="1">
         <v>0</v>
@@ -2714,15 +2723,15 @@
       <c r="A126" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>98</v>
+      <c r="B126" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C126" s="1">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D126" s="1">
         <f t="shared" si="15"/>
-        <v>127.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2730,28 +2739,28 @@
         <v>82</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C127" s="1">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="D127" s="1">
-        <f t="shared" ref="D127" si="16">C127-C127*15/100</f>
-        <v>169.15</v>
+        <f t="shared" si="15"/>
+        <v>127.5</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>61</v>
+      <c r="B128" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="C128" s="1">
         <v>199</v>
       </c>
       <c r="D128" s="1">
-        <f>C128-C128*15/100</f>
+        <f t="shared" ref="D128" si="16">C128-C128*15/100</f>
         <v>169.15</v>
       </c>
     </row>
@@ -2759,15 +2768,15 @@
       <c r="A129" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>95</v>
+      <c r="B129" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C129" s="1">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="D129" s="1">
         <f>C129-C129*15/100</f>
-        <v>126.65</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2775,14 +2784,14 @@
         <v>82</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C130" s="1">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D130" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f>C130-C130*15/100</f>
+        <v>126.65</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2790,29 +2799,29 @@
         <v>82</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C131" s="1">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D131" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="C132" s="1">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="D132" s="1">
-        <f>C132-C132*15/100</f>
-        <v>199.75</v>
+        <f t="shared" si="0"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2820,14 +2829,14 @@
         <v>83</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="C133" s="1">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="D133" s="1">
         <f>C133-C133*15/100</f>
-        <v>0</v>
+        <v>199.75</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2835,7 +2844,7 @@
         <v>83</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C134" s="1">
         <v>0</v>
@@ -2850,7 +2859,7 @@
         <v>83</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C135" s="1">
         <v>0</v>
@@ -2865,29 +2874,29 @@
         <v>83</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C136" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D136" s="1">
         <f>C136-C136*15/100</f>
-        <v>169.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>114</v>
+      <c r="B137" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="C137" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D137" s="1">
-        <f t="shared" ref="D137:D139" si="17">C137-C137*15/100</f>
-        <v>0</v>
+        <f>C137-C137*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2895,13 +2904,13 @@
         <v>83</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C138" s="1">
         <v>0</v>
       </c>
       <c r="D138" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="D138:D140" si="17">C138-C138*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -2910,7 +2919,7 @@
         <v>83</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C139" s="1">
         <v>0</v>
@@ -2925,14 +2934,14 @@
         <v>83</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C140" s="1">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D140" s="1">
-        <f t="shared" si="0"/>
-        <v>127.5</v>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2940,14 +2949,14 @@
         <v>83</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C141" s="1">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="D141" s="1">
         <f t="shared" si="0"/>
-        <v>169.15</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2955,29 +2964,29 @@
         <v>83</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C142" s="1">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="D142" s="1">
-        <f>C142-C142*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="0"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C143" s="1">
-        <v>275</v>
+        <v>215</v>
       </c>
       <c r="D143" s="1">
-        <f t="shared" si="0"/>
-        <v>233.75</v>
+        <f>C143-C143*15/100</f>
+        <v>182.75</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2985,89 +2994,89 @@
         <v>84</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C144" s="1">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="D144" s="1">
-        <f t="shared" si="0"/>
-        <v>203.15</v>
+        <f>C144-C144*15/100</f>
+        <v>242.25</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B145" s="4" t="s">
-        <v>111</v>
+      <c r="B145" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="C145" s="1">
-        <v>174</v>
+        <v>275</v>
       </c>
       <c r="D145" s="1">
         <f t="shared" si="0"/>
-        <v>147.9</v>
+        <v>233.75</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B146" s="4" t="s">
-        <v>110</v>
+      <c r="B146" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="C146" s="1">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="D146" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>203.15</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>124</v>
+        <v>84</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="C147" s="1">
-        <v>249</v>
+        <v>174</v>
       </c>
       <c r="D147" s="1">
         <f t="shared" si="0"/>
-        <v>211.65</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>62</v>
+        <v>84</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="C148" s="1">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="D148" s="1">
-        <f t="shared" ref="D148:D164" si="18">C148-C148*15/100</f>
-        <v>185.3</v>
+        <f t="shared" si="0"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="C149" s="1">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="D149" s="1">
-        <f t="shared" si="18"/>
-        <v>225.25</v>
+        <f t="shared" si="0"/>
+        <v>211.65</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3075,14 +3084,14 @@
         <v>86</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C150" s="1">
-        <v>285</v>
+        <v>218</v>
       </c>
       <c r="D150" s="1">
-        <f t="shared" si="18"/>
-        <v>242.25</v>
+        <f t="shared" ref="D150:D167" si="18">C150-C150*15/100</f>
+        <v>185.3</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3090,14 +3099,14 @@
         <v>86</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C151" s="1">
-        <v>340</v>
+        <v>265</v>
       </c>
       <c r="D151" s="1">
         <f t="shared" si="18"/>
-        <v>289</v>
+        <v>225.25</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3105,14 +3114,14 @@
         <v>86</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C152" s="1">
-        <v>215</v>
+        <v>285</v>
       </c>
       <c r="D152" s="1">
         <f t="shared" si="18"/>
-        <v>182.75</v>
+        <v>242.25</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3120,14 +3129,14 @@
         <v>86</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C153">
-        <v>299</v>
+        <v>65</v>
+      </c>
+      <c r="C153" s="1">
+        <v>340</v>
       </c>
       <c r="D153" s="1">
-        <f>C153-C153*15/100</f>
-        <v>254.15</v>
+        <f t="shared" si="18"/>
+        <v>289</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3135,14 +3144,14 @@
         <v>86</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C154">
-        <v>230</v>
+        <v>66</v>
+      </c>
+      <c r="C154" s="1">
+        <v>215</v>
       </c>
       <c r="D154" s="1">
         <f t="shared" si="18"/>
-        <v>195.5</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3150,14 +3159,14 @@
         <v>86</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C155">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="D155" s="1">
         <f>C155-C155*15/100</f>
-        <v>276.25</v>
+        <v>254.15</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3165,14 +3174,14 @@
         <v>86</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C156">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="D156" s="1">
         <f t="shared" si="18"/>
-        <v>169.15</v>
+        <v>195.5</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3180,14 +3189,14 @@
         <v>86</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C157">
-        <v>445</v>
+        <v>325</v>
       </c>
       <c r="D157" s="1">
-        <f t="shared" si="18"/>
-        <v>378.25</v>
+        <f>C157-C157*15/100</f>
+        <v>276.25</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3195,14 +3204,14 @@
         <v>86</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C158">
-        <v>400</v>
+        <v>199</v>
       </c>
       <c r="D158" s="1">
         <f t="shared" si="18"/>
-        <v>340</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3210,29 +3219,29 @@
         <v>86</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C159" s="1">
-        <v>278</v>
+        <v>71</v>
+      </c>
+      <c r="C159">
+        <v>445</v>
       </c>
       <c r="D159" s="1">
         <f t="shared" si="18"/>
-        <v>236.3</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>378.25</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C160" s="1">
-        <v>405</v>
+        <v>72</v>
+      </c>
+      <c r="C160">
+        <v>400</v>
       </c>
       <c r="D160" s="1">
         <f t="shared" si="18"/>
-        <v>344.25</v>
+        <v>340</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3240,29 +3249,29 @@
         <v>86</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="C161">
-        <v>360</v>
+        <v>285</v>
       </c>
       <c r="D161" s="1">
-        <f t="shared" si="18"/>
-        <v>306</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>C161-C161*15/100</f>
+        <v>242.25</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C162">
-        <v>249</v>
+        <v>73</v>
+      </c>
+      <c r="C162" s="1">
+        <v>278</v>
       </c>
       <c r="D162" s="1">
         <f t="shared" si="18"/>
-        <v>211.65</v>
+        <v>236.3</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3270,14 +3279,14 @@
         <v>86</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C163">
-        <v>329</v>
+        <v>74</v>
+      </c>
+      <c r="C163" s="1">
+        <v>405</v>
       </c>
       <c r="D163" s="1">
         <f t="shared" si="18"/>
-        <v>279.64999999999998</v>
+        <v>344.25</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3285,12 +3294,57 @@
         <v>86</v>
       </c>
       <c r="B164" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C164">
+        <v>360</v>
+      </c>
+      <c r="D164" s="1">
+        <f t="shared" si="18"/>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C165">
+        <v>249</v>
+      </c>
+      <c r="D165" s="1">
+        <f t="shared" si="18"/>
+        <v>211.65</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C166">
+        <v>329</v>
+      </c>
+      <c r="D166" s="1">
+        <f t="shared" si="18"/>
+        <v>279.64999999999998</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C164">
+      <c r="C167">
         <v>275</v>
       </c>
-      <c r="D164" s="1">
+      <c r="D167" s="1">
         <f t="shared" si="18"/>
         <v>233.75</v>
       </c>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5952F4C3-DDCF-41ED-80EE-48189ECEC2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679479F1-6752-41A9-8B8B-004021663393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="139">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -452,6 +452,9 @@
   </si>
   <si>
     <t>المعاصر انجليزي   ⬅️ 285</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء علوم ⬅️ 175</t>
   </si>
 </sst>
 </file>
@@ -1749,14 +1752,14 @@
         <v>78</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="C61" s="1">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D61" s="1">
         <f t="shared" ref="D61" si="7">C61-C61*15/100</f>
-        <v>0</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679479F1-6752-41A9-8B8B-004021663393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4AEF69-75E1-49B0-A5B0-BF2845014AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="141">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -455,6 +455,12 @@
   </si>
   <si>
     <t xml:space="preserve"> أضواء علوم ⬅️ 175</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء دراسات  ⬅️ 189 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء علوم  ⬅️ 189</t>
   </si>
 </sst>
 </file>
@@ -626,8 +632,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D167" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:D167" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D169" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:D169" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="كتب التأسيس" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="(نحو تأسيس سليم  أجزاء 1و2و3) _x000a_(نحو  سندباد أجزاء 1و2و3) _x000a_( نور البيان انجليزي جزئين - عربي) _x000a_( ذا بيست ستارت بوك 1و2) _x000a_( توب فونكس1و2 - جرامر 1و2و3)  _x000a_( اوكسفورد 5أجزاء)_x000a_(معلم القراءة)_x000a_(نون والقلم)" dataDxfId="1"/>
@@ -841,7 +847,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D169"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -873,7 +879,7 @@
         <v>125</v>
       </c>
       <c r="D2" s="1">
-        <f t="shared" ref="D2:D149" si="0">C2-C2*15/100</f>
+        <f t="shared" ref="D2:D151" si="0">C2-C2*15/100</f>
         <v>106.25</v>
       </c>
     </row>
@@ -2994,32 +3000,32 @@
     </row>
     <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>137</v>
+        <v>83</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="C144" s="1">
-        <v>285</v>
+        <v>189</v>
       </c>
       <c r="D144" s="1">
         <f>C144-C144*15/100</f>
-        <v>242.25</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>122</v>
+        <v>83</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="C145" s="1">
-        <v>275</v>
+        <v>189</v>
       </c>
       <c r="D145" s="1">
-        <f t="shared" si="0"/>
-        <v>233.75</v>
+        <f>C145-C145*15/100</f>
+        <v>160.65</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3027,89 +3033,89 @@
         <v>84</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C146" s="1">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="D146" s="1">
-        <f t="shared" si="0"/>
-        <v>203.15</v>
+        <f>C146-C146*15/100</f>
+        <v>242.25</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B147" s="4" t="s">
-        <v>111</v>
+      <c r="B147" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="C147" s="1">
-        <v>174</v>
+        <v>275</v>
       </c>
       <c r="D147" s="1">
         <f t="shared" si="0"/>
-        <v>147.9</v>
+        <v>233.75</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B148" s="4" t="s">
-        <v>110</v>
+      <c r="B148" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="C148" s="1">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="D148" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>203.15</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>124</v>
+        <v>84</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="C149" s="1">
-        <v>249</v>
+        <v>174</v>
       </c>
       <c r="D149" s="1">
         <f t="shared" si="0"/>
-        <v>211.65</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>62</v>
+        <v>84</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="C150" s="1">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="D150" s="1">
-        <f t="shared" ref="D150:D167" si="18">C150-C150*15/100</f>
-        <v>185.3</v>
+        <f t="shared" si="0"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="C151" s="1">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="D151" s="1">
-        <f t="shared" si="18"/>
-        <v>225.25</v>
+        <f t="shared" si="0"/>
+        <v>211.65</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3117,14 +3123,14 @@
         <v>86</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C152" s="1">
-        <v>285</v>
+        <v>218</v>
       </c>
       <c r="D152" s="1">
-        <f t="shared" si="18"/>
-        <v>242.25</v>
+        <f t="shared" ref="D152:D169" si="18">C152-C152*15/100</f>
+        <v>185.3</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3132,14 +3138,14 @@
         <v>86</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C153" s="1">
-        <v>340</v>
+        <v>265</v>
       </c>
       <c r="D153" s="1">
         <f t="shared" si="18"/>
-        <v>289</v>
+        <v>225.25</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3147,14 +3153,14 @@
         <v>86</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C154" s="1">
-        <v>215</v>
+        <v>285</v>
       </c>
       <c r="D154" s="1">
         <f t="shared" si="18"/>
-        <v>182.75</v>
+        <v>242.25</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3162,14 +3168,14 @@
         <v>86</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C155">
-        <v>299</v>
+        <v>65</v>
+      </c>
+      <c r="C155" s="1">
+        <v>340</v>
       </c>
       <c r="D155" s="1">
-        <f>C155-C155*15/100</f>
-        <v>254.15</v>
+        <f t="shared" si="18"/>
+        <v>289</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3177,14 +3183,14 @@
         <v>86</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C156">
-        <v>230</v>
+        <v>66</v>
+      </c>
+      <c r="C156" s="1">
+        <v>215</v>
       </c>
       <c r="D156" s="1">
         <f t="shared" si="18"/>
-        <v>195.5</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3192,14 +3198,14 @@
         <v>86</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C157">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="D157" s="1">
         <f>C157-C157*15/100</f>
-        <v>276.25</v>
+        <v>254.15</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3207,14 +3213,14 @@
         <v>86</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C158">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="D158" s="1">
         <f t="shared" si="18"/>
-        <v>169.15</v>
+        <v>195.5</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3222,14 +3228,14 @@
         <v>86</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C159">
-        <v>445</v>
+        <v>325</v>
       </c>
       <c r="D159" s="1">
-        <f t="shared" si="18"/>
-        <v>378.25</v>
+        <f>C159-C159*15/100</f>
+        <v>276.25</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3237,29 +3243,29 @@
         <v>86</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C160">
-        <v>400</v>
+        <v>199</v>
       </c>
       <c r="D160" s="1">
         <f t="shared" si="18"/>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>169.15</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="C161">
-        <v>285</v>
+        <v>445</v>
       </c>
       <c r="D161" s="1">
-        <f>C161-C161*15/100</f>
-        <v>242.25</v>
+        <f t="shared" si="18"/>
+        <v>378.25</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3267,14 +3273,14 @@
         <v>86</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C162" s="1">
-        <v>278</v>
+        <v>72</v>
+      </c>
+      <c r="C162">
+        <v>400</v>
       </c>
       <c r="D162" s="1">
         <f t="shared" si="18"/>
-        <v>236.3</v>
+        <v>340</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3282,29 +3288,29 @@
         <v>86</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C163" s="1">
-        <v>405</v>
+        <v>134</v>
+      </c>
+      <c r="C163">
+        <v>285</v>
       </c>
       <c r="D163" s="1">
-        <f t="shared" si="18"/>
-        <v>344.25</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>C163-C163*15/100</f>
+        <v>242.25</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C164">
-        <v>360</v>
+        <v>73</v>
+      </c>
+      <c r="C164" s="1">
+        <v>278</v>
       </c>
       <c r="D164" s="1">
         <f t="shared" si="18"/>
-        <v>306</v>
+        <v>236.3</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3312,14 +3318,14 @@
         <v>86</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C165">
-        <v>249</v>
+        <v>74</v>
+      </c>
+      <c r="C165" s="1">
+        <v>405</v>
       </c>
       <c r="D165" s="1">
         <f t="shared" si="18"/>
-        <v>211.65</v>
+        <v>344.25</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3327,14 +3333,14 @@
         <v>86</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C166">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="D166" s="1">
         <f t="shared" si="18"/>
-        <v>279.64999999999998</v>
+        <v>306</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3342,12 +3348,42 @@
         <v>86</v>
       </c>
       <c r="B167" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C167">
+        <v>249</v>
+      </c>
+      <c r="D167" s="1">
+        <f t="shared" si="18"/>
+        <v>211.65</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C168">
+        <v>329</v>
+      </c>
+      <c r="D168" s="1">
+        <f t="shared" si="18"/>
+        <v>279.64999999999998</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C167">
+      <c r="C169">
         <v>275</v>
       </c>
-      <c r="D167" s="1">
+      <c r="D169" s="1">
         <f t="shared" si="18"/>
         <v>233.75</v>
       </c>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4AEF69-75E1-49B0-A5B0-BF2845014AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3E5FB6-E65F-4710-A4A6-1679BCDE9D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="145">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -189,9 +189,6 @@
     <t xml:space="preserve"> بيت باي بيت إنجليزي ⬅️ 155</t>
   </si>
   <si>
-    <t xml:space="preserve"> المعاصر ماث ⬅️ 295</t>
-  </si>
-  <si>
     <t xml:space="preserve"> سلاح عربي ⬅️ 220</t>
   </si>
   <si>
@@ -306,9 +303,6 @@
     <t xml:space="preserve"> إمتحان علوم  ⬅️ 189</t>
   </si>
   <si>
-    <t xml:space="preserve"> إمتحان دراسات  ⬅️ </t>
-  </si>
-  <si>
     <t xml:space="preserve"> إمتحان علوم  ⬅️ </t>
   </si>
   <si>
@@ -352,9 +346,6 @@
   </si>
   <si>
     <t xml:space="preserve"> أضواء دراسات  ⬅️ 175 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> أضواء دين  ⬅️ 139</t>
   </si>
   <si>
     <t xml:space="preserve"> سلاح التلميذ دين  ⬅️ 145 </t>
@@ -461,6 +452,27 @@
   </si>
   <si>
     <t xml:space="preserve"> أضواء علوم  ⬅️ 189</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر ساينس لغات ⬅️ 375</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان دراسات  ⬅️ 199</t>
+  </si>
+  <si>
+    <t>برافو فرنساوى ⬅️ 160</t>
+  </si>
+  <si>
+    <t>ميرسي فرنساوى ⬅️ 180</t>
+  </si>
+  <si>
+    <t>برافو فرنساوى ⬅️ 175</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء دين  ⬅️ خلصان</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر ماث ⬅️ خلصان</t>
   </si>
 </sst>
 </file>
@@ -514,7 +526,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -527,6 +539,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -632,8 +647,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D169" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:D169" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D174" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:D174" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="كتب التأسيس" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="(نحو تأسيس سليم  أجزاء 1و2و3) _x000a_(نحو  سندباد أجزاء 1و2و3) _x000a_( نور البيان انجليزي جزئين - عربي) _x000a_( ذا بيست ستارت بوك 1و2) _x000a_( توب فونكس1و2 - جرامر 1و2و3)  _x000a_( اوكسفورد 5أجزاء)_x000a_(معلم القراءة)_x000a_(نون والقلم)" dataDxfId="1"/>
@@ -847,7 +862,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D169"/>
+  <dimension ref="A1:D174"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -856,21 +871,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -879,13 +894,13 @@
         <v>125</v>
       </c>
       <c r="D2" s="1">
-        <f t="shared" ref="D2:D151" si="0">C2-C2*15/100</f>
+        <f t="shared" ref="D2:D156" si="0">C2-C2*15/100</f>
         <v>106.25</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -900,10 +915,10 @@
     </row>
     <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C4" s="1">
         <v>120</v>
@@ -915,7 +930,7 @@
     </row>
     <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
@@ -930,7 +945,7 @@
     </row>
     <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -945,10 +960,10 @@
     </row>
     <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
@@ -960,10 +975,10 @@
     </row>
     <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="C8" s="1">
         <v>145</v>
@@ -975,10 +990,10 @@
     </row>
     <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C9" s="1">
         <v>0</v>
@@ -990,10 +1005,10 @@
     </row>
     <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C10" s="1">
         <v>120</v>
@@ -1005,7 +1020,7 @@
     </row>
     <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>8</v>
@@ -1020,7 +1035,7 @@
     </row>
     <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>9</v>
@@ -1035,7 +1050,7 @@
     </row>
     <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>10</v>
@@ -1050,7 +1065,7 @@
     </row>
     <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>11</v>
@@ -1065,7 +1080,7 @@
     </row>
     <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>12</v>
@@ -1080,7 +1095,7 @@
     </row>
     <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>13</v>
@@ -1095,7 +1110,7 @@
     </row>
     <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>14</v>
@@ -1110,7 +1125,7 @@
     </row>
     <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>15</v>
@@ -1125,7 +1140,7 @@
     </row>
     <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>16</v>
@@ -1140,7 +1155,7 @@
     </row>
     <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>17</v>
@@ -1155,10 +1170,10 @@
     </row>
     <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -1170,7 +1185,7 @@
     </row>
     <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>18</v>
@@ -1185,7 +1200,7 @@
     </row>
     <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>19</v>
@@ -1200,7 +1215,7 @@
     </row>
     <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>20</v>
@@ -1215,7 +1230,7 @@
     </row>
     <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>21</v>
@@ -1230,7 +1245,7 @@
     </row>
     <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>8</v>
@@ -1245,7 +1260,7 @@
     </row>
     <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>9</v>
@@ -1260,7 +1275,7 @@
     </row>
     <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>22</v>
@@ -1275,7 +1290,7 @@
     </row>
     <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>23</v>
@@ -1290,7 +1305,7 @@
     </row>
     <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>12</v>
@@ -1305,7 +1320,7 @@
     </row>
     <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>24</v>
@@ -1320,7 +1335,7 @@
     </row>
     <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>14</v>
@@ -1335,7 +1350,7 @@
     </row>
     <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>15</v>
@@ -1350,7 +1365,7 @@
     </row>
     <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>16</v>
@@ -1365,7 +1380,7 @@
     </row>
     <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>17</v>
@@ -1380,10 +1395,10 @@
     </row>
     <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C36" s="1">
         <v>0</v>
@@ -1395,10 +1410,10 @@
     </row>
     <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C37" s="1">
         <v>0</v>
@@ -1410,7 +1425,7 @@
     </row>
     <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>20</v>
@@ -1425,7 +1440,7 @@
     </row>
     <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>25</v>
@@ -1440,7 +1455,7 @@
     </row>
     <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>26</v>
@@ -1455,7 +1470,7 @@
     </row>
     <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>22</v>
@@ -1470,7 +1485,7 @@
     </row>
     <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>27</v>
@@ -1485,7 +1500,7 @@
     </row>
     <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>28</v>
@@ -1500,7 +1515,7 @@
     </row>
     <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>24</v>
@@ -1515,10 +1530,10 @@
     </row>
     <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C45" s="1">
         <v>169</v>
@@ -1530,7 +1545,7 @@
     </row>
     <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>29</v>
@@ -1545,7 +1560,7 @@
     </row>
     <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>30</v>
@@ -1560,7 +1575,7 @@
     </row>
     <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>31</v>
@@ -1575,10 +1590,10 @@
     </row>
     <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C49" s="1">
         <v>0</v>
@@ -1590,10 +1605,10 @@
     </row>
     <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C50" s="1">
         <v>0</v>
@@ -1605,7 +1620,7 @@
     </row>
     <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>32</v>
@@ -1620,7 +1635,7 @@
     </row>
     <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>33</v>
@@ -1635,7 +1650,7 @@
     </row>
     <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>34</v>
@@ -1650,7 +1665,7 @@
     </row>
     <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>35</v>
@@ -1665,7 +1680,7 @@
     </row>
     <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>36</v>
@@ -1680,7 +1695,7 @@
     </row>
     <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>37</v>
@@ -1695,7 +1710,7 @@
     </row>
     <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>38</v>
@@ -1710,7 +1725,7 @@
     </row>
     <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>39</v>
@@ -1725,7 +1740,7 @@
     </row>
     <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>40</v>
@@ -1740,7 +1755,7 @@
     </row>
     <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>41</v>
@@ -1755,10 +1770,10 @@
     </row>
     <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C61" s="1">
         <v>175</v>
@@ -1770,10 +1785,10 @@
     </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C62" s="1">
         <v>169</v>
@@ -1785,7 +1800,7 @@
     </row>
     <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>29</v>
@@ -1800,10 +1815,10 @@
     </row>
     <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C64" s="1">
         <v>150</v>
@@ -1815,7 +1830,7 @@
     </row>
     <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>42</v>
@@ -1830,10 +1845,10 @@
     </row>
     <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C66" s="1">
         <v>0</v>
@@ -1845,7 +1860,7 @@
     </row>
     <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>43</v>
@@ -1860,10 +1875,10 @@
     </row>
     <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C68" s="1">
         <v>0</v>
@@ -1875,7 +1890,7 @@
     </row>
     <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>44</v>
@@ -1890,7 +1905,7 @@
     </row>
     <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>45</v>
@@ -1905,7 +1920,7 @@
     </row>
     <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>46</v>
@@ -1920,7 +1935,7 @@
     </row>
     <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>47</v>
@@ -1935,7 +1950,7 @@
     </row>
     <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>35</v>
@@ -1950,7 +1965,7 @@
     </row>
     <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>48</v>
@@ -1965,7 +1980,7 @@
     </row>
     <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>37</v>
@@ -1980,10 +1995,10 @@
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C76" s="1">
         <v>145</v>
@@ -1995,7 +2010,7 @@
     </row>
     <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>39</v>
@@ -2010,7 +2025,7 @@
     </row>
     <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>41</v>
@@ -2025,7 +2040,7 @@
     </row>
     <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>49</v>
@@ -2040,10 +2055,10 @@
     </row>
     <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C80" s="1">
         <v>0</v>
@@ -2055,10 +2070,10 @@
     </row>
     <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C81" s="1">
         <v>179</v>
@@ -2070,7 +2085,7 @@
     </row>
     <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>50</v>
@@ -2085,7 +2100,7 @@
     </row>
     <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>51</v>
@@ -2100,7 +2115,7 @@
     </row>
     <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>42</v>
@@ -2115,10 +2130,10 @@
     </row>
     <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C85" s="1">
         <v>0</v>
@@ -2130,10 +2145,10 @@
     </row>
     <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="C86" s="1">
         <v>295</v>
@@ -2145,10 +2160,10 @@
     </row>
     <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C87" s="1">
         <v>0</v>
@@ -2160,10 +2175,10 @@
     </row>
     <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C88" s="1">
         <v>220</v>
@@ -2175,10 +2190,10 @@
     </row>
     <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C89" s="1">
         <v>190</v>
@@ -2190,10 +2205,10 @@
     </row>
     <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C90" s="1">
         <v>185</v>
@@ -2205,7 +2220,7 @@
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>37</v>
@@ -2220,7 +2235,7 @@
     </row>
     <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>3</v>
@@ -2235,10 +2250,10 @@
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C93" s="1">
         <v>199</v>
@@ -2250,7 +2265,7 @@
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>49</v>
@@ -2265,10 +2280,10 @@
     </row>
     <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C95" s="1">
         <v>165</v>
@@ -2280,10 +2295,10 @@
     </row>
     <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
@@ -2295,10 +2310,10 @@
     </row>
     <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C97" s="1">
         <v>179</v>
@@ -2310,10 +2325,10 @@
     </row>
     <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C98" s="1">
         <v>195</v>
@@ -2325,7 +2340,7 @@
     </row>
     <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>51</v>
@@ -2340,7 +2355,7 @@
     </row>
     <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>42</v>
@@ -2355,10 +2370,10 @@
     </row>
     <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C101" s="1">
         <v>0</v>
@@ -2370,10 +2385,10 @@
     </row>
     <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C102" s="1">
         <v>0</v>
@@ -2385,10 +2400,10 @@
     </row>
     <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
@@ -2400,10 +2415,10 @@
     </row>
     <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C104" s="1">
         <v>220</v>
@@ -2415,10 +2430,10 @@
     </row>
     <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C105" s="1">
         <v>187</v>
@@ -2430,10 +2445,10 @@
     </row>
     <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C106" s="1">
         <v>199</v>
@@ -2445,10 +2460,10 @@
     </row>
     <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C107" s="1">
         <v>185</v>
@@ -2460,10 +2475,10 @@
     </row>
     <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C108" s="1">
         <v>199</v>
@@ -2475,10 +2490,10 @@
     </row>
     <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C109" s="1">
         <v>0</v>
@@ -2490,10 +2505,10 @@
     </row>
     <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
@@ -2505,10 +2520,10 @@
     </row>
     <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
@@ -2520,10 +2535,10 @@
     </row>
     <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C112" s="1">
         <v>199</v>
@@ -2535,10 +2550,10 @@
     </row>
     <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C113" s="1">
         <v>185</v>
@@ -2550,10 +2565,10 @@
     </row>
     <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C114" s="1">
         <v>175</v>
@@ -2565,10 +2580,10 @@
     </row>
     <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C115" s="1">
         <v>199</v>
@@ -2580,10 +2595,10 @@
     </row>
     <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C116" s="1">
         <v>150</v>
@@ -2595,10 +2610,10 @@
     </row>
     <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="C117" s="1">
         <v>139</v>
@@ -2610,10 +2625,10 @@
     </row>
     <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C118" s="1">
         <v>0</v>
@@ -2625,40 +2640,40 @@
     </row>
     <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="C119" s="1">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="D119" s="1">
-        <f t="shared" ref="D119:D127" si="15">C119-C119*15/100</f>
-        <v>187</v>
+        <f>C119-C119*15/100</f>
+        <v>148.75</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C120" s="1">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="D120" s="1">
-        <f t="shared" si="15"/>
-        <v>160.65</v>
+        <f t="shared" ref="D120:D128" si="15">C120-C120*15/100</f>
+        <v>187</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C121" s="1">
         <v>189</v>
@@ -2670,55 +2685,55 @@
     </row>
     <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C122" s="1">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D122" s="1">
         <f t="shared" si="15"/>
-        <v>157.25</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>60</v>
+        <v>81</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="C123" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D123" s="1">
         <f t="shared" si="15"/>
-        <v>169.15</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="C124" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D124" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C125" s="1">
         <v>0</v>
@@ -2730,10 +2745,10 @@
     </row>
     <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C126" s="1">
         <v>0</v>
@@ -2745,645 +2760,720 @@
     </row>
     <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>98</v>
+        <v>81</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="C127" s="1">
-        <v>150</v>
+        <v>375</v>
       </c>
       <c r="D127" s="1">
         <f t="shared" si="15"/>
-        <v>127.5</v>
+        <v>318.75</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C128" s="1">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="D128" s="1">
-        <f t="shared" ref="D128" si="16">C128-C128*15/100</f>
-        <v>169.15</v>
+        <f t="shared" si="15"/>
+        <v>127.5</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>61</v>
+        <v>81</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C129" s="1">
         <v>199</v>
       </c>
       <c r="D129" s="1">
-        <f>C129-C129*15/100</f>
+        <f t="shared" ref="D129" si="16">C129-C129*15/100</f>
         <v>169.15</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>95</v>
+        <v>81</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C130" s="1">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="D130" s="1">
         <f>C130-C130*15/100</f>
-        <v>126.65</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C131" s="1">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D131" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f>C131-C131*15/100</f>
+        <v>126.65</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C132" s="1">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D132" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C133" s="1">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="D133" s="1">
-        <f>C133-C133*15/100</f>
-        <v>199.75</v>
+        <f t="shared" si="0"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="C134" s="1">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D134" s="1">
         <f>C134-C134*15/100</f>
-        <v>0</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="C135" s="1">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="D135" s="1">
         <f>C135-C135*15/100</f>
-        <v>0</v>
+        <v>199.75</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="C136" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D136" s="1">
         <f>C136-C136*15/100</f>
-        <v>0</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C137" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D137" s="1">
         <f>C137-C137*15/100</f>
-        <v>169.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>114</v>
+        <v>82</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="C138" s="1">
         <v>0</v>
       </c>
       <c r="D138" s="1">
-        <f t="shared" ref="D138:D140" si="17">C138-C138*15/100</f>
+        <f>C138-C138*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>112</v>
+        <v>82</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="C139" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D139" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>C139-C139*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C140" s="1">
         <v>0</v>
       </c>
       <c r="D140" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="D140:D142" si="17">C140-C140*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C141" s="1">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D141" s="1">
-        <f t="shared" si="0"/>
-        <v>127.5</v>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C142" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D142" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C143" s="1">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="D143" s="1">
-        <f>C143-C143*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="0"/>
+        <v>127.5</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>139</v>
+        <v>82</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C144" s="1">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D144" s="1">
-        <f>C144-C144*15/100</f>
-        <v>160.65</v>
+        <f t="shared" si="0"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>140</v>
+        <v>82</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C145" s="1">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D145" s="1">
         <f>C145-C145*15/100</f>
-        <v>160.65</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>137</v>
+        <v>82</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="C146" s="1">
-        <v>285</v>
+        <v>189</v>
       </c>
       <c r="D146" s="1">
         <f>C146-C146*15/100</f>
-        <v>242.25</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>122</v>
+        <v>82</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="C147" s="1">
-        <v>275</v>
+        <v>189</v>
       </c>
       <c r="D147" s="1">
-        <f t="shared" si="0"/>
-        <v>233.75</v>
+        <f>C147-C147*15/100</f>
+        <v>160.65</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>123</v>
+        <v>82</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="C148" s="1">
-        <v>239</v>
+        <v>175</v>
       </c>
       <c r="D148" s="1">
-        <f t="shared" si="0"/>
-        <v>203.15</v>
+        <f>C148-C148*15/100</f>
+        <v>148.75</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>111</v>
+        <v>83</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="C149" s="1">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D149" s="1">
-        <f t="shared" si="0"/>
-        <v>147.9</v>
+        <f>C149-C149*15/100</f>
+        <v>153</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>110</v>
+        <v>83</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="C150" s="1">
-        <v>185</v>
+        <v>285</v>
       </c>
       <c r="D150" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f>C150-C150*15/100</f>
+        <v>242.25</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C151" s="1">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="D151" s="1">
         <f t="shared" si="0"/>
-        <v>211.65</v>
+        <v>233.75</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="C152" s="1">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="D152" s="1">
-        <f t="shared" ref="D152:D169" si="18">C152-C152*15/100</f>
-        <v>185.3</v>
+        <f t="shared" si="0"/>
+        <v>203.15</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="C153" s="1">
+        <v>174</v>
+      </c>
+      <c r="D153" s="1">
+        <f t="shared" si="0"/>
+        <v>147.9</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A154" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C154" s="1">
+        <v>185</v>
+      </c>
+      <c r="D154" s="1">
+        <f t="shared" si="0"/>
+        <v>157.25</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A155" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C155" s="1">
+        <v>160</v>
+      </c>
+      <c r="D155" s="1">
+        <f>C155-C155*15/100</f>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A156" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C156" s="1">
+        <v>249</v>
+      </c>
+      <c r="D156" s="1">
+        <f t="shared" si="0"/>
+        <v>211.65</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A157" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C157" s="1">
+        <v>218</v>
+      </c>
+      <c r="D157" s="1">
+        <f t="shared" ref="D157:D174" si="18">C157-C157*15/100</f>
+        <v>185.3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A158" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C158" s="1">
         <v>265</v>
       </c>
-      <c r="D153" s="1">
+      <c r="D158" s="1">
         <f t="shared" si="18"/>
         <v>225.25</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A154" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C154" s="1">
+    <row r="159" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A159" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C159" s="1">
         <v>285</v>
       </c>
-      <c r="D154" s="1">
+      <c r="D159" s="1">
         <f t="shared" si="18"/>
         <v>242.25</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A155" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C155" s="1">
+    <row r="160" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A160" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C160" s="1">
         <v>340</v>
       </c>
-      <c r="D155" s="1">
+      <c r="D160" s="1">
         <f t="shared" si="18"/>
         <v>289</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A156" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C156" s="1">
+    <row r="161" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A161" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C161" s="1">
         <v>215</v>
       </c>
-      <c r="D156" s="1">
+      <c r="D161" s="1">
         <f t="shared" si="18"/>
         <v>182.75</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A157" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B157" s="1" t="s">
+    <row r="162" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A162" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C162">
+        <v>299</v>
+      </c>
+      <c r="D162" s="1">
+        <f>C162-C162*15/100</f>
+        <v>254.15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A163" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C157">
-        <v>299</v>
-      </c>
-      <c r="D157" s="1">
-        <f>C157-C157*15/100</f>
-        <v>254.15</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A158" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C158">
+      <c r="C163">
         <v>230</v>
       </c>
-      <c r="D158" s="1">
+      <c r="D163" s="1">
         <f t="shared" si="18"/>
         <v>195.5</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A159" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B159" s="1" t="s">
+    <row r="164" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A164" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C164">
+        <v>325</v>
+      </c>
+      <c r="D164" s="1">
+        <f>C164-C164*15/100</f>
+        <v>276.25</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A165" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C159">
-        <v>325</v>
-      </c>
-      <c r="D159" s="1">
-        <f>C159-C159*15/100</f>
-        <v>276.25</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A160" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C160">
+      <c r="C165">
         <v>199</v>
       </c>
-      <c r="D160" s="1">
+      <c r="D165" s="1">
         <f t="shared" si="18"/>
         <v>169.15</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A161" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C161">
+    <row r="166" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A166" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C166">
         <v>445</v>
       </c>
-      <c r="D161" s="1">
+      <c r="D166" s="1">
         <f t="shared" si="18"/>
         <v>378.25</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A162" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C162">
+    <row r="167" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A167" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C167">
         <v>400</v>
       </c>
-      <c r="D162" s="1">
+      <c r="D167" s="1">
         <f t="shared" si="18"/>
         <v>340</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C163">
+    <row r="168" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C168">
         <v>285</v>
       </c>
-      <c r="D163" s="1">
-        <f>C163-C163*15/100</f>
+      <c r="D168" s="1">
+        <f>C168-C168*15/100</f>
         <v>242.25</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A164" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C164" s="1">
+    <row r="169" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A169" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C169" s="1">
         <v>278</v>
       </c>
-      <c r="D164" s="1">
+      <c r="D169" s="1">
         <f t="shared" si="18"/>
         <v>236.3</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C165" s="1">
+    <row r="170" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C170" s="1">
         <v>405</v>
       </c>
-      <c r="D165" s="1">
+      <c r="D170" s="1">
         <f t="shared" si="18"/>
         <v>344.25</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C166">
+    <row r="171" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C171">
         <v>360</v>
       </c>
-      <c r="D166" s="1">
+      <c r="D171" s="1">
         <f t="shared" si="18"/>
         <v>306</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B167" s="1" t="s">
+    <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C167">
+      <c r="C172">
         <v>249</v>
       </c>
-      <c r="D167" s="1">
+      <c r="D172" s="1">
         <f t="shared" si="18"/>
         <v>211.65</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B168" s="1" t="s">
+    <row r="173" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C168">
+      <c r="C173">
         <v>329</v>
       </c>
-      <c r="D168" s="1">
+      <c r="D173" s="1">
         <f t="shared" si="18"/>
         <v>279.64999999999998</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C169">
+    <row r="174" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C174">
         <v>275</v>
       </c>
-      <c r="D169" s="1">
+      <c r="D174" s="1">
         <f t="shared" si="18"/>
         <v>233.75</v>
       </c>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3E5FB6-E65F-4710-A4A6-1679BCDE9D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC25D81A-22C0-45BB-B352-929A6902649B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,9 +87,6 @@
     <t xml:space="preserve"> المعاصر إنجليزي ⬅️ 175 </t>
   </si>
   <si>
-    <t xml:space="preserve"> المعاصر ماث لغات ⬅️ 255</t>
-  </si>
-  <si>
     <t xml:space="preserve"> المعاصر رياضه بالعربي ⬅️ 165</t>
   </si>
   <si>
@@ -160,9 +157,6 @@
   </si>
   <si>
     <t xml:space="preserve"> المعاصر إنجليزي ⬅️ 189</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> المعاصر ماث لغات ⬅️ 315</t>
   </si>
   <si>
     <t xml:space="preserve"> الإمتحان دراسات ⬅️ 169</t>
@@ -473,6 +467,12 @@
   </si>
   <si>
     <t xml:space="preserve"> المعاصر ماث ⬅️ خلصان</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر ماث لغات ⬅️ خلصان</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر ماث لغات ⬅️ قرب يخلص</t>
   </si>
 </sst>
 </file>
@@ -871,21 +871,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -900,7 +900,7 @@
     </row>
     <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -915,10 +915,10 @@
     </row>
     <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C4" s="1">
         <v>120</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -960,10 +960,10 @@
     </row>
     <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C8" s="1">
         <v>145</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C9" s="1">
         <v>0</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" s="1">
         <v>120</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>8</v>
@@ -1035,7 +1035,7 @@
     </row>
     <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>9</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>10</v>
@@ -1065,7 +1065,7 @@
     </row>
     <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>11</v>
@@ -1080,7 +1080,7 @@
     </row>
     <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>12</v>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>13</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>14</v>
@@ -1125,7 +1125,7 @@
     </row>
     <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>15</v>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>16</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>17</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="C22" s="1">
         <v>255</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" s="1">
         <v>165</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C24" s="1">
         <v>175</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C25" s="1">
         <v>169</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>8</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>9</v>
@@ -1275,10 +1275,10 @@
     </row>
     <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28" s="1">
         <v>140</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" s="1">
         <v>159</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>12</v>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C31" s="1">
         <v>139</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>14</v>
@@ -1350,7 +1350,7 @@
     </row>
     <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>15</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>16</v>
@@ -1380,7 +1380,7 @@
     </row>
     <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>17</v>
@@ -1395,10 +1395,10 @@
     </row>
     <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C36" s="1">
         <v>0</v>
@@ -1410,10 +1410,10 @@
     </row>
     <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C37" s="1">
         <v>0</v>
@@ -1425,10 +1425,10 @@
     </row>
     <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C38" s="1">
         <v>175</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C39" s="1">
         <v>190</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C40" s="1">
         <v>175</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C41" s="1">
         <v>140</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C42" s="1">
         <v>169</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C43" s="1">
         <v>165</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" s="1">
         <v>139</v>
@@ -1530,10 +1530,10 @@
     </row>
     <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C45" s="1">
         <v>169</v>
@@ -1545,10 +1545,10 @@
     </row>
     <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46" s="1">
         <v>185</v>
@@ -1560,10 +1560,10 @@
     </row>
     <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C47" s="1">
         <v>140</v>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C48" s="1">
         <v>189</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C49" s="1">
         <v>0</v>
@@ -1605,10 +1605,10 @@
     </row>
     <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C50" s="1">
         <v>0</v>
@@ -1620,10 +1620,10 @@
     </row>
     <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C51" s="1">
         <v>179</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C52" s="1">
         <v>179</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C53" s="1">
         <v>215</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C54" s="1">
         <v>185</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C55" s="1">
         <v>190</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C56" s="1">
         <v>170</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C57" s="1">
         <v>145</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C58" s="1">
         <v>195</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C59" s="1">
         <v>165</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C60" s="1">
         <v>159</v>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C61" s="1">
         <v>175</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C62" s="1">
         <v>169</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C63" s="1">
         <v>185</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C64" s="1">
         <v>150</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C65" s="1">
         <v>189</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C66" s="1">
         <v>0</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="C67" s="1">
         <v>315</v>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C68" s="1">
         <v>0</v>
@@ -1890,10 +1890,10 @@
     </row>
     <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C69" s="1">
         <v>169</v>
@@ -1905,10 +1905,10 @@
     </row>
     <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C70" s="1">
         <v>205</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C71" s="1">
         <v>189</v>
@@ -1935,10 +1935,10 @@
     </row>
     <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C72" s="1">
         <v>215</v>
@@ -1950,10 +1950,10 @@
     </row>
     <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C73" s="1">
         <v>185</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C74" s="1">
         <v>190</v>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C75" s="1">
         <v>170</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C76" s="1">
         <v>145</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C77" s="1">
         <v>195</v>
@@ -2025,10 +2025,10 @@
     </row>
     <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C78" s="1">
         <v>159</v>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C79" s="1">
         <v>169</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C80" s="1">
         <v>0</v>
@@ -2070,10 +2070,10 @@
     </row>
     <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C81" s="1">
         <v>179</v>
@@ -2085,10 +2085,10 @@
     </row>
     <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C82" s="1">
         <v>187</v>
@@ -2100,10 +2100,10 @@
     </row>
     <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C83" s="1">
         <v>155</v>
@@ -2115,10 +2115,10 @@
     </row>
     <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C84" s="1">
         <v>189</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C85" s="1">
         <v>0</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C86" s="1">
         <v>295</v>
@@ -2160,10 +2160,10 @@
     </row>
     <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C87" s="1">
         <v>0</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C88" s="1">
         <v>220</v>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C89" s="1">
         <v>190</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C90" s="1">
         <v>185</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C91" s="1">
         <v>170</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>3</v>
@@ -2250,10 +2250,10 @@
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C93" s="1">
         <v>199</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C94" s="1">
         <v>169</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C95" s="1">
         <v>165</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C97" s="1">
         <v>179</v>
@@ -2325,10 +2325,10 @@
     </row>
     <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C98" s="1">
         <v>195</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C99" s="1">
         <v>155</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C100" s="1">
         <v>189</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C101" s="1">
         <v>0</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C102" s="1">
         <v>0</v>
@@ -2400,10 +2400,10 @@
     </row>
     <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C104" s="1">
         <v>220</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C105" s="1">
         <v>187</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C106" s="1">
         <v>199</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C107" s="1">
         <v>185</v>
@@ -2475,10 +2475,10 @@
     </row>
     <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C108" s="1">
         <v>199</v>
@@ -2490,10 +2490,10 @@
     </row>
     <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C109" s="1">
         <v>0</v>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C112" s="1">
         <v>199</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C113" s="1">
         <v>185</v>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C114" s="1">
         <v>175</v>
@@ -2580,10 +2580,10 @@
     </row>
     <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C115" s="1">
         <v>199</v>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C116" s="1">
         <v>150</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C117" s="1">
         <v>139</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C118" s="1">
         <v>0</v>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C119" s="1">
         <v>175</v>
@@ -2655,10 +2655,10 @@
     </row>
     <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C120" s="1">
         <v>220</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C121" s="1">
         <v>189</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C122" s="1">
         <v>189</v>
@@ -2700,10 +2700,10 @@
     </row>
     <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C123" s="1">
         <v>185</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C124" s="1">
         <v>199</v>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C125" s="1">
         <v>0</v>
@@ -2745,10 +2745,10 @@
     </row>
     <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C126" s="1">
         <v>0</v>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C127" s="1">
         <v>375</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C128" s="1">
         <v>150</v>
@@ -2790,10 +2790,10 @@
     </row>
     <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C129" s="1">
         <v>199</v>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C130" s="1">
         <v>199</v>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C131" s="1">
         <v>149</v>
@@ -2835,10 +2835,10 @@
     </row>
     <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C132" s="1">
         <v>179</v>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C133" s="1">
         <v>185</v>
@@ -2865,145 +2865,145 @@
     </row>
     <row r="134" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C134" s="1">
         <v>175</v>
       </c>
       <c r="D134" s="1">
-        <f>C134-C134*15/100</f>
+        <f t="shared" ref="D134:D139" si="17">C134-C134*15/100</f>
         <v>148.75</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C135" s="1">
         <v>235</v>
       </c>
       <c r="D135" s="1">
-        <f>C135-C135*15/100</f>
+        <f t="shared" si="17"/>
         <v>199.75</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C136" s="1">
         <v>199</v>
       </c>
       <c r="D136" s="1">
-        <f>C136-C136*15/100</f>
+        <f t="shared" si="17"/>
         <v>169.15</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C137" s="1">
         <v>0</v>
       </c>
       <c r="D137" s="1">
-        <f>C137-C137*15/100</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C138" s="1">
         <v>0</v>
       </c>
       <c r="D138" s="1">
-        <f>C138-C138*15/100</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C139" s="1">
         <v>199</v>
       </c>
       <c r="D139" s="1">
-        <f>C139-C139*15/100</f>
+        <f t="shared" si="17"/>
         <v>169.15</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C140" s="1">
         <v>0</v>
       </c>
       <c r="D140" s="1">
-        <f t="shared" ref="D140:D142" si="17">C140-C140*15/100</f>
+        <f t="shared" ref="D140:D142" si="18">C140-C140*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C141" s="1">
         <v>0</v>
       </c>
       <c r="D141" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C142" s="1">
         <v>0</v>
       </c>
       <c r="D142" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C143" s="1">
         <v>150</v>
@@ -3015,10 +3015,10 @@
     </row>
     <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C144" s="1">
         <v>199</v>
@@ -3030,100 +3030,100 @@
     </row>
     <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C145" s="1">
         <v>215</v>
       </c>
       <c r="D145" s="1">
-        <f>C145-C145*15/100</f>
+        <f t="shared" ref="D145:D150" si="19">C145-C145*15/100</f>
         <v>182.75</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C146" s="1">
         <v>189</v>
       </c>
       <c r="D146" s="1">
-        <f>C146-C146*15/100</f>
+        <f t="shared" si="19"/>
         <v>160.65</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C147" s="1">
         <v>189</v>
       </c>
       <c r="D147" s="1">
-        <f>C147-C147*15/100</f>
+        <f t="shared" si="19"/>
         <v>160.65</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C148" s="1">
         <v>175</v>
       </c>
       <c r="D148" s="1">
-        <f>C148-C148*15/100</f>
+        <f t="shared" si="19"/>
         <v>148.75</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C149" s="1">
         <v>180</v>
       </c>
       <c r="D149" s="1">
-        <f>C149-C149*15/100</f>
+        <f t="shared" si="19"/>
         <v>153</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C150" s="1">
         <v>285</v>
       </c>
       <c r="D150" s="1">
-        <f>C150-C150*15/100</f>
+        <f t="shared" si="19"/>
         <v>242.25</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C151" s="1">
         <v>275</v>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C152" s="1">
         <v>239</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C153" s="1">
         <v>174</v>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C154" s="1">
         <v>185</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C155" s="1">
         <v>160</v>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C156" s="1">
         <v>249</v>
@@ -3210,85 +3210,85 @@
     </row>
     <row r="157" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C157" s="1">
         <v>218</v>
       </c>
       <c r="D157" s="1">
-        <f t="shared" ref="D157:D174" si="18">C157-C157*15/100</f>
+        <f t="shared" ref="D157:D174" si="20">C157-C157*15/100</f>
         <v>185.3</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C158" s="1">
         <v>265</v>
       </c>
       <c r="D158" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>225.25</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C159" s="1">
         <v>285</v>
       </c>
       <c r="D159" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>242.25</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C160" s="1">
         <v>340</v>
       </c>
       <c r="D160" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>289</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C161" s="1">
         <v>215</v>
       </c>
       <c r="D161" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>182.75</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C162">
         <v>299</v>
@@ -3300,25 +3300,25 @@
     </row>
     <row r="163" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C163">
         <v>230</v>
       </c>
       <c r="D163" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>195.5</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C164">
         <v>325</v>
@@ -3330,55 +3330,55 @@
     </row>
     <row r="165" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C165">
         <v>199</v>
       </c>
       <c r="D165" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>169.15</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C166">
         <v>445</v>
       </c>
       <c r="D166" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>378.25</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C167">
         <v>400</v>
       </c>
       <c r="D167" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>340</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C168">
         <v>285</v>
@@ -3390,37 +3390,37 @@
     </row>
     <row r="169" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C169" s="1">
         <v>278</v>
       </c>
       <c r="D169" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>236.3</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C170" s="1">
         <v>405</v>
       </c>
       <c r="D170" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>344.25</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>0</v>
@@ -3429,13 +3429,13 @@
         <v>360</v>
       </c>
       <c r="D171" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>306</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>1</v>
@@ -3444,13 +3444,13 @@
         <v>249</v>
       </c>
       <c r="D172" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>211.65</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>2</v>
@@ -3459,22 +3459,22 @@
         <v>329</v>
       </c>
       <c r="D173" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>279.64999999999998</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C174">
         <v>275</v>
       </c>
       <c r="D174" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>233.75</v>
       </c>
     </row>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC25D81A-22C0-45BB-B352-929A6902649B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD97188-9136-4280-ABA1-5C256DFBC48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="147">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -473,6 +473,12 @@
   </si>
   <si>
     <t xml:space="preserve"> المعاصر ماث لغات ⬅️ قرب يخلص</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان تاريخ (اسئله) ⬅️ 265</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان جغرافيا (اسئله) ⬅️ 270</t>
   </si>
 </sst>
 </file>
@@ -647,8 +653,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D174" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:D174" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D176" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:D176" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="كتب التأسيس" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="(نحو تأسيس سليم  أجزاء 1و2و3) _x000a_(نحو  سندباد أجزاء 1و2و3) _x000a_( نور البيان انجليزي جزئين - عربي) _x000a_( ذا بيست ستارت بوك 1و2) _x000a_( توب فونكس1و2 - جرامر 1و2و3)  _x000a_( اوكسفورد 5أجزاء)_x000a_(معلم القراءة)_x000a_(نون والقلم)" dataDxfId="1"/>
@@ -862,7 +868,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D174"/>
+  <dimension ref="A1:D176"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -3219,7 +3225,7 @@
         <v>218</v>
       </c>
       <c r="D157" s="1">
-        <f t="shared" ref="D157:D174" si="20">C157-C157*15/100</f>
+        <f t="shared" ref="D157:D176" si="20">C157-C157*15/100</f>
         <v>185.3</v>
       </c>
     </row>
@@ -3243,14 +3249,14 @@
         <v>83</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="C159" s="1">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="D159" s="1">
-        <f t="shared" si="20"/>
-        <v>242.25</v>
+        <f t="shared" ref="D159:D160" si="21">C159-C159*15/100</f>
+        <v>229.5</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3258,14 +3264,14 @@
         <v>83</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="C160" s="1">
-        <v>340</v>
+        <v>265</v>
       </c>
       <c r="D160" s="1">
-        <f t="shared" si="20"/>
-        <v>289</v>
+        <f t="shared" si="21"/>
+        <v>225.25</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3273,14 +3279,14 @@
         <v>83</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C161" s="1">
-        <v>215</v>
+        <v>285</v>
       </c>
       <c r="D161" s="1">
         <f t="shared" si="20"/>
-        <v>182.75</v>
+        <v>242.25</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3288,14 +3294,14 @@
         <v>83</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C162">
-        <v>299</v>
+        <v>62</v>
+      </c>
+      <c r="C162" s="1">
+        <v>340</v>
       </c>
       <c r="D162" s="1">
-        <f>C162-C162*15/100</f>
-        <v>254.15</v>
+        <f t="shared" si="20"/>
+        <v>289</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3303,14 +3309,14 @@
         <v>83</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C163">
-        <v>230</v>
+        <v>63</v>
+      </c>
+      <c r="C163" s="1">
+        <v>215</v>
       </c>
       <c r="D163" s="1">
         <f t="shared" si="20"/>
-        <v>195.5</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3318,14 +3324,14 @@
         <v>83</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C164">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="D164" s="1">
         <f>C164-C164*15/100</f>
-        <v>276.25</v>
+        <v>254.15</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3333,14 +3339,14 @@
         <v>83</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C165">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="D165" s="1">
         <f t="shared" si="20"/>
-        <v>169.15</v>
+        <v>195.5</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3348,14 +3354,14 @@
         <v>83</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C166">
-        <v>445</v>
+        <v>325</v>
       </c>
       <c r="D166" s="1">
-        <f t="shared" si="20"/>
-        <v>378.25</v>
+        <f>C166-C166*15/100</f>
+        <v>276.25</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3363,29 +3369,29 @@
         <v>83</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C167">
-        <v>400</v>
+        <v>199</v>
       </c>
       <c r="D167" s="1">
         <f t="shared" si="20"/>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>169.15</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="C168">
-        <v>285</v>
+        <v>445</v>
       </c>
       <c r="D168" s="1">
-        <f>C168-C168*15/100</f>
-        <v>242.25</v>
+        <f t="shared" si="20"/>
+        <v>378.25</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3393,14 +3399,14 @@
         <v>83</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C169" s="1">
-        <v>278</v>
+        <v>69</v>
+      </c>
+      <c r="C169">
+        <v>400</v>
       </c>
       <c r="D169" s="1">
         <f t="shared" si="20"/>
-        <v>236.3</v>
+        <v>340</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3408,29 +3414,29 @@
         <v>83</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C170" s="1">
-        <v>405</v>
+        <v>129</v>
+      </c>
+      <c r="C170">
+        <v>285</v>
       </c>
       <c r="D170" s="1">
-        <f t="shared" si="20"/>
-        <v>344.25</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>C170-C170*15/100</f>
+        <v>242.25</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C171">
-        <v>360</v>
+        <v>70</v>
+      </c>
+      <c r="C171" s="1">
+        <v>278</v>
       </c>
       <c r="D171" s="1">
         <f t="shared" si="20"/>
-        <v>306</v>
+        <v>236.3</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3438,14 +3444,14 @@
         <v>83</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C172">
-        <v>249</v>
+        <v>71</v>
+      </c>
+      <c r="C172" s="1">
+        <v>405</v>
       </c>
       <c r="D172" s="1">
         <f t="shared" si="20"/>
-        <v>211.65</v>
+        <v>344.25</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3453,14 +3459,14 @@
         <v>83</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C173">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="D173" s="1">
         <f t="shared" si="20"/>
-        <v>279.64999999999998</v>
+        <v>306</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3468,12 +3474,42 @@
         <v>83</v>
       </c>
       <c r="B174" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C174">
+        <v>249</v>
+      </c>
+      <c r="D174" s="1">
+        <f t="shared" si="20"/>
+        <v>211.65</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C175">
+        <v>329</v>
+      </c>
+      <c r="D175" s="1">
+        <f t="shared" si="20"/>
+        <v>279.64999999999998</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C174">
+      <c r="C176">
         <v>275</v>
       </c>
-      <c r="D174" s="1">
+      <c r="D176" s="1">
         <f t="shared" si="20"/>
         <v>233.75</v>
       </c>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD97188-9136-4280-ABA1-5C256DFBC48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBF48FE-0BCB-4B5B-8ED4-00F38DCADFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="148">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -479,6 +479,9 @@
   </si>
   <si>
     <t xml:space="preserve"> إمتحان جغرافيا (اسئله) ⬅️ 270</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء دين  ⬅️ 149</t>
   </si>
 </sst>
 </file>
@@ -653,8 +656,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D176" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:D176" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D177" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:D177" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="كتب التأسيس" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="(نحو تأسيس سليم  أجزاء 1و2و3) _x000a_(نحو  سندباد أجزاء 1و2و3) _x000a_( نور البيان انجليزي جزئين - عربي) _x000a_( ذا بيست ستارت بوك 1و2) _x000a_( توب فونكس1و2 - جرامر 1و2و3)  _x000a_( اوكسفورد 5أجزاء)_x000a_(معلم القراءة)_x000a_(نون والقلم)" dataDxfId="1"/>
@@ -868,7 +871,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D176"/>
+  <dimension ref="A1:D177"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -900,7 +903,7 @@
         <v>125</v>
       </c>
       <c r="D2" s="1">
-        <f t="shared" ref="D2:D156" si="0">C2-C2*15/100</f>
+        <f t="shared" ref="D2:D157" si="0">C2-C2*15/100</f>
         <v>106.25</v>
       </c>
     </row>
@@ -2064,14 +2067,14 @@
         <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="C80" s="1">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D80" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3045,7 +3048,7 @@
         <v>215</v>
       </c>
       <c r="D145" s="1">
-        <f t="shared" ref="D145:D150" si="19">C145-C145*15/100</f>
+        <f t="shared" ref="D145:D151" si="19">C145-C145*15/100</f>
         <v>182.75</v>
       </c>
     </row>
@@ -3083,45 +3086,45 @@
       <c r="A148" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B148" s="7" t="s">
+      <c r="B148" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C148" s="1">
+        <v>149</v>
+      </c>
+      <c r="D148" s="1">
+        <f>C148-C148*15/100</f>
+        <v>126.65</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B149" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C148" s="1">
+      <c r="C149" s="1">
         <v>175</v>
       </c>
-      <c r="D148" s="1">
+      <c r="D149" s="1">
         <f t="shared" si="19"/>
         <v>148.75</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A149" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B149" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C149" s="1">
-        <v>180</v>
-      </c>
-      <c r="D149" s="1">
-        <f t="shared" si="19"/>
-        <v>153</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>132</v>
+      <c r="B150" s="7" t="s">
+        <v>139</v>
       </c>
       <c r="C150" s="1">
-        <v>285</v>
+        <v>180</v>
       </c>
       <c r="D150" s="1">
         <f t="shared" si="19"/>
-        <v>242.25</v>
+        <v>153</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3129,14 +3132,14 @@
         <v>81</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C151" s="1">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="D151" s="1">
-        <f t="shared" si="0"/>
-        <v>233.75</v>
+        <f t="shared" si="19"/>
+        <v>242.25</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3144,29 +3147,29 @@
         <v>81</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C152" s="1">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="D152" s="1">
         <f t="shared" si="0"/>
-        <v>203.15</v>
+        <v>233.75</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B153" s="4" t="s">
-        <v>106</v>
+      <c r="B153" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C153" s="1">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="D153" s="1">
         <f t="shared" si="0"/>
-        <v>147.9</v>
+        <v>203.15</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3174,59 +3177,59 @@
         <v>81</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C154" s="1">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="D154" s="1">
         <f t="shared" si="0"/>
-        <v>157.25</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B155" s="7" t="s">
-        <v>138</v>
+      <c r="B155" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="C155" s="1">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="D155" s="1">
-        <f>C155-C155*15/100</f>
-        <v>136</v>
+        <f t="shared" si="0"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>119</v>
+        <v>81</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="C156" s="1">
-        <v>249</v>
+        <v>160</v>
       </c>
       <c r="D156" s="1">
-        <f t="shared" si="0"/>
-        <v>211.65</v>
+        <f>C156-C156*15/100</f>
+        <v>136</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="C157" s="1">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="D157" s="1">
-        <f t="shared" ref="D157:D176" si="20">C157-C157*15/100</f>
-        <v>185.3</v>
+        <f t="shared" si="0"/>
+        <v>211.65</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3234,14 +3237,14 @@
         <v>83</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C158" s="1">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="D158" s="1">
-        <f t="shared" si="20"/>
-        <v>225.25</v>
+        <f t="shared" ref="D158:D177" si="20">C158-C158*15/100</f>
+        <v>185.3</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3249,14 +3252,14 @@
         <v>83</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="C159" s="1">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D159" s="1">
-        <f t="shared" ref="D159:D160" si="21">C159-C159*15/100</f>
-        <v>229.5</v>
+        <f t="shared" si="20"/>
+        <v>225.25</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3264,14 +3267,14 @@
         <v>83</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C160" s="1">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D160" s="1">
-        <f t="shared" si="21"/>
-        <v>225.25</v>
+        <f t="shared" ref="D160:D161" si="21">C160-C160*15/100</f>
+        <v>229.5</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3279,14 +3282,14 @@
         <v>83</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>61</v>
+        <v>145</v>
       </c>
       <c r="C161" s="1">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="D161" s="1">
-        <f t="shared" si="20"/>
-        <v>242.25</v>
+        <f t="shared" si="21"/>
+        <v>225.25</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3294,14 +3297,14 @@
         <v>83</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C162" s="1">
-        <v>340</v>
+        <v>285</v>
       </c>
       <c r="D162" s="1">
         <f t="shared" si="20"/>
-        <v>289</v>
+        <v>242.25</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3309,14 +3312,14 @@
         <v>83</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C163" s="1">
-        <v>215</v>
+        <v>340</v>
       </c>
       <c r="D163" s="1">
         <f t="shared" si="20"/>
-        <v>182.75</v>
+        <v>289</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3324,14 +3327,14 @@
         <v>83</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C164">
-        <v>299</v>
+        <v>63</v>
+      </c>
+      <c r="C164" s="1">
+        <v>215</v>
       </c>
       <c r="D164" s="1">
-        <f>C164-C164*15/100</f>
-        <v>254.15</v>
+        <f t="shared" si="20"/>
+        <v>182.75</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3339,14 +3342,14 @@
         <v>83</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C165">
-        <v>230</v>
+        <v>299</v>
       </c>
       <c r="D165" s="1">
-        <f t="shared" si="20"/>
-        <v>195.5</v>
+        <f>C165-C165*15/100</f>
+        <v>254.15</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3354,14 +3357,14 @@
         <v>83</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C166">
-        <v>325</v>
+        <v>230</v>
       </c>
       <c r="D166" s="1">
-        <f>C166-C166*15/100</f>
-        <v>276.25</v>
+        <f t="shared" si="20"/>
+        <v>195.5</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3369,14 +3372,14 @@
         <v>83</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C167">
-        <v>199</v>
+        <v>325</v>
       </c>
       <c r="D167" s="1">
-        <f t="shared" si="20"/>
-        <v>169.15</v>
+        <f>C167-C167*15/100</f>
+        <v>276.25</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3384,14 +3387,14 @@
         <v>83</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C168">
-        <v>445</v>
+        <v>199</v>
       </c>
       <c r="D168" s="1">
         <f t="shared" si="20"/>
-        <v>378.25</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3399,59 +3402,59 @@
         <v>83</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C169">
-        <v>400</v>
+        <v>445</v>
       </c>
       <c r="D169" s="1">
         <f t="shared" si="20"/>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>378.25</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="C170">
-        <v>285</v>
+        <v>400</v>
       </c>
       <c r="D170" s="1">
-        <f>C170-C170*15/100</f>
-        <v>242.25</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+        <f t="shared" si="20"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B171" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C171">
+        <v>285</v>
+      </c>
+      <c r="D171" s="1">
+        <f>C171-C171*15/100</f>
+        <v>242.25</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A172" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C171" s="1">
+      <c r="C172" s="1">
         <v>278</v>
       </c>
-      <c r="D171" s="1">
+      <c r="D172" s="1">
         <f t="shared" si="20"/>
         <v>236.3</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C172" s="1">
-        <v>405</v>
-      </c>
-      <c r="D172" s="1">
-        <f t="shared" si="20"/>
-        <v>344.25</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3459,14 +3462,14 @@
         <v>83</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C173">
-        <v>360</v>
+        <v>71</v>
+      </c>
+      <c r="C173" s="1">
+        <v>405</v>
       </c>
       <c r="D173" s="1">
         <f t="shared" si="20"/>
-        <v>306</v>
+        <v>344.25</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3474,14 +3477,14 @@
         <v>83</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C174">
-        <v>249</v>
+        <v>360</v>
       </c>
       <c r="D174" s="1">
         <f t="shared" si="20"/>
-        <v>211.65</v>
+        <v>306</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3489,14 +3492,14 @@
         <v>83</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C175">
-        <v>329</v>
+        <v>249</v>
       </c>
       <c r="D175" s="1">
         <f t="shared" si="20"/>
-        <v>279.64999999999998</v>
+        <v>211.65</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3504,12 +3507,27 @@
         <v>83</v>
       </c>
       <c r="B176" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C176">
+        <v>329</v>
+      </c>
+      <c r="D176" s="1">
+        <f t="shared" si="20"/>
+        <v>279.64999999999998</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C176">
+      <c r="C177">
         <v>275</v>
       </c>
-      <c r="D176" s="1">
+      <c r="D177" s="1">
         <f t="shared" si="20"/>
         <v>233.75</v>
       </c>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBF48FE-0BCB-4B5B-8ED4-00F38DCADFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71BD162-5447-4DEF-8C05-CF88E1346173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="149">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -482,6 +482,9 @@
   </si>
   <si>
     <t xml:space="preserve"> أضواء دين  ⬅️ 149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">امتحان عربي ⬅️ 259 </t>
   </si>
 </sst>
 </file>
@@ -656,8 +659,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D177" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:D177" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D178" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:D178" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="كتب التأسيس" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="(نحو تأسيس سليم  أجزاء 1و2و3) _x000a_(نحو  سندباد أجزاء 1و2و3) _x000a_( نور البيان انجليزي جزئين - عربي) _x000a_( ذا بيست ستارت بوك 1و2) _x000a_( توب فونكس1و2 - جرامر 1و2و3)  _x000a_( اوكسفورد 5أجزاء)_x000a_(معلم القراءة)_x000a_(نون والقلم)" dataDxfId="1"/>
@@ -871,7 +874,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D177"/>
+  <dimension ref="A1:D178"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -903,7 +906,7 @@
         <v>125</v>
       </c>
       <c r="D2" s="1">
-        <f t="shared" ref="D2:D157" si="0">C2-C2*15/100</f>
+        <f t="shared" ref="D2:D158" si="0">C2-C2*15/100</f>
         <v>106.25</v>
       </c>
     </row>
@@ -3206,45 +3209,45 @@
       <c r="A156" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B156" s="7" t="s">
-        <v>138</v>
+      <c r="B156" s="4" t="s">
+        <v>148</v>
       </c>
       <c r="C156" s="1">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="D156" s="1">
         <f>C156-C156*15/100</f>
-        <v>136</v>
+        <v>220.15</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>119</v>
+        <v>81</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="C157" s="1">
-        <v>249</v>
+        <v>160</v>
       </c>
       <c r="D157" s="1">
-        <f t="shared" si="0"/>
-        <v>211.65</v>
+        <f>C157-C157*15/100</f>
+        <v>136</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="C158" s="1">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="D158" s="1">
-        <f t="shared" ref="D158:D177" si="20">C158-C158*15/100</f>
-        <v>185.3</v>
+        <f t="shared" si="0"/>
+        <v>211.65</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3252,14 +3255,14 @@
         <v>83</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C159" s="1">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="D159" s="1">
-        <f t="shared" si="20"/>
-        <v>225.25</v>
+        <f t="shared" ref="D159:D178" si="20">C159-C159*15/100</f>
+        <v>185.3</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3267,14 +3270,14 @@
         <v>83</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="C160" s="1">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D160" s="1">
-        <f t="shared" ref="D160:D161" si="21">C160-C160*15/100</f>
-        <v>229.5</v>
+        <f t="shared" si="20"/>
+        <v>225.25</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3282,14 +3285,14 @@
         <v>83</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C161" s="1">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D161" s="1">
-        <f t="shared" si="21"/>
-        <v>225.25</v>
+        <f t="shared" ref="D161:D162" si="21">C161-C161*15/100</f>
+        <v>229.5</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3297,14 +3300,14 @@
         <v>83</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>61</v>
+        <v>145</v>
       </c>
       <c r="C162" s="1">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="D162" s="1">
-        <f t="shared" si="20"/>
-        <v>242.25</v>
+        <f t="shared" si="21"/>
+        <v>225.25</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3312,14 +3315,14 @@
         <v>83</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C163" s="1">
-        <v>340</v>
+        <v>285</v>
       </c>
       <c r="D163" s="1">
         <f t="shared" si="20"/>
-        <v>289</v>
+        <v>242.25</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3327,14 +3330,14 @@
         <v>83</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C164" s="1">
-        <v>215</v>
+        <v>340</v>
       </c>
       <c r="D164" s="1">
         <f t="shared" si="20"/>
-        <v>182.75</v>
+        <v>289</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3342,14 +3345,14 @@
         <v>83</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C165">
-        <v>299</v>
+        <v>63</v>
+      </c>
+      <c r="C165" s="1">
+        <v>215</v>
       </c>
       <c r="D165" s="1">
-        <f>C165-C165*15/100</f>
-        <v>254.15</v>
+        <f t="shared" si="20"/>
+        <v>182.75</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3357,14 +3360,14 @@
         <v>83</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C166">
-        <v>230</v>
+        <v>299</v>
       </c>
       <c r="D166" s="1">
-        <f t="shared" si="20"/>
-        <v>195.5</v>
+        <f>C166-C166*15/100</f>
+        <v>254.15</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3372,14 +3375,14 @@
         <v>83</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C167">
-        <v>325</v>
+        <v>230</v>
       </c>
       <c r="D167" s="1">
-        <f>C167-C167*15/100</f>
-        <v>276.25</v>
+        <f t="shared" si="20"/>
+        <v>195.5</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3387,14 +3390,14 @@
         <v>83</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C168">
-        <v>199</v>
+        <v>325</v>
       </c>
       <c r="D168" s="1">
-        <f t="shared" si="20"/>
-        <v>169.15</v>
+        <f>C168-C168*15/100</f>
+        <v>276.25</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3402,14 +3405,14 @@
         <v>83</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C169">
-        <v>445</v>
+        <v>199</v>
       </c>
       <c r="D169" s="1">
         <f t="shared" si="20"/>
-        <v>378.25</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -3417,59 +3420,59 @@
         <v>83</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C170">
-        <v>400</v>
+        <v>445</v>
       </c>
       <c r="D170" s="1">
         <f t="shared" si="20"/>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>378.25</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="C171">
-        <v>285</v>
+        <v>400</v>
       </c>
       <c r="D171" s="1">
-        <f>C171-C171*15/100</f>
-        <v>242.25</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+        <f t="shared" si="20"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B172" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C172">
+        <v>285</v>
+      </c>
+      <c r="D172" s="1">
+        <f>C172-C172*15/100</f>
+        <v>242.25</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A173" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C172" s="1">
+      <c r="C173" s="1">
         <v>278</v>
       </c>
-      <c r="D172" s="1">
+      <c r="D173" s="1">
         <f t="shared" si="20"/>
         <v>236.3</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C173" s="1">
-        <v>405</v>
-      </c>
-      <c r="D173" s="1">
-        <f t="shared" si="20"/>
-        <v>344.25</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3477,14 +3480,14 @@
         <v>83</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C174">
-        <v>360</v>
+        <v>71</v>
+      </c>
+      <c r="C174" s="1">
+        <v>405</v>
       </c>
       <c r="D174" s="1">
         <f t="shared" si="20"/>
-        <v>306</v>
+        <v>344.25</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3492,14 +3495,14 @@
         <v>83</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C175">
-        <v>249</v>
+        <v>360</v>
       </c>
       <c r="D175" s="1">
         <f t="shared" si="20"/>
-        <v>211.65</v>
+        <v>306</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3507,14 +3510,14 @@
         <v>83</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C176">
-        <v>329</v>
+        <v>249</v>
       </c>
       <c r="D176" s="1">
         <f t="shared" si="20"/>
-        <v>279.64999999999998</v>
+        <v>211.65</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3522,12 +3525,27 @@
         <v>83</v>
       </c>
       <c r="B177" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C177">
+        <v>329</v>
+      </c>
+      <c r="D177" s="1">
+        <f t="shared" si="20"/>
+        <v>279.64999999999998</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C177">
+      <c r="C178">
         <v>275</v>
       </c>
-      <c r="D177" s="1">
+      <c r="D178" s="1">
         <f t="shared" si="20"/>
         <v>233.75</v>
       </c>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71BD162-5447-4DEF-8C05-CF88E1346173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33A35B6-2831-48BD-A15D-AD2946BACAB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الورقة1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="135">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -45,18 +45,6 @@
     <t xml:space="preserve">  سلاح دين ⬅️ 145</t>
   </si>
   <si>
-    <t xml:space="preserve"> المعاصر إنجليزي كي جي 1 ⬅️ 125</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> المعاصر ماس كي جي 1 ⬅️ 205</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> المعاصر إنجليزي كي جي 2 ⬅️ 125</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> المعاصر ماس كي جي 2 ⬅️ 210</t>
-  </si>
-  <si>
     <t xml:space="preserve"> سلاح التلميذ عربي ⬅️ 180</t>
   </si>
   <si>
@@ -90,12 +78,6 @@
     <t xml:space="preserve"> المعاصر رياضه بالعربي ⬅️ 165</t>
   </si>
   <si>
-    <t xml:space="preserve"> تأسيس سليم عربي ⬅️ 175 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> تأسيس سليم رياضيات ⬅️ 169</t>
-  </si>
-  <si>
     <t xml:space="preserve"> سلاح التلميذ دين ⬅️ 140 </t>
   </si>
   <si>
@@ -126,12 +108,6 @@
     <t xml:space="preserve"> المعاصر انجليزي ⬅️ 189</t>
   </si>
   <si>
-    <t xml:space="preserve"> التأسيس السيلم عربي  ⬅️ 179 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> التأسيس السليم حساب  ⬅️ 179 </t>
-  </si>
-  <si>
     <t xml:space="preserve"> سلاح التلميذ عربي ⬅️ 215</t>
   </si>
   <si>
@@ -165,9 +141,6 @@
     <t xml:space="preserve"> الإمتحان عربي ⬅️ 205 </t>
   </si>
   <si>
-    <t xml:space="preserve"> تأسيس سليم عربي ⬅️ 189</t>
-  </si>
-  <si>
     <t xml:space="preserve"> سلاح التلميذ عربي⬅️ 215</t>
   </si>
   <si>
@@ -325,12 +298,6 @@
   </si>
   <si>
     <t xml:space="preserve"> إمتحان عربي  ⬅️ 220 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> إمتحان دراسات  ⬅️ 187</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> المعاصر رياضيات  ⬅️ 185 </t>
   </si>
   <si>
     <t xml:space="preserve"> أضواء عربي  ⬅️ 199</t>
@@ -412,30 +379,12 @@
     <t xml:space="preserve"> بيت باي بيت  ⬅️ 150 </t>
   </si>
   <si>
-    <t>📚 مرحلة لغات (KG)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> المعاصر بلس كي جي 2 ⬅️ </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> الأضواء عربي ⬅️ </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ستيب اهيد إنجليزي كي جي 2 ⬅️ 145</t>
-  </si>
-  <si>
     <t xml:space="preserve"> سلاح التلميذ دين ⬅️145</t>
   </si>
   <si>
     <t>المعاصر انجليزي (جزء اول)  ⬅️ 285</t>
   </si>
   <si>
-    <t xml:space="preserve"> سلاح التلميذ عربي كي جي 2 ⬅️ 120</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> سلاح التلميذ عربي كي جي 1 ⬅️ 120</t>
-  </si>
-  <si>
     <t>المعاصر انجليزي   ⬅️ 285</t>
   </si>
   <si>
@@ -472,9 +421,6 @@
     <t xml:space="preserve"> المعاصر ماث لغات ⬅️ خلصان</t>
   </si>
   <si>
-    <t xml:space="preserve"> المعاصر ماث لغات ⬅️ قرب يخلص</t>
-  </si>
-  <si>
     <t xml:space="preserve"> إمتحان تاريخ (اسئله) ⬅️ 265</t>
   </si>
   <si>
@@ -485,6 +431,18 @@
   </si>
   <si>
     <t xml:space="preserve">امتحان عربي ⬅️ 259 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان دراسات  ⬅️ خلصان</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر رياضيات  ⬅️ خلصان </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر انجليزي ⬅️ خلصان </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> بيت باي بيت إنجليزي  ⬅️ خلصان </t>
   </si>
 </sst>
 </file>
@@ -557,7 +515,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="عادي" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -659,8 +617,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D178" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:D178" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D163" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:D163" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="كتب التأسيس" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="(نحو تأسيس سليم  أجزاء 1و2و3) _x000a_(نحو  سندباد أجزاء 1و2و3) _x000a_( نور البيان انجليزي جزئين - عربي) _x000a_( ذا بيست ستارت بوك 1و2) _x000a_( توب فونكس1و2 - جرامر 1و2و3)  _x000a_( اوكسفورد 5أجزاء)_x000a_(معلم القراءة)_x000a_(نون والقلم)" dataDxfId="1"/>
@@ -874,7 +832,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D178"/>
+  <dimension ref="A1:D163"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -883,1719 +841,1715 @@
   <sheetData>
     <row r="1" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>121</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="1">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="D2" s="1">
-        <f t="shared" ref="D2:D158" si="0">C2-C2*15/100</f>
-        <v>106.25</v>
+        <f t="shared" ref="D2:D4" si="0">C2-C2*15/100</f>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="D3" s="1">
         <f t="shared" si="0"/>
-        <v>174.25</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>131</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D4" s="1">
-        <f>C4-C4*15/100</f>
-        <v>102</v>
+        <f t="shared" si="0"/>
+        <v>110.5</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="D5" s="1">
-        <f t="shared" si="0"/>
-        <v>106.25</v>
+        <f t="shared" ref="D5:D143" si="1">C5-C5*15/100</f>
+        <v>126.65</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="D6" s="1">
-        <f t="shared" si="0"/>
-        <v>178.5</v>
+        <f t="shared" si="1"/>
+        <v>135.15</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>125</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D13" si="1">C7-C7*15/100</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>109.65</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="1"/>
-        <v>123.25</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>126</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="1"/>
-        <v>102</v>
+        <v>114.75</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="1"/>
-        <v>153</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="C12" s="1">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="1"/>
-        <v>144.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="C13" s="1">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="D13" s="1">
-        <f t="shared" si="1"/>
-        <v>110.5</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" s="1">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="D14" s="1">
-        <f t="shared" si="0"/>
-        <v>126.65</v>
+        <f t="shared" ref="D14:D17" si="2">C14-C14*15/100</f>
+        <v>140.25</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C15" s="1">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f t="shared" si="2"/>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C16" s="1">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" si="0"/>
-        <v>109.65</v>
+        <f t="shared" si="2"/>
+        <v>144.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
+        <f t="shared" si="2"/>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
+        <f t="shared" si="1"/>
+        <v>135.15</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="0"/>
-        <v>114.75</v>
+        <f t="shared" si="1"/>
+        <v>135.15</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="1">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="0"/>
-        <v>148.75</v>
+        <f t="shared" si="1"/>
+        <v>118.15</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>109</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>140.25</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="C22" s="1">
-        <v>255</v>
+        <v>165</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" ref="D22:D28" si="2">C22-C22*15/100</f>
-        <v>216.75</v>
+        <f t="shared" si="1"/>
+        <v>140.25</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C23" s="1">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="2"/>
-        <v>140.25</v>
+        <f t="shared" si="1"/>
+        <v>114.75</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C24" s="1">
         <v>175</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>148.75</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="C25" s="1">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="D25" s="1">
-        <f t="shared" si="2"/>
-        <v>143.65</v>
+        <f t="shared" ref="D25" si="3">C25-C25*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="C26" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="D26" s="1">
-        <f t="shared" si="2"/>
-        <v>153</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C27" s="1">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D27" s="1">
-        <f t="shared" si="2"/>
-        <v>144.5</v>
+        <f>C27-C27*15/100</f>
+        <v>161.5</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C28" s="1">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="D28" s="1">
-        <f t="shared" si="2"/>
-        <v>119</v>
+        <f>C28-C28*15/100</f>
+        <v>148.75</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D29" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f>C29-C29*15/100</f>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C30" s="1">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D30" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f t="shared" si="1"/>
+        <v>143.65</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C31" s="1">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" si="0"/>
-        <v>118.15</v>
+        <f t="shared" si="1"/>
+        <v>140.25</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="D32" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
+        <f t="shared" si="1"/>
+        <v>118.15</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="C33" s="1">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D33" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
+        <f>C33-C33*15/100</f>
+        <v>143.65</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C34" s="1">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="D34" s="1">
-        <f t="shared" si="0"/>
-        <v>114.75</v>
+        <f t="shared" si="1"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C35" s="1">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" si="0"/>
-        <v>148.75</v>
+        <f t="shared" si="1"/>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C36" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D36" s="1">
-        <f t="shared" ref="D36" si="3">C36-C36*15/100</f>
-        <v>0</v>
+        <f>C36-C36*15/100</f>
+        <v>160.65</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C37" s="1">
         <v>0</v>
       </c>
       <c r="D37" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D37" si="4">C37-C37*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="C38" s="1">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" si="0"/>
-        <v>148.75</v>
+        <f t="shared" ref="D38" si="5">C38-C38*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C39" s="1">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="D39" s="1">
         <f>C39-C39*15/100</f>
-        <v>161.5</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C40" s="1">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D40" s="1">
         <f>C40-C40*15/100</f>
-        <v>148.75</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C41" s="1">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="D41" s="1">
         <f>C41-C41*15/100</f>
-        <v>119</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C42" s="1">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D42" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f>C42-C42*15/100</f>
+        <v>144.5</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>27</v>
+        <v>66</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="C43" s="1">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="D43" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
+        <f t="shared" ref="D43" si="6">C43-C43*15/100</f>
+        <v>123.25</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C44" s="1">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="D44" s="1">
-        <f t="shared" si="0"/>
-        <v>118.15</v>
+        <f t="shared" si="1"/>
+        <v>165.75</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="C45" s="1">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D45" s="1">
-        <f>C45-C45*15/100</f>
-        <v>143.65</v>
+        <f t="shared" si="1"/>
+        <v>140.25</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C46" s="1">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="D46" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f t="shared" si="1"/>
+        <v>135.15</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>29</v>
+        <v>66</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="C47" s="1">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="D47" s="1">
-        <f t="shared" si="0"/>
-        <v>119</v>
+        <f t="shared" ref="D47" si="7">C47-C47*15/100</f>
+        <v>148.75</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="C48" s="1">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D48" s="1">
         <f>C48-C48*15/100</f>
-        <v>160.65</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="C49" s="1">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D49" s="1">
-        <f t="shared" ref="D49" si="4">C49-C49*15/100</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C50" s="1">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D50" s="1">
-        <f t="shared" ref="D50" si="5">C50-C50*15/100</f>
-        <v>0</v>
+        <f>C50-C50*15/100</f>
+        <v>127.5</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C51" s="1">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D51" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f t="shared" si="1"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="C52" s="1">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D52" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="C53" s="1">
-        <v>215</v>
+        <v>315</v>
       </c>
       <c r="D53" s="1">
         <f>C53-C53*15/100</f>
-        <v>182.75</v>
+        <v>267.75</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="C54" s="1">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="D54" s="1">
-        <f>C54-C54*15/100</f>
-        <v>157.25</v>
+        <f t="shared" ref="D54" si="8">C54-C54*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C55" s="1">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="D55" s="1">
-        <f>C55-C55*15/100</f>
-        <v>161.5</v>
+        <f t="shared" si="1"/>
+        <v>143.65</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C56" s="1">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="D56" s="1">
-        <f>C56-C56*15/100</f>
-        <v>144.5</v>
+        <f t="shared" si="1"/>
+        <v>174.25</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>37</v>
+        <v>67</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="C57" s="1">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="D57" s="1">
-        <f t="shared" ref="D57" si="6">C57-C57*15/100</f>
-        <v>123.25</v>
+        <f>C57-C57*15/100</f>
+        <v>182.75</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C58" s="1">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D58" s="1">
-        <f t="shared" si="0"/>
-        <v>165.75</v>
+        <f>C58-C58*15/100</f>
+        <v>157.25</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C59" s="1">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="D59" s="1">
-        <f t="shared" si="0"/>
-        <v>140.25</v>
+        <f>C59-C59*15/100</f>
+        <v>161.5</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>40</v>
+        <v>67</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="C60" s="1">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D60" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f>C60-C60*15/100</f>
+        <v>144.5</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="C61" s="1">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="D61" s="1">
-        <f t="shared" ref="D61" si="7">C61-C61*15/100</f>
-        <v>148.75</v>
+        <f t="shared" ref="D61" si="9">C61-C61*15/100</f>
+        <v>123.25</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>114</v>
+        <v>30</v>
       </c>
       <c r="C62" s="1">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="D62" s="1">
-        <f>C62-C62*15/100</f>
-        <v>143.65</v>
+        <f t="shared" si="1"/>
+        <v>165.75</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C63" s="1">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="D63" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f t="shared" si="1"/>
+        <v>135.15</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>123</v>
+        <v>38</v>
       </c>
       <c r="C64" s="1">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="D64" s="1">
-        <f>C64-C64*15/100</f>
-        <v>127.5</v>
+        <f t="shared" si="1"/>
+        <v>143.65</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>41</v>
+        <v>67</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="C65" s="1">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="D65" s="1">
-        <f t="shared" si="0"/>
-        <v>160.65</v>
+        <f t="shared" si="1"/>
+        <v>148.75</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="C66" s="1">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="D66" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>C66-C66*15/100</f>
+        <v>152.15</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>143</v>
+        <v>39</v>
       </c>
       <c r="C67" s="1">
-        <v>315</v>
+        <v>187</v>
       </c>
       <c r="D67" s="1">
-        <f>C67-C67*15/100</f>
-        <v>267.75</v>
+        <f t="shared" si="1"/>
+        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C68" s="1">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="D68" s="1">
-        <f t="shared" ref="D68" si="8">C68-C68*15/100</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>131.75</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C69" s="1">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f t="shared" si="1"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="C70" s="1">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="D70" s="1">
-        <f t="shared" si="0"/>
-        <v>174.25</v>
+        <f t="shared" ref="D70" si="10">C70-C70*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="C71" s="1">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="D71" s="1">
-        <f t="shared" si="0"/>
-        <v>160.65</v>
+        <f t="shared" ref="D71:D77" si="11">C71-C71*15/100</f>
+        <v>250.75</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="C72" s="1">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="D72" s="1">
-        <f>C72-C72*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C73" s="1">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="D73" s="1">
-        <f>C73-C73*15/100</f>
-        <v>157.25</v>
+        <f t="shared" si="11"/>
+        <v>187</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C74" s="1">
         <v>190</v>
       </c>
       <c r="D74" s="1">
-        <f>C74-C74*15/100</f>
+        <f t="shared" si="11"/>
         <v>161.5</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>36</v>
+        <v>68</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="C75" s="1">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="D75" s="1">
-        <f>C75-C75*15/100</f>
-        <v>144.5</v>
+        <f t="shared" si="11"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="C76" s="1">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="D76" s="1">
-        <f t="shared" ref="D76" si="9">C76-C76*15/100</f>
-        <v>123.25</v>
+        <f t="shared" si="11"/>
+        <v>144.5</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>38</v>
+        <v>68</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="C77" s="1">
-        <v>195</v>
+        <v>145</v>
       </c>
       <c r="D77" s="1">
-        <f t="shared" si="0"/>
-        <v>165.75</v>
+        <f t="shared" si="11"/>
+        <v>123.25</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C78" s="1">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="D78" s="1">
-        <f t="shared" si="0"/>
-        <v>135.15</v>
+        <f t="shared" si="1"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C79" s="1">
         <v>169</v>
       </c>
       <c r="D79" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>143.65</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>133</v>
+        <v>68</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="C80" s="1">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" si="0"/>
-        <v>148.75</v>
+        <f t="shared" ref="D80:D81" si="12">C80-C80*15/100</f>
+        <v>140.25</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="C81" s="1">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D81" s="1">
-        <f>C81-C81*15/100</f>
-        <v>152.15</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C82" s="1">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D82" s="1">
-        <f t="shared" si="0"/>
-        <v>158.94999999999999</v>
+        <f t="shared" si="1"/>
+        <v>152.15</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C83" s="1">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="D83" s="1">
-        <f t="shared" si="0"/>
-        <v>131.75</v>
+        <f t="shared" si="1"/>
+        <v>165.75</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C84" s="1">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="D84" s="1">
-        <f t="shared" si="0"/>
-        <v>160.65</v>
+        <f t="shared" si="1"/>
+        <v>131.75</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="C85" s="1">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="D85" s="1">
-        <f t="shared" ref="D85" si="10">C85-C85*15/100</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="C86" s="1">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="D86" s="1">
-        <f t="shared" ref="D86:D92" si="11">C86-C86*15/100</f>
-        <v>250.75</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C87" s="1">
         <v>0</v>
       </c>
       <c r="D87" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="C88" s="1">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D88" s="1">
-        <f t="shared" si="11"/>
-        <v>187</v>
+        <f t="shared" ref="D88" si="13">C88-C88*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="C89" s="1">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="D89" s="1">
-        <f t="shared" si="11"/>
-        <v>161.5</v>
+        <f>C89-C89*15/100</f>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="C90" s="1">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D90" s="1">
-        <f t="shared" si="11"/>
-        <v>157.25</v>
+        <v>187</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="C91" s="1">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="D91" s="1">
-        <f t="shared" si="11"/>
-        <v>144.5</v>
+        <f>C91-C91*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>3</v>
+        <v>69</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="C92" s="1">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="D92" s="1">
-        <f t="shared" si="11"/>
-        <v>123.25</v>
+        <v>185</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="C93" s="1">
         <v>199</v>
       </c>
       <c r="D93" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <v>199</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="C94" s="1">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="D94" s="1">
-        <f t="shared" si="0"/>
-        <v>143.65</v>
+        <f t="shared" ref="D94:D96" si="14">C94-C94*15/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="C95" s="1">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="D95" s="1">
-        <f t="shared" ref="D95:D96" si="12">C95-C95*15/100</f>
-        <v>140.25</v>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>84</v>
+        <v>69</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
       </c>
       <c r="D96" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C97" s="1">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="D97" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f t="shared" si="1"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="C98" s="1">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D98" s="1">
-        <f t="shared" si="0"/>
-        <v>165.75</v>
+        <f>C98-C98*15/100</f>
+        <v>157.25</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="C99" s="1">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="D99" s="1">
-        <f t="shared" si="0"/>
-        <v>131.75</v>
+        <f>C99-C99*15/100</f>
+        <v>148.75</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="C100" s="1">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D100" s="1">
-        <f t="shared" si="0"/>
-        <v>160.65</v>
+        <f>C100-C100*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>109</v>
+        <v>69</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="C101" s="1">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D101" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>C101-C101*15/100</f>
+        <v>127.5</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>107</v>
+        <v>69</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>124</v>
       </c>
       <c r="C102" s="1">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D102" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>118.15</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>108</v>
+        <v>69</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
       </c>
       <c r="D103" s="1">
-        <f t="shared" ref="D103" si="13">C103-C103*15/100</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>97</v>
+        <v>69</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="C104" s="1">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="D104" s="1">
         <f>C104-C104*15/100</f>
-        <v>187</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>98</v>
+        <v>70</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C105" s="1">
+        <v>220</v>
+      </c>
+      <c r="D105" s="1">
+        <f t="shared" ref="D105:D113" si="15">C105-C105*15/100</f>
         <v>187</v>
-      </c>
-      <c r="D105" s="1">
-        <f>C105-C105*15/100</f>
-        <v>158.94999999999999</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C106" s="1">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D106" s="1">
-        <f>C106-C106*15/100</f>
-        <v>169.15</v>
+        <f t="shared" si="15"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="C107" s="1">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D107" s="1">
-        <f>C107-C107*15/100</f>
-        <v>157.25</v>
+        <f t="shared" si="15"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>57</v>
+        <v>70</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C108" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D108" s="1">
-        <f>C108-C108*15/100</f>
-        <v>169.15</v>
+        <f t="shared" si="15"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="C109" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" ref="D109:D111" si="14">C109-C109*15/100</f>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
       </c>
       <c r="D110" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
       </c>
       <c r="D111" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C112" s="1">
-        <v>199</v>
+        <v>375</v>
       </c>
       <c r="D112" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f t="shared" si="15"/>
+        <v>318.75</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>101</v>
+        <v>70</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="C113" s="1">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="D113" s="1">
-        <f>C113-C113*15/100</f>
-        <v>157.25</v>
+        <f t="shared" si="15"/>
+        <v>127.5</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>102</v>
+        <v>70</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C114" s="1">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="D114" s="1">
-        <f>C114-C114*15/100</f>
-        <v>148.75</v>
+        <f t="shared" ref="D114" si="16">C114-C114*15/100</f>
+        <v>169.15</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="C115" s="1">
         <v>199</v>
@@ -2607,945 +2561,720 @@
     </row>
     <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C116" s="1">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D116" s="1">
         <f>C116-C116*15/100</f>
-        <v>127.5</v>
+        <v>126.65</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>141</v>
+        <v>70</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C117" s="1">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="D117" s="1">
-        <f t="shared" si="0"/>
-        <v>118.15</v>
+        <f t="shared" si="1"/>
+        <v>152.15</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="C118" s="1">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D118" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="C119" s="1">
         <v>175</v>
       </c>
       <c r="D119" s="1">
-        <f>C119-C119*15/100</f>
+        <f t="shared" ref="D119:D124" si="17">C119-C119*15/100</f>
         <v>148.75</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="C120" s="1">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="D120" s="1">
-        <f t="shared" ref="D120:D128" si="15">C120-C120*15/100</f>
-        <v>187</v>
+        <f t="shared" si="17"/>
+        <v>199.75</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="C121" s="1">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D121" s="1">
-        <f t="shared" si="15"/>
-        <v>160.65</v>
+        <f t="shared" si="17"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="C122" s="1">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="D122" s="1">
-        <f t="shared" si="15"/>
-        <v>160.65</v>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C123" s="1">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="D123" s="1">
-        <f t="shared" si="15"/>
-        <v>157.25</v>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>57</v>
+        <v>71</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="C124" s="1">
         <v>199</v>
       </c>
       <c r="D124" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>169.15</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C125" s="1">
         <v>0</v>
       </c>
       <c r="D125" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="D125:D127" si="18">C125-C125*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C126" s="1">
         <v>0</v>
       </c>
       <c r="D126" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="C127" s="1">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="D127" s="1">
-        <f t="shared" si="15"/>
-        <v>318.75</v>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="C128" s="1">
         <v>150</v>
       </c>
       <c r="D128" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="1"/>
         <v>127.5</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>95</v>
+        <v>71</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="C129" s="1">
         <v>199</v>
       </c>
       <c r="D129" s="1">
-        <f t="shared" ref="D129" si="16">C129-C129*15/100</f>
+        <f t="shared" si="1"/>
         <v>169.15</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C130" s="1">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="D130" s="1">
-        <f>C130-C130*15/100</f>
-        <v>169.15</v>
+        <f t="shared" ref="D130:D136" si="19">C130-C130*15/100</f>
+        <v>182.75</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="C131" s="1">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="D131" s="1">
-        <f>C131-C131*15/100</f>
-        <v>126.65</v>
+        <f t="shared" si="19"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="C132" s="1">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D132" s="1">
-        <f t="shared" si="0"/>
-        <v>152.15</v>
+        <f t="shared" si="19"/>
+        <v>160.65</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="C133" s="1">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="D133" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f>C133-C133*15/100</f>
+        <v>126.65</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="C134" s="1">
         <v>175</v>
       </c>
       <c r="D134" s="1">
-        <f t="shared" ref="D134:D139" si="17">C134-C134*15/100</f>
+        <f t="shared" si="19"/>
         <v>148.75</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B135" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B135" s="7" t="s">
         <v>122</v>
       </c>
       <c r="C135" s="1">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="D135" s="1">
-        <f t="shared" si="17"/>
-        <v>199.75</v>
+        <f t="shared" si="19"/>
+        <v>153</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>137</v>
+        <v>72</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C136" s="1">
-        <v>199</v>
+        <v>285</v>
       </c>
       <c r="D136" s="1">
-        <f t="shared" si="17"/>
-        <v>169.15</v>
+        <f t="shared" si="19"/>
+        <v>242.25</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C137" s="1">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="D137" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>233.75</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>89</v>
+        <v>72</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C138" s="1">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="D138" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>203.15</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>90</v>
+        <v>72</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="C139" s="1">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="D139" s="1">
-        <f t="shared" si="17"/>
-        <v>169.15</v>
+        <f t="shared" si="1"/>
+        <v>147.9</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>109</v>
+        <v>72</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="C140" s="1">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D140" s="1">
-        <f t="shared" ref="D140:D142" si="18">C140-C140*15/100</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>157.25</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>107</v>
+        <v>72</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="C141" s="1">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="D141" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>C141-C141*15/100</f>
+        <v>220.15</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>108</v>
+        <v>72</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="C142" s="1">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="D142" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>C142-C142*15/100</f>
+        <v>136</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C143" s="1">
-        <v>150</v>
+        <v>249</v>
       </c>
       <c r="D143" s="1">
-        <f t="shared" si="0"/>
-        <v>127.5</v>
+        <f t="shared" si="1"/>
+        <v>211.65</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="C144" s="1">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="D144" s="1">
-        <f t="shared" si="0"/>
-        <v>169.15</v>
+        <f t="shared" ref="D144:D163" si="20">C144-C144*15/100</f>
+        <v>185.3</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="C145" s="1">
-        <v>215</v>
+        <v>265</v>
       </c>
       <c r="D145" s="1">
-        <f t="shared" ref="D145:D151" si="19">C145-C145*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="20"/>
+        <v>225.25</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>134</v>
+        <v>74</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="C146" s="1">
-        <v>189</v>
+        <v>270</v>
       </c>
       <c r="D146" s="1">
-        <f t="shared" si="19"/>
-        <v>160.65</v>
+        <f t="shared" ref="D146:D147" si="21">C146-C146*15/100</f>
+        <v>229.5</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>135</v>
+        <v>74</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="C147" s="1">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="D147" s="1">
-        <f t="shared" si="19"/>
-        <v>160.65</v>
+        <f t="shared" si="21"/>
+        <v>225.25</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>147</v>
+        <v>74</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="C148" s="1">
-        <v>149</v>
+        <v>285</v>
       </c>
       <c r="D148" s="1">
-        <f>C148-C148*15/100</f>
-        <v>126.65</v>
+        <f t="shared" si="20"/>
+        <v>242.25</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B149" s="7" t="s">
-        <v>140</v>
+        <v>74</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="C149" s="1">
-        <v>175</v>
+        <v>340</v>
       </c>
       <c r="D149" s="1">
-        <f t="shared" si="19"/>
-        <v>148.75</v>
+        <f t="shared" si="20"/>
+        <v>289</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>139</v>
+        <v>74</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="C150" s="1">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="D150" s="1">
-        <f t="shared" si="19"/>
-        <v>153</v>
+        <f t="shared" si="20"/>
+        <v>182.75</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C151" s="1">
-        <v>285</v>
+        <v>55</v>
+      </c>
+      <c r="C151">
+        <v>299</v>
       </c>
       <c r="D151" s="1">
-        <f t="shared" si="19"/>
-        <v>242.25</v>
+        <f>C151-C151*15/100</f>
+        <v>254.15</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C152" s="1">
-        <v>275</v>
+        <v>56</v>
+      </c>
+      <c r="C152">
+        <v>230</v>
       </c>
       <c r="D152" s="1">
-        <f t="shared" si="0"/>
-        <v>233.75</v>
+        <f t="shared" si="20"/>
+        <v>195.5</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C153" s="1">
-        <v>239</v>
+        <v>57</v>
+      </c>
+      <c r="C153">
+        <v>325</v>
       </c>
       <c r="D153" s="1">
-        <f t="shared" si="0"/>
-        <v>203.15</v>
+        <f>C153-C153*15/100</f>
+        <v>276.25</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C154" s="1">
-        <v>174</v>
+        <v>74</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C154">
+        <v>199</v>
       </c>
       <c r="D154" s="1">
-        <f t="shared" si="0"/>
-        <v>147.9</v>
+        <f t="shared" si="20"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C155" s="1">
-        <v>185</v>
+        <v>74</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C155">
+        <v>445</v>
       </c>
       <c r="D155" s="1">
-        <f t="shared" si="0"/>
-        <v>157.25</v>
+        <f t="shared" si="20"/>
+        <v>378.25</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B156" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C156" s="1">
-        <v>259</v>
+        <v>74</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C156">
+        <v>400</v>
       </c>
       <c r="D156" s="1">
-        <f>C156-C156*15/100</f>
-        <v>220.15</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+        <f t="shared" si="20"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B157" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C157" s="1">
-        <v>160</v>
+        <v>74</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C157">
+        <v>285</v>
       </c>
       <c r="D157" s="1">
         <f>C157-C157*15/100</f>
-        <v>136</v>
+        <v>242.25</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="C158" s="1">
-        <v>249</v>
+        <v>278</v>
       </c>
       <c r="D158" s="1">
-        <f t="shared" si="0"/>
-        <v>211.65</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+        <f t="shared" si="20"/>
+        <v>236.3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C159" s="1">
-        <v>218</v>
+        <v>405</v>
       </c>
       <c r="D159" s="1">
-        <f t="shared" ref="D159:D178" si="20">C159-C159*15/100</f>
-        <v>185.3</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+        <f t="shared" si="20"/>
+        <v>344.25</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C160" s="1">
-        <v>265</v>
+        <v>0</v>
+      </c>
+      <c r="C160">
+        <v>360</v>
       </c>
       <c r="D160" s="1">
         <f t="shared" si="20"/>
-        <v>225.25</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C161" s="1">
-        <v>270</v>
+        <v>1</v>
+      </c>
+      <c r="C161">
+        <v>249</v>
       </c>
       <c r="D161" s="1">
-        <f t="shared" ref="D161:D162" si="21">C161-C161*15/100</f>
-        <v>229.5</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A162" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C162" s="1">
-        <v>265</v>
-      </c>
-      <c r="D162" s="1">
-        <f t="shared" si="21"/>
-        <v>225.25</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A163" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C163" s="1">
-        <v>285</v>
-      </c>
-      <c r="D163" s="1">
-        <f t="shared" si="20"/>
-        <v>242.25</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A164" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C164" s="1">
-        <v>340</v>
-      </c>
-      <c r="D164" s="1">
-        <f t="shared" si="20"/>
-        <v>289</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A165" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C165" s="1">
-        <v>215</v>
-      </c>
-      <c r="D165" s="1">
-        <f t="shared" si="20"/>
-        <v>182.75</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A166" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C166">
-        <v>299</v>
-      </c>
-      <c r="D166" s="1">
-        <f>C166-C166*15/100</f>
-        <v>254.15</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A167" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C167">
-        <v>230</v>
-      </c>
-      <c r="D167" s="1">
-        <f t="shared" si="20"/>
-        <v>195.5</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A168" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C168">
-        <v>325</v>
-      </c>
-      <c r="D168" s="1">
-        <f>C168-C168*15/100</f>
-        <v>276.25</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A169" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C169">
-        <v>199</v>
-      </c>
-      <c r="D169" s="1">
-        <f t="shared" si="20"/>
-        <v>169.15</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A170" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C170">
-        <v>445</v>
-      </c>
-      <c r="D170" s="1">
-        <f t="shared" si="20"/>
-        <v>378.25</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A171" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C171">
-        <v>400</v>
-      </c>
-      <c r="D171" s="1">
-        <f t="shared" si="20"/>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C172">
-        <v>285</v>
-      </c>
-      <c r="D172" s="1">
-        <f>C172-C172*15/100</f>
-        <v>242.25</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A173" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C173" s="1">
-        <v>278</v>
-      </c>
-      <c r="D173" s="1">
-        <f t="shared" si="20"/>
-        <v>236.3</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C174" s="1">
-        <v>405</v>
-      </c>
-      <c r="D174" s="1">
-        <f t="shared" si="20"/>
-        <v>344.25</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C175">
-        <v>360</v>
-      </c>
-      <c r="D175" s="1">
-        <f t="shared" si="20"/>
-        <v>306</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C176">
-        <v>249</v>
-      </c>
-      <c r="D176" s="1">
         <f t="shared" si="20"/>
         <v>211.65</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B177" s="1" t="s">
+    <row r="162" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C177">
+      <c r="C162">
         <v>329</v>
       </c>
-      <c r="D177" s="1">
+      <c r="D162" s="1">
         <f t="shared" si="20"/>
         <v>279.64999999999998</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C178">
+    <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C163">
         <v>275</v>
       </c>
-      <c r="D178" s="1">
+      <c r="D163" s="1">
         <f t="shared" si="20"/>
         <v>233.75</v>
       </c>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33A35B6-2831-48BD-A15D-AD2946BACAB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64729D76-7980-4AF6-B2F6-20D0C0F69BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الورقة1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="139">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -271,9 +271,6 @@
   </si>
   <si>
     <t xml:space="preserve"> إمتحان علوم  ⬅️ </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> المعاصر رياضيات  ⬅️ </t>
   </si>
   <si>
     <t xml:space="preserve"> المعاصر انجليزي ⬅️  </t>
@@ -443,6 +440,21 @@
   </si>
   <si>
     <t xml:space="preserve"> بيت باي بيت إنجليزي  ⬅️ خلصان </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر رياضيات  ⬅️ 175</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر بلس ⬅️  205</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر بلس ⬅️</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر بلس ⬅️  199</t>
+  </si>
+  <si>
+    <t>نحو وصرف أضواء 229</t>
   </si>
 </sst>
 </file>
@@ -515,7 +527,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -617,8 +629,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D163" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:D163" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D164" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:D164" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="كتب التأسيس" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="(نحو تأسيس سليم  أجزاء 1و2و3) _x000a_(نحو  سندباد أجزاء 1و2و3) _x000a_( نور البيان انجليزي جزئين - عربي) _x000a_( ذا بيست ستارت بوك 1و2) _x000a_( توب فونكس1و2 - جرامر 1و2و3)  _x000a_( اوكسفورد 5أجزاء)_x000a_(معلم القراءة)_x000a_(نون والقلم)" dataDxfId="1"/>
@@ -832,7 +844,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:D164"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -841,16 +853,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1008,7 +1020,7 @@
         <v>63</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C12" s="1">
         <v>0</v>
@@ -1023,7 +1035,7 @@
         <v>63</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="1">
         <v>255</v>
@@ -1202,14 +1214,14 @@
         <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C25" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D25" s="1">
         <f t="shared" ref="D25" si="3">C25-C25*15/100</f>
-        <v>0</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1217,7 +1229,7 @@
         <v>64</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C26" s="1">
         <v>0</v>
@@ -1322,7 +1334,7 @@
         <v>65</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C33" s="1">
         <v>169</v>
@@ -1382,14 +1394,14 @@
         <v>65</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="C37" s="1">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="D37" s="1">
         <f t="shared" ref="D37" si="4">C37-C37*15/100</f>
-        <v>0</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1397,7 +1409,7 @@
         <v>65</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C38" s="1">
         <v>0</v>
@@ -1532,7 +1544,7 @@
         <v>66</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C47" s="1">
         <v>175</v>
@@ -1547,7 +1559,7 @@
         <v>66</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C48" s="1">
         <v>169</v>
@@ -1577,7 +1589,7 @@
         <v>66</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C50" s="1">
         <v>150</v>
@@ -1607,14 +1619,14 @@
         <v>66</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="C52" s="1">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="D52" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1622,7 +1634,7 @@
         <v>66</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C53" s="1">
         <v>315</v>
@@ -1637,7 +1649,7 @@
         <v>66</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C54" s="1">
         <v>0</v>
@@ -1742,7 +1754,7 @@
         <v>67</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C61" s="1">
         <v>145</v>
@@ -1802,7 +1814,7 @@
         <v>67</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C65" s="1">
         <v>175</v>
@@ -1877,14 +1889,14 @@
         <v>67</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="C70" s="1">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="D70" s="1">
         <f t="shared" ref="D70" si="10">C70-C70*15/100</f>
-        <v>0</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1892,7 +1904,7 @@
         <v>67</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C71" s="1">
         <v>295</v>
@@ -1907,7 +1919,7 @@
         <v>67</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C72" s="1">
         <v>0</v>
@@ -2117,14 +2129,14 @@
         <v>68</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="C86" s="1">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="D86" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2132,7 +2144,7 @@
         <v>68</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C87" s="1">
         <v>0</v>
@@ -2147,7 +2159,7 @@
         <v>68</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C88" s="1">
         <v>0</v>
@@ -2162,7 +2174,7 @@
         <v>69</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C89" s="1">
         <v>220</v>
@@ -2177,7 +2189,7 @@
         <v>69</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C90" s="1">
         <v>187</v>
@@ -2191,7 +2203,7 @@
         <v>69</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C91" s="1">
         <v>199</v>
@@ -2206,7 +2218,7 @@
         <v>69</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C92" s="1">
         <v>185</v>
@@ -2220,7 +2232,7 @@
         <v>69</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C93" s="1">
         <v>199</v>
@@ -2234,14 +2246,14 @@
         <v>69</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="C94" s="1">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="D94" s="1">
         <f t="shared" ref="D94:D96" si="14">C94-C94*15/100</f>
-        <v>0</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2249,7 +2261,7 @@
         <v>69</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C95" s="1">
         <v>0</v>
@@ -2264,7 +2276,7 @@
         <v>69</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
@@ -2279,7 +2291,7 @@
         <v>69</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C97" s="1">
         <v>199</v>
@@ -2294,7 +2306,7 @@
         <v>69</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C98" s="1">
         <v>185</v>
@@ -2309,7 +2321,7 @@
         <v>69</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C99" s="1">
         <v>175</v>
@@ -2324,7 +2336,7 @@
         <v>69</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C100" s="1">
         <v>199</v>
@@ -2339,7 +2351,7 @@
         <v>69</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C101" s="1">
         <v>150</v>
@@ -2354,7 +2366,7 @@
         <v>69</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C102" s="1">
         <v>139</v>
@@ -2369,7 +2381,7 @@
         <v>69</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
@@ -2384,7 +2396,7 @@
         <v>69</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C104" s="1">
         <v>175</v>
@@ -2444,7 +2456,7 @@
         <v>70</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C108" s="1">
         <v>185</v>
@@ -2474,7 +2486,7 @@
         <v>70</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
@@ -2489,7 +2501,7 @@
         <v>70</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
@@ -2504,7 +2516,7 @@
         <v>70</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C112" s="1">
         <v>375</v>
@@ -2519,7 +2531,7 @@
         <v>70</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C113" s="1">
         <v>150</v>
@@ -2534,7 +2546,7 @@
         <v>70</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C114" s="1">
         <v>199</v>
@@ -2564,7 +2576,7 @@
         <v>70</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C116" s="1">
         <v>149</v>
@@ -2579,7 +2591,7 @@
         <v>70</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C117" s="1">
         <v>179</v>
@@ -2594,7 +2606,7 @@
         <v>70</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C118" s="1">
         <v>185</v>
@@ -2609,7 +2621,7 @@
         <v>70</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C119" s="1">
         <v>175</v>
@@ -2624,7 +2636,7 @@
         <v>71</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C120" s="1">
         <v>235</v>
@@ -2639,7 +2651,7 @@
         <v>71</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C121" s="1">
         <v>199</v>
@@ -2669,14 +2681,14 @@
         <v>71</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="C123" s="1">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D123" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2684,7 +2696,7 @@
         <v>71</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C124" s="1">
         <v>199</v>
@@ -2699,14 +2711,14 @@
         <v>71</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="C125" s="1">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="D125" s="1">
         <f t="shared" ref="D125:D127" si="18">C125-C125*15/100</f>
-        <v>0</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2714,7 +2726,7 @@
         <v>71</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C126" s="1">
         <v>0</v>
@@ -2729,7 +2741,7 @@
         <v>71</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C127" s="1">
         <v>0</v>
@@ -2744,7 +2756,7 @@
         <v>71</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C128" s="1">
         <v>150</v>
@@ -2759,7 +2771,7 @@
         <v>71</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C129" s="1">
         <v>199</v>
@@ -2774,7 +2786,7 @@
         <v>71</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C130" s="1">
         <v>215</v>
@@ -2789,7 +2801,7 @@
         <v>71</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C131" s="1">
         <v>189</v>
@@ -2804,7 +2816,7 @@
         <v>71</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C132" s="1">
         <v>189</v>
@@ -2819,7 +2831,7 @@
         <v>71</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C133" s="1">
         <v>149</v>
@@ -2834,7 +2846,7 @@
         <v>71</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C134" s="1">
         <v>175</v>
@@ -2849,7 +2861,7 @@
         <v>72</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C135" s="1">
         <v>180</v>
@@ -2864,7 +2876,7 @@
         <v>72</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C136" s="1">
         <v>285</v>
@@ -2879,7 +2891,7 @@
         <v>72</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C137" s="1">
         <v>275</v>
@@ -2894,7 +2906,7 @@
         <v>72</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C138" s="1">
         <v>239</v>
@@ -2909,7 +2921,7 @@
         <v>72</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C139" s="1">
         <v>174</v>
@@ -2924,7 +2936,7 @@
         <v>72</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C140" s="1">
         <v>185</v>
@@ -2939,7 +2951,7 @@
         <v>72</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C141" s="1">
         <v>259</v>
@@ -2954,7 +2966,7 @@
         <v>72</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C142" s="1">
         <v>160</v>
@@ -2969,7 +2981,7 @@
         <v>73</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C143" s="1">
         <v>249</v>
@@ -3014,7 +3026,7 @@
         <v>74</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C146" s="1">
         <v>270</v>
@@ -3029,7 +3041,7 @@
         <v>74</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C147" s="1">
         <v>265</v>
@@ -3179,7 +3191,7 @@
         <v>74</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C157">
         <v>285</v>
@@ -3269,7 +3281,7 @@
         <v>74</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C163">
         <v>275</v>
@@ -3277,6 +3289,21 @@
       <c r="D163" s="1">
         <f t="shared" si="20"/>
         <v>233.75</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C164">
+        <v>229</v>
+      </c>
+      <c r="D164" s="1">
+        <f>C164-C164*15/100</f>
+        <v>194.65</v>
       </c>
     </row>
   </sheetData>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64729D76-7980-4AF6-B2F6-20D0C0F69BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188C8CE2-223E-415D-B721-85CE4C2EB829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="138">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -256,9 +256,6 @@
   </si>
   <si>
     <t>🎓 الثانوية العامة (تالتة ثانوي)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> أضواء علوم ⬅️ </t>
   </si>
   <si>
     <t xml:space="preserve"> إمتحان عربي  ⬅️ 220 .00</t>
@@ -853,16 +850,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1020,7 +1017,7 @@
         <v>63</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C12" s="1">
         <v>0</v>
@@ -1035,7 +1032,7 @@
         <v>63</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="1">
         <v>255</v>
@@ -1214,7 +1211,7 @@
         <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C25" s="1">
         <v>199</v>
@@ -1229,7 +1226,7 @@
         <v>64</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C26" s="1">
         <v>0</v>
@@ -1334,7 +1331,7 @@
         <v>65</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C33" s="1">
         <v>169</v>
@@ -1394,7 +1391,7 @@
         <v>65</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C37" s="1">
         <v>205</v>
@@ -1409,7 +1406,7 @@
         <v>65</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C38" s="1">
         <v>0</v>
@@ -1544,7 +1541,7 @@
         <v>66</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C47" s="1">
         <v>175</v>
@@ -1559,7 +1556,7 @@
         <v>66</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C48" s="1">
         <v>169</v>
@@ -1589,7 +1586,7 @@
         <v>66</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C50" s="1">
         <v>150</v>
@@ -1619,7 +1616,7 @@
         <v>66</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C52" s="1">
         <v>205</v>
@@ -1634,7 +1631,7 @@
         <v>66</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C53" s="1">
         <v>315</v>
@@ -1649,7 +1646,7 @@
         <v>66</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C54" s="1">
         <v>0</v>
@@ -1754,7 +1751,7 @@
         <v>67</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C61" s="1">
         <v>145</v>
@@ -1814,7 +1811,7 @@
         <v>67</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C65" s="1">
         <v>175</v>
@@ -1889,7 +1886,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C70" s="1">
         <v>205</v>
@@ -1904,7 +1901,7 @@
         <v>67</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C71" s="1">
         <v>295</v>
@@ -1919,7 +1916,7 @@
         <v>67</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C72" s="1">
         <v>0</v>
@@ -2054,14 +2051,14 @@
         <v>68</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="C81" s="1">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D81" s="1">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2129,7 +2126,7 @@
         <v>68</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C86" s="1">
         <v>205</v>
@@ -2144,7 +2141,7 @@
         <v>68</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C87" s="1">
         <v>0</v>
@@ -2159,7 +2156,7 @@
         <v>68</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C88" s="1">
         <v>0</v>
@@ -2174,7 +2171,7 @@
         <v>69</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C89" s="1">
         <v>220</v>
@@ -2189,7 +2186,7 @@
         <v>69</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C90" s="1">
         <v>187</v>
@@ -2203,7 +2200,7 @@
         <v>69</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C91" s="1">
         <v>199</v>
@@ -2218,7 +2215,7 @@
         <v>69</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C92" s="1">
         <v>185</v>
@@ -2232,7 +2229,7 @@
         <v>69</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C93" s="1">
         <v>199</v>
@@ -2246,7 +2243,7 @@
         <v>69</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C94" s="1">
         <v>205</v>
@@ -2261,7 +2258,7 @@
         <v>69</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C95" s="1">
         <v>0</v>
@@ -2276,7 +2273,7 @@
         <v>69</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
@@ -2291,7 +2288,7 @@
         <v>69</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C97" s="1">
         <v>199</v>
@@ -2306,7 +2303,7 @@
         <v>69</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C98" s="1">
         <v>185</v>
@@ -2321,7 +2318,7 @@
         <v>69</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C99" s="1">
         <v>175</v>
@@ -2336,7 +2333,7 @@
         <v>69</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C100" s="1">
         <v>199</v>
@@ -2351,7 +2348,7 @@
         <v>69</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C101" s="1">
         <v>150</v>
@@ -2366,7 +2363,7 @@
         <v>69</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C102" s="1">
         <v>139</v>
@@ -2381,7 +2378,7 @@
         <v>69</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
@@ -2396,7 +2393,7 @@
         <v>69</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C104" s="1">
         <v>175</v>
@@ -2411,7 +2408,7 @@
         <v>70</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C105" s="1">
         <v>220</v>
@@ -2426,7 +2423,7 @@
         <v>70</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C106" s="1">
         <v>189</v>
@@ -2441,7 +2438,7 @@
         <v>70</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C107" s="1">
         <v>189</v>
@@ -2456,7 +2453,7 @@
         <v>70</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C108" s="1">
         <v>185</v>
@@ -2486,7 +2483,7 @@
         <v>70</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
@@ -2501,7 +2498,7 @@
         <v>70</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
@@ -2516,7 +2513,7 @@
         <v>70</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C112" s="1">
         <v>375</v>
@@ -2531,7 +2528,7 @@
         <v>70</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C113" s="1">
         <v>150</v>
@@ -2546,7 +2543,7 @@
         <v>70</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C114" s="1">
         <v>199</v>
@@ -2576,7 +2573,7 @@
         <v>70</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C116" s="1">
         <v>149</v>
@@ -2591,7 +2588,7 @@
         <v>70</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C117" s="1">
         <v>179</v>
@@ -2606,7 +2603,7 @@
         <v>70</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C118" s="1">
         <v>185</v>
@@ -2621,7 +2618,7 @@
         <v>70</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C119" s="1">
         <v>175</v>
@@ -2636,7 +2633,7 @@
         <v>71</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C120" s="1">
         <v>235</v>
@@ -2651,7 +2648,7 @@
         <v>71</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C121" s="1">
         <v>199</v>
@@ -2666,7 +2663,7 @@
         <v>71</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C122" s="1">
         <v>0</v>
@@ -2681,7 +2678,7 @@
         <v>71</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C123" s="1">
         <v>175</v>
@@ -2696,7 +2693,7 @@
         <v>71</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C124" s="1">
         <v>199</v>
@@ -2711,7 +2708,7 @@
         <v>71</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C125" s="1">
         <v>205</v>
@@ -2726,7 +2723,7 @@
         <v>71</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C126" s="1">
         <v>0</v>
@@ -2741,7 +2738,7 @@
         <v>71</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C127" s="1">
         <v>0</v>
@@ -2756,7 +2753,7 @@
         <v>71</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C128" s="1">
         <v>150</v>
@@ -2771,7 +2768,7 @@
         <v>71</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C129" s="1">
         <v>199</v>
@@ -2786,7 +2783,7 @@
         <v>71</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C130" s="1">
         <v>215</v>
@@ -2801,7 +2798,7 @@
         <v>71</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C131" s="1">
         <v>189</v>
@@ -2816,7 +2813,7 @@
         <v>71</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C132" s="1">
         <v>189</v>
@@ -2831,7 +2828,7 @@
         <v>71</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C133" s="1">
         <v>149</v>
@@ -2846,7 +2843,7 @@
         <v>71</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C134" s="1">
         <v>175</v>
@@ -2861,7 +2858,7 @@
         <v>72</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C135" s="1">
         <v>180</v>
@@ -2876,7 +2873,7 @@
         <v>72</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C136" s="1">
         <v>285</v>
@@ -2891,7 +2888,7 @@
         <v>72</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C137" s="1">
         <v>275</v>
@@ -2906,7 +2903,7 @@
         <v>72</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C138" s="1">
         <v>239</v>
@@ -2921,7 +2918,7 @@
         <v>72</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C139" s="1">
         <v>174</v>
@@ -2936,7 +2933,7 @@
         <v>72</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C140" s="1">
         <v>185</v>
@@ -2951,7 +2948,7 @@
         <v>72</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C141" s="1">
         <v>259</v>
@@ -2966,7 +2963,7 @@
         <v>72</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C142" s="1">
         <v>160</v>
@@ -2981,7 +2978,7 @@
         <v>73</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C143" s="1">
         <v>249</v>
@@ -3026,7 +3023,7 @@
         <v>74</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C146" s="1">
         <v>270</v>
@@ -3041,7 +3038,7 @@
         <v>74</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C147" s="1">
         <v>265</v>
@@ -3191,7 +3188,7 @@
         <v>74</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C157">
         <v>285</v>
@@ -3281,7 +3278,7 @@
         <v>74</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C163">
         <v>275</v>
@@ -3296,7 +3293,7 @@
         <v>74</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C164">
         <v>229</v>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188C8CE2-223E-415D-B721-85CE4C2EB829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76C41F9-5176-4FD9-B761-C7AB5C41A12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="137">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -437,9 +437,6 @@
   </si>
   <si>
     <t xml:space="preserve"> بيت باي بيت إنجليزي  ⬅️ خلصان </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> المعاصر رياضيات  ⬅️ 175</t>
   </si>
   <si>
     <t xml:space="preserve"> المعاصر بلس ⬅️  205</t>
@@ -1038,7 +1035,7 @@
         <v>255</v>
       </c>
       <c r="D13" s="1">
-        <v>255</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1211,7 +1208,7 @@
         <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C25" s="1">
         <v>199</v>
@@ -1391,7 +1388,7 @@
         <v>65</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C37" s="1">
         <v>205</v>
@@ -1616,7 +1613,7 @@
         <v>66</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C52" s="1">
         <v>205</v>
@@ -1637,8 +1634,7 @@
         <v>315</v>
       </c>
       <c r="D53" s="1">
-        <f>C53-C53*15/100</f>
-        <v>267.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1886,7 +1882,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C70" s="1">
         <v>205</v>
@@ -1907,8 +1903,7 @@
         <v>295</v>
       </c>
       <c r="D71" s="1">
-        <f t="shared" ref="D71:D77" si="11">C71-C71*15/100</f>
-        <v>250.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1922,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D72" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="D71:D77" si="11">C72-C72*15/100</f>
         <v>0</v>
       </c>
     </row>
@@ -2126,7 +2121,7 @@
         <v>68</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C86" s="1">
         <v>205</v>
@@ -2192,7 +2187,7 @@
         <v>187</v>
       </c>
       <c r="D90" s="1">
-        <v>187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2221,7 +2216,7 @@
         <v>185</v>
       </c>
       <c r="D92" s="1">
-        <v>185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2235,7 +2230,7 @@
         <v>199</v>
       </c>
       <c r="D93" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2243,7 +2238,7 @@
         <v>69</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C94" s="1">
         <v>205</v>
@@ -2369,8 +2364,7 @@
         <v>139</v>
       </c>
       <c r="D102" s="1">
-        <f t="shared" si="1"/>
-        <v>118.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2483,7 +2477,7 @@
         <v>70</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
@@ -2534,8 +2528,7 @@
         <v>150</v>
       </c>
       <c r="D113" s="1">
-        <f t="shared" si="15"/>
-        <v>127.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2678,14 +2671,14 @@
         <v>71</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="C123" s="1">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D123" s="1">
         <f t="shared" si="17"/>
-        <v>148.75</v>
+        <v>157.25</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2708,7 +2701,7 @@
         <v>71</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C125" s="1">
         <v>205</v>
@@ -3293,7 +3286,7 @@
         <v>74</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C164">
         <v>229</v>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76C41F9-5176-4FD9-B761-C7AB5C41A12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16ED3377-5E79-48AE-88BF-05299796B60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="135">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -42,9 +42,6 @@
     <t>الأضواء عربي (اسئلة) ⬅️ 329</t>
   </si>
   <si>
-    <t xml:space="preserve">  سلاح دين ⬅️ 145</t>
-  </si>
-  <si>
     <t xml:space="preserve"> سلاح التلميذ عربي ⬅️ 180</t>
   </si>
   <si>
@@ -60,9 +57,6 @@
     <t xml:space="preserve"> أضواء عربي ⬅️ 159</t>
   </si>
   <si>
-    <t xml:space="preserve"> أضواء دين ⬅️ 129 </t>
-  </si>
-  <si>
     <t xml:space="preserve"> أضواء جيم إنجليزي ⬅️ 165</t>
   </si>
   <si>
@@ -84,9 +78,6 @@
     <t xml:space="preserve"> أضواء رياضيات ⬅️ 159</t>
   </si>
   <si>
-    <t xml:space="preserve"> أضواء دين ⬅️ 139</t>
-  </si>
-  <si>
     <t xml:space="preserve"> سلاح التلميذ عربي ⬅️ 190 </t>
   </si>
   <si>
@@ -120,9 +111,6 @@
     <t xml:space="preserve"> سلاح التلميذ علوم ⬅️ 170</t>
   </si>
   <si>
-    <t xml:space="preserve"> سلاح التلميذ دين ⬅️ 145 </t>
-  </si>
-  <si>
     <t xml:space="preserve"> أضواء عربي ⬅️ 195 </t>
   </si>
   <si>
@@ -273,9 +261,6 @@
     <t xml:space="preserve"> المعاصر انجليزي ⬅️  </t>
   </si>
   <si>
-    <t xml:space="preserve"> الاضواء دين ⬅️ 149 </t>
-  </si>
-  <si>
     <t xml:space="preserve"> أضواء دراسات  ⬅️ 179 </t>
   </si>
   <si>
@@ -303,9 +288,6 @@
     <t xml:space="preserve"> أضواء دراسات  ⬅️ 175 </t>
   </si>
   <si>
-    <t xml:space="preserve"> سلاح التلميذ دين  ⬅️ 145 </t>
-  </si>
-  <si>
     <t xml:space="preserve"> أضواء عربي  ⬅️ 215</t>
   </si>
   <si>
@@ -319,9 +301,6 @@
   </si>
   <si>
     <t xml:space="preserve"> المعاصر ساينس لغات ⬅️ </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> المعاصر بلس ⬅️  </t>
   </si>
   <si>
     <t>كتب التأسيس</t>
@@ -373,9 +352,6 @@
     <t xml:space="preserve"> بيت باي بيت  ⬅️ 150 </t>
   </si>
   <si>
-    <t xml:space="preserve"> سلاح التلميذ دين ⬅️145</t>
-  </si>
-  <si>
     <t>المعاصر انجليزي (جزء اول)  ⬅️ 285</t>
   </si>
   <si>
@@ -421,9 +397,6 @@
     <t xml:space="preserve"> إمتحان جغرافيا (اسئله) ⬅️ 270</t>
   </si>
   <si>
-    <t xml:space="preserve"> أضواء دين  ⬅️ 149</t>
-  </si>
-  <si>
     <t xml:space="preserve">امتحان عربي ⬅️ 259 </t>
   </si>
   <si>
@@ -442,13 +415,34 @@
     <t xml:space="preserve"> المعاصر بلس ⬅️  205</t>
   </si>
   <si>
-    <t xml:space="preserve"> المعاصر بلس ⬅️</t>
-  </si>
-  <si>
     <t xml:space="preserve"> المعاصر بلس ⬅️  199</t>
   </si>
   <si>
     <t>نحو وصرف أضواء 229</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر بلس ⬅️ 205</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء دين ⬅️ خلصان </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أضواء دين ⬅️ خلصان</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ دين ⬅️ خلصان </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ دين ⬅️ خلصان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  سلاح دين ⬅️ خلصان</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سلاح التلميذ دين  ⬅️ خلصان </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> الاضواء دين ⬅️ خلصان </t>
   </si>
 </sst>
 </file>
@@ -847,24 +841,24 @@
   <sheetData>
     <row r="1" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1">
         <v>180</v>
@@ -876,10 +870,10 @@
     </row>
     <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1">
         <v>170</v>
@@ -891,10 +885,10 @@
     </row>
     <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1">
         <v>130</v>
@@ -906,10 +900,10 @@
     </row>
     <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1">
         <v>149</v>
@@ -921,10 +915,10 @@
     </row>
     <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1">
         <v>159</v>
@@ -936,25 +930,24 @@
     </row>
     <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>128</v>
       </c>
       <c r="C7" s="1">
         <v>129</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" si="1"/>
-        <v>109.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1">
         <v>165</v>
@@ -966,10 +959,10 @@
     </row>
     <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" s="1">
         <v>165</v>
@@ -981,10 +974,10 @@
     </row>
     <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1">
         <v>135</v>
@@ -996,10 +989,10 @@
     </row>
     <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" s="1">
         <v>175</v>
@@ -1011,25 +1004,25 @@
     </row>
     <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="C12" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C13" s="1">
         <v>255</v>
@@ -1040,10 +1033,10 @@
     </row>
     <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1">
         <v>165</v>
@@ -1055,10 +1048,10 @@
     </row>
     <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="1">
         <v>180</v>
@@ -1070,10 +1063,10 @@
     </row>
     <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="1">
         <v>170</v>
@@ -1085,10 +1078,10 @@
     </row>
     <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>140</v>
@@ -1100,10 +1093,10 @@
     </row>
     <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C18" s="1">
         <v>159</v>
@@ -1115,10 +1108,10 @@
     </row>
     <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="1">
         <v>159</v>
@@ -1130,25 +1123,24 @@
     </row>
     <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="C20" s="1">
         <v>139</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="1"/>
-        <v>118.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C21" s="1">
         <v>165</v>
@@ -1160,10 +1152,10 @@
     </row>
     <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C22" s="1">
         <v>165</v>
@@ -1175,10 +1167,10 @@
     </row>
     <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1">
         <v>135</v>
@@ -1190,10 +1182,10 @@
     </row>
     <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C24" s="1">
         <v>175</v>
@@ -1205,10 +1197,10 @@
     </row>
     <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C25" s="1">
         <v>199</v>
@@ -1220,10 +1212,10 @@
     </row>
     <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C26" s="1">
         <v>0</v>
@@ -1235,10 +1227,10 @@
     </row>
     <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>190</v>
@@ -1250,10 +1242,10 @@
     </row>
     <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C28" s="1">
         <v>175</v>
@@ -1265,10 +1257,10 @@
     </row>
     <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C29" s="1">
         <v>140</v>
@@ -1280,10 +1272,10 @@
     </row>
     <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1">
         <v>169</v>
@@ -1295,10 +1287,10 @@
     </row>
     <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C31" s="1">
         <v>165</v>
@@ -1310,25 +1302,24 @@
     </row>
     <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="C32" s="1">
         <v>139</v>
       </c>
       <c r="D32" s="1">
-        <f t="shared" si="1"/>
-        <v>118.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C33" s="1">
         <v>169</v>
@@ -1340,10 +1331,10 @@
     </row>
     <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C34" s="1">
         <v>185</v>
@@ -1355,10 +1346,10 @@
     </row>
     <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C35" s="1">
         <v>140</v>
@@ -1370,10 +1361,10 @@
     </row>
     <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C36" s="1">
         <v>189</v>
@@ -1385,10 +1376,10 @@
     </row>
     <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C37" s="1">
         <v>205</v>
@@ -1400,10 +1391,10 @@
     </row>
     <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C38" s="1">
         <v>0</v>
@@ -1415,10 +1406,10 @@
     </row>
     <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C39" s="1">
         <v>215</v>
@@ -1430,10 +1421,10 @@
     </row>
     <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C40" s="1">
         <v>185</v>
@@ -1445,10 +1436,10 @@
     </row>
     <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C41" s="1">
         <v>190</v>
@@ -1460,10 +1451,10 @@
     </row>
     <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C42" s="1">
         <v>170</v>
@@ -1475,25 +1466,24 @@
     </row>
     <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="C43" s="1">
         <v>145</v>
       </c>
       <c r="D43" s="1">
-        <f t="shared" ref="D43" si="6">C43-C43*15/100</f>
-        <v>123.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C44" s="1">
         <v>195</v>
@@ -1505,10 +1495,10 @@
     </row>
     <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C45" s="1">
         <v>165</v>
@@ -1520,10 +1510,10 @@
     </row>
     <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C46" s="1">
         <v>159</v>
@@ -1535,25 +1525,25 @@
     </row>
     <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C47" s="1">
         <v>175</v>
       </c>
       <c r="D47" s="1">
-        <f t="shared" ref="D47" si="7">C47-C47*15/100</f>
+        <f t="shared" ref="D47" si="6">C47-C47*15/100</f>
         <v>148.75</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C48" s="1">
         <v>169</v>
@@ -1565,10 +1555,10 @@
     </row>
     <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C49" s="1">
         <v>185</v>
@@ -1580,10 +1570,10 @@
     </row>
     <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C50" s="1">
         <v>150</v>
@@ -1595,10 +1585,10 @@
     </row>
     <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C51" s="1">
         <v>189</v>
@@ -1610,10 +1600,10 @@
     </row>
     <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C52" s="1">
         <v>205</v>
@@ -1625,10 +1615,10 @@
     </row>
     <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C53" s="1">
         <v>315</v>
@@ -1639,25 +1629,25 @@
     </row>
     <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C54" s="1">
         <v>0</v>
       </c>
       <c r="D54" s="1">
-        <f t="shared" ref="D54" si="8">C54-C54*15/100</f>
+        <f t="shared" ref="D54" si="7">C54-C54*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C55" s="1">
         <v>169</v>
@@ -1669,10 +1659,10 @@
     </row>
     <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C56" s="1">
         <v>205</v>
@@ -1684,10 +1674,10 @@
     </row>
     <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C57" s="1">
         <v>215</v>
@@ -1699,10 +1689,10 @@
     </row>
     <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C58" s="1">
         <v>185</v>
@@ -1714,10 +1704,10 @@
     </row>
     <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C59" s="1">
         <v>190</v>
@@ -1729,10 +1719,10 @@
     </row>
     <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C60" s="1">
         <v>170</v>
@@ -1744,25 +1734,24 @@
     </row>
     <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C61" s="1">
         <v>145</v>
       </c>
       <c r="D61" s="1">
-        <f t="shared" ref="D61" si="9">C61-C61*15/100</f>
-        <v>123.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C62" s="1">
         <v>195</v>
@@ -1774,10 +1763,10 @@
     </row>
     <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C63" s="1">
         <v>159</v>
@@ -1789,10 +1778,10 @@
     </row>
     <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C64" s="1">
         <v>169</v>
@@ -1804,10 +1793,10 @@
     </row>
     <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C65" s="1">
         <v>175</v>
@@ -1819,10 +1808,10 @@
     </row>
     <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C66" s="1">
         <v>179</v>
@@ -1834,10 +1823,10 @@
     </row>
     <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C67" s="1">
         <v>187</v>
@@ -1849,10 +1838,10 @@
     </row>
     <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C68" s="1">
         <v>155</v>
@@ -1864,10 +1853,10 @@
     </row>
     <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C69" s="1">
         <v>189</v>
@@ -1879,25 +1868,25 @@
     </row>
     <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C70" s="1">
         <v>205</v>
       </c>
       <c r="D70" s="1">
-        <f t="shared" ref="D70" si="10">C70-C70*15/100</f>
+        <f t="shared" ref="D70" si="8">C70-C70*15/100</f>
         <v>174.25</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C71" s="1">
         <v>295</v>
@@ -1908,100 +1897,99 @@
     </row>
     <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C72" s="1">
         <v>0</v>
       </c>
       <c r="D72" s="1">
-        <f t="shared" ref="D71:D77" si="11">C72-C72*15/100</f>
+        <f t="shared" ref="D72:D77" si="9">C72-C72*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C73" s="1">
         <v>220</v>
       </c>
       <c r="D73" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>187</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C74" s="1">
         <v>190</v>
       </c>
       <c r="D74" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>161.5</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C75" s="1">
         <v>185</v>
       </c>
       <c r="D75" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>157.25</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C76" s="1">
         <v>170</v>
       </c>
       <c r="D76" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>144.5</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="C77" s="1">
         <v>145</v>
       </c>
       <c r="D77" s="1">
-        <f t="shared" si="11"/>
-        <v>123.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C78" s="1">
         <v>199</v>
@@ -2013,10 +2001,10 @@
     </row>
     <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C79" s="1">
         <v>169</v>
@@ -2028,40 +2016,40 @@
     </row>
     <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C80" s="1">
         <v>165</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" ref="D80:D81" si="12">C80-C80*15/100</f>
+        <f t="shared" ref="D80:D81" si="10">C80-C80*15/100</f>
         <v>140.25</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C81" s="1">
         <v>175</v>
       </c>
       <c r="D81" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>148.75</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C82" s="1">
         <v>179</v>
@@ -2073,10 +2061,10 @@
     </row>
     <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C83" s="1">
         <v>195</v>
@@ -2088,10 +2076,10 @@
     </row>
     <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C84" s="1">
         <v>155</v>
@@ -2103,10 +2091,10 @@
     </row>
     <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C85" s="1">
         <v>189</v>
@@ -2118,10 +2106,10 @@
     </row>
     <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C86" s="1">
         <v>205</v>
@@ -2133,10 +2121,10 @@
     </row>
     <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C87" s="1">
         <v>0</v>
@@ -2148,25 +2136,25 @@
     </row>
     <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C88" s="1">
         <v>0</v>
       </c>
       <c r="D88" s="1">
-        <f t="shared" ref="D88" si="13">C88-C88*15/100</f>
+        <f t="shared" ref="D88" si="11">C88-C88*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C89" s="1">
         <v>220</v>
@@ -2178,10 +2166,10 @@
     </row>
     <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C90" s="1">
         <v>187</v>
@@ -2192,10 +2180,10 @@
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C91" s="1">
         <v>199</v>
@@ -2207,10 +2195,10 @@
     </row>
     <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C92" s="1">
         <v>185</v>
@@ -2221,10 +2209,10 @@
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C93" s="1">
         <v>199</v>
@@ -2235,55 +2223,55 @@
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C94" s="1">
         <v>205</v>
       </c>
       <c r="D94" s="1">
-        <f t="shared" ref="D94:D96" si="14">C94-C94*15/100</f>
+        <f t="shared" ref="D94:D96" si="12">C94-C94*15/100</f>
         <v>174.25</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C95" s="1">
         <v>0</v>
       </c>
       <c r="D95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
       </c>
       <c r="D96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C97" s="1">
         <v>199</v>
@@ -2295,10 +2283,10 @@
     </row>
     <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C98" s="1">
         <v>185</v>
@@ -2310,10 +2298,10 @@
     </row>
     <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C99" s="1">
         <v>175</v>
@@ -2325,10 +2313,10 @@
     </row>
     <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C100" s="1">
         <v>199</v>
@@ -2340,10 +2328,10 @@
     </row>
     <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C101" s="1">
         <v>150</v>
@@ -2355,10 +2343,10 @@
     </row>
     <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C102" s="1">
         <v>139</v>
@@ -2369,10 +2357,10 @@
     </row>
     <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
@@ -2384,10 +2372,10 @@
     </row>
     <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C104" s="1">
         <v>175</v>
@@ -2399,130 +2387,130 @@
     </row>
     <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C105" s="1">
         <v>220</v>
       </c>
       <c r="D105" s="1">
-        <f t="shared" ref="D105:D113" si="15">C105-C105*15/100</f>
+        <f t="shared" ref="D105:D112" si="13">C105-C105*15/100</f>
         <v>187</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C106" s="1">
         <v>189</v>
       </c>
       <c r="D106" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>160.65</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C107" s="1">
         <v>189</v>
       </c>
       <c r="D107" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>160.65</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C108" s="1">
         <v>185</v>
       </c>
       <c r="D108" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>157.25</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C109" s="1">
         <v>199</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>169.15</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C110" s="1">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="D110" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>174.25</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
       </c>
       <c r="D111" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C112" s="1">
         <v>375</v>
       </c>
       <c r="D112" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>318.75</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C113" s="1">
         <v>150</v>
@@ -2533,25 +2521,25 @@
     </row>
     <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C114" s="1">
         <v>199</v>
       </c>
       <c r="D114" s="1">
-        <f t="shared" ref="D114" si="16">C114-C114*15/100</f>
+        <f t="shared" ref="D114" si="14">C114-C114*15/100</f>
         <v>169.15</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C115" s="1">
         <v>199</v>
@@ -2563,25 +2551,24 @@
     </row>
     <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="C116" s="1">
         <v>149</v>
       </c>
       <c r="D116" s="1">
-        <f>C116-C116*15/100</f>
-        <v>126.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C117" s="1">
         <v>179</v>
@@ -2593,10 +2580,10 @@
     </row>
     <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C118" s="1">
         <v>185</v>
@@ -2608,145 +2595,145 @@
     </row>
     <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C119" s="1">
         <v>175</v>
       </c>
       <c r="D119" s="1">
-        <f t="shared" ref="D119:D124" si="17">C119-C119*15/100</f>
+        <f t="shared" ref="D119:D124" si="15">C119-C119*15/100</f>
         <v>148.75</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C120" s="1">
         <v>235</v>
       </c>
       <c r="D120" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>199.75</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C121" s="1">
         <v>199</v>
       </c>
       <c r="D121" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>169.15</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C122" s="1">
         <v>0</v>
       </c>
       <c r="D122" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C123" s="1">
         <v>185</v>
       </c>
       <c r="D123" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>157.25</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C124" s="1">
         <v>199</v>
       </c>
       <c r="D124" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>169.15</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C125" s="1">
         <v>205</v>
       </c>
       <c r="D125" s="1">
-        <f t="shared" ref="D125:D127" si="18">C125-C125*15/100</f>
+        <f t="shared" ref="D125:D127" si="16">C125-C125*15/100</f>
         <v>174.25</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C126" s="1">
         <v>0</v>
       </c>
       <c r="D126" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C127" s="1">
         <v>0</v>
       </c>
       <c r="D127" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C128" s="1">
         <v>150</v>
@@ -2758,10 +2745,10 @@
     </row>
     <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C129" s="1">
         <v>199</v>
@@ -2773,115 +2760,114 @@
     </row>
     <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C130" s="1">
         <v>215</v>
       </c>
       <c r="D130" s="1">
-        <f t="shared" ref="D130:D136" si="19">C130-C130*15/100</f>
+        <f t="shared" ref="D130:D136" si="17">C130-C130*15/100</f>
         <v>182.75</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C131" s="1">
         <v>189</v>
       </c>
       <c r="D131" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>160.65</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C132" s="1">
         <v>189</v>
       </c>
       <c r="D132" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>160.65</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C133" s="1">
         <v>149</v>
       </c>
       <c r="D133" s="1">
-        <f>C133-C133*15/100</f>
-        <v>126.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C134" s="1">
         <v>175</v>
       </c>
       <c r="D134" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>148.75</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C135" s="1">
         <v>180</v>
       </c>
       <c r="D135" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>153</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C136" s="1">
         <v>285</v>
       </c>
       <c r="D136" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>242.25</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C137" s="1">
         <v>275</v>
@@ -2893,10 +2879,10 @@
     </row>
     <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C138" s="1">
         <v>239</v>
@@ -2908,10 +2894,10 @@
     </row>
     <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C139" s="1">
         <v>174</v>
@@ -2923,10 +2909,10 @@
     </row>
     <row r="140" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C140" s="1">
         <v>185</v>
@@ -2938,10 +2924,10 @@
     </row>
     <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C141" s="1">
         <v>259</v>
@@ -2953,10 +2939,10 @@
     </row>
     <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C142" s="1">
         <v>160</v>
@@ -2968,10 +2954,10 @@
     </row>
     <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C143" s="1">
         <v>249</v>
@@ -2983,115 +2969,115 @@
     </row>
     <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C144" s="1">
         <v>218</v>
       </c>
       <c r="D144" s="1">
-        <f t="shared" ref="D144:D163" si="20">C144-C144*15/100</f>
+        <f t="shared" ref="D144:D163" si="18">C144-C144*15/100</f>
         <v>185.3</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C145" s="1">
         <v>265</v>
       </c>
       <c r="D145" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>225.25</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C146" s="1">
         <v>270</v>
       </c>
       <c r="D146" s="1">
-        <f t="shared" ref="D146:D147" si="21">C146-C146*15/100</f>
+        <f t="shared" ref="D146:D147" si="19">C146-C146*15/100</f>
         <v>229.5</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C147" s="1">
         <v>265</v>
       </c>
       <c r="D147" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>225.25</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C148" s="1">
         <v>285</v>
       </c>
       <c r="D148" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>242.25</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C149" s="1">
         <v>340</v>
       </c>
       <c r="D149" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>289</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C150" s="1">
         <v>215</v>
       </c>
       <c r="D150" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>182.75</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C151">
         <v>299</v>
@@ -3103,25 +3089,25 @@
     </row>
     <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C152">
         <v>230</v>
       </c>
       <c r="D152" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>195.5</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C153">
         <v>325</v>
@@ -3133,55 +3119,55 @@
     </row>
     <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C154">
         <v>199</v>
       </c>
       <c r="D154" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>169.15</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C155">
         <v>445</v>
       </c>
       <c r="D155" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>378.25</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C156">
         <v>400</v>
       </c>
       <c r="D156" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>340</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C157">
         <v>285</v>
@@ -3193,37 +3179,37 @@
     </row>
     <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C158" s="1">
         <v>278</v>
       </c>
       <c r="D158" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>236.3</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C159" s="1">
         <v>405</v>
       </c>
       <c r="D159" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>344.25</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>0</v>
@@ -3232,13 +3218,13 @@
         <v>360</v>
       </c>
       <c r="D160" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>306</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>1</v>
@@ -3247,13 +3233,13 @@
         <v>249</v>
       </c>
       <c r="D161" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>211.65</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>2</v>
@@ -3262,31 +3248,31 @@
         <v>329</v>
       </c>
       <c r="D162" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>279.64999999999998</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C163">
         <v>275</v>
       </c>
       <c r="D163" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>233.75</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C164">
         <v>229</v>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16ED3377-5E79-48AE-88BF-05299796B60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E287304B-0AA0-4677-B075-8F6870D3DB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="134">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -72,9 +72,6 @@
     <t xml:space="preserve"> المعاصر رياضه بالعربي ⬅️ 165</t>
   </si>
   <si>
-    <t xml:space="preserve"> سلاح التلميذ دين ⬅️ 140 </t>
-  </si>
-  <si>
     <t xml:space="preserve"> أضواء رياضيات ⬅️ 159</t>
   </si>
   <si>
@@ -165,9 +162,6 @@
     <t xml:space="preserve"> ستيب أهيد إنجليزي ⬅️ 195 </t>
   </si>
   <si>
-    <t xml:space="preserve"> المعاصر انجليزي ⬅️ 199 </t>
-  </si>
-  <si>
     <t xml:space="preserve"> الاضواء عربي ⬅️ 199 </t>
   </si>
   <si>
@@ -253,9 +247,6 @@
   </si>
   <si>
     <t xml:space="preserve"> إمتحان علوم  ⬅️ 189</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> إمتحان علوم  ⬅️ </t>
   </si>
   <si>
     <t xml:space="preserve"> المعاصر انجليزي ⬅️  </t>
@@ -443,6 +434,12 @@
   </si>
   <si>
     <t xml:space="preserve"> الاضواء دين ⬅️ خلصان </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان علوم  ⬅️ خلصان</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر إنجليزي ⬅️ خلصان</t>
   </si>
 </sst>
 </file>
@@ -841,21 +838,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="102" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -870,7 +867,7 @@
     </row>
     <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>4</v>
@@ -885,7 +882,7 @@
     </row>
     <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -900,7 +897,7 @@
     </row>
     <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
@@ -915,7 +912,7 @@
     </row>
     <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -930,10 +927,10 @@
     </row>
     <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C7" s="1">
         <v>129</v>
@@ -944,7 +941,7 @@
     </row>
     <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
@@ -959,7 +956,7 @@
     </row>
     <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
@@ -974,7 +971,7 @@
     </row>
     <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
@@ -989,7 +986,7 @@
     </row>
     <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>11</v>
@@ -1004,10 +1001,10 @@
     </row>
     <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C12" s="1">
         <v>199</v>
@@ -1019,10 +1016,10 @@
     </row>
     <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C13" s="1">
         <v>255</v>
@@ -1033,7 +1030,7 @@
     </row>
     <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
@@ -1048,7 +1045,7 @@
     </row>
     <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>3</v>
@@ -1063,7 +1060,7 @@
     </row>
     <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>4</v>
@@ -1078,25 +1075,24 @@
     </row>
     <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="C17" s="1">
         <v>140</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="2"/>
-        <v>119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>159</v>
@@ -1108,7 +1104,7 @@
     </row>
     <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
@@ -1123,10 +1119,10 @@
     </row>
     <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C20" s="1">
         <v>139</v>
@@ -1137,7 +1133,7 @@
     </row>
     <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
@@ -1152,7 +1148,7 @@
     </row>
     <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>9</v>
@@ -1167,7 +1163,7 @@
     </row>
     <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>10</v>
@@ -1182,7 +1178,7 @@
     </row>
     <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>11</v>
@@ -1197,10 +1193,10 @@
     </row>
     <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C25" s="1">
         <v>199</v>
@@ -1212,10 +1208,10 @@
     </row>
     <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C26" s="1">
         <v>0</v>
@@ -1227,10 +1223,10 @@
     </row>
     <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" s="1">
         <v>190</v>
@@ -1242,10 +1238,10 @@
     </row>
     <row r="28" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>175</v>
@@ -1257,25 +1253,24 @@
     </row>
     <row r="29" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="C29" s="1">
         <v>140</v>
       </c>
       <c r="D29" s="1">
-        <f>C29-C29*15/100</f>
-        <v>119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C30" s="1">
         <v>169</v>
@@ -1287,10 +1282,10 @@
     </row>
     <row r="31" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C31" s="1">
         <v>165</v>
@@ -1302,10 +1297,10 @@
     </row>
     <row r="32" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C32" s="1">
         <v>139</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="33" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C33" s="1">
         <v>169</v>
@@ -1331,10 +1326,10 @@
     </row>
     <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C34" s="1">
         <v>185</v>
@@ -1346,10 +1341,10 @@
     </row>
     <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C35" s="1">
         <v>140</v>
@@ -1361,10 +1356,10 @@
     </row>
     <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C36" s="1">
         <v>189</v>
@@ -1376,10 +1371,10 @@
     </row>
     <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C37" s="1">
         <v>205</v>
@@ -1391,10 +1386,10 @@
     </row>
     <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C38" s="1">
         <v>0</v>
@@ -1406,10 +1401,10 @@
     </row>
     <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C39" s="1">
         <v>215</v>
@@ -1421,10 +1416,10 @@
     </row>
     <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C40" s="1">
         <v>185</v>
@@ -1436,10 +1431,10 @@
     </row>
     <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C41" s="1">
         <v>190</v>
@@ -1451,10 +1446,10 @@
     </row>
     <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C42" s="1">
         <v>170</v>
@@ -1466,10 +1461,10 @@
     </row>
     <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C43" s="1">
         <v>145</v>
@@ -1480,10 +1475,10 @@
     </row>
     <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="1">
         <v>195</v>
@@ -1495,10 +1490,10 @@
     </row>
     <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="1">
         <v>165</v>
@@ -1510,10 +1505,10 @@
     </row>
     <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="1">
         <v>159</v>
@@ -1525,10 +1520,10 @@
     </row>
     <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C47" s="1">
         <v>175</v>
@@ -1540,10 +1535,10 @@
     </row>
     <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C48" s="1">
         <v>169</v>
@@ -1555,10 +1550,10 @@
     </row>
     <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C49" s="1">
         <v>185</v>
@@ -1570,10 +1565,10 @@
     </row>
     <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C50" s="1">
         <v>150</v>
@@ -1585,10 +1580,10 @@
     </row>
     <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C51" s="1">
         <v>189</v>
@@ -1600,10 +1595,10 @@
     </row>
     <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C52" s="1">
         <v>205</v>
@@ -1615,10 +1610,10 @@
     </row>
     <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C53" s="1">
         <v>315</v>
@@ -1629,10 +1624,10 @@
     </row>
     <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C54" s="1">
         <v>0</v>
@@ -1644,10 +1639,10 @@
     </row>
     <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C55" s="1">
         <v>169</v>
@@ -1659,10 +1654,10 @@
     </row>
     <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C56" s="1">
         <v>205</v>
@@ -1674,10 +1669,10 @@
     </row>
     <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C57" s="1">
         <v>215</v>
@@ -1689,10 +1684,10 @@
     </row>
     <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C58" s="1">
         <v>185</v>
@@ -1704,10 +1699,10 @@
     </row>
     <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C59" s="1">
         <v>190</v>
@@ -1719,10 +1714,10 @@
     </row>
     <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C60" s="1">
         <v>170</v>
@@ -1734,10 +1729,10 @@
     </row>
     <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C61" s="1">
         <v>145</v>
@@ -1748,10 +1743,10 @@
     </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C62" s="1">
         <v>195</v>
@@ -1763,10 +1758,10 @@
     </row>
     <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C63" s="1">
         <v>159</v>
@@ -1778,10 +1773,10 @@
     </row>
     <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C64" s="1">
         <v>169</v>
@@ -1793,10 +1788,10 @@
     </row>
     <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C65" s="1">
         <v>175</v>
@@ -1808,10 +1803,10 @@
     </row>
     <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C66" s="1">
         <v>179</v>
@@ -1823,10 +1818,10 @@
     </row>
     <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C67" s="1">
         <v>187</v>
@@ -1838,10 +1833,10 @@
     </row>
     <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C68" s="1">
         <v>155</v>
@@ -1853,25 +1848,24 @@
     </row>
     <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="C69" s="1">
         <v>189</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" si="1"/>
-        <v>160.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C70" s="1">
         <v>205</v>
@@ -1883,10 +1877,10 @@
     </row>
     <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C71" s="1">
         <v>295</v>
@@ -1897,25 +1891,25 @@
     </row>
     <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C72" s="1">
         <v>0</v>
       </c>
       <c r="D72" s="1">
-        <f t="shared" ref="D72:D77" si="9">C72-C72*15/100</f>
+        <f t="shared" ref="D72:D76" si="9">C72-C72*15/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C73" s="1">
         <v>220</v>
@@ -1927,10 +1921,10 @@
     </row>
     <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C74" s="1">
         <v>190</v>
@@ -1942,10 +1936,10 @@
     </row>
     <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C75" s="1">
         <v>185</v>
@@ -1957,10 +1951,10 @@
     </row>
     <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C76" s="1">
         <v>170</v>
@@ -1972,10 +1966,10 @@
     </row>
     <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C77" s="1">
         <v>145</v>
@@ -1986,10 +1980,10 @@
     </row>
     <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C78" s="1">
         <v>199</v>
@@ -2001,10 +1995,10 @@
     </row>
     <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C79" s="1">
         <v>169</v>
@@ -2016,10 +2010,10 @@
     </row>
     <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C80" s="1">
         <v>165</v>
@@ -2031,10 +2025,10 @@
     </row>
     <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C81" s="1">
         <v>175</v>
@@ -2046,10 +2040,10 @@
     </row>
     <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C82" s="1">
         <v>179</v>
@@ -2061,10 +2055,10 @@
     </row>
     <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C83" s="1">
         <v>195</v>
@@ -2076,10 +2070,10 @@
     </row>
     <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C84" s="1">
         <v>155</v>
@@ -2091,25 +2085,24 @@
     </row>
     <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="C85" s="1">
         <v>189</v>
       </c>
       <c r="D85" s="1">
-        <f t="shared" si="1"/>
-        <v>160.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C86" s="1">
         <v>205</v>
@@ -2121,10 +2114,10 @@
     </row>
     <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C87" s="1">
         <v>0</v>
@@ -2136,10 +2129,10 @@
     </row>
     <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C88" s="1">
         <v>0</v>
@@ -2151,10 +2144,10 @@
     </row>
     <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C89" s="1">
         <v>220</v>
@@ -2166,10 +2159,10 @@
     </row>
     <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C90" s="1">
         <v>187</v>
@@ -2180,25 +2173,24 @@
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="C91" s="1">
         <v>199</v>
       </c>
       <c r="D91" s="1">
-        <f>C91-C91*15/100</f>
-        <v>169.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C92" s="1">
         <v>185</v>
@@ -2209,10 +2201,10 @@
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C93" s="1">
         <v>199</v>
@@ -2223,10 +2215,10 @@
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C94" s="1">
         <v>205</v>
@@ -2238,10 +2230,10 @@
     </row>
     <row r="95" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C95" s="1">
         <v>0</v>
@@ -2253,10 +2245,10 @@
     </row>
     <row r="96" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
@@ -2268,10 +2260,10 @@
     </row>
     <row r="97" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C97" s="1">
         <v>199</v>
@@ -2283,10 +2275,10 @@
     </row>
     <row r="98" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C98" s="1">
         <v>185</v>
@@ -2298,10 +2290,10 @@
     </row>
     <row r="99" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C99" s="1">
         <v>175</v>
@@ -2313,10 +2305,10 @@
     </row>
     <row r="100" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C100" s="1">
         <v>199</v>
@@ -2328,10 +2320,10 @@
     </row>
     <row r="101" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C101" s="1">
         <v>150</v>
@@ -2343,10 +2335,10 @@
     </row>
     <row r="102" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C102" s="1">
         <v>139</v>
@@ -2357,10 +2349,10 @@
     </row>
     <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
@@ -2372,10 +2364,10 @@
     </row>
     <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C104" s="1">
         <v>175</v>
@@ -2387,10 +2379,10 @@
     </row>
     <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C105" s="1">
         <v>220</v>
@@ -2402,10 +2394,10 @@
     </row>
     <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C106" s="1">
         <v>189</v>
@@ -2417,10 +2409,10 @@
     </row>
     <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C107" s="1">
         <v>189</v>
@@ -2432,10 +2424,10 @@
     </row>
     <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C108" s="1">
         <v>185</v>
@@ -2447,25 +2439,24 @@
     </row>
     <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="C109" s="1">
         <v>199</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" si="13"/>
-        <v>169.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C110" s="1">
         <v>205</v>
@@ -2477,10 +2468,10 @@
     </row>
     <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
@@ -2492,10 +2483,10 @@
     </row>
     <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C112" s="1">
         <v>375</v>
@@ -2507,10 +2498,10 @@
     </row>
     <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C113" s="1">
         <v>150</v>
@@ -2521,10 +2512,10 @@
     </row>
     <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C114" s="1">
         <v>199</v>
@@ -2536,10 +2527,10 @@
     </row>
     <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C115" s="1">
         <v>199</v>
@@ -2551,10 +2542,10 @@
     </row>
     <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C116" s="1">
         <v>149</v>
@@ -2565,10 +2556,10 @@
     </row>
     <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C117" s="1">
         <v>179</v>
@@ -2580,10 +2571,10 @@
     </row>
     <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C118" s="1">
         <v>185</v>
@@ -2595,10 +2586,10 @@
     </row>
     <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C119" s="1">
         <v>175</v>
@@ -2610,10 +2601,10 @@
     </row>
     <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C120" s="1">
         <v>235</v>
@@ -2625,10 +2616,10 @@
     </row>
     <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C121" s="1">
         <v>199</v>
@@ -2640,25 +2631,25 @@
     </row>
     <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C122" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D122" s="1">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C123" s="1">
         <v>185</v>
@@ -2670,10 +2661,10 @@
     </row>
     <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C124" s="1">
         <v>199</v>
@@ -2685,10 +2676,10 @@
     </row>
     <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C125" s="1">
         <v>205</v>
@@ -2700,10 +2691,10 @@
     </row>
     <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C126" s="1">
         <v>0</v>
@@ -2715,10 +2706,10 @@
     </row>
     <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C127" s="1">
         <v>0</v>
@@ -2730,10 +2721,10 @@
     </row>
     <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C128" s="1">
         <v>150</v>
@@ -2745,10 +2736,10 @@
     </row>
     <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C129" s="1">
         <v>199</v>
@@ -2760,10 +2751,10 @@
     </row>
     <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C130" s="1">
         <v>215</v>
@@ -2775,10 +2766,10 @@
     </row>
     <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C131" s="1">
         <v>189</v>
@@ -2790,10 +2781,10 @@
     </row>
     <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C132" s="1">
         <v>189</v>
@@ -2805,10 +2796,10 @@
     </row>
     <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C133" s="1">
         <v>149</v>
@@ -2819,10 +2810,10 @@
     </row>
     <row r="134" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C134" s="1">
         <v>175</v>
@@ -2834,10 +2825,10 @@
     </row>
     <row r="135" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C135" s="1">
         <v>180</v>
@@ -2849,10 +2840,10 @@
     </row>
     <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C136" s="1">
         <v>285</v>
@@ -2864,10 +2855,10 @@
     </row>
     <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C137" s="1">
         <v>275</v>
@@ -2879,10 +2870,10 @@
     </row>
     <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C138" s="1">
         <v>239</v>
@@ -2894,10 +2885,10 @@
     </row>
     <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C139" s="1">
         <v>174</v>
@@ -2909,10 +2900,10 @@
     </row>
     <row r="140" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C140" s="1">
         <v>185</v>
@@ -2924,10 +2915,10 @@
     </row>
     <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C141" s="1">
         <v>259</v>
@@ -2939,10 +2930,10 @@
     </row>
     <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C142" s="1">
         <v>160</v>
@@ -2954,10 +2945,10 @@
     </row>
     <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C143" s="1">
         <v>249</v>
@@ -2969,10 +2960,10 @@
     </row>
     <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C144" s="1">
         <v>218</v>
@@ -2984,10 +2975,10 @@
     </row>
     <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C145" s="1">
         <v>265</v>
@@ -2999,10 +2990,10 @@
     </row>
     <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C146" s="1">
         <v>270</v>
@@ -3014,10 +3005,10 @@
     </row>
     <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C147" s="1">
         <v>265</v>
@@ -3029,10 +3020,10 @@
     </row>
     <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C148" s="1">
         <v>285</v>
@@ -3044,10 +3035,10 @@
     </row>
     <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C149" s="1">
         <v>340</v>
@@ -3059,10 +3050,10 @@
     </row>
     <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C150" s="1">
         <v>215</v>
@@ -3074,10 +3065,10 @@
     </row>
     <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C151">
         <v>299</v>
@@ -3089,10 +3080,10 @@
     </row>
     <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C152">
         <v>230</v>
@@ -3104,10 +3095,10 @@
     </row>
     <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C153">
         <v>325</v>
@@ -3119,10 +3110,10 @@
     </row>
     <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C154">
         <v>199</v>
@@ -3134,10 +3125,10 @@
     </row>
     <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C155">
         <v>445</v>
@@ -3149,10 +3140,10 @@
     </row>
     <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C156">
         <v>400</v>
@@ -3164,10 +3155,10 @@
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C157">
         <v>285</v>
@@ -3179,10 +3170,10 @@
     </row>
     <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C158" s="1">
         <v>278</v>
@@ -3194,10 +3185,10 @@
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C159" s="1">
         <v>405</v>
@@ -3209,7 +3200,7 @@
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>0</v>
@@ -3224,7 +3215,7 @@
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>1</v>
@@ -3239,7 +3230,7 @@
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>2</v>
@@ -3254,10 +3245,10 @@
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C163">
         <v>275</v>
@@ -3269,10 +3260,10 @@
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C164">
         <v>229</v>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E287304B-0AA0-4677-B075-8F6870D3DB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02811A17-7865-4D14-886A-05C684E359B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="135">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -391,15 +391,6 @@
     <t xml:space="preserve">امتحان عربي ⬅️ 259 </t>
   </si>
   <si>
-    <t xml:space="preserve"> إمتحان دراسات  ⬅️ خلصان</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> المعاصر رياضيات  ⬅️ خلصان </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> المعاصر انجليزي ⬅️ خلصان </t>
-  </si>
-  <si>
     <t xml:space="preserve"> بيت باي بيت إنجليزي  ⬅️ خلصان </t>
   </si>
   <si>
@@ -440,6 +431,18 @@
   </si>
   <si>
     <t xml:space="preserve"> المعاصر إنجليزي ⬅️ خلصان</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر انجليزي ⬅️ 199 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر رياضيات  ⬅️ بدون خصم </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إمتحان دراسات  ⬅️ بدون خصم</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر انجليزي ⬅️ بدون خصم </t>
   </si>
 </sst>
 </file>
@@ -930,7 +933,7 @@
         <v>57</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C7" s="1">
         <v>129</v>
@@ -1004,7 +1007,7 @@
         <v>57</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C12" s="1">
         <v>199</v>
@@ -1039,7 +1042,7 @@
         <v>165</v>
       </c>
       <c r="D14" s="1">
-        <f t="shared" ref="D14:D17" si="2">C14-C14*15/100</f>
+        <f t="shared" ref="D14:D16" si="2">C14-C14*15/100</f>
         <v>140.25</v>
       </c>
     </row>
@@ -1078,7 +1081,7 @@
         <v>58</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C17" s="1">
         <v>140</v>
@@ -1122,7 +1125,7 @@
         <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C20" s="1">
         <v>139</v>
@@ -1196,7 +1199,7 @@
         <v>58</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C25" s="1">
         <v>199</v>
@@ -1256,7 +1259,7 @@
         <v>59</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C29" s="1">
         <v>140</v>
@@ -1300,7 +1303,7 @@
         <v>59</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C32" s="1">
         <v>139</v>
@@ -1374,7 +1377,7 @@
         <v>59</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C37" s="1">
         <v>205</v>
@@ -1464,7 +1467,7 @@
         <v>60</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C43" s="1">
         <v>145</v>
@@ -1598,7 +1601,7 @@
         <v>60</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C52" s="1">
         <v>205</v>
@@ -1732,7 +1735,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C61" s="1">
         <v>145</v>
@@ -1851,7 +1854,7 @@
         <v>61</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C69" s="1">
         <v>189</v>
@@ -1865,7 +1868,7 @@
         <v>61</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C70" s="1">
         <v>205</v>
@@ -1969,7 +1972,7 @@
         <v>62</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C77" s="1">
         <v>145</v>
@@ -2088,7 +2091,7 @@
         <v>62</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C85" s="1">
         <v>189</v>
@@ -2102,7 +2105,7 @@
         <v>62</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C86" s="1">
         <v>205</v>
@@ -2162,13 +2165,13 @@
         <v>63</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="C90" s="1">
         <v>187</v>
       </c>
       <c r="D90" s="1">
-        <v>0</v>
+        <v>187</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2176,7 +2179,7 @@
         <v>63</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C91" s="1">
         <v>199</v>
@@ -2190,13 +2193,13 @@
         <v>63</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="C92" s="1">
         <v>185</v>
       </c>
       <c r="D92" s="1">
-        <v>0</v>
+        <v>185</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2204,13 +2207,13 @@
         <v>63</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="C93" s="1">
         <v>199</v>
       </c>
       <c r="D93" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2218,13 +2221,13 @@
         <v>63</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C94" s="1">
         <v>205</v>
       </c>
       <c r="D94" s="1">
-        <f t="shared" ref="D94:D96" si="12">C94-C94*15/100</f>
+        <f t="shared" ref="D90:D96" si="12">C94-C94*15/100</f>
         <v>174.25</v>
       </c>
     </row>
@@ -2352,7 +2355,7 @@
         <v>63</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
@@ -2442,13 +2445,14 @@
         <v>64</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C109" s="1">
         <v>199</v>
       </c>
       <c r="D109" s="1">
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>169.15</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2456,7 +2460,7 @@
         <v>64</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C110" s="1">
         <v>205</v>
@@ -2501,7 +2505,7 @@
         <v>64</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C113" s="1">
         <v>150</v>
@@ -2545,7 +2549,7 @@
         <v>64</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C116" s="1">
         <v>149</v>
@@ -2679,7 +2683,7 @@
         <v>65</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C125" s="1">
         <v>205</v>
@@ -3263,7 +3267,7 @@
         <v>68</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C164">
         <v>229</v>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamdi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02811A17-7865-4D14-886A-05C684E359B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6AA556-EF49-465A-90AB-884C044DB496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9630" yWindow="345" windowWidth="12105" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الورقة1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="137">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -319,9 +319,6 @@
   </si>
   <si>
     <t xml:space="preserve"> الأضواء عربي ⬅️ 239</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> الأضواء عربي ⬅️ 249</t>
   </si>
   <si>
     <t>أضواء جيم انجليزي (جزء اول)  ⬅️ 275</t>
@@ -443,6 +440,15 @@
   </si>
   <si>
     <t xml:space="preserve"> المعاصر انجليزي ⬅️ بدون خصم </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر ماث لغات ⬅️ 299</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر انجليزي بكالوريا ⬅️ 340</t>
+  </si>
+  <si>
+    <t>مندليف كيمياء أسئلة 320</t>
   </si>
 </sst>
 </file>
@@ -617,8 +623,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D164" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:D164" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:D165" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:D165" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="كتب التأسيس" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="(نحو تأسيس سليم  أجزاء 1و2و3) _x000a_(نحو  سندباد أجزاء 1و2و3) _x000a_( نور البيان انجليزي جزئين - عربي) _x000a_( ذا بيست ستارت بوك 1و2) _x000a_( توب فونكس1و2 - جرامر 1و2و3)  _x000a_( اوكسفورد 5أجزاء)_x000a_(معلم القراءة)_x000a_(نون والقلم)" dataDxfId="1"/>
@@ -832,7 +838,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D164"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -844,7 +850,7 @@
         <v>87</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>89</v>
@@ -933,7 +939,7 @@
         <v>57</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1">
         <v>129</v>
@@ -1007,7 +1013,7 @@
         <v>57</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="1">
         <v>199</v>
@@ -1022,7 +1028,7 @@
         <v>57</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C13" s="1">
         <v>255</v>
@@ -1081,7 +1087,7 @@
         <v>58</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C17" s="1">
         <v>140</v>
@@ -1125,7 +1131,7 @@
         <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C20" s="1">
         <v>139</v>
@@ -1199,7 +1205,7 @@
         <v>58</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C25" s="1">
         <v>199</v>
@@ -1259,7 +1265,7 @@
         <v>59</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C29" s="1">
         <v>140</v>
@@ -1303,7 +1309,7 @@
         <v>59</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C32" s="1">
         <v>139</v>
@@ -1377,7 +1383,7 @@
         <v>59</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C37" s="1">
         <v>205</v>
@@ -1467,7 +1473,7 @@
         <v>60</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C43" s="1">
         <v>145</v>
@@ -1526,7 +1532,7 @@
         <v>60</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C47" s="1">
         <v>175</v>
@@ -1571,7 +1577,7 @@
         <v>60</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C50" s="1">
         <v>150</v>
@@ -1601,7 +1607,7 @@
         <v>60</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C52" s="1">
         <v>205</v>
@@ -1616,7 +1622,7 @@
         <v>60</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C53" s="1">
         <v>315</v>
@@ -1735,7 +1741,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C61" s="1">
         <v>145</v>
@@ -1794,7 +1800,7 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C65" s="1">
         <v>175</v>
@@ -1854,7 +1860,7 @@
         <v>61</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C69" s="1">
         <v>189</v>
@@ -1868,7 +1874,7 @@
         <v>61</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C70" s="1">
         <v>205</v>
@@ -1883,7 +1889,7 @@
         <v>61</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C71" s="1">
         <v>295</v>
@@ -1972,7 +1978,7 @@
         <v>62</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C77" s="1">
         <v>145</v>
@@ -2031,7 +2037,7 @@
         <v>62</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C81" s="1">
         <v>175</v>
@@ -2091,7 +2097,7 @@
         <v>62</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C85" s="1">
         <v>189</v>
@@ -2105,7 +2111,7 @@
         <v>62</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C86" s="1">
         <v>205</v>
@@ -2120,14 +2126,14 @@
         <v>62</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="C87" s="1">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="D87" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>254.15</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2165,7 +2171,7 @@
         <v>63</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C90" s="1">
         <v>187</v>
@@ -2179,7 +2185,7 @@
         <v>63</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C91" s="1">
         <v>199</v>
@@ -2193,7 +2199,7 @@
         <v>63</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C92" s="1">
         <v>185</v>
@@ -2207,7 +2213,7 @@
         <v>63</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C93" s="1">
         <v>199</v>
@@ -2221,13 +2227,13 @@
         <v>63</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C94" s="1">
         <v>205</v>
       </c>
       <c r="D94" s="1">
-        <f t="shared" ref="D90:D96" si="12">C94-C94*15/100</f>
+        <f t="shared" ref="D94:D96" si="12">C94-C94*15/100</f>
         <v>174.25</v>
       </c>
     </row>
@@ -2341,7 +2347,7 @@
         <v>63</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C102" s="1">
         <v>139</v>
@@ -2355,7 +2361,7 @@
         <v>63</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C103" s="1">
         <v>0</v>
@@ -2370,7 +2376,7 @@
         <v>63</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C104" s="1">
         <v>175</v>
@@ -2445,7 +2451,7 @@
         <v>64</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C109" s="1">
         <v>199</v>
@@ -2460,7 +2466,7 @@
         <v>64</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C110" s="1">
         <v>205</v>
@@ -2490,7 +2496,7 @@
         <v>64</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C112" s="1">
         <v>375</v>
@@ -2505,7 +2511,7 @@
         <v>64</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C113" s="1">
         <v>150</v>
@@ -2549,7 +2555,7 @@
         <v>64</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C116" s="1">
         <v>149</v>
@@ -2593,7 +2599,7 @@
         <v>64</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C119" s="1">
         <v>175</v>
@@ -2608,7 +2614,7 @@
         <v>65</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C120" s="1">
         <v>235</v>
@@ -2623,7 +2629,7 @@
         <v>65</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C121" s="1">
         <v>199</v>
@@ -2683,7 +2689,7 @@
         <v>65</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C125" s="1">
         <v>205</v>
@@ -2773,7 +2779,7 @@
         <v>65</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C131" s="1">
         <v>189</v>
@@ -2788,7 +2794,7 @@
         <v>65</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C132" s="1">
         <v>189</v>
@@ -2803,7 +2809,7 @@
         <v>65</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C133" s="1">
         <v>149</v>
@@ -2817,7 +2823,7 @@
         <v>65</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C134" s="1">
         <v>175</v>
@@ -2832,7 +2838,7 @@
         <v>66</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C135" s="1">
         <v>180</v>
@@ -2847,7 +2853,7 @@
         <v>66</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C136" s="1">
         <v>285</v>
@@ -2922,7 +2928,7 @@
         <v>66</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C141" s="1">
         <v>259</v>
@@ -2937,7 +2943,7 @@
         <v>66</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C142" s="1">
         <v>160</v>
@@ -2952,14 +2958,14 @@
         <v>67</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="C143" s="1">
-        <v>249</v>
+        <v>340</v>
       </c>
       <c r="D143" s="1">
         <f t="shared" si="1"/>
-        <v>211.65</v>
+        <v>289</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -2997,7 +3003,7 @@
         <v>68</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C146" s="1">
         <v>270</v>
@@ -3012,7 +3018,7 @@
         <v>68</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C147" s="1">
         <v>265</v>
@@ -3162,7 +3168,7 @@
         <v>68</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C157">
         <v>285</v>
@@ -3252,7 +3258,7 @@
         <v>68</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C163">
         <v>275</v>
@@ -3267,7 +3273,7 @@
         <v>68</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C164">
         <v>229</v>
@@ -3275,6 +3281,21 @@
       <c r="D164" s="1">
         <f>C164-C164*15/100</f>
         <v>194.65</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C165">
+        <v>320</v>
+      </c>
+      <c r="D165" s="1">
+        <f>C165-C165*15/100</f>
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5407CE68-2BA6-470C-BC71-EA9111CBB406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:10000001_{582E1C95-4790-4A49-91CE-7C5C2B213A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="الورقة1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="220">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -315,16 +316,6 @@
     <t>أضواء جيم انجليزي (جزء اول)  ⬅️ 275</t>
   </si>
   <si>
-    <t>(نحو تأسيس سليم  أجزاء 1و2و3) 
-(نحو  سندباد أجزاء 1و2و3) 
-( نور البيان انجليزي جزئين - عربي) 
-( ذا بيست ستارت بوك 1و2) 
-( توب فونكس1و2 - جرامر 1و2و3)  
-( اوكسفورد 5أجزاء)
-(معلم القراءة)
-(نون والقلم)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> إمتحان عربي  ⬅️ 235</t>
   </si>
   <si>
@@ -599,6 +590,108 @@
   </si>
   <si>
     <t>الإجمالي</t>
+  </si>
+  <si>
+    <t>(معلم القراءة)</t>
+  </si>
+  <si>
+    <t>(نون والقلم)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  (نحو تأسيس سليم  جزاء 1) معلم القراءة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  (نحو تأسيس سليم  جزاء 2) 1و2و3 ابتدائي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  (نحو تأسيس سليم  جزاء 2) 4و5و6 ابتدائي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">( نور البيان انجليزي جزء1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">( نور البيان انجليزي جزء2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">( نور البيان عربي ) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">( نور البيان حساب ) </t>
+  </si>
+  <si>
+    <t>( ذا بيست ستارت بوك 2)  لونج فاولز</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ( ذا بيست ستارت بوك 1) شورت فاولز</t>
+  </si>
+  <si>
+    <t>( توب فونكس 1) شورت فاولز</t>
+  </si>
+  <si>
+    <t>( توب فونكس 2)   لونج فاولز</t>
+  </si>
+  <si>
+    <t>( توب جرامر 1)</t>
+  </si>
+  <si>
+    <t>( توب جرامر 2)</t>
+  </si>
+  <si>
+    <t>( توب جرامر 3)</t>
+  </si>
+  <si>
+    <t>( اوكسفورد 5أجزاء)  المجموعه 450</t>
+  </si>
+  <si>
+    <t>( اوكسفورد الجزء الواحد) 100ج</t>
+  </si>
+  <si>
+    <t>( كتاب المطالعة الأولية)</t>
+  </si>
+  <si>
+    <t>(نحو  سندباد جزاء 1)  نحو 1و2و3 ابتدائي</t>
+  </si>
+  <si>
+    <t>(نحو  سندباد جزاء 2)  نحو 4ب</t>
+  </si>
+  <si>
+    <t>(نحو  سندباد جزاء 3)  نحو 5 ابتدائي</t>
+  </si>
+  <si>
+    <t>(نحو  سندباد جزاء 4)  نحو 6ابتداي</t>
+  </si>
+  <si>
+    <t>معلم القراءة</t>
+  </si>
+  <si>
+    <t>دار الرحمة</t>
+  </si>
+  <si>
+    <t>تأسيس سليم</t>
+  </si>
+  <si>
+    <t>سندباد</t>
+  </si>
+  <si>
+    <t>نور البيان</t>
+  </si>
+  <si>
+    <t>ذا بيست ستارت</t>
+  </si>
+  <si>
+    <t>توب</t>
+  </si>
+  <si>
+    <t>اوكسفورد</t>
+  </si>
+  <si>
+    <t>قران كريم</t>
+  </si>
+  <si>
+    <t>جزء عم</t>
+  </si>
+  <si>
+    <t>العشر الأخير</t>
   </si>
 </sst>
 </file>
@@ -657,7 +750,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -679,6 +772,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1075,8 +1178,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:K168" totalsRowCount="1" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="A1:K167" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:K192" totalsRowCount="1" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:K191" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="الصف" totalsRowLabel="الإجمالي" dataDxfId="19" totalsRowDxfId="9"/>
     <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="بيان الأصناف" dataDxfId="18" totalsRowDxfId="8"/>
@@ -1299,7 +1402,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K168"/>
+  <dimension ref="A1:K192"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -1314,60 +1417,60 @@
   <sheetData>
     <row r="1" spans="1:11" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="D1" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>94</v>
+      <c r="B2" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="C2" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>140</v>
+        <v>209</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>186</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H2" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1378,27 +1481,26 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
+      <c r="A3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>204</v>
       </c>
       <c r="C3" s="1">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1">
-        <f t="shared" ref="D3:D5" si="0">C3-C3*15/100</f>
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>157</v>
+        <v>209</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>204</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="H3" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1409,27 +1511,26 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
+      <c r="A4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>187</v>
       </c>
       <c r="C4" s="1">
-        <v>170</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1">
-        <f t="shared" si="0"/>
-        <v>144.5</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>158</v>
+        <v>210</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="H4" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1440,27 +1541,26 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
+      <c r="A5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>188</v>
       </c>
       <c r="C5" s="1">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="D5" s="1">
-        <f t="shared" si="0"/>
-        <v>110.5</v>
+        <v>175</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>164</v>
+        <v>211</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>188</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="H5" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1471,27 +1571,26 @@
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
+      <c r="A6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>189</v>
       </c>
       <c r="C6" s="1">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="D6" s="1">
-        <f t="shared" ref="D6:D144" si="1">C6-C6*15/100</f>
-        <v>126.65</v>
+        <v>175</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>158</v>
+        <v>211</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>189</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="H6" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1502,27 +1601,26 @@
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
+      <c r="A7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>190</v>
       </c>
       <c r="C7" s="1">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" si="1"/>
-        <v>135.15</v>
+        <v>175</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>157</v>
+        <v>211</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>190</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="H7" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1533,26 +1631,26 @@
       <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>117</v>
+      <c r="A8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>205</v>
       </c>
       <c r="C8" s="1">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>164</v>
+        <v>212</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="H8" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1563,27 +1661,26 @@
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>206</v>
       </c>
       <c r="C9" s="1">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="D9" s="1">
-        <f t="shared" si="1"/>
-        <v>140.25</v>
+        <v>140</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>156</v>
+        <v>212</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H9" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1594,27 +1691,26 @@
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
+      <c r="A10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>207</v>
       </c>
       <c r="C10" s="1">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="D10" s="1">
-        <f t="shared" si="1"/>
-        <v>140.25</v>
+        <v>140</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>156</v>
+        <v>212</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>207</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H10" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1625,27 +1721,26 @@
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
+      <c r="A11" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>208</v>
       </c>
       <c r="C11" s="1">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D11" s="1">
-        <f t="shared" si="1"/>
-        <v>114.75</v>
+        <v>140</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>156</v>
+        <v>212</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>208</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H11" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1656,27 +1751,26 @@
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>11</v>
+      <c r="A12" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>191</v>
       </c>
       <c r="C12" s="1">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="D12" s="1">
-        <f t="shared" si="1"/>
-        <v>148.75</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>156</v>
+        <v>213</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="H12" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1687,27 +1781,26 @@
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>114</v>
+      <c r="A13" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>192</v>
       </c>
       <c r="C13" s="1">
-        <v>199</v>
+        <v>25</v>
       </c>
       <c r="D13" s="1">
-        <f t="shared" si="1"/>
-        <v>169.15</v>
+        <v>25</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>165</v>
+        <v>213</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="H13" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1718,26 +1811,26 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>108</v>
+      <c r="A14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>193</v>
       </c>
       <c r="C14" s="1">
-        <v>255</v>
+        <v>25</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>166</v>
+        <v>213</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>193</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="H14" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1748,27 +1841,26 @@
       <c r="K14" s="1"/>
     </row>
     <row r="15" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>12</v>
+      <c r="A15" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>194</v>
       </c>
       <c r="C15" s="1">
-        <v>165</v>
+        <v>25</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" ref="D15:D17" si="2">C15-C15*15/100</f>
-        <v>140.25</v>
+        <v>25</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>158</v>
+        <v>213</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>194</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="H15" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1779,27 +1871,26 @@
       <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>3</v>
+      <c r="A16" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="C16" s="1">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" si="2"/>
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>157</v>
+        <v>214</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>196</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="H16" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1810,27 +1901,26 @@
       <c r="K16" s="1"/>
     </row>
     <row r="17" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>4</v>
+      <c r="A17" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>195</v>
       </c>
       <c r="C17" s="1">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="2"/>
-        <v>144.5</v>
+        <v>100</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>158</v>
+        <v>214</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>195</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="H17" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1841,26 +1931,26 @@
       <c r="K17" s="1"/>
     </row>
     <row r="18" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>119</v>
+      <c r="A18" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>197</v>
       </c>
       <c r="C18" s="1">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>164</v>
+        <v>215</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>197</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="H18" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1871,27 +1961,26 @@
       <c r="K18" s="1"/>
     </row>
     <row r="19" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>13</v>
+      <c r="A19" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>198</v>
       </c>
       <c r="C19" s="1">
-        <v>159</v>
+        <v>90</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="1"/>
-        <v>135.15</v>
+        <v>90</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>158</v>
+        <v>215</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>198</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="H19" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1902,27 +1991,26 @@
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
+      <c r="A20" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>199</v>
       </c>
       <c r="C20" s="1">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="1"/>
-        <v>135.15</v>
+        <v>95</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>157</v>
+        <v>215</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>199</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="H20" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1933,26 +2021,26 @@
       <c r="K20" s="1"/>
     </row>
     <row r="21" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>118</v>
+      <c r="A21" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>200</v>
       </c>
       <c r="C21" s="1">
+        <v>95</v>
+      </c>
+      <c r="D21" s="1">
+        <v>95</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="H21" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1963,27 +2051,26 @@
       <c r="K21" s="1"/>
     </row>
     <row r="22" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>8</v>
+      <c r="A22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>201</v>
       </c>
       <c r="C22" s="1">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" si="1"/>
-        <v>140.25</v>
+        <v>115</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>156</v>
+        <v>215</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>201</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="H22" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1994,27 +2081,26 @@
       <c r="K22" s="1"/>
     </row>
     <row r="23" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>9</v>
+      <c r="A23" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>202</v>
       </c>
       <c r="C23" s="1">
-        <v>165</v>
+        <v>450</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="1"/>
-        <v>140.25</v>
+        <v>450</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>156</v>
+        <v>216</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>202</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="H23" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2025,27 +2111,26 @@
       <c r="K23" s="1"/>
     </row>
     <row r="24" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>10</v>
+      <c r="A24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="C24" s="1">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" si="1"/>
-        <v>114.75</v>
+        <v>100</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>156</v>
+        <v>216</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>203</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="H24" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2056,29 +2141,28 @@
       <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>11</v>
+      <c r="A25" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>218</v>
       </c>
       <c r="C25" s="1">
-        <v>175</v>
+        <v>5</v>
       </c>
       <c r="D25" s="1">
-        <f t="shared" si="1"/>
-        <v>148.75</v>
+        <v>5</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>156</v>
+        <v>217</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>218</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H25" s="1">
+        <v>139</v>
+      </c>
+      <c r="H25" s="11">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
@@ -2087,29 +2171,28 @@
       <c r="K25" s="1"/>
     </row>
     <row r="26" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>114</v>
+      <c r="A26" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>219</v>
       </c>
       <c r="C26" s="1">
-        <v>199</v>
+        <v>10</v>
       </c>
       <c r="D26" s="1">
-        <f t="shared" ref="D26" si="3">C26-C26*15/100</f>
-        <v>169.15</v>
+        <v>10</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>165</v>
+        <v>217</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>219</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H26" s="1">
+        <v>139</v>
+      </c>
+      <c r="H26" s="11">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
@@ -2119,26 +2202,26 @@
     </row>
     <row r="27" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="C27" s="1">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="D27" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" ref="D16:D31" si="0">C27-C27*15/100</f>
+        <v>153</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H27" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2150,26 +2233,26 @@
     </row>
     <row r="28" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C28" s="1">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="D28" s="1">
-        <f>C28-C28*15/100</f>
-        <v>161.5</v>
+        <f t="shared" si="0"/>
+        <v>144.5</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>157</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H28" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2181,26 +2264,26 @@
     </row>
     <row r="29" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C29" s="1">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="D29" s="1">
-        <f>C29-C29*15/100</f>
-        <v>148.75</v>
+        <f t="shared" si="0"/>
+        <v>110.5</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H29" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2212,25 +2295,26 @@
     </row>
     <row r="30" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="C30" s="1">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>126.65</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>143</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H30" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2242,26 +2326,26 @@
     </row>
     <row r="31" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C31" s="1">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" si="1"/>
-        <v>143.65</v>
+        <f t="shared" si="0"/>
+        <v>135.15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H31" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2273,26 +2357,25 @@
     </row>
     <row r="32" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="C32" s="1">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="D32" s="1">
-        <f t="shared" si="1"/>
-        <v>140.25</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H32" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2304,25 +2387,26 @@
     </row>
     <row r="33" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="C33" s="1">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <f>C33-C33*15/100</f>
+        <v>140.25</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H33" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2334,26 +2418,26 @@
     </row>
     <row r="34" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="C34" s="1">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D34" s="1">
         <f>C34-C34*15/100</f>
-        <v>143.65</v>
+        <v>140.25</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H34" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2365,26 +2449,26 @@
     </row>
     <row r="35" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C35" s="1">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" si="1"/>
-        <v>157.25</v>
+        <f>C35-C35*15/100</f>
+        <v>114.75</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H35" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2396,26 +2480,26 @@
     </row>
     <row r="36" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>168</v>
+        <v>11</v>
       </c>
       <c r="C36" s="1">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="D36" s="1">
-        <f t="shared" si="1"/>
-        <v>119</v>
+        <f>C36-C36*15/100</f>
+        <v>148.75</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H36" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2427,26 +2511,26 @@
     </row>
     <row r="37" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="C37" s="1">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D37" s="1">
         <f>C37-C37*15/100</f>
-        <v>160.65</v>
+        <v>169.15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H37" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2458,26 +2542,25 @@
     </row>
     <row r="38" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C38" s="1">
-        <v>205</v>
+        <v>255</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" ref="D38" si="4">C38-C38*15/100</f>
-        <v>174.25</v>
+        <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>165</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H38" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2489,26 +2572,26 @@
     </row>
     <row r="39" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="C39" s="1">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" ref="D39" si="5">C39-C39*15/100</f>
-        <v>0</v>
+        <f>C39-C39*15/100</f>
+        <v>140.25</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H39" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2520,26 +2603,26 @@
     </row>
     <row r="40" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C40" s="1">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="D40" s="1">
         <f>C40-C40*15/100</f>
-        <v>182.75</v>
+        <v>153</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H40" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2551,26 +2634,26 @@
     </row>
     <row r="41" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C41" s="1">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="D41" s="1">
         <f>C41-C41*15/100</f>
-        <v>157.25</v>
+        <v>144.5</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H41" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2582,26 +2665,25 @@
     </row>
     <row r="42" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>22</v>
+        <v>118</v>
       </c>
       <c r="C42" s="1">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="D42" s="1">
-        <f>C42-C42*15/100</f>
-        <v>161.5</v>
+        <v>0</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H42" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2613,26 +2695,26 @@
     </row>
     <row r="43" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C43" s="1">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D43" s="1">
         <f>C43-C43*15/100</f>
-        <v>144.5</v>
+        <v>135.15</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>143</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H43" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2644,25 +2726,26 @@
     </row>
     <row r="44" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>119</v>
+        <v>57</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C44" s="1">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="D44" s="1">
-        <v>0</v>
+        <f>C44-C44*15/100</f>
+        <v>135.15</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>143</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H44" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2674,26 +2757,25 @@
     </row>
     <row r="45" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="C45" s="1">
-        <v>195</v>
+        <v>139</v>
       </c>
       <c r="D45" s="1">
-        <f t="shared" si="1"/>
-        <v>165.75</v>
+        <v>0</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H45" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2705,26 +2787,26 @@
     </row>
     <row r="46" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C46" s="1">
         <v>165</v>
       </c>
       <c r="D46" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="D46:D53" si="1">C46-C46*15/100</f>
         <v>140.25</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H46" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2736,26 +2818,26 @@
     </row>
     <row r="47" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C47" s="1">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D47" s="1">
         <f t="shared" si="1"/>
-        <v>135.15</v>
+        <v>140.25</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H47" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2767,26 +2849,26 @@
     </row>
     <row r="48" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>98</v>
+        <v>57</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C48" s="1">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D48" s="1">
-        <f t="shared" ref="D48" si="6">C48-C48*15/100</f>
-        <v>148.75</v>
+        <f t="shared" si="1"/>
+        <v>114.75</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H48" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2798,26 +2880,26 @@
     </row>
     <row r="49" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="C49" s="1">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D49" s="1">
-        <f>C49-C49*15/100</f>
-        <v>143.65</v>
+        <f t="shared" si="1"/>
+        <v>148.75</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H49" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2829,26 +2911,26 @@
     </row>
     <row r="50" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="C50" s="1">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D50" s="1">
         <f t="shared" si="1"/>
-        <v>157.25</v>
+        <v>169.15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H50" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2860,26 +2942,26 @@
     </row>
     <row r="51" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C51" s="1">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D51" s="1">
-        <f>C51-C51*15/100</f>
-        <v>127.5</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H51" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2891,26 +2973,26 @@
     </row>
     <row r="52" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C52" s="1">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D52" s="1">
         <f t="shared" si="1"/>
-        <v>160.65</v>
+        <v>161.5</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>156</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H52" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2922,26 +3004,26 @@
     </row>
     <row r="53" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
       <c r="C53" s="1">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="D53" s="1">
         <f t="shared" si="1"/>
-        <v>174.25</v>
+        <v>148.75</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H53" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2953,25 +3035,25 @@
     </row>
     <row r="54" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C54" s="1">
-        <v>315</v>
+        <v>140</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H54" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2983,26 +3065,26 @@
     </row>
     <row r="55" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D55" s="1">
-        <f t="shared" ref="D55" si="7">C55-C55*15/100</f>
-        <v>0</v>
+        <f>C55-C55*15/100</f>
+        <v>143.65</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H55" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3014,26 +3096,26 @@
     </row>
     <row r="56" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D56" s="1">
-        <f t="shared" si="1"/>
-        <v>143.65</v>
+        <f>C56-C56*15/100</f>
+        <v>140.25</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H56" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3045,26 +3127,25 @@
     </row>
     <row r="57" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="C57" s="1">
-        <v>205</v>
+        <v>139</v>
       </c>
       <c r="D57" s="1">
-        <f t="shared" si="1"/>
-        <v>174.25</v>
+        <v>0</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H57" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3076,26 +3157,26 @@
     </row>
     <row r="58" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="C58" s="1">
-        <v>215</v>
+        <v>169</v>
       </c>
       <c r="D58" s="1">
-        <f>C58-C58*15/100</f>
-        <v>182.75</v>
+        <f t="shared" ref="D58:D67" si="2">C58-C58*15/100</f>
+        <v>143.65</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>143</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H58" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3107,26 +3188,26 @@
     </row>
     <row r="59" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C59" s="1">
         <v>185</v>
       </c>
       <c r="D59" s="1">
-        <f>C59-C59*15/100</f>
+        <f t="shared" si="2"/>
         <v>157.25</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H59" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3138,26 +3219,26 @@
     </row>
     <row r="60" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="C60" s="1">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="D60" s="1">
-        <f>C60-C60*15/100</f>
-        <v>161.5</v>
+        <f t="shared" si="2"/>
+        <v>119</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H60" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3169,26 +3250,26 @@
     </row>
     <row r="61" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>23</v>
+        <v>58</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C61" s="1">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="D61" s="1">
-        <f>C61-C61*15/100</f>
-        <v>144.5</v>
+        <f t="shared" si="2"/>
+        <v>160.65</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H61" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3200,25 +3281,26 @@
     </row>
     <row r="62" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>120</v>
+        <v>58</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C62" s="1">
+        <v>205</v>
+      </c>
+      <c r="D62" s="1">
+        <f t="shared" si="2"/>
+        <v>174.25</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="D62" s="1">
-        <v>0</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>164</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H62" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3230,26 +3312,26 @@
     </row>
     <row r="63" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="C63" s="1">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="D63" s="1">
-        <f t="shared" si="1"/>
-        <v>165.75</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H63" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3261,26 +3343,26 @@
     </row>
     <row r="64" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C64" s="1">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="D64" s="1">
-        <f t="shared" si="1"/>
-        <v>135.15</v>
+        <f t="shared" si="2"/>
+        <v>182.75</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H64" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3292,26 +3374,26 @@
     </row>
     <row r="65" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C65" s="1">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="D65" s="1">
-        <f t="shared" si="1"/>
-        <v>143.65</v>
+        <f t="shared" si="2"/>
+        <v>157.25</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H65" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3323,26 +3405,26 @@
     </row>
     <row r="66" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C66" s="1">
+        <v>190</v>
+      </c>
+      <c r="D66" s="1">
+        <f t="shared" si="2"/>
+        <v>161.5</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="D66" s="1">
-        <f t="shared" si="1"/>
-        <v>148.75</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="H66" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3354,26 +3436,26 @@
     </row>
     <row r="67" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C67" s="1">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D67" s="1">
-        <f>C67-C67*15/100</f>
-        <v>152.15</v>
+        <f t="shared" si="2"/>
+        <v>144.5</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H67" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3385,26 +3467,25 @@
     </row>
     <row r="68" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>33</v>
+        <v>59</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="C68" s="1">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="D68" s="1">
-        <f t="shared" si="1"/>
-        <v>158.94999999999999</v>
+        <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H68" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3416,26 +3497,26 @@
     </row>
     <row r="69" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C69" s="1">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" si="1"/>
-        <v>131.75</v>
+        <f t="shared" ref="D69:D77" si="3">C69-C69*15/100</f>
+        <v>165.75</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>156</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H69" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3447,25 +3528,26 @@
     </row>
     <row r="70" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="C70" s="1">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="D70" s="1">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>140.25</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H70" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3477,26 +3559,26 @@
     </row>
     <row r="71" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="C71" s="1">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="D71" s="1">
-        <f t="shared" ref="D71" si="8">C71-C71*15/100</f>
-        <v>174.25</v>
+        <f t="shared" si="3"/>
+        <v>135.15</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H71" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3508,25 +3590,26 @@
     </row>
     <row r="72" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>107</v>
+        <v>59</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C72" s="1">
-        <v>295</v>
+        <v>175</v>
       </c>
       <c r="D72" s="1">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>148.75</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H72" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3538,26 +3621,26 @@
     </row>
     <row r="73" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C73" s="1">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D73" s="1">
-        <f t="shared" ref="D73:D77" si="9">C73-C73*15/100</f>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>143.65</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H73" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3569,26 +3652,26 @@
     </row>
     <row r="74" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C74" s="1">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="D74" s="1">
-        <f t="shared" si="9"/>
-        <v>187</v>
+        <f t="shared" si="3"/>
+        <v>157.25</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H74" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3600,26 +3683,26 @@
     </row>
     <row r="75" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C75" s="1">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="D75" s="1">
-        <f t="shared" si="9"/>
-        <v>161.5</v>
+        <f t="shared" si="3"/>
+        <v>127.5</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H75" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3631,26 +3714,26 @@
     </row>
     <row r="76" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C76" s="1">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D76" s="1">
-        <f t="shared" si="9"/>
-        <v>157.25</v>
+        <f t="shared" si="3"/>
+        <v>160.65</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H76" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3662,26 +3745,26 @@
     </row>
     <row r="77" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>23</v>
+        <v>59</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C77" s="1">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="D77" s="1">
-        <f t="shared" si="9"/>
-        <v>144.5</v>
+        <f t="shared" si="3"/>
+        <v>174.25</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H77" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3693,25 +3776,25 @@
     </row>
     <row r="78" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>121</v>
+        <v>59</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C78" s="1">
+        <v>315</v>
+      </c>
+      <c r="D78" s="1">
+        <v>0</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D78" s="1">
-        <v>0</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="F78" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H78" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3723,26 +3806,26 @@
     </row>
     <row r="79" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="C79" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D79" s="1">
-        <f t="shared" si="1"/>
-        <v>169.15</v>
+        <f t="shared" ref="D79:D85" si="4">C79-C79*15/100</f>
+        <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H79" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3754,26 +3837,26 @@
     </row>
     <row r="80" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C80" s="1">
         <v>169</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>143.65</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H80" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3785,26 +3868,26 @@
     </row>
     <row r="81" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C81" s="1">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="D81" s="1">
-        <f t="shared" ref="D81:D82" si="10">C81-C81*15/100</f>
-        <v>140.25</v>
+        <f t="shared" si="4"/>
+        <v>174.25</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H81" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3816,26 +3899,26 @@
     </row>
     <row r="82" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>98</v>
+        <v>60</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C82" s="1">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="D82" s="1">
-        <f t="shared" si="10"/>
-        <v>148.75</v>
+        <f t="shared" si="4"/>
+        <v>182.75</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H82" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3847,26 +3930,26 @@
     </row>
     <row r="83" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C83" s="1">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D83" s="1">
-        <f t="shared" si="1"/>
-        <v>152.15</v>
+        <f t="shared" si="4"/>
+        <v>157.25</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H83" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3878,26 +3961,26 @@
     </row>
     <row r="84" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C84" s="1">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D84" s="1">
-        <f t="shared" si="1"/>
-        <v>165.75</v>
+        <f t="shared" si="4"/>
+        <v>161.5</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H84" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3909,26 +3992,26 @@
     </row>
     <row r="85" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>34</v>
+        <v>60</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C85" s="1">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="D85" s="1">
-        <f t="shared" si="1"/>
-        <v>131.75</v>
+        <f t="shared" si="4"/>
+        <v>144.5</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H85" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3940,25 +4023,25 @@
     </row>
     <row r="86" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>125</v>
+        <v>60</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="C86" s="1">
-        <v>189</v>
+        <v>145</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H86" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3970,26 +4053,26 @@
     </row>
     <row r="87" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>113</v>
+        <v>24</v>
       </c>
       <c r="C87" s="1">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D87" s="1">
-        <f t="shared" si="1"/>
-        <v>174.25</v>
+        <f t="shared" ref="D87:D93" si="5">C87-C87*15/100</f>
+        <v>165.75</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H87" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4001,26 +4084,26 @@
     </row>
     <row r="88" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="C88" s="1">
-        <v>299</v>
+        <v>159</v>
       </c>
       <c r="D88" s="1">
-        <f t="shared" si="1"/>
-        <v>254.15</v>
+        <f t="shared" si="5"/>
+        <v>135.15</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H88" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4032,26 +4115,26 @@
     </row>
     <row r="89" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="C89" s="1">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D89" s="1">
-        <f t="shared" ref="D89" si="11">C89-C89*15/100</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>143.65</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H89" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4063,26 +4146,26 @@
     </row>
     <row r="90" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>77</v>
+        <v>60</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C90" s="1">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="D90" s="1">
-        <f>C90-C90*15/100</f>
-        <v>187</v>
+        <f t="shared" si="5"/>
+        <v>148.75</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H90" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4094,25 +4177,26 @@
     </row>
     <row r="91" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>128</v>
+        <v>40</v>
       </c>
       <c r="C91" s="1">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D91" s="1">
-        <v>187</v>
+        <f t="shared" si="5"/>
+        <v>152.15</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H91" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4124,25 +4208,26 @@
     </row>
     <row r="92" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>124</v>
+        <v>60</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="C92" s="1">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D92" s="1">
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>158.94999999999999</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H92" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4154,25 +4239,26 @@
     </row>
     <row r="93" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="C93" s="1">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="D93" s="1">
-        <v>185</v>
+        <f t="shared" si="5"/>
+        <v>131.75</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H93" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4184,25 +4270,25 @@
     </row>
     <row r="94" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C94" s="1">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D94" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H94" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4214,26 +4300,26 @@
     </row>
     <row r="95" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C95" s="1">
         <v>205</v>
       </c>
       <c r="D95" s="1">
-        <f t="shared" ref="D95:D97" si="12">C95-C95*15/100</f>
+        <f>C95-C95*15/100</f>
         <v>174.25</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H95" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4245,26 +4331,25 @@
     </row>
     <row r="96" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="C96" s="1">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="D96" s="1">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H96" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4276,7 +4361,7 @@
     </row>
     <row r="97" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>85</v>
@@ -4285,17 +4370,17 @@
         <v>0</v>
       </c>
       <c r="D97" s="1">
-        <f t="shared" si="12"/>
+        <f>C97-C97*15/100</f>
         <v>0</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H97" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4307,26 +4392,26 @@
     </row>
     <row r="98" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="C98" s="1">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="D98" s="1">
-        <f t="shared" si="1"/>
-        <v>169.15</v>
+        <f>C98-C98*15/100</f>
+        <v>187</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H98" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4338,26 +4423,26 @@
     </row>
     <row r="99" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="C99" s="1">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D99" s="1">
         <f>C99-C99*15/100</f>
-        <v>157.25</v>
+        <v>161.5</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H99" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4369,26 +4454,26 @@
     </row>
     <row r="100" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C100" s="1">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D100" s="1">
         <f>C100-C100*15/100</f>
-        <v>148.75</v>
+        <v>157.25</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H100" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4400,26 +4485,26 @@
     </row>
     <row r="101" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>75</v>
+        <v>61</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C101" s="1">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="D101" s="1">
         <f>C101-C101*15/100</f>
-        <v>169.15</v>
+        <v>144.5</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H101" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4431,26 +4516,25 @@
     </row>
     <row r="102" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="C102" s="1">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D102" s="1">
-        <f>C102-C102*15/100</f>
-        <v>127.5</v>
+        <v>0</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H102" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4462,25 +4546,26 @@
     </row>
     <row r="103" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>106</v>
+        <v>61</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="C103" s="1">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="D103" s="1">
-        <v>0</v>
+        <f t="shared" ref="D103:D109" si="6">C103-C103*15/100</f>
+        <v>169.15</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H103" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4492,26 +4577,26 @@
     </row>
     <row r="104" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>122</v>
+        <v>61</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="C104" s="1">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D104" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>143.65</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>143</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H104" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4523,26 +4608,26 @@
     </row>
     <row r="105" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>105</v>
+        <v>61</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="C105" s="1">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D105" s="1">
-        <f>C105-C105*15/100</f>
-        <v>148.75</v>
+        <f t="shared" si="6"/>
+        <v>140.25</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H105" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4554,26 +4639,26 @@
     </row>
     <row r="106" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C106" s="1">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="D106" s="1">
-        <f t="shared" ref="D106:D113" si="13">C106-C106*15/100</f>
-        <v>187</v>
+        <f t="shared" si="6"/>
+        <v>148.75</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H106" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4585,26 +4670,26 @@
     </row>
     <row r="107" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="C107" s="1">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D107" s="1">
-        <f t="shared" si="13"/>
-        <v>160.65</v>
+        <f t="shared" si="6"/>
+        <v>152.15</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H107" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4616,26 +4701,26 @@
     </row>
     <row r="108" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="C108" s="1">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D108" s="1">
-        <f t="shared" si="13"/>
-        <v>160.65</v>
+        <f t="shared" si="6"/>
+        <v>165.75</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H108" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4647,26 +4732,26 @@
     </row>
     <row r="109" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>76</v>
+        <v>61</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="C109" s="1">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" si="13"/>
-        <v>157.25</v>
+        <f t="shared" si="6"/>
+        <v>131.75</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H109" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4678,26 +4763,25 @@
     </row>
     <row r="110" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C110" s="1">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D110" s="1">
-        <f t="shared" si="13"/>
-        <v>169.15</v>
+        <v>0</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H110" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4709,26 +4793,26 @@
     </row>
     <row r="111" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C111" s="1">
         <v>205</v>
       </c>
       <c r="D111" s="1">
-        <f t="shared" si="13"/>
+        <f>C111-C111*15/100</f>
         <v>174.25</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H111" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4740,26 +4824,26 @@
     </row>
     <row r="112" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="C112" s="1">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="D112" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f>C112-C112*15/100</f>
+        <v>254.15</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H112" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4771,26 +4855,26 @@
     </row>
     <row r="113" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C113" s="1">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="D113" s="1">
-        <f t="shared" si="13"/>
-        <v>318.75</v>
+        <f>C113-C113*15/100</f>
+        <v>0</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H113" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4802,25 +4886,26 @@
     </row>
     <row r="114" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>112</v>
+        <v>62</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="C114" s="1">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="D114" s="1">
-        <v>0</v>
+        <f>C114-C114*15/100</f>
+        <v>187</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>156</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H114" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4832,26 +4917,25 @@
     </row>
     <row r="115" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>75</v>
+        <v>62</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="C115" s="1">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D115" s="1">
-        <f t="shared" ref="D115" si="14">C115-C115*15/100</f>
-        <v>169.15</v>
+        <v>187</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H115" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4863,26 +4947,25 @@
     </row>
     <row r="116" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="C116" s="1">
         <v>199</v>
       </c>
       <c r="D116" s="1">
-        <f>C116-C116*15/100</f>
-        <v>169.15</v>
+        <v>0</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H116" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4894,25 +4977,25 @@
     </row>
     <row r="117" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>123</v>
+        <v>62</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C117" s="1">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="D117" s="1">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H117" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4924,26 +5007,25 @@
     </row>
     <row r="118" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="C118" s="1">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="D118" s="1">
-        <f t="shared" si="1"/>
-        <v>152.15</v>
+        <v>199</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H118" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4955,26 +5037,26 @@
     </row>
     <row r="119" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>73</v>
+        <v>62</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C119" s="1">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="D119" s="1">
-        <f t="shared" si="1"/>
-        <v>157.25</v>
+        <f t="shared" ref="D119:D126" si="7">C119-C119*15/100</f>
+        <v>174.25</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H119" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4986,26 +5068,26 @@
     </row>
     <row r="120" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>105</v>
+        <v>62</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="C120" s="1">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="D120" s="1">
-        <f t="shared" ref="D120:D125" si="15">C120-C120*15/100</f>
-        <v>148.75</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H120" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5017,26 +5099,26 @@
     </row>
     <row r="121" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>95</v>
+        <v>62</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="C121" s="1">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="D121" s="1">
-        <f t="shared" si="15"/>
-        <v>199.75</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H121" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5048,26 +5130,26 @@
     </row>
     <row r="122" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>102</v>
+        <v>62</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="C122" s="1">
         <v>199</v>
       </c>
       <c r="D122" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="7"/>
         <v>169.15</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H122" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5079,26 +5161,26 @@
     </row>
     <row r="123" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>87</v>
+        <v>62</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="C123" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D123" s="1">
-        <f t="shared" si="15"/>
-        <v>169.15</v>
+        <f t="shared" si="7"/>
+        <v>157.25</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H123" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5110,26 +5192,26 @@
     </row>
     <row r="124" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>76</v>
+        <v>62</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="C124" s="1">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D124" s="1">
-        <f t="shared" si="15"/>
-        <v>157.25</v>
+        <f t="shared" si="7"/>
+        <v>148.75</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H124" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5141,26 +5223,26 @@
     </row>
     <row r="125" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="C125" s="1">
         <v>199</v>
       </c>
       <c r="D125" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="7"/>
         <v>169.15</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H125" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5172,26 +5254,26 @@
     </row>
     <row r="126" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>113</v>
+        <v>62</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C126" s="1">
-        <v>205</v>
+        <v>150</v>
       </c>
       <c r="D126" s="1">
-        <f t="shared" ref="D126:D128" si="16">C126-C126*15/100</f>
-        <v>174.25</v>
+        <f t="shared" si="7"/>
+        <v>127.5</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H126" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5203,26 +5285,25 @@
     </row>
     <row r="127" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>84</v>
+        <v>62</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="C127" s="1">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D127" s="1">
-        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H127" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5234,26 +5315,26 @@
     </row>
     <row r="128" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>85</v>
+        <v>62</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="C128" s="1">
         <v>0</v>
       </c>
       <c r="D128" s="1">
-        <f t="shared" si="16"/>
+        <f>C128-C128*15/100</f>
         <v>0</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H128" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5265,26 +5346,26 @@
     </row>
     <row r="129" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>74</v>
+        <v>62</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="C129" s="1">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="D129" s="1">
-        <f t="shared" si="1"/>
-        <v>127.5</v>
+        <f>C129-C129*15/100</f>
+        <v>148.75</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H129" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5296,17 +5377,17 @@
     </row>
     <row r="130" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>90</v>
+        <v>63</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C130" s="1">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="D130" s="1">
-        <f t="shared" si="1"/>
-        <v>169.15</v>
+        <f t="shared" ref="D130:D137" si="8">C130-C130*15/100</f>
+        <v>187</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>144</v>
@@ -5315,7 +5396,7 @@
         <v>156</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H130" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5327,26 +5408,26 @@
     </row>
     <row r="131" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>81</v>
+        <v>63</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="C131" s="1">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="D131" s="1">
-        <f t="shared" ref="D131:D137" si="17">C131-C131*15/100</f>
-        <v>182.75</v>
+        <f t="shared" si="8"/>
+        <v>160.65</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H131" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5358,26 +5439,26 @@
     </row>
     <row r="132" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="C132" s="1">
         <v>189</v>
       </c>
       <c r="D132" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="8"/>
         <v>160.65</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H132" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5389,26 +5470,26 @@
     </row>
     <row r="133" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="C133" s="1">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D133" s="1">
-        <f t="shared" si="17"/>
-        <v>160.65</v>
+        <f t="shared" si="8"/>
+        <v>157.25</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H133" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5420,25 +5501,26 @@
     </row>
     <row r="134" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>106</v>
+        <v>63</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C134" s="1">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="D134" s="1">
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>169.15</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H134" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5450,26 +5532,26 @@
     </row>
     <row r="135" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>105</v>
+        <v>63</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C135" s="1">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="D135" s="1">
-        <f t="shared" si="17"/>
-        <v>148.75</v>
+        <f t="shared" si="8"/>
+        <v>174.25</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H135" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5481,26 +5563,26 @@
     </row>
     <row r="136" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B136" s="7" t="s">
-        <v>104</v>
+        <v>63</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="C136" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="D136" s="1">
-        <f t="shared" si="17"/>
-        <v>153</v>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H136" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5512,26 +5594,26 @@
     </row>
     <row r="137" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C137" s="1">
-        <v>285</v>
+        <v>375</v>
       </c>
       <c r="D137" s="1">
-        <f t="shared" si="17"/>
-        <v>242.25</v>
+        <f t="shared" si="8"/>
+        <v>318.75</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H137" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5543,26 +5625,25 @@
     </row>
     <row r="138" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>91</v>
+        <v>63</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="C138" s="1">
-        <v>275</v>
+        <v>150</v>
       </c>
       <c r="D138" s="1">
-        <f t="shared" si="1"/>
-        <v>233.75</v>
+        <v>0</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H138" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5574,26 +5655,26 @@
     </row>
     <row r="139" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>92</v>
+        <v>63</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="C139" s="1">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="D139" s="1">
-        <f t="shared" si="1"/>
-        <v>203.15</v>
+        <f>C139-C139*15/100</f>
+        <v>169.15</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H139" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5605,26 +5686,26 @@
     </row>
     <row r="140" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="C140" s="1">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="D140" s="1">
-        <f t="shared" si="1"/>
-        <v>147.9</v>
+        <f>C140-C140*15/100</f>
+        <v>169.15</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H140" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5636,26 +5717,25 @@
     </row>
     <row r="141" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>82</v>
+        <v>63</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="C141" s="1">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="D141" s="1">
-        <f t="shared" si="1"/>
-        <v>157.25</v>
+        <v>0</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H141" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5667,26 +5747,26 @@
     </row>
     <row r="142" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>111</v>
+        <v>63</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="C142" s="1">
-        <v>259</v>
+        <v>179</v>
       </c>
       <c r="D142" s="1">
         <f>C142-C142*15/100</f>
-        <v>220.15</v>
+        <v>152.15</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H142" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5698,26 +5778,26 @@
     </row>
     <row r="143" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B143" s="7" t="s">
-        <v>103</v>
+        <v>63</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="C143" s="1">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="D143" s="1">
         <f>C143-C143*15/100</f>
-        <v>136</v>
+        <v>157.25</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H143" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5729,26 +5809,26 @@
     </row>
     <row r="144" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="C144" s="1">
-        <v>340</v>
+        <v>175</v>
       </c>
       <c r="D144" s="1">
-        <f t="shared" si="1"/>
-        <v>289</v>
+        <f t="shared" ref="D144:D149" si="9">C144-C144*15/100</f>
+        <v>148.75</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H144" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5760,26 +5840,26 @@
     </row>
     <row r="145" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>43</v>
+        <v>64</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="C145" s="1">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="D145" s="1">
-        <f t="shared" ref="D145:D164" si="18">C145-C145*15/100</f>
-        <v>185.3</v>
+        <f t="shared" si="9"/>
+        <v>199.75</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H145" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5791,26 +5871,26 @@
     </row>
     <row r="146" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>44</v>
+        <v>64</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="C146" s="1">
-        <v>265</v>
+        <v>199</v>
       </c>
       <c r="D146" s="1">
-        <f t="shared" si="18"/>
-        <v>225.25</v>
+        <f t="shared" si="9"/>
+        <v>169.15</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H146" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5822,26 +5902,26 @@
     </row>
     <row r="147" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>110</v>
+        <v>64</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C147" s="1">
-        <v>270</v>
+        <v>199</v>
       </c>
       <c r="D147" s="1">
-        <f t="shared" ref="D147:D148" si="19">C147-C147*15/100</f>
-        <v>229.5</v>
+        <f t="shared" si="9"/>
+        <v>169.15</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H147" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5853,26 +5933,26 @@
     </row>
     <row r="148" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>109</v>
+        <v>64</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C148" s="1">
-        <v>265</v>
+        <v>185</v>
       </c>
       <c r="D148" s="1">
-        <f t="shared" si="19"/>
-        <v>225.25</v>
+        <f t="shared" si="9"/>
+        <v>157.25</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H148" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5884,26 +5964,26 @@
     </row>
     <row r="149" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>45</v>
+        <v>64</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="C149" s="1">
-        <v>285</v>
+        <v>199</v>
       </c>
       <c r="D149" s="1">
-        <f t="shared" si="18"/>
-        <v>242.25</v>
+        <f t="shared" si="9"/>
+        <v>169.15</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H149" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5915,26 +5995,26 @@
     </row>
     <row r="150" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="C150" s="1">
-        <v>340</v>
+        <v>205</v>
       </c>
       <c r="D150" s="1">
-        <f t="shared" si="18"/>
-        <v>289</v>
+        <f>C150-C150*15/100</f>
+        <v>174.25</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H150" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5946,26 +6026,26 @@
     </row>
     <row r="151" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C151" s="1">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="D151" s="1">
-        <f t="shared" si="18"/>
-        <v>182.75</v>
+        <f>C151-C151*15/100</f>
+        <v>0</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H151" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5977,26 +6057,26 @@
     </row>
     <row r="152" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C152">
-        <v>299</v>
+        <v>85</v>
+      </c>
+      <c r="C152" s="1">
+        <v>0</v>
       </c>
       <c r="D152" s="1">
         <f>C152-C152*15/100</f>
-        <v>254.15</v>
+        <v>0</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H152" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6008,26 +6088,26 @@
     </row>
     <row r="153" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C153">
-        <v>230</v>
+        <v>74</v>
+      </c>
+      <c r="C153" s="1">
+        <v>150</v>
       </c>
       <c r="D153" s="1">
-        <f t="shared" si="18"/>
-        <v>195.5</v>
+        <f>C153-C153*15/100</f>
+        <v>127.5</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H153" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6039,26 +6119,26 @@
     </row>
     <row r="154" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C154">
-        <v>325</v>
+        <v>90</v>
+      </c>
+      <c r="C154" s="1">
+        <v>199</v>
       </c>
       <c r="D154" s="1">
         <f>C154-C154*15/100</f>
-        <v>276.25</v>
+        <v>169.15</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H154" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6070,26 +6150,26 @@
     </row>
     <row r="155" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C155">
-        <v>199</v>
+        <v>81</v>
+      </c>
+      <c r="C155" s="1">
+        <v>215</v>
       </c>
       <c r="D155" s="1">
-        <f t="shared" si="18"/>
-        <v>169.15</v>
+        <f t="shared" ref="D155:D161" si="10">C155-C155*15/100</f>
+        <v>182.75</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H155" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6101,26 +6181,26 @@
     </row>
     <row r="156" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C156">
-        <v>445</v>
+        <v>64</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C156" s="1">
+        <v>189</v>
       </c>
       <c r="D156" s="1">
-        <f t="shared" si="18"/>
-        <v>378.25</v>
+        <f t="shared" si="10"/>
+        <v>160.65</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H156" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6132,26 +6212,26 @@
     </row>
     <row r="157" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C157">
-        <v>400</v>
+        <v>64</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C157" s="1">
+        <v>189</v>
       </c>
       <c r="D157" s="1">
-        <f t="shared" si="18"/>
-        <v>340</v>
+        <f t="shared" si="10"/>
+        <v>160.65</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H157" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6161,28 +6241,27 @@
       <c r="J157" s="1"/>
       <c r="K157" s="1"/>
     </row>
-    <row r="158" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C158">
-        <v>285</v>
+        <v>64</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C158" s="1">
+        <v>149</v>
       </c>
       <c r="D158" s="1">
-        <f>C158-C158*15/100</f>
-        <v>242.25</v>
+        <v>0</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H158" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6194,26 +6273,26 @@
     </row>
     <row r="159" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="C159" s="1">
-        <v>278</v>
+        <v>175</v>
       </c>
       <c r="D159" s="1">
-        <f t="shared" si="18"/>
-        <v>236.3</v>
+        <f t="shared" si="10"/>
+        <v>148.75</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H159" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6223,28 +6302,28 @@
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
     </row>
-    <row r="160" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="C160" s="1">
-        <v>405</v>
+        <v>180</v>
       </c>
       <c r="D160" s="1">
-        <f t="shared" si="18"/>
-        <v>344.25</v>
+        <f t="shared" si="10"/>
+        <v>153</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H160" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6254,28 +6333,28 @@
       <c r="J160" s="1"/>
       <c r="K160" s="1"/>
     </row>
-    <row r="161" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C161">
-        <v>360</v>
+        <v>96</v>
+      </c>
+      <c r="C161" s="1">
+        <v>285</v>
       </c>
       <c r="D161" s="1">
-        <f t="shared" si="18"/>
-        <v>306</v>
+        <f t="shared" si="10"/>
+        <v>242.25</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H161" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6285,28 +6364,28 @@
       <c r="J161" s="1"/>
       <c r="K161" s="1"/>
     </row>
-    <row r="162" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C162">
-        <v>249</v>
+        <v>91</v>
+      </c>
+      <c r="C162" s="1">
+        <v>275</v>
       </c>
       <c r="D162" s="1">
-        <f t="shared" si="18"/>
-        <v>211.65</v>
+        <f t="shared" ref="D162:D168" si="11">C162-C162*15/100</f>
+        <v>233.75</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H162" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6316,28 +6395,28 @@
       <c r="J162" s="1"/>
       <c r="K162" s="1"/>
     </row>
-    <row r="163" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C163">
-        <v>329</v>
+        <v>92</v>
+      </c>
+      <c r="C163" s="1">
+        <v>239</v>
       </c>
       <c r="D163" s="1">
-        <f t="shared" si="18"/>
-        <v>279.64999999999998</v>
+        <f t="shared" si="11"/>
+        <v>203.15</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H163" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6347,28 +6426,28 @@
       <c r="J163" s="1"/>
       <c r="K163" s="1"/>
     </row>
-    <row r="164" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C164">
-        <v>275</v>
+        <v>65</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C164" s="1">
+        <v>174</v>
       </c>
       <c r="D164" s="1">
-        <f t="shared" si="18"/>
-        <v>233.75</v>
+        <f t="shared" si="11"/>
+        <v>147.9</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H164" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6378,28 +6457,28 @@
       <c r="J164" s="1"/>
       <c r="K164" s="1"/>
     </row>
-    <row r="165" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C165">
-        <v>229</v>
+        <v>65</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C165" s="1">
+        <v>185</v>
       </c>
       <c r="D165" s="1">
-        <f>C165-C165*15/100</f>
-        <v>194.65</v>
+        <f t="shared" si="11"/>
+        <v>157.25</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H165" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6409,28 +6488,28 @@
       <c r="J165" s="1"/>
       <c r="K165" s="1"/>
     </row>
-    <row r="166" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C166">
-        <v>320</v>
+        <v>65</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C166" s="1">
+        <v>259</v>
       </c>
       <c r="D166" s="1">
-        <f>C166-C166*15/100</f>
-        <v>272</v>
+        <f t="shared" si="11"/>
+        <v>220.15</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H166" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6440,28 +6519,28 @@
       <c r="J166" s="1"/>
       <c r="K166" s="1"/>
     </row>
-    <row r="167" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C167">
-        <v>320</v>
+        <v>65</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C167" s="1">
+        <v>160</v>
       </c>
       <c r="D167" s="1">
-        <f>C167-C167*15/100</f>
-        <v>272</v>
+        <f t="shared" si="11"/>
+        <v>136</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H167" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6471,19 +6550,763 @@
       <c r="J167" s="1"/>
       <c r="K167" s="1"/>
     </row>
-    <row r="168" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B168" s="1"/>
-      <c r="D168" s="1"/>
-      <c r="E168" s="1"/>
-      <c r="F168" s="1"/>
-      <c r="G168" s="1"/>
-      <c r="H168" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C168" s="1">
+        <v>340</v>
+      </c>
+      <c r="D168" s="1">
+        <f t="shared" si="11"/>
+        <v>289</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H168" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
       <c r="I168" s="1"/>
       <c r="J168" s="1"/>
-      <c r="K168" s="1">
+      <c r="K168" s="1"/>
+    </row>
+    <row r="169" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A169" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C169" s="1">
+        <v>218</v>
+      </c>
+      <c r="D169" s="1">
+        <f t="shared" ref="D169:D188" si="12">C169-C169*15/100</f>
+        <v>185.3</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H169" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I169" s="1"/>
+      <c r="J169" s="1"/>
+      <c r="K169" s="1"/>
+    </row>
+    <row r="170" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A170" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C170" s="1">
+        <v>265</v>
+      </c>
+      <c r="D170" s="1">
+        <f t="shared" si="12"/>
+        <v>225.25</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H170" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I170" s="1"/>
+      <c r="J170" s="1"/>
+      <c r="K170" s="1"/>
+    </row>
+    <row r="171" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A171" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C171" s="1">
+        <v>270</v>
+      </c>
+      <c r="D171" s="1">
+        <f>C171-C171*15/100</f>
+        <v>229.5</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H171" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I171" s="1"/>
+      <c r="J171" s="1"/>
+      <c r="K171" s="1"/>
+    </row>
+    <row r="172" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A172" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C172" s="1">
+        <v>265</v>
+      </c>
+      <c r="D172" s="1">
+        <f>C172-C172*15/100</f>
+        <v>225.25</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H172" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I172" s="1"/>
+      <c r="J172" s="1"/>
+      <c r="K172" s="1"/>
+    </row>
+    <row r="173" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A173" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C173" s="1">
+        <v>285</v>
+      </c>
+      <c r="D173" s="1">
+        <f t="shared" si="12"/>
+        <v>242.25</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H173" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I173" s="1"/>
+      <c r="J173" s="1"/>
+      <c r="K173" s="1"/>
+    </row>
+    <row r="174" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A174" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C174" s="1">
+        <v>340</v>
+      </c>
+      <c r="D174" s="1">
+        <f t="shared" si="12"/>
+        <v>289</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H174" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I174" s="1"/>
+      <c r="J174" s="1"/>
+      <c r="K174" s="1"/>
+    </row>
+    <row r="175" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A175" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C175" s="1">
+        <v>215</v>
+      </c>
+      <c r="D175" s="1">
+        <f t="shared" si="12"/>
+        <v>182.75</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H175" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I175" s="1"/>
+      <c r="J175" s="1"/>
+      <c r="K175" s="1"/>
+    </row>
+    <row r="176" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A176" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C176">
+        <v>299</v>
+      </c>
+      <c r="D176" s="1">
+        <f>C176-C176*15/100</f>
+        <v>254.15</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H176" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I176" s="1"/>
+      <c r="J176" s="1"/>
+      <c r="K176" s="1"/>
+    </row>
+    <row r="177" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A177" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C177">
+        <v>230</v>
+      </c>
+      <c r="D177" s="1">
+        <f t="shared" si="12"/>
+        <v>195.5</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H177" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I177" s="1"/>
+      <c r="J177" s="1"/>
+      <c r="K177" s="1"/>
+    </row>
+    <row r="178" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A178" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C178">
+        <v>325</v>
+      </c>
+      <c r="D178" s="1">
+        <f>C178-C178*15/100</f>
+        <v>276.25</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H178" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I178" s="1"/>
+      <c r="J178" s="1"/>
+      <c r="K178" s="1"/>
+    </row>
+    <row r="179" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A179" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C179">
+        <v>199</v>
+      </c>
+      <c r="D179" s="1">
+        <f t="shared" si="12"/>
+        <v>169.15</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H179" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I179" s="1"/>
+      <c r="J179" s="1"/>
+      <c r="K179" s="1"/>
+    </row>
+    <row r="180" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A180" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C180">
+        <v>445</v>
+      </c>
+      <c r="D180" s="1">
+        <f t="shared" si="12"/>
+        <v>378.25</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H180" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I180" s="1"/>
+      <c r="J180" s="1"/>
+      <c r="K180" s="1"/>
+    </row>
+    <row r="181" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A181" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C181">
+        <v>400</v>
+      </c>
+      <c r="D181" s="1">
+        <f t="shared" si="12"/>
+        <v>340</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H181" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I181" s="1"/>
+      <c r="J181" s="1"/>
+      <c r="K181" s="1"/>
+    </row>
+    <row r="182" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C182">
+        <v>285</v>
+      </c>
+      <c r="D182" s="1">
+        <f>C182-C182*15/100</f>
+        <v>242.25</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H182" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I182" s="1"/>
+      <c r="J182" s="1"/>
+      <c r="K182" s="1"/>
+    </row>
+    <row r="183" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A183" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C183" s="1">
+        <v>278</v>
+      </c>
+      <c r="D183" s="1">
+        <f t="shared" si="12"/>
+        <v>236.3</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H183" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I183" s="1"/>
+      <c r="J183" s="1"/>
+      <c r="K183" s="1"/>
+    </row>
+    <row r="184" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C184" s="1">
+        <v>405</v>
+      </c>
+      <c r="D184" s="1">
+        <f t="shared" si="12"/>
+        <v>344.25</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H184" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I184" s="1"/>
+      <c r="J184" s="1"/>
+      <c r="K184" s="1"/>
+    </row>
+    <row r="185" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C185">
+        <v>360</v>
+      </c>
+      <c r="D185" s="1">
+        <f t="shared" si="12"/>
+        <v>306</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H185" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I185" s="1"/>
+      <c r="J185" s="1"/>
+      <c r="K185" s="1"/>
+    </row>
+    <row r="186" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C186">
+        <v>249</v>
+      </c>
+      <c r="D186" s="1">
+        <f t="shared" si="12"/>
+        <v>211.65</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H186" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I186" s="1"/>
+      <c r="J186" s="1"/>
+      <c r="K186" s="1"/>
+    </row>
+    <row r="187" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C187">
+        <v>329</v>
+      </c>
+      <c r="D187" s="1">
+        <f t="shared" si="12"/>
+        <v>279.64999999999998</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H187" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I187" s="1"/>
+      <c r="J187" s="1"/>
+      <c r="K187" s="1"/>
+    </row>
+    <row r="188" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C188">
+        <v>275</v>
+      </c>
+      <c r="D188" s="1">
+        <f t="shared" si="12"/>
+        <v>233.75</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H188" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I188" s="1"/>
+      <c r="J188" s="1"/>
+      <c r="K188" s="1"/>
+    </row>
+    <row r="189" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C189">
+        <v>229</v>
+      </c>
+      <c r="D189" s="1">
+        <f>C189-C189*15/100</f>
+        <v>194.65</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H189" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I189" s="1"/>
+      <c r="J189" s="1"/>
+      <c r="K189" s="1"/>
+    </row>
+    <row r="190" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C190">
+        <v>320</v>
+      </c>
+      <c r="D190" s="1">
+        <f>C190-C190*15/100</f>
+        <v>272</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H190" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I190" s="1"/>
+      <c r="J190" s="1"/>
+      <c r="K190" s="1"/>
+    </row>
+    <row r="191" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C191">
+        <v>320</v>
+      </c>
+      <c r="D191" s="1">
+        <f>C191-C191*15/100</f>
+        <v>272</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H191" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I191" s="1"/>
+      <c r="J191" s="1"/>
+      <c r="K191" s="1"/>
+    </row>
+    <row r="192" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B192" s="1"/>
+      <c r="D192" s="1"/>
+      <c r="E192" s="1"/>
+      <c r="F192" s="1"/>
+      <c r="G192" s="1"/>
+      <c r="H192" s="1"/>
+      <c r="I192" s="1"/>
+      <c r="J192" s="1"/>
+      <c r="K192" s="1">
         <f>SUBTOTAL(103,الجدول1[فاتورة شراء 1])</f>
         <v>0</v>
       </c>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:10000001_{582E1C95-4790-4A49-91CE-7C5C2B213A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0CC75C-54BA-413A-863C-7BBF8E4E16DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="الورقة1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="245">
   <si>
     <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
   </si>
@@ -451,9 +450,6 @@
     <t>فاتورة شراء 1</t>
   </si>
   <si>
-    <t>تأسيس</t>
-  </si>
-  <si>
     <t>بيان الأصناف</t>
   </si>
   <si>
@@ -664,9 +660,6 @@
     <t>معلم القراءة</t>
   </si>
   <si>
-    <t>دار الرحمة</t>
-  </si>
-  <si>
     <t>تأسيس سليم</t>
   </si>
   <si>
@@ -692,13 +685,94 @@
   </si>
   <si>
     <t>العشر الأخير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">معلم القراءة </t>
+  </si>
+  <si>
+    <t>تاسيس</t>
+  </si>
+  <si>
+    <t>عربي معلم القراءة جزء 1</t>
+  </si>
+  <si>
+    <t>عربي معلم القراءة جزء 2</t>
+  </si>
+  <si>
+    <t>عربي ( كتاب المطالعة الأولية)</t>
+  </si>
+  <si>
+    <t>عربي   (نحو) معلم القراءة</t>
+  </si>
+  <si>
+    <t>عربي   (نحو) 1و2و3 ابتدائي</t>
+  </si>
+  <si>
+    <t>عربي   (نحو) 4و5و6 ابتدائي</t>
+  </si>
+  <si>
+    <t>عربي (نحو)  1و2و3 ابتدائي</t>
+  </si>
+  <si>
+    <t>عربي (نحو)  4 ابتدائي</t>
+  </si>
+  <si>
+    <t>عربي (نحو)  5 ابتدائي</t>
+  </si>
+  <si>
+    <t>عربي (نحو)  6ابتداي</t>
+  </si>
+  <si>
+    <t>انجليزي (الكبير) جزء 1</t>
+  </si>
+  <si>
+    <t>انجليزي (الصغير) جزء 2</t>
+  </si>
+  <si>
+    <t>عربي (تجويد ومدود ونحو)</t>
+  </si>
+  <si>
+    <t>انجليزي (  بوك 1) شورت فاولز</t>
+  </si>
+  <si>
+    <t>انجليزي ( بوك 2)  لونج فاولز</t>
+  </si>
+  <si>
+    <t>انجليزي (جزء 1) شورت فاولز</t>
+  </si>
+  <si>
+    <t>انجليزي ( 2)   لونج فاولز</t>
+  </si>
+  <si>
+    <t>انجليزي ( جرامر 1)</t>
+  </si>
+  <si>
+    <t>انجليزي ( جرامر 2)</t>
+  </si>
+  <si>
+    <t>انجليزي ( جرامر 3)</t>
+  </si>
+  <si>
+    <t>انجليزي ( 5أجزاء)  المجموعه 450</t>
+  </si>
+  <si>
+    <t>انجليزي ( الجزء الواحد) 100ج</t>
+  </si>
+  <si>
+    <t>عربي (نون والقلم) درا الرحمة</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2(معلم القراءة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> الأضواء عربي بكالوريا ⬅️ 340</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -729,6 +803,28 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -750,7 +846,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -776,13 +872,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -1178,8 +1277,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:K192" totalsRowCount="1" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="A1:K191" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:K194" totalsRowCount="1" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:K193" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="الصف" totalsRowLabel="الإجمالي" dataDxfId="19" totalsRowDxfId="9"/>
     <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="بيان الأصناف" dataDxfId="18" totalsRowDxfId="8"/>
@@ -1402,7 +1501,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K192"/>
+  <dimension ref="A1:K194"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -1410,7 +1509,7 @@
     <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" customWidth="1"/>
     <col min="7" max="7" width="7.7109375" customWidth="1"/>
     <col min="8" max="9" width="7.42578125" customWidth="1"/>
   </cols>
@@ -1420,7 +1519,7 @@
         <v>132</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>133</v>
@@ -1432,16 +1531,16 @@
         <v>135</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>136</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>137</v>
@@ -1455,7 +1554,7 @@
         <v>86</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
@@ -1464,19 +1563,21 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>186</v>
+        <v>208</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H2" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I2" s="1"/>
+      <c r="I2" s="1">
+        <v>8</v>
+      </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
@@ -1485,7 +1586,7 @@
         <v>86</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>204</v>
+        <v>243</v>
       </c>
       <c r="C3" s="1">
         <v>15</v>
@@ -1494,19 +1595,21 @@
         <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>204</v>
+        <v>208</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H3" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I3" s="1"/>
+      <c r="I3" s="1">
+        <v>12</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
@@ -1515,28 +1618,30 @@
         <v>86</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="C4" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>187</v>
+        <v>208</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>222</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H4" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1">
+        <v>11</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
@@ -1544,29 +1649,31 @@
       <c r="A5" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>188</v>
+      <c r="B5" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="C5" s="1">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>188</v>
+        <v>218</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>242</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H5" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1">
+        <v>20</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
@@ -1575,7 +1682,7 @@
         <v>86</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C6" s="1">
         <v>175</v>
@@ -1584,19 +1691,22 @@
         <v>175</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>189</v>
+        <v>209</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H6" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>140</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
@@ -1605,7 +1715,7 @@
         <v>86</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C7" s="1">
         <v>175</v>
@@ -1614,19 +1724,22 @@
         <v>175</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>190</v>
+        <v>209</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H7" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>140</v>
+      </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
@@ -1634,29 +1747,32 @@
       <c r="A8" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>205</v>
+      <c r="B8" s="6" t="s">
+        <v>189</v>
       </c>
       <c r="C8" s="1">
+        <v>175</v>
+      </c>
+      <c r="D8" s="1">
+        <v>175</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H8" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>140</v>
       </c>
-      <c r="D8" s="1">
-        <v>140</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="H8" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
@@ -1665,7 +1781,7 @@
         <v>86</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C9" s="1">
         <v>140</v>
@@ -1674,19 +1790,22 @@
         <v>140</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>206</v>
+        <v>210</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>226</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="H9" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>112</v>
+      </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
@@ -1695,7 +1814,7 @@
         <v>86</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C10" s="1">
         <v>140</v>
@@ -1704,19 +1823,22 @@
         <v>140</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>207</v>
+        <v>210</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>227</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>176</v>
+        <v>219</v>
       </c>
       <c r="H10" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I10" s="1"/>
+      <c r="I10" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>112</v>
+      </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
@@ -1725,7 +1847,7 @@
         <v>86</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C11" s="1">
         <v>140</v>
@@ -1734,19 +1856,22 @@
         <v>140</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>228</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="H11" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>112</v>
+      </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
@@ -1755,28 +1880,31 @@
         <v>86</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="C12" s="1">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="D12" s="1">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>191</v>
+        <v>210</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>229</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H12" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>112</v>
+      </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
@@ -1785,7 +1913,7 @@
         <v>86</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C13" s="1">
         <v>25</v>
@@ -1794,19 +1922,21 @@
         <v>25</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>192</v>
+        <v>211</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>230</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H13" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1">
+        <v>20</v>
+      </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
@@ -1815,7 +1945,7 @@
         <v>86</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C14" s="1">
         <v>25</v>
@@ -1824,19 +1954,21 @@
         <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>193</v>
+        <v>211</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>231</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H14" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1">
+        <v>20</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
@@ -1845,7 +1977,7 @@
         <v>86</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C15" s="1">
         <v>25</v>
@@ -1854,19 +1986,21 @@
         <v>25</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>194</v>
+        <v>211</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>232</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H15" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1">
+        <v>20</v>
+      </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
@@ -1875,28 +2009,30 @@
         <v>86</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C16" s="1">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="D16" s="1">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>196</v>
+        <v>211</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>156</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H16" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I16" s="1"/>
+      <c r="I16" s="1">
+        <v>20</v>
+      </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -1908,25 +2044,28 @@
         <v>195</v>
       </c>
       <c r="C17" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D17" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>195</v>
+        <v>212</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>233</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H17" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I17" s="1"/>
+      <c r="I17" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>64</v>
+      </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
@@ -1935,28 +2074,31 @@
         <v>86</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C18" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D18" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>197</v>
+        <v>212</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>234</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H18" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I18" s="1"/>
+      <c r="I18" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>80</v>
+      </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
@@ -1965,28 +2107,31 @@
         <v>86</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C19" s="1">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D19" s="1">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>198</v>
+        <v>213</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>235</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H19" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I19" s="1"/>
+      <c r="I19" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>56</v>
+      </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
@@ -1995,28 +2140,31 @@
         <v>86</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C20" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D20" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>199</v>
+        <v>213</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>236</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H20" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I20" s="1"/>
+      <c r="I20" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>72</v>
+      </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
@@ -2025,7 +2173,7 @@
         <v>86</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C21" s="1">
         <v>95</v>
@@ -2034,19 +2182,22 @@
         <v>95</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>200</v>
+        <v>213</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>237</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H21" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I21" s="1"/>
+      <c r="I21" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>76</v>
+      </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
@@ -2055,28 +2206,31 @@
         <v>86</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C22" s="1">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="D22" s="1">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>201</v>
+        <v>213</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>238</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H22" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I22" s="1"/>
+      <c r="I22" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>76</v>
+      </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
@@ -2085,28 +2239,31 @@
         <v>86</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C23" s="1">
-        <v>450</v>
+        <v>115</v>
       </c>
       <c r="D23" s="1">
-        <v>450</v>
+        <v>115</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>239</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H23" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I23" s="1"/>
+      <c r="I23" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>92</v>
+      </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
@@ -2115,28 +2272,31 @@
         <v>86</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C24" s="1">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="D24" s="1">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>203</v>
+        <v>214</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>240</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="H24" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I24" s="1"/>
+      <c r="I24" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>360</v>
+      </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
@@ -2145,28 +2305,31 @@
         <v>86</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="C25" s="1">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="D25" s="1">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>218</v>
+        <v>214</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="H25" s="11">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="1"/>
+        <v>219</v>
+      </c>
+      <c r="H25" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>80</v>
+      </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
     </row>
@@ -2175,59 +2338,62 @@
         <v>86</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C26" s="1">
+        <v>5</v>
+      </c>
+      <c r="D26" s="1">
+        <v>5</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C26" s="1">
-        <v>10</v>
-      </c>
-      <c r="D26" s="1">
-        <v>10</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="H26" s="11">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="1"/>
+      <c r="H26" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
+        <v>3.5</v>
+      </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
     </row>
-    <row r="27" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>3</v>
+    <row r="27" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>217</v>
       </c>
       <c r="C27" s="1">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="D27" s="1">
-        <f t="shared" ref="D16:D31" si="0">C27-C27*15/100</f>
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>156</v>
+        <v>215</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>217</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="H27" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I27" s="1"/>
+      <c r="I27" s="1">
+        <v>8</v>
+      </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
     </row>
@@ -2236,29 +2402,32 @@
         <v>56</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" s="1">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D28" s="1">
-        <f t="shared" si="0"/>
-        <v>144.5</v>
+        <f t="shared" ref="D28:D32" si="0">C28-C28*15/100</f>
+        <v>153</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H28" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I28" s="1"/>
+      <c r="I28" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.9</f>
+        <v>148.5</v>
+      </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
     </row>
@@ -2267,29 +2436,32 @@
         <v>56</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" s="1">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="D29" s="1">
         <f t="shared" si="0"/>
-        <v>110.5</v>
+        <v>144.5</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H29" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I29" s="1"/>
+      <c r="I29" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.95</f>
+        <v>140.35</v>
+      </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
     </row>
@@ -2298,29 +2470,32 @@
         <v>56</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="1">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="D30" s="1">
         <f t="shared" si="0"/>
-        <v>126.65</v>
+        <v>110.5</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H30" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I30" s="1"/>
+      <c r="I30" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.73</f>
+        <v>107.33</v>
+      </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
@@ -2329,23 +2504,23 @@
         <v>56</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="1">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D31" s="1">
         <f t="shared" si="0"/>
-        <v>135.15</v>
+        <v>126.65</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>156</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H31" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2360,22 +2535,23 @@
         <v>56</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>116</v>
+        <v>7</v>
       </c>
       <c r="C32" s="1">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>135.15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H32" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2390,23 +2566,22 @@
         <v>56</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="C33" s="1">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="D33" s="1">
-        <f>C33-C33*15/100</f>
-        <v>140.25</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H33" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2421,7 +2596,7 @@
         <v>56</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34" s="1">
         <v>165</v>
@@ -2431,13 +2606,13 @@
         <v>140.25</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H34" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2452,23 +2627,23 @@
         <v>56</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C35" s="1">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="D35" s="1">
         <f>C35-C35*15/100</f>
-        <v>114.75</v>
+        <v>140.25</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>147</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H35" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2483,23 +2658,23 @@
         <v>56</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D36" s="1">
         <f>C36-C36*15/100</f>
-        <v>148.75</v>
+        <v>114.75</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H36" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2514,23 +2689,23 @@
         <v>56</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="C37" s="1">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="D37" s="1">
         <f>C37-C37*15/100</f>
-        <v>169.15</v>
+        <v>148.75</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H37" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2545,22 +2720,22 @@
         <v>56</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C38" s="1">
-        <v>255</v>
+        <v>199</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H38" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2575,23 +2750,22 @@
         <v>56</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="C39" s="1">
-        <v>165</v>
+        <v>255</v>
       </c>
       <c r="D39" s="1">
-        <f>C39-C39*15/100</f>
-        <v>140.25</v>
+        <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H39" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2603,26 +2777,26 @@
     </row>
     <row r="40" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C40" s="1">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D40" s="1">
         <f>C40-C40*15/100</f>
-        <v>153</v>
+        <v>140.25</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>156</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H40" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2637,29 +2811,32 @@
         <v>57</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41" s="1">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D41" s="1">
         <f>C41-C41*15/100</f>
-        <v>144.5</v>
+        <v>153</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H41" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I41" s="1"/>
+      <c r="I41" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.9</f>
+        <v>148.5</v>
+      </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
     </row>
@@ -2668,28 +2845,32 @@
         <v>57</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="C42" s="1">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <f>C42-C42*15/100</f>
+        <v>144.5</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H42" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I42" s="1"/>
+      <c r="I42" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.95</f>
+        <v>140.35</v>
+      </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
     </row>
@@ -2698,29 +2879,31 @@
         <v>57</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="C43" s="1">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D43" s="1">
-        <f>C43-C43*15/100</f>
-        <v>135.15</v>
+        <v>0</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H43" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I43" s="1"/>
+      <c r="I43" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.73</f>
+        <v>115.53</v>
+      </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
     </row>
@@ -2729,7 +2912,7 @@
         <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C44" s="1">
         <v>159</v>
@@ -2739,13 +2922,13 @@
         <v>135.15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>156</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H44" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2760,22 +2943,23 @@
         <v>57</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>117</v>
+        <v>7</v>
       </c>
       <c r="C45" s="1">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D45" s="1">
-        <v>0</v>
+        <f>C45-C45*15/100</f>
+        <v>135.15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H45" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2790,23 +2974,22 @@
         <v>57</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="C46" s="1">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="D46" s="1">
-        <f t="shared" ref="D46:D53" si="1">C46-C46*15/100</f>
-        <v>140.25</v>
+        <v>0</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H46" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2821,23 +3004,23 @@
         <v>57</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C47" s="1">
         <v>165</v>
       </c>
       <c r="D47" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="D47:D54" si="1">C47-C47*15/100</f>
         <v>140.25</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H47" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2852,23 +3035,23 @@
         <v>57</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C48" s="1">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="D48" s="1">
         <f t="shared" si="1"/>
-        <v>114.75</v>
+        <v>140.25</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>147</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H48" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2883,23 +3066,23 @@
         <v>57</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C49" s="1">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D49" s="1">
         <f t="shared" si="1"/>
-        <v>148.75</v>
+        <v>114.75</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H49" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2914,23 +3097,23 @@
         <v>57</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="C50" s="1">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="D50" s="1">
         <f t="shared" si="1"/>
-        <v>169.15</v>
+        <v>148.75</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H50" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2945,23 +3128,22 @@
         <v>57</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="C51" s="1">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D51" s="1">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H51" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2973,26 +3155,26 @@
     </row>
     <row r="52" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="C52" s="1">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="D52" s="1">
         <f t="shared" si="1"/>
-        <v>161.5</v>
+        <v>0</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H52" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3007,29 +3189,32 @@
         <v>58</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C53" s="1">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="D53" s="1">
         <f t="shared" si="1"/>
-        <v>148.75</v>
+        <v>161.5</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H53" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I53" s="1"/>
+      <c r="I53" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.95</f>
+        <v>156.75</v>
+      </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
     </row>
@@ -3038,28 +3223,32 @@
         <v>58</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="C54" s="1">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="D54" s="1">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>148.75</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H54" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I54" s="1"/>
+      <c r="I54" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.95</f>
+        <v>144.44999999999999</v>
+      </c>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
     </row>
@@ -3068,29 +3257,31 @@
         <v>58</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="C55" s="1">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="D55" s="1">
-        <f>C55-C55*15/100</f>
-        <v>143.65</v>
+        <v>0</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H55" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I55" s="1"/>
+      <c r="I55" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.73</f>
+        <v>115.53</v>
+      </c>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
     </row>
@@ -3099,23 +3290,23 @@
         <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C56" s="1">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D56" s="1">
         <f>C56-C56*15/100</f>
-        <v>140.25</v>
+        <v>143.65</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H56" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3130,22 +3321,23 @@
         <v>58</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="C57" s="1">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="D57" s="1">
-        <v>0</v>
+        <f>C57-C57*15/100</f>
+        <v>140.25</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H57" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3160,23 +3352,22 @@
         <v>58</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="C58" s="1">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="D58" s="1">
-        <f t="shared" ref="D58:D67" si="2">C58-C58*15/100</f>
-        <v>143.65</v>
+        <v>0</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H58" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3191,23 +3382,23 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="C59" s="1">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D59" s="1">
-        <f t="shared" si="2"/>
-        <v>157.25</v>
+        <f t="shared" ref="D59:D68" si="2">C59-C59*15/100</f>
+        <v>143.65</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H59" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3222,23 +3413,23 @@
         <v>58</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>167</v>
+        <v>18</v>
       </c>
       <c r="C60" s="1">
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="D60" s="1">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>157.25</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>147</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H60" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3253,23 +3444,23 @@
         <v>58</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>19</v>
+        <v>166</v>
       </c>
       <c r="C61" s="1">
-        <v>189</v>
+        <v>140</v>
       </c>
       <c r="D61" s="1">
         <f t="shared" si="2"/>
-        <v>160.65</v>
+        <v>119</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H61" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3284,23 +3475,23 @@
         <v>58</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="C62" s="1">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D62" s="1">
         <f t="shared" si="2"/>
-        <v>174.25</v>
+        <v>160.65</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H62" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3315,23 +3506,22 @@
         <v>58</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C63" s="1">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="D63" s="1">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H63" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3343,26 +3533,26 @@
     </row>
     <row r="64" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="C64" s="1">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="D64" s="1">
         <f t="shared" si="2"/>
-        <v>182.75</v>
+        <v>0</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H64" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3377,29 +3567,32 @@
         <v>59</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C65" s="1">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="D65" s="1">
         <f t="shared" si="2"/>
-        <v>157.25</v>
+        <v>182.75</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H65" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I65" s="1"/>
+      <c r="I65" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+1.08</f>
+        <v>177.38000000000002</v>
+      </c>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
     </row>
@@ -3408,29 +3601,32 @@
         <v>59</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C66" s="1">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D66" s="1">
         <f t="shared" si="2"/>
-        <v>161.5</v>
+        <v>157.25</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H66" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I66" s="1"/>
+      <c r="I66" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.93</f>
+        <v>152.63</v>
+      </c>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
     </row>
@@ -3439,29 +3635,32 @@
         <v>59</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C67" s="1">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D67" s="1">
         <f t="shared" si="2"/>
-        <v>144.5</v>
+        <v>161.5</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H67" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I67" s="1"/>
+      <c r="I67" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.95</f>
+        <v>156.75</v>
+      </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
     </row>
@@ -3469,29 +3668,33 @@
       <c r="A68" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>118</v>
+      <c r="B68" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C68" s="1">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="D68" s="1">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>144.5</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H68" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I68" s="1"/>
+      <c r="I68" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.85</f>
+        <v>140.25</v>
+      </c>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
     </row>
@@ -3499,30 +3702,32 @@
       <c r="A69" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>24</v>
+      <c r="B69" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="C69" s="1">
-        <v>195</v>
+        <v>145</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" ref="D69:D77" si="3">C69-C69*15/100</f>
-        <v>165.75</v>
+        <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H69" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I69" s="1"/>
+      <c r="I69" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.73</f>
+        <v>119.63000000000001</v>
+      </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
     </row>
@@ -3531,23 +3736,23 @@
         <v>59</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C70" s="1">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="D70" s="1">
-        <f t="shared" si="3"/>
-        <v>140.25</v>
+        <f t="shared" ref="D70:D77" si="3">C70-C70*15/100</f>
+        <v>165.75</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H70" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3562,23 +3767,23 @@
         <v>59</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C71" s="1">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D71" s="1">
         <f t="shared" si="3"/>
-        <v>135.15</v>
+        <v>140.25</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H71" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3592,24 +3797,24 @@
       <c r="A72" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>97</v>
+      <c r="B72" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C72" s="1">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="D72" s="1">
         <f t="shared" si="3"/>
-        <v>148.75</v>
+        <v>135.15</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H72" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3623,24 +3828,24 @@
       <c r="A73" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>88</v>
+      <c r="B73" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C73" s="1">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D73" s="1">
         <f t="shared" si="3"/>
-        <v>143.65</v>
+        <v>148.75</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H73" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3655,23 +3860,23 @@
         <v>59</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="C74" s="1">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D74" s="1">
         <f t="shared" si="3"/>
-        <v>157.25</v>
+        <v>143.65</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H74" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3686,23 +3891,23 @@
         <v>59</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="C75" s="1">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="D75" s="1">
         <f t="shared" si="3"/>
-        <v>127.5</v>
+        <v>157.25</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>147</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H75" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3717,23 +3922,23 @@
         <v>59</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="C76" s="1">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="D76" s="1">
         <f t="shared" si="3"/>
-        <v>160.65</v>
+        <v>127.5</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H76" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3748,23 +3953,23 @@
         <v>59</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="C77" s="1">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D77" s="1">
         <f t="shared" si="3"/>
-        <v>174.25</v>
+        <v>160.65</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H77" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3779,22 +3984,22 @@
         <v>59</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C78" s="1">
-        <v>315</v>
+        <v>205</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H78" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3809,23 +4014,22 @@
         <v>59</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="C79" s="1">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="D79" s="1">
-        <f t="shared" ref="D79:D85" si="4">C79-C79*15/100</f>
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H79" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3840,23 +4044,23 @@
         <v>59</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="C80" s="1">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" si="4"/>
-        <v>143.65</v>
+        <f t="shared" ref="D80:D86" si="4">C80-C80*15/100</f>
+        <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H80" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3871,23 +4075,23 @@
         <v>59</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C81" s="1">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D81" s="1">
         <f t="shared" si="4"/>
-        <v>174.25</v>
+        <v>143.65</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H81" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3899,26 +4103,26 @@
     </row>
     <row r="82" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C82" s="1">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D82" s="1">
         <f t="shared" si="4"/>
-        <v>182.75</v>
+        <v>174.25</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H82" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3933,29 +4137,32 @@
         <v>60</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C83" s="1">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="D83" s="1">
         <f t="shared" si="4"/>
-        <v>157.25</v>
+        <v>182.75</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H83" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I83" s="1"/>
+      <c r="I83" s="15">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+1.08</f>
+        <v>177.38000000000002</v>
+      </c>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
     </row>
@@ -3964,29 +4171,32 @@
         <v>60</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C84" s="1">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D84" s="1">
         <f t="shared" si="4"/>
-        <v>161.5</v>
+        <v>157.25</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H84" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I84" s="1"/>
+      <c r="I84" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.93</f>
+        <v>152.63</v>
+      </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
     </row>
@@ -3994,30 +4204,33 @@
       <c r="A85" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>23</v>
+      <c r="B85" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C85" s="1">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D85" s="1">
         <f t="shared" si="4"/>
-        <v>144.5</v>
+        <v>161.5</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H85" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I85" s="1"/>
+      <c r="I85" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.95</f>
+        <v>156.75</v>
+      </c>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
     </row>
@@ -4026,28 +4239,32 @@
         <v>60</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="C86" s="1">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="D86" s="1">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>144.5</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H86" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I86" s="1"/>
+      <c r="I86" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.85</f>
+        <v>140.25</v>
+      </c>
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
     </row>
@@ -4055,30 +4272,32 @@
       <c r="A87" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>24</v>
+      <c r="B87" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="C87" s="1">
-        <v>195</v>
+        <v>145</v>
       </c>
       <c r="D87" s="1">
-        <f t="shared" ref="D87:D93" si="5">C87-C87*15/100</f>
-        <v>165.75</v>
+        <v>0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H87" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I87" s="1"/>
+      <c r="I87" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.73</f>
+        <v>119.63000000000001</v>
+      </c>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
     </row>
@@ -4087,23 +4306,23 @@
         <v>60</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C88" s="1">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="D88" s="1">
-        <f t="shared" si="5"/>
-        <v>135.15</v>
+        <f t="shared" ref="D88:D94" si="5">C88-C88*15/100</f>
+        <v>165.75</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H88" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4118,23 +4337,23 @@
         <v>60</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C89" s="1">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D89" s="1">
         <f t="shared" si="5"/>
-        <v>143.65</v>
+        <v>135.15</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H89" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4148,24 +4367,24 @@
       <c r="A90" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>97</v>
+      <c r="B90" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="C90" s="1">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D90" s="1">
         <f t="shared" si="5"/>
-        <v>148.75</v>
+        <v>143.65</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H90" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4179,24 +4398,24 @@
       <c r="A91" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>40</v>
+      <c r="B91" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C91" s="1">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D91" s="1">
         <f t="shared" si="5"/>
-        <v>152.15</v>
+        <v>148.75</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H91" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4211,23 +4430,23 @@
         <v>60</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C92" s="1">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D92" s="1">
         <f t="shared" si="5"/>
-        <v>158.94999999999999</v>
+        <v>152.15</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H92" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4242,23 +4461,23 @@
         <v>60</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C93" s="1">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="D93" s="1">
         <f t="shared" si="5"/>
-        <v>131.75</v>
+        <v>158.94999999999999</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>147</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H93" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4273,22 +4492,23 @@
         <v>60</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="C94" s="1">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="D94" s="1">
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>131.75</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H94" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4303,23 +4523,22 @@
         <v>60</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C95" s="1">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D95" s="1">
-        <f>C95-C95*15/100</f>
-        <v>174.25</v>
+        <v>0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H95" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4334,22 +4553,22 @@
         <v>60</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C96" s="1">
-        <v>295</v>
+        <v>205</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H96" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4364,23 +4583,22 @@
         <v>60</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C97" s="1">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="D97" s="1">
-        <f>C97-C97*15/100</f>
         <v>0</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H97" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4392,26 +4610,26 @@
     </row>
     <row r="98" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="C98" s="1">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D98" s="1">
         <f>C98-C98*15/100</f>
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H98" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4426,29 +4644,32 @@
         <v>61</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C99" s="1">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="D99" s="1">
         <f>C99-C99*15/100</f>
-        <v>161.5</v>
+        <v>187</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H99" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I99" s="1"/>
+      <c r="I99" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+1.1</f>
+        <v>181.5</v>
+      </c>
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
     </row>
@@ -4457,29 +4678,32 @@
         <v>61</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C100" s="1">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D100" s="1">
         <f>C100-C100*15/100</f>
-        <v>157.25</v>
+        <v>161.5</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H100" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I100" s="1"/>
+      <c r="I100" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.95</f>
+        <v>156.75</v>
+      </c>
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
     </row>
@@ -4487,30 +4711,33 @@
       <c r="A101" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>23</v>
+      <c r="B101" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="C101" s="1">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="D101" s="1">
         <f>C101-C101*15/100</f>
-        <v>144.5</v>
+        <v>157.25</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H101" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I101" s="1"/>
+      <c r="I101" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.93</f>
+        <v>152.63</v>
+      </c>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
     </row>
@@ -4519,28 +4746,32 @@
         <v>61</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="C102" s="1">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="D102" s="1">
-        <v>0</v>
+        <f>C102-C102*15/100</f>
+        <v>144.5</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H102" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I102" s="1"/>
+      <c r="I102" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.85</f>
+        <v>140.25</v>
+      </c>
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
     </row>
@@ -4548,30 +4779,32 @@
       <c r="A103" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>38</v>
+      <c r="B103" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="C103" s="1">
-        <v>199</v>
+        <v>145</v>
       </c>
       <c r="D103" s="1">
-        <f t="shared" ref="D103:D109" si="6">C103-C103*15/100</f>
-        <v>169.15</v>
+        <v>0</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H103" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I103" s="1"/>
+      <c r="I103" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.73</f>
+        <v>119.63000000000001</v>
+      </c>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
     </row>
@@ -4580,23 +4813,23 @@
         <v>61</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C104" s="1">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="D104" s="1">
-        <f t="shared" si="6"/>
-        <v>143.65</v>
+        <f t="shared" ref="D104:D110" si="6">C104-C104*15/100</f>
+        <v>169.15</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H104" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4611,23 +4844,23 @@
         <v>61</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C105" s="1">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D105" s="1">
         <f t="shared" si="6"/>
-        <v>140.25</v>
+        <v>143.65</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H105" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4641,24 +4874,24 @@
       <c r="A106" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>97</v>
+      <c r="B106" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="C106" s="1">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D106" s="1">
         <f t="shared" si="6"/>
-        <v>148.75</v>
+        <v>140.25</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H106" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4672,24 +4905,24 @@
       <c r="A107" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>40</v>
+      <c r="B107" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C107" s="1">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D107" s="1">
         <f t="shared" si="6"/>
-        <v>152.15</v>
+        <v>148.75</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H107" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4704,23 +4937,23 @@
         <v>61</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C108" s="1">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D108" s="1">
         <f t="shared" si="6"/>
-        <v>165.75</v>
+        <v>152.15</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H108" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4735,23 +4968,23 @@
         <v>61</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C109" s="1">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="D109" s="1">
         <f t="shared" si="6"/>
-        <v>131.75</v>
+        <v>165.75</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>147</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H109" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4766,22 +4999,23 @@
         <v>61</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="C110" s="1">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="D110" s="1">
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>131.75</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H110" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4796,23 +5030,22 @@
         <v>61</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C111" s="1">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D111" s="1">
-        <f>C111-C111*15/100</f>
-        <v>174.25</v>
+        <v>0</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H111" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4827,23 +5060,22 @@
         <v>61</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C112" s="1">
-        <v>299</v>
+        <v>205</v>
       </c>
       <c r="D112" s="1">
-        <f>C112-C112*15/100</f>
-        <v>254.15</v>
+        <v>0</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H112" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4858,23 +5090,22 @@
         <v>61</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="C113" s="1">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="D113" s="1">
-        <f>C113-C113*15/100</f>
         <v>0</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H113" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4886,26 +5117,26 @@
     </row>
     <row r="114" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C114" s="1">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D114" s="1">
         <f>C114-C114*15/100</f>
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H114" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4920,22 +5151,23 @@
         <v>62</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="C115" s="1">
+        <v>220</v>
+      </c>
+      <c r="D115" s="1">
+        <f>C115-C115*15/100</f>
         <v>187</v>
       </c>
-      <c r="D115" s="1">
-        <v>187</v>
-      </c>
       <c r="E115" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H115" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4949,23 +5181,23 @@
       <c r="A116" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>123</v>
+      <c r="B116" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="C116" s="1">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D116" s="1">
         <v>0</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H116" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4979,23 +5211,23 @@
       <c r="A117" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>126</v>
+      <c r="B117" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="C117" s="1">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D117" s="1">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>157</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H117" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5010,22 +5242,22 @@
         <v>62</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C118" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D118" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H118" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5040,23 +5272,22 @@
         <v>62</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C119" s="1">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D119" s="1">
-        <f t="shared" ref="D119:D126" si="7">C119-C119*15/100</f>
-        <v>174.25</v>
+        <v>0</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H119" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5071,23 +5302,22 @@
         <v>62</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C120" s="1">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="D120" s="1">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H120" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5102,23 +5332,22 @@
         <v>62</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C121" s="1">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="D121" s="1">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H121" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5133,23 +5362,23 @@
         <v>62</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C122" s="1">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D122" s="1">
-        <f t="shared" si="7"/>
-        <v>169.15</v>
+        <f t="shared" ref="D122:D127" si="7">C122-C122*15/100</f>
+        <v>0</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H122" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5164,23 +5393,22 @@
         <v>62</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C123" s="1">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D123" s="1">
-        <f t="shared" si="7"/>
-        <v>157.25</v>
+        <v>0</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H123" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5195,23 +5423,22 @@
         <v>62</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C124" s="1">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D124" s="1">
-        <f t="shared" si="7"/>
-        <v>148.75</v>
+        <v>0</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H124" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5226,23 +5453,22 @@
         <v>62</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C125" s="1">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="D125" s="1">
-        <f t="shared" si="7"/>
-        <v>169.15</v>
+        <v>0</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H125" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5256,24 +5482,23 @@
       <c r="A126" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>74</v>
+      <c r="B126" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="C126" s="1">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="D126" s="1">
-        <f t="shared" si="7"/>
-        <v>127.5</v>
+        <v>0</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H126" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5287,23 +5512,24 @@
       <c r="A127" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B127" s="3" t="s">
-        <v>105</v>
+      <c r="B127" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C127" s="1">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D127" s="1">
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>127.5</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H127" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5317,24 +5543,23 @@
       <c r="A128" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>121</v>
+      <c r="B128" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="C128" s="1">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D128" s="1">
-        <f>C128-C128*15/100</f>
         <v>0</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>142</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H128" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5348,55 +5573,57 @@
       <c r="A129" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B129" s="7" t="s">
-        <v>104</v>
+      <c r="B129" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="C129" s="1">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="D129" s="1">
-        <f>C129-C129*15/100</f>
-        <v>148.75</v>
+        <v>0</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H129" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I129" s="1"/>
+      <c r="I129" s="14">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.73</f>
+        <v>119.63000000000001</v>
+      </c>
       <c r="J129" s="1"/>
       <c r="K129" s="1"/>
     </row>
     <row r="130" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="C130" s="1">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="D130" s="1">
-        <f t="shared" ref="D130:D137" si="8">C130-C130*15/100</f>
-        <v>187</v>
+        <f>C130-C130*15/100</f>
+        <v>148.75</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H130" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5411,23 +5638,23 @@
         <v>63</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C131" s="1">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="D131" s="1">
-        <f t="shared" si="8"/>
-        <v>160.65</v>
+        <f t="shared" ref="D131:D137" si="8">C131-C131*15/100</f>
+        <v>187</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H131" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5442,7 +5669,7 @@
         <v>63</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C132" s="1">
         <v>189</v>
@@ -5452,13 +5679,13 @@
         <v>160.65</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H132" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5473,23 +5700,23 @@
         <v>63</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C133" s="1">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D133" s="1">
         <f t="shared" si="8"/>
-        <v>157.25</v>
+        <v>160.65</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>157</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H133" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5503,24 +5730,24 @@
       <c r="A134" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>125</v>
+      <c r="B134" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C134" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D134" s="1">
         <f t="shared" si="8"/>
-        <v>169.15</v>
+        <v>157.25</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H134" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5535,23 +5762,23 @@
         <v>63</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C135" s="1">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D135" s="1">
         <f t="shared" si="8"/>
-        <v>174.25</v>
+        <v>169.15</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H135" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5566,23 +5793,22 @@
         <v>63</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="C136" s="1">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="D136" s="1">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H136" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5597,23 +5823,23 @@
         <v>63</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C137" s="1">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="D137" s="1">
         <f t="shared" si="8"/>
-        <v>318.75</v>
+        <v>0</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H137" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5627,23 +5853,23 @@
       <c r="A138" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>111</v>
+      <c r="B138" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="C138" s="1">
-        <v>150</v>
+        <v>375</v>
       </c>
       <c r="D138" s="1">
         <v>0</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H138" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5658,23 +5884,22 @@
         <v>63</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="C139" s="1">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="D139" s="1">
-        <f>C139-C139*15/100</f>
-        <v>169.15</v>
+        <v>0</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H139" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5688,8 +5913,8 @@
       <c r="A140" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>42</v>
+      <c r="B140" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="C140" s="1">
         <v>199</v>
@@ -5699,13 +5924,13 @@
         <v>169.15</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H140" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5719,23 +5944,24 @@
       <c r="A141" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>122</v>
+      <c r="B141" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="C141" s="1">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="D141" s="1">
-        <v>0</v>
+        <f>C141-C141*15/100</f>
+        <v>169.15</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H141" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5750,23 +5976,22 @@
         <v>63</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="C142" s="1">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D142" s="1">
-        <f>C142-C142*15/100</f>
-        <v>152.15</v>
+        <v>0</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H142" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5781,23 +6006,23 @@
         <v>63</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C143" s="1">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D143" s="1">
         <f>C143-C143*15/100</f>
-        <v>157.25</v>
+        <v>152.15</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H143" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5811,24 +6036,24 @@
       <c r="A144" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B144" s="7" t="s">
-        <v>104</v>
+      <c r="B144" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="C144" s="1">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D144" s="1">
-        <f t="shared" ref="D144:D149" si="9">C144-C144*15/100</f>
-        <v>148.75</v>
+        <f>C144-C144*15/100</f>
+        <v>157.25</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H144" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5840,26 +6065,26 @@
     </row>
     <row r="145" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>94</v>
+        <v>63</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="C145" s="1">
-        <v>235</v>
+        <v>175</v>
       </c>
       <c r="D145" s="1">
-        <f t="shared" si="9"/>
-        <v>199.75</v>
+        <f t="shared" ref="D145:D150" si="9">C145-C145*15/100</f>
+        <v>148.75</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H145" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5874,23 +6099,23 @@
         <v>64</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C146" s="1">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="D146" s="1">
         <f t="shared" si="9"/>
-        <v>169.15</v>
+        <v>199.75</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H146" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5905,7 +6130,7 @@
         <v>64</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C147" s="1">
         <v>199</v>
@@ -5915,13 +6140,13 @@
         <v>169.15</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H147" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5936,23 +6161,23 @@
         <v>64</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C148" s="1">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D148" s="1">
         <f t="shared" si="9"/>
-        <v>157.25</v>
+        <v>169.15</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>157</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H148" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5967,23 +6192,23 @@
         <v>64</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C149" s="1">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D149" s="1">
         <f t="shared" si="9"/>
-        <v>169.15</v>
+        <v>157.25</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H149" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5997,24 +6222,24 @@
       <c r="A150" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>112</v>
+      <c r="B150" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="C150" s="1">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D150" s="1">
-        <f>C150-C150*15/100</f>
-        <v>174.25</v>
+        <f t="shared" si="9"/>
+        <v>169.15</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H150" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6029,23 +6254,22 @@
         <v>64</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C151" s="1">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="D151" s="1">
-        <f>C151-C151*15/100</f>
         <v>0</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H151" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6060,7 +6284,7 @@
         <v>64</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C152" s="1">
         <v>0</v>
@@ -6070,13 +6294,13 @@
         <v>0</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H152" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6091,23 +6315,23 @@
         <v>64</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C153" s="1">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D153" s="1">
         <f>C153-C153*15/100</f>
-        <v>127.5</v>
+        <v>0</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H153" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6122,23 +6346,23 @@
         <v>64</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C154" s="1">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="D154" s="1">
         <f>C154-C154*15/100</f>
-        <v>169.15</v>
+        <v>127.5</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H154" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6153,23 +6377,23 @@
         <v>64</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C155" s="1">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="D155" s="1">
-        <f t="shared" ref="D155:D161" si="10">C155-C155*15/100</f>
-        <v>182.75</v>
+        <f>C155-C155*15/100</f>
+        <v>169.15</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H155" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6183,24 +6407,24 @@
       <c r="A156" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>98</v>
+      <c r="B156" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="C156" s="1">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D156" s="1">
-        <f t="shared" si="10"/>
-        <v>160.65</v>
+        <f t="shared" ref="D156:D162" si="10">C156-C156*15/100</f>
+        <v>182.75</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H156" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6215,7 +6439,7 @@
         <v>64</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C157" s="1">
         <v>189</v>
@@ -6225,13 +6449,13 @@
         <v>160.65</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H157" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6246,22 +6470,23 @@
         <v>64</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C158" s="1">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="D158" s="1">
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>160.65</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H158" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6275,24 +6500,23 @@
       <c r="A159" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B159" s="7" t="s">
-        <v>104</v>
+      <c r="B159" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="C159" s="1">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="D159" s="1">
-        <f t="shared" si="10"/>
-        <v>148.75</v>
+        <v>0</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H159" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6304,26 +6528,26 @@
     </row>
     <row r="160" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C160" s="1">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D160" s="1">
         <f t="shared" si="10"/>
-        <v>153</v>
+        <v>148.75</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H160" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6337,24 +6561,24 @@
       <c r="A161" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>96</v>
+      <c r="B161" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="C161" s="1">
-        <v>285</v>
+        <v>180</v>
       </c>
       <c r="D161" s="1">
         <f t="shared" si="10"/>
-        <v>242.25</v>
+        <v>153</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H161" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6369,23 +6593,23 @@
         <v>65</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C162" s="1">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="D162" s="1">
-        <f t="shared" ref="D162:D168" si="11">C162-C162*15/100</f>
-        <v>233.75</v>
+        <f t="shared" si="10"/>
+        <v>242.25</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H162" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6400,23 +6624,23 @@
         <v>65</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C163" s="1">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="D163" s="1">
-        <f t="shared" si="11"/>
-        <v>203.15</v>
+        <f t="shared" ref="D163:D169" si="11">C163-C163*15/100</f>
+        <v>233.75</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H163" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6430,24 +6654,24 @@
       <c r="A164" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B164" s="4" t="s">
-        <v>83</v>
+      <c r="B164" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="C164" s="1">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="D164" s="1">
         <f t="shared" si="11"/>
-        <v>147.9</v>
+        <v>203.15</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H164" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6462,23 +6686,23 @@
         <v>65</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C165" s="1">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="D165" s="1">
         <f t="shared" si="11"/>
-        <v>157.25</v>
+        <v>147.9</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H165" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6493,23 +6717,23 @@
         <v>65</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="C166" s="1">
-        <v>259</v>
+        <v>185</v>
       </c>
       <c r="D166" s="1">
         <f t="shared" si="11"/>
-        <v>220.15</v>
+        <v>157.25</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H166" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6523,24 +6747,24 @@
       <c r="A167" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B167" s="7" t="s">
-        <v>102</v>
+      <c r="B167" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="C167" s="1">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="D167" s="1">
         <f t="shared" si="11"/>
-        <v>136</v>
+        <v>220.15</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H167" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6552,26 +6776,26 @@
     </row>
     <row r="168" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>130</v>
+        <v>65</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="C168" s="1">
-        <v>340</v>
+        <v>160</v>
       </c>
       <c r="D168" s="1">
         <f t="shared" si="11"/>
-        <v>289</v>
+        <v>136</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H168" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6583,23 +6807,23 @@
     </row>
     <row r="169" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="C169" s="1">
-        <v>218</v>
+        <v>340</v>
       </c>
       <c r="D169" s="1">
-        <f t="shared" ref="D169:D188" si="12">C169-C169*15/100</f>
-        <v>185.3</v>
+        <f t="shared" si="11"/>
+        <v>289</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>182</v>
@@ -6614,28 +6838,28 @@
     </row>
     <row r="170" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>44</v>
+        <v>244</v>
       </c>
       <c r="C170" s="1">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="D170" s="1">
-        <f t="shared" si="12"/>
-        <v>225.25</v>
+        <f>C170-C170*15/100</f>
+        <v>254.15</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H170" s="1">
+      <c r="H170" s="16">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
@@ -6648,23 +6872,23 @@
         <v>67</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="C171" s="1">
-        <v>270</v>
+        <v>218</v>
       </c>
       <c r="D171" s="1">
-        <f>C171-C171*15/100</f>
-        <v>229.5</v>
+        <f t="shared" ref="D171:D190" si="12">C171-C171*15/100</f>
+        <v>185.3</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H171" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6679,23 +6903,23 @@
         <v>67</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="C172" s="1">
         <v>265</v>
       </c>
       <c r="D172" s="1">
-        <f>C172-C172*15/100</f>
+        <f t="shared" si="12"/>
         <v>225.25</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H172" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6710,23 +6934,23 @@
         <v>67</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="C173" s="1">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="D173" s="1">
-        <f t="shared" si="12"/>
-        <v>242.25</v>
+        <f>C173-C173*15/100</f>
+        <v>229.5</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H173" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6741,23 +6965,23 @@
         <v>67</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="C174" s="1">
-        <v>340</v>
+        <v>265</v>
       </c>
       <c r="D174" s="1">
-        <f t="shared" si="12"/>
-        <v>289</v>
+        <f>C174-C174*15/100</f>
+        <v>225.25</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H174" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6772,23 +6996,23 @@
         <v>67</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C175" s="1">
-        <v>215</v>
+        <v>285</v>
       </c>
       <c r="D175" s="1">
         <f t="shared" si="12"/>
-        <v>182.75</v>
+        <v>242.25</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>160</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H175" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6803,23 +7027,23 @@
         <v>67</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C176">
-        <v>299</v>
+        <v>46</v>
+      </c>
+      <c r="C176" s="1">
+        <v>340</v>
       </c>
       <c r="D176" s="1">
-        <f>C176-C176*15/100</f>
-        <v>254.15</v>
+        <f t="shared" si="12"/>
+        <v>289</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>160</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H176" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6834,23 +7058,23 @@
         <v>67</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C177">
-        <v>230</v>
+        <v>47</v>
+      </c>
+      <c r="C177" s="1">
+        <v>215</v>
       </c>
       <c r="D177" s="1">
         <f t="shared" si="12"/>
-        <v>195.5</v>
+        <v>182.75</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H177" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6865,23 +7089,23 @@
         <v>67</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C178">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="D178" s="1">
         <f>C178-C178*15/100</f>
-        <v>276.25</v>
+        <v>254.15</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H178" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6896,23 +7120,23 @@
         <v>67</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C179">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="D179" s="1">
         <f t="shared" si="12"/>
-        <v>169.15</v>
+        <v>195.5</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H179" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6927,23 +7151,23 @@
         <v>67</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C180">
-        <v>445</v>
+        <v>325</v>
       </c>
       <c r="D180" s="1">
-        <f t="shared" si="12"/>
-        <v>378.25</v>
+        <f>C180-C180*15/100</f>
+        <v>276.25</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H180" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6958,23 +7182,23 @@
         <v>67</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C181">
-        <v>400</v>
+        <v>199</v>
       </c>
       <c r="D181" s="1">
         <f t="shared" si="12"/>
-        <v>340</v>
+        <v>169.15</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H181" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6984,28 +7208,28 @@
       <c r="J181" s="1"/>
       <c r="K181" s="1"/>
     </row>
-    <row r="182" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="C182">
-        <v>285</v>
+        <v>445</v>
       </c>
       <c r="D182" s="1">
-        <f>C182-C182*15/100</f>
-        <v>242.25</v>
+        <f t="shared" si="12"/>
+        <v>378.25</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H182" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7020,14 +7244,14 @@
         <v>67</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C183" s="1">
-        <v>278</v>
+        <v>53</v>
+      </c>
+      <c r="C183">
+        <v>400</v>
       </c>
       <c r="D183" s="1">
         <f t="shared" si="12"/>
-        <v>236.3</v>
+        <v>340</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>144</v>
@@ -7036,7 +7260,7 @@
         <v>156</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H183" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7051,23 +7275,23 @@
         <v>67</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C184" s="1">
-        <v>405</v>
+        <v>95</v>
+      </c>
+      <c r="C184">
+        <v>285</v>
       </c>
       <c r="D184" s="1">
-        <f t="shared" si="12"/>
-        <v>344.25</v>
+        <f>C184-C184*15/100</f>
+        <v>242.25</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>144</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H184" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7077,28 +7301,28 @@
       <c r="J184" s="1"/>
       <c r="K184" s="1"/>
     </row>
-    <row r="185" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C185">
-        <v>360</v>
+        <v>54</v>
+      </c>
+      <c r="C185" s="1">
+        <v>278</v>
       </c>
       <c r="D185" s="1">
         <f t="shared" si="12"/>
-        <v>306</v>
+        <v>236.3</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H185" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7113,23 +7337,23 @@
         <v>67</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C186">
-        <v>249</v>
+        <v>55</v>
+      </c>
+      <c r="C186" s="1">
+        <v>405</v>
       </c>
       <c r="D186" s="1">
         <f t="shared" si="12"/>
-        <v>211.65</v>
+        <v>344.25</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>143</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H186" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7144,23 +7368,23 @@
         <v>67</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C187">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="D187" s="1">
         <f t="shared" si="12"/>
-        <v>279.64999999999998</v>
+        <v>306</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H187" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7175,23 +7399,23 @@
         <v>67</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="C188">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="D188" s="1">
         <f t="shared" si="12"/>
-        <v>233.75</v>
+        <v>211.65</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>155</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H188" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7206,23 +7430,23 @@
         <v>67</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>114</v>
+        <v>2</v>
       </c>
       <c r="C189">
-        <v>229</v>
+        <v>329</v>
       </c>
       <c r="D189" s="1">
-        <f>C189-C189*15/100</f>
-        <v>194.65</v>
+        <f t="shared" si="12"/>
+        <v>279.64999999999998</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H189" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7237,23 +7461,23 @@
         <v>67</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="C190">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="D190" s="1">
-        <f>C190-C190*15/100</f>
-        <v>272</v>
+        <f t="shared" si="12"/>
+        <v>233.75</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H190" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7268,23 +7492,23 @@
         <v>67</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="C191">
-        <v>320</v>
+        <v>229</v>
       </c>
       <c r="D191" s="1">
         <f>C191-C191*15/100</f>
-        <v>272</v>
+        <v>194.65</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H191" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7296,17 +7520,79 @@
     </row>
     <row r="192" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B192" s="1"/>
-      <c r="D192" s="1"/>
-      <c r="E192" s="1"/>
-      <c r="F192" s="1"/>
-      <c r="G192" s="1"/>
-      <c r="H192" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C192">
+        <v>320</v>
+      </c>
+      <c r="D192" s="1">
+        <f>C192-C192*15/100</f>
+        <v>272</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H192" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
       <c r="I192" s="1"/>
       <c r="J192" s="1"/>
-      <c r="K192" s="1">
+      <c r="K192" s="1"/>
+    </row>
+    <row r="193" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C193">
+        <v>320</v>
+      </c>
+      <c r="D193" s="1">
+        <f>C193-C193*15/100</f>
+        <v>272</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H193" s="1">
+        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <v>0</v>
+      </c>
+      <c r="I193" s="1"/>
+      <c r="J193" s="1"/>
+      <c r="K193" s="1"/>
+    </row>
+    <row r="194" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B194" s="1"/>
+      <c r="D194" s="1"/>
+      <c r="E194" s="1"/>
+      <c r="F194" s="1"/>
+      <c r="G194" s="1"/>
+      <c r="H194" s="1"/>
+      <c r="I194" s="1"/>
+      <c r="J194" s="1"/>
+      <c r="K194" s="1">
         <f>SUBTOTAL(103,الجدول1[فاتورة شراء 1])</f>
         <v>0</v>
       </c>
@@ -7314,8 +7600,9 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0CC75C-54BA-413A-863C-7BBF8E4E16DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45467FD6-B9EC-4296-AE06-D9833B60F247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -765,7 +765,7 @@
     <t xml:space="preserve"> 2(معلم القراءة)</t>
   </si>
   <si>
-    <t xml:space="preserve"> الأضواء عربي بكالوريا ⬅️ 340</t>
+    <t xml:space="preserve"> الأضواء عربي بكالوريا ⬅️ 299</t>
   </si>
 </sst>
 </file>
@@ -846,7 +846,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -881,7 +881,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -6859,7 +6858,7 @@
       <c r="G170" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H170" s="16">
+      <c r="H170" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45467FD6-B9EC-4296-AE06-D9833B60F247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3976BA2-F58B-4524-BB1D-27B8C6B487BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,9 +33,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="245">
   <si>
-    <t>الكيان عربي شرح 4 أجزاء ⬅️ 360</t>
-  </si>
-  <si>
     <t>الأضواء عربي (شرح) ⬅️ 249</t>
   </si>
   <si>
@@ -766,6 +763,9 @@
   </si>
   <si>
     <t xml:space="preserve"> الأضواء عربي بكالوريا ⬅️ 299</t>
+  </si>
+  <si>
+    <t>الكيان عربي اسئلة 4 أجزاء ⬅️ 360</t>
   </si>
 </sst>
 </file>
@@ -1515,45 +1515,45 @@
   <sheetData>
     <row r="1" spans="1:11" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="D1" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
@@ -1562,13 +1562,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H2" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1582,10 +1582,10 @@
     </row>
     <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C3" s="1">
         <v>15</v>
@@ -1594,13 +1594,13 @@
         <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H3" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1614,10 +1614,10 @@
     </row>
     <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C4" s="1">
         <v>15</v>
@@ -1626,13 +1626,13 @@
         <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H4" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C5" s="1">
         <v>25</v>
@@ -1658,13 +1658,13 @@
         <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="H5" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="6" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C6" s="1">
         <v>175</v>
@@ -1690,13 +1690,13 @@
         <v>175</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H6" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1711,10 +1711,10 @@
     </row>
     <row r="7" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C7" s="1">
         <v>175</v>
@@ -1723,13 +1723,13 @@
         <v>175</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H7" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1744,10 +1744,10 @@
     </row>
     <row r="8" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C8" s="1">
         <v>175</v>
@@ -1756,13 +1756,13 @@
         <v>175</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H8" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1777,10 +1777,10 @@
     </row>
     <row r="9" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C9" s="1">
         <v>140</v>
@@ -1789,13 +1789,13 @@
         <v>140</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H9" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="10" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C10" s="1">
         <v>140</v>
@@ -1822,13 +1822,13 @@
         <v>140</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H10" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C11" s="1">
         <v>140</v>
@@ -1855,13 +1855,13 @@
         <v>140</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H11" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="12" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C12" s="1">
         <v>140</v>
@@ -1888,13 +1888,13 @@
         <v>140</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H12" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="13" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C13" s="1">
         <v>25</v>
@@ -1921,13 +1921,13 @@
         <v>25</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H13" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="14" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C14" s="1">
         <v>25</v>
@@ -1953,13 +1953,13 @@
         <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H14" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="15" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C15" s="1">
         <v>25</v>
@@ -1985,13 +1985,13 @@
         <v>25</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H15" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="16" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C16" s="1">
         <v>25</v>
@@ -2017,13 +2017,13 @@
         <v>25</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H16" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2037,10 +2037,10 @@
     </row>
     <row r="17" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C17" s="1">
         <v>80</v>
@@ -2049,13 +2049,13 @@
         <v>80</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H17" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2070,10 +2070,10 @@
     </row>
     <row r="18" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C18" s="1">
         <v>100</v>
@@ -2082,13 +2082,13 @@
         <v>100</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H18" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="19" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C19" s="1">
         <v>70</v>
@@ -2115,13 +2115,13 @@
         <v>70</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H19" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="20" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C20" s="1">
         <v>90</v>
@@ -2148,13 +2148,13 @@
         <v>90</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H20" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="21" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C21" s="1">
         <v>95</v>
@@ -2181,13 +2181,13 @@
         <v>95</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H21" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2202,10 +2202,10 @@
     </row>
     <row r="22" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C22" s="1">
         <v>95</v>
@@ -2214,13 +2214,13 @@
         <v>95</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H22" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2235,10 +2235,10 @@
     </row>
     <row r="23" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C23" s="1">
         <v>115</v>
@@ -2247,13 +2247,13 @@
         <v>115</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H23" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2268,10 +2268,10 @@
     </row>
     <row r="24" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C24" s="1">
         <v>450</v>
@@ -2280,13 +2280,13 @@
         <v>450</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H24" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="25" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C25" s="1">
         <v>100</v>
@@ -2313,13 +2313,13 @@
         <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H25" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="26" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C26" s="1">
         <v>5</v>
@@ -2346,13 +2346,13 @@
         <v>5</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F26" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>216</v>
-      </c>
       <c r="G26" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H26" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2366,10 +2366,10 @@
     </row>
     <row r="27" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C27" s="1">
         <v>10</v>
@@ -2378,13 +2378,13 @@
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H27" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2398,10 +2398,10 @@
     </row>
     <row r="28" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" s="1">
         <v>180</v>
@@ -2411,13 +2411,13 @@
         <v>153</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H28" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="29" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" s="1">
         <v>170</v>
@@ -2445,13 +2445,13 @@
         <v>144.5</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H29" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2466,26 +2466,25 @@
     </row>
     <row r="30" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" s="1">
         <v>130</v>
       </c>
       <c r="D30" s="1">
-        <f t="shared" si="0"/>
-        <v>110.5</v>
+        <v>130</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H30" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2500,10 +2499,10 @@
     </row>
     <row r="31" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" s="1">
         <v>149</v>
@@ -2513,13 +2512,13 @@
         <v>126.65</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H31" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2531,10 +2530,10 @@
     </row>
     <row r="32" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" s="1">
         <v>159</v>
@@ -2544,13 +2543,13 @@
         <v>135.15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H32" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2562,10 +2561,10 @@
     </row>
     <row r="33" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C33" s="1">
         <v>129</v>
@@ -2574,13 +2573,13 @@
         <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H33" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2592,10 +2591,10 @@
     </row>
     <row r="34" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" s="1">
         <v>165</v>
@@ -2605,13 +2604,13 @@
         <v>140.25</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H34" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2623,10 +2622,10 @@
     </row>
     <row r="35" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C35" s="1">
         <v>165</v>
@@ -2636,13 +2635,13 @@
         <v>140.25</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H35" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2654,10 +2653,10 @@
     </row>
     <row r="36" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36" s="1">
         <v>135</v>
@@ -2667,13 +2666,13 @@
         <v>114.75</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H36" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2685,10 +2684,10 @@
     </row>
     <row r="37" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C37" s="1">
         <v>175</v>
@@ -2698,13 +2697,13 @@
         <v>148.75</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H37" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2716,10 +2715,10 @@
     </row>
     <row r="38" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C38" s="1">
         <v>199</v>
@@ -2728,13 +2727,13 @@
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H38" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2746,10 +2745,10 @@
     </row>
     <row r="39" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C39" s="1">
         <v>255</v>
@@ -2758,13 +2757,13 @@
         <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H39" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2776,10 +2775,10 @@
     </row>
     <row r="40" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C40" s="1">
         <v>165</v>
@@ -2789,13 +2788,13 @@
         <v>140.25</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H40" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2807,10 +2806,10 @@
     </row>
     <row r="41" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" s="1">
         <v>180</v>
@@ -2820,13 +2819,13 @@
         <v>153</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H41" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2841,10 +2840,10 @@
     </row>
     <row r="42" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C42" s="1">
         <v>170</v>
@@ -2854,13 +2853,13 @@
         <v>144.5</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H42" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2875,10 +2874,10 @@
     </row>
     <row r="43" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C43" s="1">
         <v>140</v>
@@ -2887,13 +2886,13 @@
         <v>0</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H43" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2908,10 +2907,10 @@
     </row>
     <row r="44" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C44" s="1">
         <v>159</v>
@@ -2921,13 +2920,13 @@
         <v>135.15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H44" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2939,10 +2938,10 @@
     </row>
     <row r="45" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C45" s="1">
         <v>159</v>
@@ -2952,13 +2951,13 @@
         <v>135.15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H45" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -2970,10 +2969,10 @@
     </row>
     <row r="46" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C46" s="1">
         <v>139</v>
@@ -2982,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H46" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3000,10 +2999,10 @@
     </row>
     <row r="47" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C47" s="1">
         <v>165</v>
@@ -3013,13 +3012,13 @@
         <v>140.25</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H47" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3031,10 +3030,10 @@
     </row>
     <row r="48" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C48" s="1">
         <v>165</v>
@@ -3044,13 +3043,13 @@
         <v>140.25</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H48" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3062,10 +3061,10 @@
     </row>
     <row r="49" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C49" s="1">
         <v>135</v>
@@ -3075,13 +3074,13 @@
         <v>114.75</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H49" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3093,10 +3092,10 @@
     </row>
     <row r="50" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C50" s="1">
         <v>175</v>
@@ -3106,13 +3105,13 @@
         <v>148.75</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H50" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3124,10 +3123,10 @@
     </row>
     <row r="51" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="1">
         <v>199</v>
@@ -3136,13 +3135,13 @@
         <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H51" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3154,10 +3153,10 @@
     </row>
     <row r="52" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C52" s="1">
         <v>0</v>
@@ -3167,13 +3166,13 @@
         <v>0</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H52" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3185,10 +3184,10 @@
     </row>
     <row r="53" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C53" s="1">
         <v>190</v>
@@ -3198,13 +3197,13 @@
         <v>161.5</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H53" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3219,10 +3218,10 @@
     </row>
     <row r="54" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C54" s="1">
         <v>175</v>
@@ -3232,13 +3231,13 @@
         <v>148.75</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H54" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3253,10 +3252,10 @@
     </row>
     <row r="55" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C55" s="1">
         <v>140</v>
@@ -3265,13 +3264,13 @@
         <v>0</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H55" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3286,10 +3285,10 @@
     </row>
     <row r="56" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C56" s="1">
         <v>169</v>
@@ -3299,13 +3298,13 @@
         <v>143.65</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H56" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3317,10 +3316,10 @@
     </row>
     <row r="57" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C57" s="1">
         <v>165</v>
@@ -3330,13 +3329,13 @@
         <v>140.25</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H57" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3348,10 +3347,10 @@
     </row>
     <row r="58" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C58" s="1">
         <v>139</v>
@@ -3360,13 +3359,13 @@
         <v>0</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H58" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3378,10 +3377,10 @@
     </row>
     <row r="59" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C59" s="1">
         <v>169</v>
@@ -3391,13 +3390,13 @@
         <v>143.65</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H59" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3409,10 +3408,10 @@
     </row>
     <row r="60" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C60" s="1">
         <v>185</v>
@@ -3422,13 +3421,13 @@
         <v>157.25</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H60" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3440,10 +3439,10 @@
     </row>
     <row r="61" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C61" s="1">
         <v>140</v>
@@ -3453,13 +3452,13 @@
         <v>119</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H61" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3471,10 +3470,10 @@
     </row>
     <row r="62" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C62" s="1">
         <v>189</v>
@@ -3484,13 +3483,13 @@
         <v>160.65</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H62" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3502,10 +3501,10 @@
     </row>
     <row r="63" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C63" s="1">
         <v>205</v>
@@ -3514,13 +3513,13 @@
         <v>0</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H63" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3532,10 +3531,10 @@
     </row>
     <row r="64" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C64" s="1">
         <v>0</v>
@@ -3545,13 +3544,13 @@
         <v>0</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H64" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3563,10 +3562,10 @@
     </row>
     <row r="65" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C65" s="1">
         <v>215</v>
@@ -3576,13 +3575,13 @@
         <v>182.75</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H65" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3597,10 +3596,10 @@
     </row>
     <row r="66" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C66" s="1">
         <v>185</v>
@@ -3610,13 +3609,13 @@
         <v>157.25</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H66" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3631,10 +3630,10 @@
     </row>
     <row r="67" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C67" s="1">
         <v>190</v>
@@ -3644,13 +3643,13 @@
         <v>161.5</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H67" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3665,10 +3664,10 @@
     </row>
     <row r="68" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C68" s="1">
         <v>170</v>
@@ -3678,13 +3677,13 @@
         <v>144.5</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H68" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3699,10 +3698,10 @@
     </row>
     <row r="69" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C69" s="1">
         <v>145</v>
@@ -3711,13 +3710,13 @@
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H69" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3732,10 +3731,10 @@
     </row>
     <row r="70" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C70" s="1">
         <v>195</v>
@@ -3745,13 +3744,13 @@
         <v>165.75</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H70" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3763,10 +3762,10 @@
     </row>
     <row r="71" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C71" s="1">
         <v>165</v>
@@ -3776,13 +3775,13 @@
         <v>140.25</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H71" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3794,10 +3793,10 @@
     </row>
     <row r="72" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C72" s="1">
         <v>159</v>
@@ -3807,13 +3806,13 @@
         <v>135.15</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H72" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3825,10 +3824,10 @@
     </row>
     <row r="73" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C73" s="1">
         <v>175</v>
@@ -3838,13 +3837,13 @@
         <v>148.75</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H73" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3856,10 +3855,10 @@
     </row>
     <row r="74" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C74" s="1">
         <v>169</v>
@@ -3869,13 +3868,13 @@
         <v>143.65</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H74" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3887,10 +3886,10 @@
     </row>
     <row r="75" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C75" s="1">
         <v>185</v>
@@ -3900,13 +3899,13 @@
         <v>157.25</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H75" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3918,10 +3917,10 @@
     </row>
     <row r="76" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C76" s="1">
         <v>150</v>
@@ -3931,13 +3930,13 @@
         <v>127.5</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H76" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3949,10 +3948,10 @@
     </row>
     <row r="77" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C77" s="1">
         <v>189</v>
@@ -3962,13 +3961,13 @@
         <v>160.65</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H77" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -3980,10 +3979,10 @@
     </row>
     <row r="78" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C78" s="1">
         <v>205</v>
@@ -3992,13 +3991,13 @@
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H78" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4010,10 +4009,10 @@
     </row>
     <row r="79" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C79" s="1">
         <v>315</v>
@@ -4022,13 +4021,13 @@
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H79" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4040,10 +4039,10 @@
     </row>
     <row r="80" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C80" s="1">
         <v>0</v>
@@ -4053,13 +4052,13 @@
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H80" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4071,10 +4070,10 @@
     </row>
     <row r="81" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C81" s="1">
         <v>169</v>
@@ -4084,13 +4083,13 @@
         <v>143.65</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H81" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4102,10 +4101,10 @@
     </row>
     <row r="82" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C82" s="1">
         <v>205</v>
@@ -4115,13 +4114,13 @@
         <v>174.25</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H82" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4133,10 +4132,10 @@
     </row>
     <row r="83" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C83" s="1">
         <v>215</v>
@@ -4146,13 +4145,13 @@
         <v>182.75</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H83" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4167,10 +4166,10 @@
     </row>
     <row r="84" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C84" s="1">
         <v>185</v>
@@ -4180,13 +4179,13 @@
         <v>157.25</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H84" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4201,10 +4200,10 @@
     </row>
     <row r="85" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C85" s="1">
         <v>190</v>
@@ -4214,13 +4213,13 @@
         <v>161.5</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H85" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4235,10 +4234,10 @@
     </row>
     <row r="86" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C86" s="1">
         <v>170</v>
@@ -4248,13 +4247,13 @@
         <v>144.5</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H86" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4269,10 +4268,10 @@
     </row>
     <row r="87" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C87" s="1">
         <v>145</v>
@@ -4281,13 +4280,13 @@
         <v>0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H87" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4302,10 +4301,10 @@
     </row>
     <row r="88" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C88" s="1">
         <v>195</v>
@@ -4315,13 +4314,13 @@
         <v>165.75</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H88" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4333,10 +4332,10 @@
     </row>
     <row r="89" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C89" s="1">
         <v>159</v>
@@ -4346,13 +4345,13 @@
         <v>135.15</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H89" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4364,10 +4363,10 @@
     </row>
     <row r="90" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C90" s="1">
         <v>169</v>
@@ -4377,13 +4376,13 @@
         <v>143.65</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H90" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4395,10 +4394,10 @@
     </row>
     <row r="91" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C91" s="1">
         <v>175</v>
@@ -4408,13 +4407,13 @@
         <v>148.75</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H91" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4426,10 +4425,10 @@
     </row>
     <row r="92" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C92" s="1">
         <v>179</v>
@@ -4439,13 +4438,13 @@
         <v>152.15</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H92" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4457,10 +4456,10 @@
     </row>
     <row r="93" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C93" s="1">
         <v>187</v>
@@ -4470,13 +4469,13 @@
         <v>158.94999999999999</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H93" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4488,10 +4487,10 @@
     </row>
     <row r="94" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C94" s="1">
         <v>155</v>
@@ -4501,13 +4500,13 @@
         <v>131.75</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H94" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4519,10 +4518,10 @@
     </row>
     <row r="95" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C95" s="1">
         <v>189</v>
@@ -4531,13 +4530,13 @@
         <v>0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H95" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4549,10 +4548,10 @@
     </row>
     <row r="96" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C96" s="1">
         <v>205</v>
@@ -4561,13 +4560,13 @@
         <v>0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H96" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4579,10 +4578,10 @@
     </row>
     <row r="97" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C97" s="1">
         <v>295</v>
@@ -4591,13 +4590,13 @@
         <v>0</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H97" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4609,10 +4608,10 @@
     </row>
     <row r="98" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C98" s="1">
         <v>0</v>
@@ -4622,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H98" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4640,10 +4639,10 @@
     </row>
     <row r="99" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C99" s="1">
         <v>220</v>
@@ -4653,13 +4652,13 @@
         <v>187</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H99" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4674,10 +4673,10 @@
     </row>
     <row r="100" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C100" s="1">
         <v>190</v>
@@ -4687,13 +4686,13 @@
         <v>161.5</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H100" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4708,10 +4707,10 @@
     </row>
     <row r="101" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C101" s="1">
         <v>185</v>
@@ -4721,13 +4720,13 @@
         <v>157.25</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H101" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4742,10 +4741,10 @@
     </row>
     <row r="102" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C102" s="1">
         <v>170</v>
@@ -4755,13 +4754,13 @@
         <v>144.5</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H102" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4776,10 +4775,10 @@
     </row>
     <row r="103" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C103" s="1">
         <v>145</v>
@@ -4788,13 +4787,13 @@
         <v>0</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H103" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4809,10 +4808,10 @@
     </row>
     <row r="104" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C104" s="1">
         <v>199</v>
@@ -4822,13 +4821,13 @@
         <v>169.15</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H104" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4840,10 +4839,10 @@
     </row>
     <row r="105" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C105" s="1">
         <v>169</v>
@@ -4853,13 +4852,13 @@
         <v>143.65</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H105" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4871,10 +4870,10 @@
     </row>
     <row r="106" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C106" s="1">
         <v>165</v>
@@ -4884,13 +4883,13 @@
         <v>140.25</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H106" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4902,10 +4901,10 @@
     </row>
     <row r="107" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C107" s="1">
         <v>175</v>
@@ -4915,13 +4914,13 @@
         <v>148.75</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H107" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4933,10 +4932,10 @@
     </row>
     <row r="108" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C108" s="1">
         <v>179</v>
@@ -4946,13 +4945,13 @@
         <v>152.15</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H108" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4964,10 +4963,10 @@
     </row>
     <row r="109" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C109" s="1">
         <v>195</v>
@@ -4977,13 +4976,13 @@
         <v>165.75</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H109" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -4995,10 +4994,10 @@
     </row>
     <row r="110" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C110" s="1">
         <v>155</v>
@@ -5008,13 +5007,13 @@
         <v>131.75</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H110" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5026,10 +5025,10 @@
     </row>
     <row r="111" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C111" s="1">
         <v>189</v>
@@ -5038,13 +5037,13 @@
         <v>0</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H111" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5056,10 +5055,10 @@
     </row>
     <row r="112" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C112" s="1">
         <v>205</v>
@@ -5068,13 +5067,13 @@
         <v>0</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H112" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5086,10 +5085,10 @@
     </row>
     <row r="113" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C113" s="1">
         <v>299</v>
@@ -5098,13 +5097,13 @@
         <v>0</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H113" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5116,10 +5115,10 @@
     </row>
     <row r="114" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C114" s="1">
         <v>0</v>
@@ -5129,13 +5128,13 @@
         <v>0</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H114" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5147,10 +5146,10 @@
     </row>
     <row r="115" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C115" s="1">
         <v>220</v>
@@ -5160,13 +5159,13 @@
         <v>187</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H115" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5178,10 +5177,10 @@
     </row>
     <row r="116" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C116" s="1">
         <v>187</v>
@@ -5190,13 +5189,13 @@
         <v>0</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H116" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5208,10 +5207,10 @@
     </row>
     <row r="117" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C117" s="1">
         <v>199</v>
@@ -5220,13 +5219,13 @@
         <v>0</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H117" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5238,10 +5237,10 @@
     </row>
     <row r="118" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C118" s="1">
         <v>185</v>
@@ -5250,13 +5249,13 @@
         <v>185</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H118" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5268,10 +5267,10 @@
     </row>
     <row r="119" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C119" s="1">
         <v>199</v>
@@ -5280,13 +5279,13 @@
         <v>0</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H119" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5298,10 +5297,10 @@
     </row>
     <row r="120" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C120" s="1">
         <v>205</v>
@@ -5310,13 +5309,13 @@
         <v>0</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H120" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5328,10 +5327,10 @@
     </row>
     <row r="121" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C121" s="1">
         <v>299</v>
@@ -5340,13 +5339,13 @@
         <v>0</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H121" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5358,10 +5357,10 @@
     </row>
     <row r="122" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C122" s="1">
         <v>0</v>
@@ -5371,13 +5370,13 @@
         <v>0</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H122" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5389,10 +5388,10 @@
     </row>
     <row r="123" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C123" s="1">
         <v>199</v>
@@ -5401,13 +5400,13 @@
         <v>0</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H123" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5419,10 +5418,10 @@
     </row>
     <row r="124" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C124" s="1">
         <v>185</v>
@@ -5431,13 +5430,13 @@
         <v>0</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H124" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5449,10 +5448,10 @@
     </row>
     <row r="125" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C125" s="1">
         <v>175</v>
@@ -5461,13 +5460,13 @@
         <v>0</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H125" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5479,10 +5478,10 @@
     </row>
     <row r="126" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C126" s="1">
         <v>199</v>
@@ -5491,13 +5490,13 @@
         <v>0</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H126" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5509,10 +5508,10 @@
     </row>
     <row r="127" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C127" s="1">
         <v>150</v>
@@ -5522,13 +5521,13 @@
         <v>127.5</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H127" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5540,10 +5539,10 @@
     </row>
     <row r="128" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C128" s="1">
         <v>139</v>
@@ -5552,13 +5551,13 @@
         <v>0</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H128" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5570,10 +5569,10 @@
     </row>
     <row r="129" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C129" s="1">
         <v>145</v>
@@ -5582,13 +5581,13 @@
         <v>0</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H129" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5603,10 +5602,10 @@
     </row>
     <row r="130" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C130" s="1">
         <v>175</v>
@@ -5616,13 +5615,13 @@
         <v>148.75</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H130" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5634,10 +5633,10 @@
     </row>
     <row r="131" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C131" s="1">
         <v>220</v>
@@ -5647,13 +5646,13 @@
         <v>187</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H131" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5665,10 +5664,10 @@
     </row>
     <row r="132" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C132" s="1">
         <v>189</v>
@@ -5678,13 +5677,13 @@
         <v>160.65</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H132" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5696,10 +5695,10 @@
     </row>
     <row r="133" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C133" s="1">
         <v>189</v>
@@ -5709,13 +5708,13 @@
         <v>160.65</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H133" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5727,10 +5726,10 @@
     </row>
     <row r="134" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C134" s="1">
         <v>185</v>
@@ -5740,13 +5739,13 @@
         <v>157.25</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H134" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5758,10 +5757,10 @@
     </row>
     <row r="135" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C135" s="1">
         <v>199</v>
@@ -5771,13 +5770,13 @@
         <v>169.15</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H135" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5789,10 +5788,10 @@
     </row>
     <row r="136" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C136" s="1">
         <v>205</v>
@@ -5801,13 +5800,13 @@
         <v>0</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H136" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5819,10 +5818,10 @@
     </row>
     <row r="137" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C137" s="1">
         <v>0</v>
@@ -5832,13 +5831,13 @@
         <v>0</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H137" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5850,10 +5849,10 @@
     </row>
     <row r="138" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C138" s="1">
         <v>375</v>
@@ -5862,13 +5861,13 @@
         <v>0</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H138" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5880,10 +5879,10 @@
     </row>
     <row r="139" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C139" s="1">
         <v>150</v>
@@ -5892,13 +5891,13 @@
         <v>0</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H139" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5910,10 +5909,10 @@
     </row>
     <row r="140" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C140" s="1">
         <v>199</v>
@@ -5923,13 +5922,13 @@
         <v>169.15</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H140" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5941,10 +5940,10 @@
     </row>
     <row r="141" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C141" s="1">
         <v>199</v>
@@ -5954,13 +5953,13 @@
         <v>169.15</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H141" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -5972,10 +5971,10 @@
     </row>
     <row r="142" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C142" s="1">
         <v>149</v>
@@ -5984,13 +5983,13 @@
         <v>0</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H142" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6002,10 +6001,10 @@
     </row>
     <row r="143" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C143" s="1">
         <v>179</v>
@@ -6015,13 +6014,13 @@
         <v>152.15</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H143" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6033,10 +6032,10 @@
     </row>
     <row r="144" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C144" s="1">
         <v>185</v>
@@ -6046,13 +6045,13 @@
         <v>157.25</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H144" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6064,10 +6063,10 @@
     </row>
     <row r="145" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C145" s="1">
         <v>175</v>
@@ -6077,13 +6076,13 @@
         <v>148.75</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H145" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6095,10 +6094,10 @@
     </row>
     <row r="146" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C146" s="1">
         <v>235</v>
@@ -6108,13 +6107,13 @@
         <v>199.75</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H146" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6126,10 +6125,10 @@
     </row>
     <row r="147" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C147" s="1">
         <v>199</v>
@@ -6139,13 +6138,13 @@
         <v>169.15</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H147" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6157,10 +6156,10 @@
     </row>
     <row r="148" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C148" s="1">
         <v>199</v>
@@ -6170,13 +6169,13 @@
         <v>169.15</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H148" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6188,10 +6187,10 @@
     </row>
     <row r="149" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C149" s="1">
         <v>185</v>
@@ -6201,13 +6200,13 @@
         <v>157.25</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H149" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6219,10 +6218,10 @@
     </row>
     <row r="150" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C150" s="1">
         <v>199</v>
@@ -6232,13 +6231,13 @@
         <v>169.15</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H150" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6250,10 +6249,10 @@
     </row>
     <row r="151" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C151" s="1">
         <v>205</v>
@@ -6262,13 +6261,13 @@
         <v>0</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H151" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6280,10 +6279,10 @@
     </row>
     <row r="152" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C152" s="1">
         <v>0</v>
@@ -6293,13 +6292,13 @@
         <v>0</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H152" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6311,10 +6310,10 @@
     </row>
     <row r="153" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C153" s="1">
         <v>0</v>
@@ -6324,13 +6323,13 @@
         <v>0</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H153" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6342,10 +6341,10 @@
     </row>
     <row r="154" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C154" s="1">
         <v>150</v>
@@ -6355,13 +6354,13 @@
         <v>127.5</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H154" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6373,10 +6372,10 @@
     </row>
     <row r="155" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C155" s="1">
         <v>199</v>
@@ -6386,13 +6385,13 @@
         <v>169.15</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H155" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6404,10 +6403,10 @@
     </row>
     <row r="156" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C156" s="1">
         <v>215</v>
@@ -6417,13 +6416,13 @@
         <v>182.75</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H156" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6435,10 +6434,10 @@
     </row>
     <row r="157" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C157" s="1">
         <v>189</v>
@@ -6448,13 +6447,13 @@
         <v>160.65</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H157" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6466,10 +6465,10 @@
     </row>
     <row r="158" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C158" s="1">
         <v>189</v>
@@ -6479,13 +6478,13 @@
         <v>160.65</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H158" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6497,10 +6496,10 @@
     </row>
     <row r="159" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C159" s="1">
         <v>149</v>
@@ -6509,13 +6508,13 @@
         <v>0</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H159" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6527,10 +6526,10 @@
     </row>
     <row r="160" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C160" s="1">
         <v>175</v>
@@ -6540,13 +6539,13 @@
         <v>148.75</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H160" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6558,10 +6557,10 @@
     </row>
     <row r="161" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C161" s="1">
         <v>180</v>
@@ -6571,13 +6570,13 @@
         <v>153</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H161" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6589,10 +6588,10 @@
     </row>
     <row r="162" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C162" s="1">
         <v>285</v>
@@ -6602,13 +6601,13 @@
         <v>242.25</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H162" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6620,10 +6619,10 @@
     </row>
     <row r="163" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C163" s="1">
         <v>275</v>
@@ -6633,13 +6632,13 @@
         <v>233.75</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H163" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6651,10 +6650,10 @@
     </row>
     <row r="164" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C164" s="1">
         <v>239</v>
@@ -6664,13 +6663,13 @@
         <v>203.15</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H164" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6682,10 +6681,10 @@
     </row>
     <row r="165" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C165" s="1">
         <v>174</v>
@@ -6695,13 +6694,13 @@
         <v>147.9</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H165" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6713,10 +6712,10 @@
     </row>
     <row r="166" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C166" s="1">
         <v>185</v>
@@ -6726,13 +6725,13 @@
         <v>157.25</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H166" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6744,10 +6743,10 @@
     </row>
     <row r="167" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C167" s="1">
         <v>259</v>
@@ -6757,13 +6756,13 @@
         <v>220.15</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H167" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6775,10 +6774,10 @@
     </row>
     <row r="168" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C168" s="1">
         <v>160</v>
@@ -6788,13 +6787,13 @@
         <v>136</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H168" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6806,10 +6805,10 @@
     </row>
     <row r="169" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C169" s="1">
         <v>340</v>
@@ -6819,13 +6818,13 @@
         <v>289</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H169" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6837,10 +6836,10 @@
     </row>
     <row r="170" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C170" s="1">
         <v>299</v>
@@ -6850,13 +6849,13 @@
         <v>254.15</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H170" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6868,10 +6867,10 @@
     </row>
     <row r="171" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C171" s="1">
         <v>218</v>
@@ -6881,13 +6880,13 @@
         <v>185.3</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H171" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6899,10 +6898,10 @@
     </row>
     <row r="172" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C172" s="1">
         <v>265</v>
@@ -6912,13 +6911,13 @@
         <v>225.25</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H172" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6930,10 +6929,10 @@
     </row>
     <row r="173" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C173" s="1">
         <v>270</v>
@@ -6943,13 +6942,13 @@
         <v>229.5</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H173" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6961,10 +6960,10 @@
     </row>
     <row r="174" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C174" s="1">
         <v>265</v>
@@ -6974,13 +6973,13 @@
         <v>225.25</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H174" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -6992,10 +6991,10 @@
     </row>
     <row r="175" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C175" s="1">
         <v>285</v>
@@ -7005,13 +7004,13 @@
         <v>242.25</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H175" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7023,10 +7022,10 @@
     </row>
     <row r="176" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C176" s="1">
         <v>340</v>
@@ -7036,13 +7035,13 @@
         <v>289</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H176" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7054,10 +7053,10 @@
     </row>
     <row r="177" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C177" s="1">
         <v>215</v>
@@ -7067,13 +7066,13 @@
         <v>182.75</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H177" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7085,10 +7084,10 @@
     </row>
     <row r="178" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C178">
         <v>299</v>
@@ -7098,13 +7097,13 @@
         <v>254.15</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H178" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7116,10 +7115,10 @@
     </row>
     <row r="179" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C179">
         <v>230</v>
@@ -7129,13 +7128,13 @@
         <v>195.5</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H179" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7147,10 +7146,10 @@
     </row>
     <row r="180" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C180">
         <v>325</v>
@@ -7160,13 +7159,13 @@
         <v>276.25</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H180" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7178,10 +7177,10 @@
     </row>
     <row r="181" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C181">
         <v>199</v>
@@ -7191,13 +7190,13 @@
         <v>169.15</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H181" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7209,10 +7208,10 @@
     </row>
     <row r="182" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C182">
         <v>445</v>
@@ -7222,13 +7221,13 @@
         <v>378.25</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H182" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7240,10 +7239,10 @@
     </row>
     <row r="183" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C183">
         <v>400</v>
@@ -7253,13 +7252,13 @@
         <v>340</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H183" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7271,10 +7270,10 @@
     </row>
     <row r="184" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C184">
         <v>285</v>
@@ -7284,13 +7283,13 @@
         <v>242.25</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H184" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7302,10 +7301,10 @@
     </row>
     <row r="185" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C185" s="1">
         <v>278</v>
@@ -7315,13 +7314,13 @@
         <v>236.3</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H185" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7333,10 +7332,10 @@
     </row>
     <row r="186" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C186" s="1">
         <v>405</v>
@@ -7346,13 +7345,13 @@
         <v>344.25</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H186" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7364,10 +7363,10 @@
     </row>
     <row r="187" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="C187">
         <v>360</v>
@@ -7377,13 +7376,13 @@
         <v>306</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H187" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7395,10 +7394,10 @@
     </row>
     <row r="188" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C188">
         <v>249</v>
@@ -7408,13 +7407,13 @@
         <v>211.65</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H188" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7426,10 +7425,10 @@
     </row>
     <row r="189" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C189">
         <v>329</v>
@@ -7439,13 +7438,13 @@
         <v>279.64999999999998</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H189" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7457,10 +7456,10 @@
     </row>
     <row r="190" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C190">
         <v>275</v>
@@ -7470,13 +7469,13 @@
         <v>233.75</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H190" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7488,10 +7487,10 @@
     </row>
     <row r="191" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C191">
         <v>229</v>
@@ -7501,13 +7500,13 @@
         <v>194.65</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H191" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7519,10 +7518,10 @@
     </row>
     <row r="192" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C192">
         <v>320</v>
@@ -7532,13 +7531,13 @@
         <v>272</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H192" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7550,10 +7549,10 @@
     </row>
     <row r="193" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C193">
         <v>320</v>
@@ -7563,13 +7562,13 @@
         <v>272</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H193" s="1">
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
@@ -7581,7 +7580,7 @@
     </row>
     <row r="194" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B194" s="1"/>
       <c r="D194" s="1"/>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3976BA2-F58B-4524-BB1D-27B8C6B487BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A48FEA-AC9B-47A9-9BE7-16BD576F66FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -772,7 +772,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -804,23 +804,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -846,7 +831,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -879,8 +864,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -2423,8 +2406,8 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I28" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.9</f>
+      <c r="I28" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>148.5</v>
       </c>
       <c r="J28" s="1"/>
@@ -2457,9 +2440,9 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I29" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.95</f>
-        <v>140.35</v>
+      <c r="I29" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>140.25</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -2490,9 +2473,9 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I30" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.73</f>
-        <v>107.33</v>
+      <c r="I30" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>107.25</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -2524,7 +2507,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I31" s="1"/>
+      <c r="I31" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>122.18</v>
+      </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
@@ -2555,7 +2541,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I32" s="1"/>
+      <c r="I32" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>130.38</v>
+      </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
     </row>
@@ -2585,7 +2574,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I33" s="1"/>
+      <c r="I33" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>105.78</v>
+      </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
     </row>
@@ -2616,7 +2608,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I34" s="1"/>
+      <c r="I34" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>135.30000000000001</v>
+      </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
     </row>
@@ -2647,7 +2642,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I35" s="1"/>
+      <c r="I35" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>132</v>
+      </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
     </row>
@@ -2678,7 +2676,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I36" s="1"/>
+      <c r="I36" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>110.7</v>
+      </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
     </row>
@@ -2709,7 +2710,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I37" s="1"/>
+      <c r="I37" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>143.5</v>
+      </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
     </row>
@@ -2739,7 +2743,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I38" s="1"/>
+      <c r="I38" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
     </row>
@@ -2769,7 +2776,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I39" s="1"/>
+      <c r="I39" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>209.1</v>
+      </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
     </row>
@@ -2800,7 +2810,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I40" s="1"/>
+      <c r="I40" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>135.30000000000001</v>
+      </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
     </row>
@@ -2831,8 +2844,8 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I41" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.9</f>
+      <c r="I41" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>148.5</v>
       </c>
       <c r="J41" s="1"/>
@@ -2865,9 +2878,9 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I42" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.95</f>
-        <v>140.35</v>
+      <c r="I42" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>140.25</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -2898,9 +2911,9 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I43" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.73</f>
-        <v>115.53</v>
+      <c r="I43" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>115.5</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -2932,7 +2945,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I44" s="1"/>
+      <c r="I44" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>130.38</v>
+      </c>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
     </row>
@@ -2963,7 +2979,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I45" s="1"/>
+      <c r="I45" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>130.38</v>
+      </c>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
     </row>
@@ -2993,7 +3012,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I46" s="1"/>
+      <c r="I46" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>113.98</v>
+      </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
     </row>
@@ -3024,7 +3046,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I47" s="1"/>
+      <c r="I47" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>135.30000000000001</v>
+      </c>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
     </row>
@@ -3055,7 +3080,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I48" s="1"/>
+      <c r="I48" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>132</v>
+      </c>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
     </row>
@@ -3086,7 +3114,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I49" s="1"/>
+      <c r="I49" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>110.7</v>
+      </c>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
     </row>
@@ -3117,7 +3148,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I50" s="1"/>
+      <c r="I50" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>143.5</v>
+      </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
     </row>
@@ -3147,7 +3181,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I51" s="1"/>
+      <c r="I51" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
     </row>
@@ -3178,7 +3215,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I52" s="1"/>
+      <c r="I52" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>0</v>
+      </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
     </row>
@@ -3210,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="13">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.95</f>
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>156.75</v>
       </c>
       <c r="J53" s="1"/>
@@ -3243,9 +3283,9 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I54" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.95</f>
-        <v>144.44999999999999</v>
+      <c r="I54" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>144.375</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -3276,9 +3316,9 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I55" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.73</f>
-        <v>115.53</v>
+      <c r="I55" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>115.5</v>
       </c>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -3310,7 +3350,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I56" s="1"/>
+      <c r="I56" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>138.58000000000001</v>
+      </c>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
     </row>
@@ -3341,7 +3384,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I57" s="1"/>
+      <c r="I57" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>135.30000000000001</v>
+      </c>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
     </row>
@@ -3371,7 +3417,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I58" s="1"/>
+      <c r="I58" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>113.98</v>
+      </c>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
     </row>
@@ -3402,7 +3451,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I59" s="1"/>
+      <c r="I59" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>138.58000000000001</v>
+      </c>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
     </row>
@@ -3433,7 +3485,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I60" s="1"/>
+      <c r="I60" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>148</v>
+      </c>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
     </row>
@@ -3464,7 +3519,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I61" s="1"/>
+      <c r="I61" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>114.8</v>
+      </c>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
     </row>
@@ -3495,7 +3553,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I62" s="1"/>
+      <c r="I62" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>154.98000000000002</v>
+      </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
     </row>
@@ -3525,7 +3586,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I63" s="1"/>
+      <c r="I63" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>168.1</v>
+      </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
     </row>
@@ -3556,7 +3620,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I64" s="1"/>
+      <c r="I64" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>0</v>
+      </c>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
     </row>
@@ -3588,8 +3655,8 @@
         <v>0</v>
       </c>
       <c r="I65" s="13">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+1.08</f>
-        <v>177.38000000000002</v>
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>177.375</v>
       </c>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
@@ -3621,9 +3688,9 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I66" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.93</f>
-        <v>152.63</v>
+      <c r="I66" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>152.625</v>
       </c>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
@@ -3655,8 +3722,8 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I67" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.95</f>
+      <c r="I67" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>156.75</v>
       </c>
       <c r="J67" s="1"/>
@@ -3689,8 +3756,8 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I68" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.85</f>
+      <c r="I68" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>140.25</v>
       </c>
       <c r="J68" s="1"/>
@@ -3722,9 +3789,9 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I69" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.73</f>
-        <v>119.63000000000001</v>
+      <c r="I69" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>119.625</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -3756,7 +3823,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I70" s="1"/>
+      <c r="I70" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>159.9</v>
+      </c>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
     </row>
@@ -3787,7 +3857,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I71" s="1"/>
+      <c r="I71" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>135.30000000000001</v>
+      </c>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
     </row>
@@ -3818,7 +3891,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I72" s="1"/>
+      <c r="I72" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>130.38</v>
+      </c>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
     </row>
@@ -3849,7 +3925,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I73" s="1"/>
+      <c r="I73" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>143.5</v>
+      </c>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
     </row>
@@ -3880,7 +3959,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I74" s="1"/>
+      <c r="I74" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>138.58000000000001</v>
+      </c>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
     </row>
@@ -3911,7 +3993,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I75" s="1"/>
+      <c r="I75" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>148</v>
+      </c>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
     </row>
@@ -3942,7 +4027,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I76" s="1"/>
+      <c r="I76" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>123</v>
+      </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
     </row>
@@ -3973,7 +4061,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I77" s="1"/>
+      <c r="I77" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>154.98000000000002</v>
+      </c>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
     </row>
@@ -4003,7 +4094,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I78" s="1"/>
+      <c r="I78" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>168.1</v>
+      </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
     </row>
@@ -4033,7 +4127,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I79" s="1"/>
+      <c r="I79" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>258.3</v>
+      </c>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
     </row>
@@ -4064,7 +4161,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I80" s="1"/>
+      <c r="I80" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>0</v>
+      </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
     </row>
@@ -4095,7 +4195,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I81" s="1"/>
+      <c r="I81" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>138.58000000000001</v>
+      </c>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
     </row>
@@ -4126,7 +4229,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I82" s="1"/>
+      <c r="I82" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>168.1</v>
+      </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
     </row>
@@ -4157,9 +4263,9 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I83" s="15">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+1.08</f>
-        <v>177.38000000000002</v>
+      <c r="I83" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>177.375</v>
       </c>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
@@ -4191,9 +4297,9 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I84" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.93</f>
-        <v>152.63</v>
+      <c r="I84" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>152.625</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
@@ -4225,8 +4331,8 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I85" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.95</f>
+      <c r="I85" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>156.75</v>
       </c>
       <c r="J85" s="1"/>
@@ -4259,8 +4365,8 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I86" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.85</f>
+      <c r="I86" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>140.25</v>
       </c>
       <c r="J86" s="1"/>
@@ -4292,9 +4398,9 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I87" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.73</f>
-        <v>119.63000000000001</v>
+      <c r="I87" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>119.625</v>
       </c>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
@@ -4326,7 +4432,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I88" s="1"/>
+      <c r="I88" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>159.9</v>
+      </c>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
     </row>
@@ -4357,7 +4466,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I89" s="1"/>
+      <c r="I89" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>130.38</v>
+      </c>
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
     </row>
@@ -4388,7 +4500,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I90" s="1"/>
+      <c r="I90" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>138.58000000000001</v>
+      </c>
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
     </row>
@@ -4419,7 +4534,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I91" s="1"/>
+      <c r="I91" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>143.5</v>
+      </c>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
     </row>
@@ -4450,7 +4568,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I92" s="1"/>
+      <c r="I92" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>146.78</v>
+      </c>
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
     </row>
@@ -4481,7 +4602,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I93" s="1"/>
+      <c r="I93" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>149.6</v>
+      </c>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
     </row>
@@ -4512,7 +4636,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I94" s="1"/>
+      <c r="I94" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>127.1</v>
+      </c>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
     </row>
@@ -4542,7 +4669,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I95" s="1"/>
+      <c r="I95" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>154.98000000000002</v>
+      </c>
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
     </row>
@@ -4572,7 +4702,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I96" s="1"/>
+      <c r="I96" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>168.1</v>
+      </c>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
     </row>
@@ -4602,7 +4735,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I97" s="1"/>
+      <c r="I97" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>241.9</v>
+      </c>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
     </row>
@@ -4633,7 +4769,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I98" s="1"/>
+      <c r="I98" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>0</v>
+      </c>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
     </row>
@@ -4665,7 +4804,7 @@
         <v>0</v>
       </c>
       <c r="I99" s="13">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+1.1</f>
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>181.5</v>
       </c>
       <c r="J99" s="1"/>
@@ -4698,8 +4837,8 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I100" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.95</f>
+      <c r="I100" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>156.75</v>
       </c>
       <c r="J100" s="1"/>
@@ -4732,9 +4871,9 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I101" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.93</f>
-        <v>152.63</v>
+      <c r="I101" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>152.625</v>
       </c>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
@@ -4766,8 +4905,8 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I102" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.85</f>
+      <c r="I102" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>140.25</v>
       </c>
       <c r="J102" s="1"/>
@@ -4799,9 +4938,9 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I103" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.73</f>
-        <v>119.63000000000001</v>
+      <c r="I103" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>119.625</v>
       </c>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
@@ -4833,7 +4972,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I104" s="1"/>
+      <c r="I104" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
     </row>
@@ -4864,7 +5006,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I105" s="1"/>
+      <c r="I105" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>138.58000000000001</v>
+      </c>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
     </row>
@@ -4895,7 +5040,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I106" s="1"/>
+      <c r="I106" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>135.30000000000001</v>
+      </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
     </row>
@@ -4926,7 +5074,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I107" s="1"/>
+      <c r="I107" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>143.5</v>
+      </c>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
     </row>
@@ -4957,7 +5108,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I108" s="1"/>
+      <c r="I108" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>146.78</v>
+      </c>
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
     </row>
@@ -4988,7 +5142,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I109" s="1"/>
+      <c r="I109" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>156</v>
+      </c>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
     </row>
@@ -5019,7 +5176,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I110" s="1"/>
+      <c r="I110" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>127.1</v>
+      </c>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
     </row>
@@ -5049,7 +5209,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I111" s="1"/>
+      <c r="I111" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>154.98000000000002</v>
+      </c>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
     </row>
@@ -5079,7 +5242,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I112" s="1"/>
+      <c r="I112" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>168.1</v>
+      </c>
       <c r="J112" s="1"/>
       <c r="K112" s="1"/>
     </row>
@@ -5109,7 +5275,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I113" s="1"/>
+      <c r="I113" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>245.18</v>
+      </c>
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
     </row>
@@ -5140,7 +5309,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I114" s="1"/>
+      <c r="I114" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>0</v>
+      </c>
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
     </row>
@@ -5171,7 +5343,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I115" s="1"/>
+      <c r="I115" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>180.4</v>
+      </c>
       <c r="J115" s="1"/>
       <c r="K115" s="1"/>
     </row>
@@ -5201,7 +5376,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I116" s="1"/>
+      <c r="I116" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>153.34</v>
+      </c>
       <c r="J116" s="1"/>
       <c r="K116" s="1"/>
     </row>
@@ -5231,7 +5409,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I117" s="1"/>
+      <c r="I117" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J117" s="1"/>
       <c r="K117" s="1"/>
     </row>
@@ -5261,7 +5442,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I118" s="1"/>
+      <c r="I118" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>151.69999999999999</v>
+      </c>
       <c r="J118" s="1"/>
       <c r="K118" s="1"/>
     </row>
@@ -5291,7 +5475,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I119" s="1"/>
+      <c r="I119" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J119" s="1"/>
       <c r="K119" s="1"/>
     </row>
@@ -5321,7 +5508,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I120" s="1"/>
+      <c r="I120" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>168.1</v>
+      </c>
       <c r="J120" s="1"/>
       <c r="K120" s="1"/>
     </row>
@@ -5351,7 +5541,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I121" s="1"/>
+      <c r="I121" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>245.18</v>
+      </c>
       <c r="J121" s="1"/>
       <c r="K121" s="1"/>
     </row>
@@ -5363,11 +5556,11 @@
         <v>84</v>
       </c>
       <c r="C122" s="1">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="D122" s="1">
         <f t="shared" ref="D122:D127" si="7">C122-C122*15/100</f>
-        <v>0</v>
+        <v>331.5</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>143</v>
@@ -5382,7 +5575,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I122" s="1"/>
+      <c r="I122" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>319.8</v>
+      </c>
       <c r="J122" s="1"/>
       <c r="K122" s="1"/>
     </row>
@@ -5412,7 +5608,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I123" s="1"/>
+      <c r="I123" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J123" s="1"/>
       <c r="K123" s="1"/>
     </row>
@@ -5442,7 +5641,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I124" s="1"/>
+      <c r="I124" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>151.69999999999999</v>
+      </c>
       <c r="J124" s="1"/>
       <c r="K124" s="1"/>
     </row>
@@ -5472,7 +5674,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I125" s="1"/>
+      <c r="I125" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>143.5</v>
+      </c>
       <c r="J125" s="1"/>
       <c r="K125" s="1"/>
     </row>
@@ -5502,7 +5707,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I126" s="1"/>
+      <c r="I126" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J126" s="1"/>
       <c r="K126" s="1"/>
     </row>
@@ -5533,7 +5741,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I127" s="1"/>
+      <c r="I127" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>123</v>
+      </c>
       <c r="J127" s="1"/>
       <c r="K127" s="1"/>
     </row>
@@ -5563,7 +5774,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I128" s="1"/>
+      <c r="I128" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>113.98</v>
+      </c>
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
     </row>
@@ -5593,9 +5807,9 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I129" s="14">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18/100+0.73</f>
-        <v>119.63000000000001</v>
+      <c r="I129" s="13">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
+        <v>119.625</v>
       </c>
       <c r="J129" s="1"/>
       <c r="K129" s="1"/>
@@ -5627,7 +5841,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I130" s="1"/>
+      <c r="I130" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>140</v>
+      </c>
       <c r="J130" s="1"/>
       <c r="K130" s="1"/>
     </row>
@@ -5658,7 +5875,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I131" s="1"/>
+      <c r="I131" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>180.4</v>
+      </c>
       <c r="J131" s="1"/>
       <c r="K131" s="1"/>
     </row>
@@ -5689,7 +5909,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I132" s="1"/>
+      <c r="I132" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>154.98000000000002</v>
+      </c>
       <c r="J132" s="1"/>
       <c r="K132" s="1"/>
     </row>
@@ -5720,7 +5943,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I133" s="1"/>
+      <c r="I133" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>154.98000000000002</v>
+      </c>
       <c r="J133" s="1"/>
       <c r="K133" s="1"/>
     </row>
@@ -5751,7 +5977,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I134" s="1"/>
+      <c r="I134" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>151.69999999999999</v>
+      </c>
       <c r="J134" s="1"/>
       <c r="K134" s="1"/>
     </row>
@@ -5782,7 +6011,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I135" s="1"/>
+      <c r="I135" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
     </row>
@@ -5812,7 +6044,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I136" s="1"/>
+      <c r="I136" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>168.1</v>
+      </c>
       <c r="J136" s="1"/>
       <c r="K136" s="1"/>
     </row>
@@ -5843,7 +6078,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I137" s="1"/>
+      <c r="I137" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>0</v>
+      </c>
       <c r="J137" s="1"/>
       <c r="K137" s="1"/>
     </row>
@@ -5873,7 +6111,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I138" s="1"/>
+      <c r="I138" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>307.5</v>
+      </c>
       <c r="J138" s="1"/>
       <c r="K138" s="1"/>
     </row>
@@ -5903,7 +6144,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I139" s="1"/>
+      <c r="I139" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>123</v>
+      </c>
       <c r="J139" s="1"/>
       <c r="K139" s="1"/>
     </row>
@@ -5934,7 +6178,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I140" s="1"/>
+      <c r="I140" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J140" s="1"/>
       <c r="K140" s="1"/>
     </row>
@@ -5965,7 +6212,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I141" s="1"/>
+      <c r="I141" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J141" s="1"/>
       <c r="K141" s="1"/>
     </row>
@@ -5995,7 +6245,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I142" s="1"/>
+      <c r="I142" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>122.18</v>
+      </c>
       <c r="J142" s="1"/>
       <c r="K142" s="1"/>
     </row>
@@ -6026,7 +6279,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I143" s="1"/>
+      <c r="I143" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>146.78</v>
+      </c>
       <c r="J143" s="1"/>
       <c r="K143" s="1"/>
     </row>
@@ -6057,7 +6313,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I144" s="1"/>
+      <c r="I144" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>151.69999999999999</v>
+      </c>
       <c r="J144" s="1"/>
       <c r="K144" s="1"/>
     </row>
@@ -6088,7 +6347,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I145" s="1"/>
+      <c r="I145" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>140</v>
+      </c>
       <c r="J145" s="1"/>
       <c r="K145" s="1"/>
     </row>
@@ -6119,7 +6381,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I146" s="1"/>
+      <c r="I146" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>192.7</v>
+      </c>
       <c r="J146" s="1"/>
       <c r="K146" s="1"/>
     </row>
@@ -6150,7 +6415,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I147" s="1"/>
+      <c r="I147" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J147" s="1"/>
       <c r="K147" s="1"/>
     </row>
@@ -6181,7 +6449,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I148" s="1"/>
+      <c r="I148" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J148" s="1"/>
       <c r="K148" s="1"/>
     </row>
@@ -6212,7 +6483,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I149" s="1"/>
+      <c r="I149" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>151.69999999999999</v>
+      </c>
       <c r="J149" s="1"/>
       <c r="K149" s="1"/>
     </row>
@@ -6243,7 +6517,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I150" s="1"/>
+      <c r="I150" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J150" s="1"/>
       <c r="K150" s="1"/>
     </row>
@@ -6273,7 +6550,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I151" s="1"/>
+      <c r="I151" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>168.1</v>
+      </c>
       <c r="J151" s="1"/>
       <c r="K151" s="1"/>
     </row>
@@ -6304,7 +6584,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I152" s="1"/>
+      <c r="I152" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>0</v>
+      </c>
       <c r="J152" s="1"/>
       <c r="K152" s="1"/>
     </row>
@@ -6335,7 +6618,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I153" s="1"/>
+      <c r="I153" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>0</v>
+      </c>
       <c r="J153" s="1"/>
       <c r="K153" s="1"/>
     </row>
@@ -6366,7 +6652,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I154" s="1"/>
+      <c r="I154" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>123</v>
+      </c>
       <c r="J154" s="1"/>
       <c r="K154" s="1"/>
     </row>
@@ -6397,7 +6686,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I155" s="1"/>
+      <c r="I155" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J155" s="1"/>
       <c r="K155" s="1"/>
     </row>
@@ -6428,7 +6720,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I156" s="1"/>
+      <c r="I156" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>176.3</v>
+      </c>
       <c r="J156" s="1"/>
       <c r="K156" s="1"/>
     </row>
@@ -6459,7 +6754,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I157" s="1"/>
+      <c r="I157" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>154.98000000000002</v>
+      </c>
       <c r="J157" s="1"/>
       <c r="K157" s="1"/>
     </row>
@@ -6490,7 +6788,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I158" s="1"/>
+      <c r="I158" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>154.98000000000002</v>
+      </c>
       <c r="J158" s="1"/>
       <c r="K158" s="1"/>
     </row>
@@ -6520,7 +6821,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I159" s="1"/>
+      <c r="I159" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>122.18</v>
+      </c>
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
     </row>
@@ -6551,7 +6855,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I160" s="1"/>
+      <c r="I160" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>140</v>
+      </c>
       <c r="J160" s="1"/>
       <c r="K160" s="1"/>
     </row>
@@ -6582,7 +6889,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I161" s="1"/>
+      <c r="I161" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>144</v>
+      </c>
       <c r="J161" s="1"/>
       <c r="K161" s="1"/>
     </row>
@@ -6613,7 +6923,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I162" s="1"/>
+      <c r="I162" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>233.7</v>
+      </c>
       <c r="J162" s="1"/>
       <c r="K162" s="1"/>
     </row>
@@ -6644,7 +6957,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I163" s="1"/>
+      <c r="I163" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>225.5</v>
+      </c>
       <c r="J163" s="1"/>
       <c r="K163" s="1"/>
     </row>
@@ -6675,7 +6991,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I164" s="1"/>
+      <c r="I164" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>195.98000000000002</v>
+      </c>
       <c r="J164" s="1"/>
       <c r="K164" s="1"/>
     </row>
@@ -6706,7 +7025,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I165" s="1"/>
+      <c r="I165" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>142.68</v>
+      </c>
       <c r="J165" s="1"/>
       <c r="K165" s="1"/>
     </row>
@@ -6737,7 +7059,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I166" s="1"/>
+      <c r="I166" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>151.69999999999999</v>
+      </c>
       <c r="J166" s="1"/>
       <c r="K166" s="1"/>
     </row>
@@ -6768,7 +7093,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I167" s="1"/>
+      <c r="I167" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>212.38</v>
+      </c>
       <c r="J167" s="1"/>
       <c r="K167" s="1"/>
     </row>
@@ -6799,7 +7127,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I168" s="1"/>
+      <c r="I168" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>128</v>
+      </c>
       <c r="J168" s="1"/>
       <c r="K168" s="1"/>
     </row>
@@ -6830,7 +7161,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I169" s="1"/>
+      <c r="I169" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>278.8</v>
+      </c>
       <c r="J169" s="1"/>
       <c r="K169" s="1"/>
     </row>
@@ -6861,7 +7195,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I170" s="1"/>
+      <c r="I170" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>245.18</v>
+      </c>
       <c r="J170" s="1"/>
       <c r="K170" s="1"/>
     </row>
@@ -6892,7 +7229,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I171" s="1"/>
+      <c r="I171" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>178.76</v>
+      </c>
       <c r="J171" s="1"/>
       <c r="K171" s="1"/>
     </row>
@@ -6923,7 +7263,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I172" s="1"/>
+      <c r="I172" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>217.3</v>
+      </c>
       <c r="J172" s="1"/>
       <c r="K172" s="1"/>
     </row>
@@ -6954,7 +7297,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I173" s="1"/>
+      <c r="I173" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>221.4</v>
+      </c>
       <c r="J173" s="1"/>
       <c r="K173" s="1"/>
     </row>
@@ -6985,7 +7331,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I174" s="1"/>
+      <c r="I174" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>217.3</v>
+      </c>
       <c r="J174" s="1"/>
       <c r="K174" s="1"/>
     </row>
@@ -7016,7 +7365,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I175" s="1"/>
+      <c r="I175" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>233.7</v>
+      </c>
       <c r="J175" s="1"/>
       <c r="K175" s="1"/>
     </row>
@@ -7047,7 +7399,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I176" s="1"/>
+      <c r="I176" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>278.8</v>
+      </c>
       <c r="J176" s="1"/>
       <c r="K176" s="1"/>
     </row>
@@ -7078,7 +7433,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I177" s="1"/>
+      <c r="I177" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>176.3</v>
+      </c>
       <c r="J177" s="1"/>
       <c r="K177" s="1"/>
     </row>
@@ -7109,7 +7467,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I178" s="1"/>
+      <c r="I178" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>245.18</v>
+      </c>
       <c r="J178" s="1"/>
       <c r="K178" s="1"/>
     </row>
@@ -7140,7 +7501,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I179" s="1"/>
+      <c r="I179" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>188.6</v>
+      </c>
       <c r="J179" s="1"/>
       <c r="K179" s="1"/>
     </row>
@@ -7171,7 +7535,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I180" s="1"/>
+      <c r="I180" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>266.5</v>
+      </c>
       <c r="J180" s="1"/>
       <c r="K180" s="1"/>
     </row>
@@ -7202,7 +7569,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I181" s="1"/>
+      <c r="I181" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
       <c r="J181" s="1"/>
       <c r="K181" s="1"/>
     </row>
@@ -7233,7 +7603,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I182" s="1"/>
+      <c r="I182" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>364.9</v>
+      </c>
       <c r="J182" s="1"/>
       <c r="K182" s="1"/>
     </row>
@@ -7264,7 +7637,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I183" s="1"/>
+      <c r="I183" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>328</v>
+      </c>
       <c r="J183" s="1"/>
       <c r="K183" s="1"/>
     </row>
@@ -7295,7 +7671,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I184" s="1"/>
+      <c r="I184" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>233.7</v>
+      </c>
       <c r="J184" s="1"/>
       <c r="K184" s="1"/>
     </row>
@@ -7326,7 +7705,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I185" s="1"/>
+      <c r="I185" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>227.96</v>
+      </c>
       <c r="J185" s="1"/>
       <c r="K185" s="1"/>
     </row>
@@ -7357,7 +7739,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I186" s="1"/>
+      <c r="I186" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>332.1</v>
+      </c>
       <c r="J186" s="1"/>
       <c r="K186" s="1"/>
     </row>
@@ -7388,7 +7773,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I187" s="1"/>
+      <c r="I187" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>288</v>
+      </c>
       <c r="J187" s="1"/>
       <c r="K187" s="1"/>
     </row>
@@ -7419,7 +7807,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I188" s="1"/>
+      <c r="I188" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>204.18</v>
+      </c>
       <c r="J188" s="1"/>
       <c r="K188" s="1"/>
     </row>
@@ -7450,7 +7841,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I189" s="1"/>
+      <c r="I189" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>269.77999999999997</v>
+      </c>
       <c r="J189" s="1"/>
       <c r="K189" s="1"/>
     </row>
@@ -7481,7 +7875,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I190" s="1"/>
+      <c r="I190" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>225.5</v>
+      </c>
       <c r="J190" s="1"/>
       <c r="K190" s="1"/>
     </row>
@@ -7512,7 +7909,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I191" s="1"/>
+      <c r="I191" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>187.78</v>
+      </c>
       <c r="J191" s="1"/>
       <c r="K191" s="1"/>
     </row>
@@ -7543,7 +7943,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I192" s="1"/>
+      <c r="I192" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>256</v>
+      </c>
       <c r="J192" s="1"/>
       <c r="K192" s="1"/>
     </row>
@@ -7574,7 +7977,10 @@
         <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
         <v>0</v>
       </c>
-      <c r="I193" s="1"/>
+      <c r="I193" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>256</v>
+      </c>
       <c r="J193" s="1"/>
       <c r="K193" s="1"/>
     </row>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A48FEA-AC9B-47A9-9BE7-16BD576F66FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AA84B3-632E-43A8-BC7C-15F822821FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="247">
   <si>
     <t>الأضواء عربي (شرح) ⬅️ 249</t>
   </si>
@@ -766,6 +766,12 @@
   </si>
   <si>
     <t>الكيان عربي اسئلة 4 أجزاء ⬅️ 360</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر ماث لغات ⬅️ 260</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاصر ساينس لغات ⬅️ 275</t>
   </si>
 </sst>
 </file>
@@ -3193,13 +3199,12 @@
         <v>56</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>83</v>
+        <v>245</v>
       </c>
       <c r="C52" s="1">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="D52" s="1">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -3217,7 +3222,7 @@
       </c>
       <c r="I52" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>0</v>
+        <v>213.2</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -4139,13 +4144,12 @@
         <v>58</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>84</v>
+        <v>246</v>
       </c>
       <c r="C80" s="1">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" ref="D80:D86" si="4">C80-C80*15/100</f>
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
@@ -4163,7 +4167,7 @@
       </c>
       <c r="I80" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>0</v>
+        <v>225.5</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
@@ -4179,7 +4183,7 @@
         <v>169</v>
       </c>
       <c r="D81" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="D80:D86" si="4">C81-C81*15/100</f>
         <v>143.65</v>
       </c>
       <c r="E81" s="1" t="s">
@@ -4747,14 +4751,13 @@
         <v>59</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>84</v>
+        <v>246</v>
       </c>
       <c r="C98" s="1">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="D98" s="1">
-        <f>C98-C98*15/100</f>
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>143</v>
@@ -4771,7 +4774,7 @@
       </c>
       <c r="I98" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>0</v>
+        <v>225.5</v>
       </c>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>

--- a/BookClac.xlsx
+++ b/BookClac.xlsx
@@ -1,37 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AA84B3-632E-43A8-BC7C-15F822821FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEF4C000-0282-4A10-A9A6-03309D05FB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الورقة1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="249">
   <si>
     <t>الأضواء عربي (شرح) ⬅️ 249</t>
   </si>
@@ -438,15 +428,6 @@
     <t>دار نشر</t>
   </si>
   <si>
-    <t>الرصيد الحالي</t>
-  </si>
-  <si>
-    <t>فاتورة شراء 2</t>
-  </si>
-  <si>
-    <t>فاتورة شراء 1</t>
-  </si>
-  <si>
     <t>بيان الأصناف</t>
   </si>
   <si>
@@ -772,6 +753,21 @@
   </si>
   <si>
     <t xml:space="preserve"> المعاصر ساينس لغات ⬅️ 275</t>
+  </si>
+  <si>
+    <t>امتحان عربي 2 بكالوريا</t>
+  </si>
+  <si>
+    <t>التفوق فيزياء أسئلة</t>
+  </si>
+  <si>
+    <t>عربي أسئلة</t>
+  </si>
+  <si>
+    <t>عربي شرح</t>
+  </si>
+  <si>
+    <t>فاتورة شراء - 1</t>
   </si>
 </sst>
 </file>
@@ -874,7 +870,7 @@
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="16">
     <dxf>
       <font>
         <b val="0"/>
@@ -1112,109 +1108,6 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1265,24 +1158,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:K194" totalsRowCount="1" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="A1:K193" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="الصف" totalsRowLabel="الإجمالي" dataDxfId="19" totalsRowDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="بيان الأصناف" dataDxfId="18" totalsRowDxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}" name="الجدول1" displayName="الجدول1" ref="A1:I196" totalsRowCount="1" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:I195" xr:uid="{A3732221-4191-4877-9D07-517759747CAF}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A59:I193">
+    <sortCondition ref="E1:E193"/>
+  </sortState>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{931861BC-C1A1-41C8-B2BE-2CE14068F4CF}" name="الصف" totalsRowLabel="الإجمالي" dataDxfId="12" totalsRowDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{D244CAF5-BC20-41FA-A7EA-E7F86A4741F0}" name="بيان الأصناف" dataDxfId="10" totalsRowDxfId="11"/>
     <tableColumn id="3" xr3:uid="{18281C2B-AE74-4493-8A8B-816AFDD52349}" name="سعر الغلاف"/>
-    <tableColumn id="4" xr3:uid="{0BC2C3D8-7FE3-4D02-BC47-E5D5B75D5119}" name="بعد الخصم" dataDxfId="17" totalsRowDxfId="7">
+    <tableColumn id="4" xr3:uid="{0BC2C3D8-7FE3-4D02-BC47-E5D5B75D5119}" name="بعد الخصم" dataDxfId="8" totalsRowDxfId="9">
       <calculatedColumnFormula>C2-C2*15/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{C8C8358C-407D-46CF-9CD0-E10403825CCB}" name="دار نشر" dataDxfId="16" totalsRowDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{77942F0C-9BAA-4860-8BA4-B6342B23E604}" name="مادة" dataDxfId="15" totalsRowDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{5145A455-0062-4306-9339-D70135665B07}" name="الصف الدراسي" dataDxfId="14" totalsRowDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{C1E3BA3A-59F6-4C98-98BC-3FEAF1455CFF}" name="الرصيد الحالي" dataDxfId="13" totalsRowDxfId="3">
-      <calculatedColumnFormula>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{C8C8358C-407D-46CF-9CD0-E10403825CCB}" name="دار نشر" dataDxfId="6" totalsRowDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{77942F0C-9BAA-4860-8BA4-B6342B23E604}" name="مادة" dataDxfId="4" totalsRowDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{5145A455-0062-4306-9339-D70135665B07}" name="الصف الدراسي" dataDxfId="2" totalsRowDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{06AB1CA4-0028-4BB8-BCD3-540944A0C992}" name="سعر الشراء" dataDxfId="0" totalsRowDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="فاتورة شراء - 1" totalsRowFunction="custom">
+      <totalsRowFormula>SUMPRODUCT(الجدول1[فاتورة شراء - 1],الجدول1[سعر الشراء])-(SUMPRODUCT(الجدول1[فاتورة شراء - 1],الجدول1[سعر الشراء])*2%)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{06AB1CA4-0028-4BB8-BCD3-540944A0C992}" name="سعر الشراء" dataDxfId="12" totalsRowDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{64D629DB-FC3B-4AB4-90A0-E10B2C9D6F79}" name="فاتورة شراء 2" dataDxfId="11" totalsRowDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{9A8DF73E-F7C3-4CEC-AD61-88FC64236287}" name="فاتورة شراء 1" totalsRowFunction="count" dataDxfId="10" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1489,7 +1383,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K194"/>
+  <dimension ref="A1:I198"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -1499,15 +1393,15 @@
     <col min="5" max="5" width="7" customWidth="1"/>
     <col min="6" max="6" width="6.85546875" customWidth="1"/>
     <col min="7" max="7" width="7.7109375" customWidth="1"/>
-    <col min="8" max="9" width="7.42578125" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="9" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>131</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>132</v>
@@ -1519,30 +1413,24 @@
         <v>134</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
@@ -1551,30 +1439,25 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H2" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="1">
         <v>8</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C3" s="1">
         <v>15</v>
@@ -1583,30 +1466,25 @@
         <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H3" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="1">
         <v>12</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C4" s="1">
         <v>15</v>
@@ -1615,30 +1493,25 @@
         <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H4" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="1">
         <v>11</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C5" s="1">
         <v>25</v>
@@ -1647,30 +1520,25 @@
         <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H5" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="1">
         <v>20</v>
       </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C6" s="1">
         <v>175</v>
@@ -1679,31 +1547,26 @@
         <v>175</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H6" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>140</v>
       </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C7" s="1">
         <v>175</v>
@@ -1712,31 +1575,26 @@
         <v>175</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H7" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>140</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C8" s="1">
         <v>175</v>
@@ -1745,31 +1603,26 @@
         <v>175</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H8" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>140</v>
       </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C9" s="1">
         <v>140</v>
@@ -1778,31 +1631,26 @@
         <v>140</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H9" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>112</v>
       </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C10" s="1">
         <v>140</v>
@@ -1811,31 +1659,26 @@
         <v>140</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H10" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>112</v>
       </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C11" s="1">
         <v>140</v>
@@ -1844,31 +1687,26 @@
         <v>140</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H11" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>112</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C12" s="1">
         <v>140</v>
@@ -1877,31 +1715,26 @@
         <v>140</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H12" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>112</v>
       </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C13" s="1">
         <v>25</v>
@@ -1910,30 +1743,25 @@
         <v>25</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H13" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
         <v>20</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C14" s="1">
         <v>25</v>
@@ -1942,30 +1770,25 @@
         <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H14" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
         <v>20</v>
       </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C15" s="1">
         <v>25</v>
@@ -1974,30 +1797,25 @@
         <v>25</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H15" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="1">
         <v>20</v>
       </c>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C16" s="1">
         <v>25</v>
@@ -2006,30 +1824,25 @@
         <v>25</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H16" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="1">
         <v>20</v>
       </c>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C17" s="1">
         <v>80</v>
@@ -2038,31 +1851,26 @@
         <v>80</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H17" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>64</v>
       </c>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C18" s="1">
         <v>100</v>
@@ -2071,31 +1879,26 @@
         <v>100</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H18" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>80</v>
       </c>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C19" s="1">
         <v>70</v>
@@ -2104,31 +1907,26 @@
         <v>70</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H19" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>56</v>
       </c>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C20" s="1">
         <v>90</v>
@@ -2137,31 +1935,26 @@
         <v>90</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H20" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>72</v>
       </c>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C21" s="1">
         <v>95</v>
@@ -2170,31 +1963,26 @@
         <v>95</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H21" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>76</v>
       </c>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-    </row>
-    <row r="22" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C22" s="1">
         <v>95</v>
@@ -2203,31 +1991,26 @@
         <v>95</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H22" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>76</v>
       </c>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C23" s="1">
         <v>115</v>
@@ -2236,31 +2019,26 @@
         <v>115</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H23" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>92</v>
       </c>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-    </row>
-    <row r="24" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C24" s="1">
         <v>450</v>
@@ -2269,31 +2047,26 @@
         <v>450</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H24" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>360</v>
       </c>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C25" s="1">
         <v>100</v>
@@ -2302,31 +2075,26 @@
         <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H25" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>80</v>
       </c>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-    </row>
-    <row r="26" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C26" s="1">
         <v>5</v>
@@ -2335,30 +2103,25 @@
         <v>5</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F26" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="H26" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="1">
         <v>3.5</v>
       </c>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-    </row>
-    <row r="27" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C27" s="1">
         <v>10</v>
@@ -2367,25 +2130,20 @@
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H27" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="1">
         <v>8</v>
       </c>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-    </row>
-    <row r="28" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
@@ -2400,26 +2158,21 @@
         <v>153</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H28" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="13">
+        <v>167</v>
+      </c>
+      <c r="H28" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>148.5</v>
       </c>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-    </row>
-    <row r="29" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>55</v>
       </c>
@@ -2434,26 +2187,21 @@
         <v>144.5</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H29" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="13">
+        <v>167</v>
+      </c>
+      <c r="H29" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>140.25</v>
       </c>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-    </row>
-    <row r="30" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>55</v>
       </c>
@@ -2467,26 +2215,21 @@
         <v>130</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H30" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="13">
+        <v>167</v>
+      </c>
+      <c r="H30" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>107.25</v>
       </c>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-    </row>
-    <row r="31" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>55</v>
       </c>
@@ -2501,26 +2244,21 @@
         <v>126.65</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H31" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>122.18</v>
       </c>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-    </row>
-    <row r="32" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>55</v>
       </c>
@@ -2535,26 +2273,21 @@
         <v>135.15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H32" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>130.38</v>
       </c>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-    </row>
-    <row r="33" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>55</v>
       </c>
@@ -2568,26 +2301,21 @@
         <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H33" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>105.78</v>
       </c>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-    </row>
-    <row r="34" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>55</v>
       </c>
@@ -2602,26 +2330,21 @@
         <v>140.25</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H34" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I34" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>135.30000000000001</v>
       </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-    </row>
-    <row r="35" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>55</v>
       </c>
@@ -2636,26 +2359,21 @@
         <v>140.25</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H35" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>132</v>
       </c>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-    </row>
-    <row r="36" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>55</v>
       </c>
@@ -2670,26 +2388,21 @@
         <v>114.75</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H36" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I36" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>110.7</v>
       </c>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-    </row>
-    <row r="37" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>55</v>
       </c>
@@ -2704,26 +2417,21 @@
         <v>148.75</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H37" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I37" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>143.5</v>
       </c>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-    </row>
-    <row r="38" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>55</v>
       </c>
@@ -2737,26 +2445,21 @@
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H38" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I38" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>163.18</v>
       </c>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-    </row>
-    <row r="39" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>55</v>
       </c>
@@ -2770,26 +2473,21 @@
         <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H39" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I39" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>209.1</v>
       </c>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-    </row>
-    <row r="40" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>55</v>
       </c>
@@ -2804,26 +2502,21 @@
         <v>140.25</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H40" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>135.30000000000001</v>
       </c>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-    </row>
-    <row r="41" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>56</v>
       </c>
@@ -2838,26 +2531,21 @@
         <v>153</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="H41" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I41" s="13">
+        <v>168</v>
+      </c>
+      <c r="H41" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>148.5</v>
       </c>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-    </row>
-    <row r="42" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>56</v>
       </c>
@@ -2872,26 +2560,21 @@
         <v>144.5</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="H42" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="13">
+        <v>168</v>
+      </c>
+      <c r="H42" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>140.25</v>
       </c>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-    </row>
-    <row r="43" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I42" s="1"/>
+    </row>
+    <row r="43" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>56</v>
       </c>
@@ -2905,26 +2588,21 @@
         <v>0</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="H43" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I43" s="13">
+        <v>168</v>
+      </c>
+      <c r="H43" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>115.5</v>
       </c>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-    </row>
-    <row r="44" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I43" s="1"/>
+    </row>
+    <row r="44" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>56</v>
       </c>
@@ -2939,26 +2617,21 @@
         <v>135.15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H44" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I44" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>130.38</v>
       </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-    </row>
-    <row r="45" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I44" s="1"/>
+    </row>
+    <row r="45" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>56</v>
       </c>
@@ -2973,26 +2646,21 @@
         <v>135.15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H45" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I45" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>130.38</v>
       </c>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-    </row>
-    <row r="46" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>56</v>
       </c>
@@ -3006,26 +2674,21 @@
         <v>0</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H46" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I46" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>113.98</v>
       </c>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-    </row>
-    <row r="47" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>56</v>
       </c>
@@ -3040,26 +2703,21 @@
         <v>140.25</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H47" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>135.30000000000001</v>
       </c>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-    </row>
-    <row r="48" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I47" s="1"/>
+    </row>
+    <row r="48" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,26 +2732,21 @@
         <v>140.25</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H48" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I48" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>132</v>
       </c>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-    </row>
-    <row r="49" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I48" s="1"/>
+    </row>
+    <row r="49" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>56</v>
       </c>
@@ -3108,26 +2761,21 @@
         <v>114.75</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H49" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I49" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>110.7</v>
       </c>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-    </row>
-    <row r="50" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I49" s="1"/>
+    </row>
+    <row r="50" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
@@ -3142,26 +2790,21 @@
         <v>148.75</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H50" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I50" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>143.5</v>
       </c>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-    </row>
-    <row r="51" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>56</v>
       </c>
@@ -3175,31 +2818,26 @@
         <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H51" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I51" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>163.18</v>
       </c>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-    </row>
-    <row r="52" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C52" s="1">
         <v>260</v>
@@ -3208,26 +2846,21 @@
         <v>0</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H52" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I52" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>213.2</v>
       </c>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-    </row>
-    <row r="53" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>57</v>
       </c>
@@ -3242,26 +2875,21 @@
         <v>161.5</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="H53" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I53" s="13">
+        <v>169</v>
+      </c>
+      <c r="H53" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>156.75</v>
       </c>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-    </row>
-    <row r="54" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I53" s="1"/>
+    </row>
+    <row r="54" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>57</v>
       </c>
@@ -3276,26 +2904,21 @@
         <v>148.75</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="H54" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I54" s="13">
+        <v>169</v>
+      </c>
+      <c r="H54" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>144.375</v>
       </c>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-    </row>
-    <row r="55" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I54" s="1"/>
+    </row>
+    <row r="55" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>57</v>
       </c>
@@ -3309,26 +2932,21 @@
         <v>0</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="H55" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="13">
+        <v>169</v>
+      </c>
+      <c r="H55" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>115.5</v>
       </c>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-    </row>
-    <row r="56" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I55" s="1"/>
+    </row>
+    <row r="56" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>57</v>
       </c>
@@ -3343,26 +2961,21 @@
         <v>143.65</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H56" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I56" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>138.58000000000001</v>
       </c>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-    </row>
-    <row r="57" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I56" s="1"/>
+    </row>
+    <row r="57" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>57</v>
       </c>
@@ -3377,26 +2990,21 @@
         <v>140.25</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H57" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I57" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>135.30000000000001</v>
       </c>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-    </row>
-    <row r="58" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I57" s="1"/>
+    </row>
+    <row r="58" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>57</v>
       </c>
@@ -3410,26 +3018,21 @@
         <v>0</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H58" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I58" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>113.98</v>
       </c>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-    </row>
-    <row r="59" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I58" s="1"/>
+    </row>
+    <row r="59" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>57</v>
       </c>
@@ -3440,30 +3043,25 @@
         <v>169</v>
       </c>
       <c r="D59" s="1">
-        <f t="shared" ref="D59:D68" si="2">C59-C59*15/100</f>
+        <f>C59-C59*15/100</f>
         <v>143.65</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H59" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I59" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>138.58000000000001</v>
       </c>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-    </row>
-    <row r="60" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I59" s="1"/>
+    </row>
+    <row r="60" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>57</v>
       </c>
@@ -3474,64 +3072,54 @@
         <v>185</v>
       </c>
       <c r="D60" s="1">
-        <f t="shared" si="2"/>
+        <f>C60-C60*15/100</f>
         <v>157.25</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H60" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I60" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>148</v>
       </c>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-    </row>
-    <row r="61" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I60" s="1"/>
+    </row>
+    <row r="61" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C61" s="1">
         <v>140</v>
       </c>
       <c r="D61" s="1">
-        <f t="shared" si="2"/>
+        <f>C61-C61*15/100</f>
         <v>119</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H61" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I61" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>114.8</v>
       </c>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-    </row>
-    <row r="62" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I61" s="1"/>
+    </row>
+    <row r="62" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>57</v>
       </c>
@@ -3542,30 +3130,25 @@
         <v>189</v>
       </c>
       <c r="D62" s="1">
-        <f t="shared" si="2"/>
+        <f>C62-C62*15/100</f>
         <v>160.65</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H62" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I62" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>154.98000000000002</v>
       </c>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-    </row>
-    <row r="63" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I62" s="1"/>
+    </row>
+    <row r="63" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>57</v>
       </c>
@@ -3579,26 +3162,21 @@
         <v>0</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H63" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I63" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>168.1</v>
       </c>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-    </row>
-    <row r="64" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I63" s="1"/>
+    </row>
+    <row r="64" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>57</v>
       </c>
@@ -3609,30 +3187,25 @@
         <v>0</v>
       </c>
       <c r="D64" s="1">
-        <f t="shared" si="2"/>
+        <f>C64-C64*15/100</f>
         <v>0</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H64" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>0</v>
       </c>
-      <c r="I64" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>0</v>
-      </c>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-    </row>
-    <row r="65" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I64" s="1"/>
+    </row>
+    <row r="65" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>58</v>
       </c>
@@ -3643,30 +3216,25 @@
         <v>215</v>
       </c>
       <c r="D65" s="1">
-        <f t="shared" si="2"/>
+        <f>C65-C65*15/100</f>
         <v>182.75</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H65" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I65" s="13">
+        <v>170</v>
+      </c>
+      <c r="H65" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>177.375</v>
       </c>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-    </row>
-    <row r="66" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I65" s="1"/>
+    </row>
+    <row r="66" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3677,30 +3245,25 @@
         <v>185</v>
       </c>
       <c r="D66" s="1">
-        <f t="shared" si="2"/>
+        <f>C66-C66*15/100</f>
         <v>157.25</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H66" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I66" s="13">
+        <v>170</v>
+      </c>
+      <c r="H66" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>152.625</v>
       </c>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-    </row>
-    <row r="67" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I66" s="1"/>
+    </row>
+    <row r="67" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3711,30 +3274,25 @@
         <v>190</v>
       </c>
       <c r="D67" s="1">
-        <f t="shared" si="2"/>
+        <f>C67-C67*15/100</f>
         <v>161.5</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H67" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I67" s="13">
+        <v>170</v>
+      </c>
+      <c r="H67" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>156.75</v>
       </c>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-    </row>
-    <row r="68" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I67" s="1"/>
+    </row>
+    <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>58</v>
       </c>
@@ -3745,30 +3303,25 @@
         <v>170</v>
       </c>
       <c r="D68" s="1">
-        <f t="shared" si="2"/>
+        <f>C68-C68*15/100</f>
         <v>144.5</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H68" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I68" s="13">
+        <v>170</v>
+      </c>
+      <c r="H68" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>140.25</v>
       </c>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-    </row>
-    <row r="69" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I68" s="1"/>
+    </row>
+    <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>58</v>
       </c>
@@ -3782,26 +3335,21 @@
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H69" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I69" s="13">
+        <v>170</v>
+      </c>
+      <c r="H69" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>119.625</v>
       </c>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-    </row>
-    <row r="70" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I69" s="1"/>
+    </row>
+    <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>58</v>
       </c>
@@ -3812,30 +3360,25 @@
         <v>195</v>
       </c>
       <c r="D70" s="1">
-        <f t="shared" ref="D70:D77" si="3">C70-C70*15/100</f>
+        <f>C70-C70*15/100</f>
         <v>165.75</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H70" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I70" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>159.9</v>
       </c>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-    </row>
-    <row r="71" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I70" s="1"/>
+    </row>
+    <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>58</v>
       </c>
@@ -3846,30 +3389,25 @@
         <v>165</v>
       </c>
       <c r="D71" s="1">
-        <f t="shared" si="3"/>
+        <f>C71-C71*15/100</f>
         <v>140.25</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H71" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I71" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>135.30000000000001</v>
       </c>
-      <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
-    </row>
-    <row r="72" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I71" s="1"/>
+    </row>
+    <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>58</v>
       </c>
@@ -3880,30 +3418,25 @@
         <v>159</v>
       </c>
       <c r="D72" s="1">
-        <f t="shared" si="3"/>
+        <f>C72-C72*15/100</f>
         <v>135.15</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H72" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I72" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>130.38</v>
       </c>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-    </row>
-    <row r="73" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I72" s="1"/>
+    </row>
+    <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>58</v>
       </c>
@@ -3914,30 +3447,25 @@
         <v>175</v>
       </c>
       <c r="D73" s="1">
-        <f t="shared" si="3"/>
+        <f>C73-C73*15/100</f>
         <v>148.75</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H73" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I73" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>143.5</v>
       </c>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
-    </row>
-    <row r="74" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I73" s="1"/>
+    </row>
+    <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>58</v>
       </c>
@@ -3948,64 +3476,54 @@
         <v>169</v>
       </c>
       <c r="D74" s="1">
-        <f t="shared" si="3"/>
+        <f>C74-C74*15/100</f>
         <v>143.65</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H74" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I74" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>138.58000000000001</v>
       </c>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
-    </row>
-    <row r="75" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I74" s="1"/>
+    </row>
+    <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C75" s="1">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D75" s="1">
-        <f t="shared" si="3"/>
-        <v>157.25</v>
+        <f>C75-C75*15/100</f>
+        <v>152.15</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H75" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I75" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
-        <v>148</v>
-      </c>
-      <c r="J75" s="1"/>
-      <c r="K75" s="1"/>
-    </row>
-    <row r="76" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>146.78</v>
+      </c>
+      <c r="I75" s="1"/>
+    </row>
+    <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>58</v>
       </c>
@@ -4016,30 +3534,25 @@
         <v>150</v>
       </c>
       <c r="D76" s="1">
-        <f t="shared" si="3"/>
+        <f>C76-C76*15/100</f>
         <v>127.5</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H76" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I76" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>123</v>
       </c>
-      <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
-    </row>
-    <row r="77" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I76" s="1"/>
+    </row>
+    <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>58</v>
       </c>
@@ -4050,30 +3563,25 @@
         <v>189</v>
       </c>
       <c r="D77" s="1">
-        <f t="shared" si="3"/>
+        <f>C77-C77*15/100</f>
         <v>160.65</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H77" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I77" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>154.98000000000002</v>
       </c>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
-    </row>
-    <row r="78" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I77" s="1"/>
+    </row>
+    <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>58</v>
       </c>
@@ -4087,26 +3595,21 @@
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H78" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I78" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>168.1</v>
       </c>
-      <c r="J78" s="1"/>
-      <c r="K78" s="1"/>
-    </row>
-    <row r="79" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I78" s="1"/>
+    </row>
+    <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>58</v>
       </c>
@@ -4120,31 +3623,26 @@
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H79" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I79" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>258.3</v>
       </c>
-      <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
-    </row>
-    <row r="80" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I79" s="1"/>
+    </row>
+    <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C80" s="1">
         <v>275</v>
@@ -4153,26 +3651,21 @@
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H80" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I80" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>225.5</v>
       </c>
-      <c r="J80" s="1"/>
-      <c r="K80" s="1"/>
-    </row>
-    <row r="81" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I80" s="1"/>
+    </row>
+    <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>58</v>
       </c>
@@ -4183,30 +3676,25 @@
         <v>169</v>
       </c>
       <c r="D81" s="1">
-        <f t="shared" ref="D80:D86" si="4">C81-C81*15/100</f>
+        <f>C81-C81*15/100</f>
         <v>143.65</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H81" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I81" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>138.58000000000001</v>
       </c>
-      <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
-    </row>
-    <row r="82" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I81" s="1"/>
+    </row>
+    <row r="82" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>58</v>
       </c>
@@ -4217,30 +3705,25 @@
         <v>205</v>
       </c>
       <c r="D82" s="1">
-        <f t="shared" si="4"/>
+        <f>C82-C82*15/100</f>
         <v>174.25</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H82" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I82" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>168.1</v>
       </c>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-    </row>
-    <row r="83" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I82" s="1"/>
+    </row>
+    <row r="83" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>59</v>
       </c>
@@ -4251,30 +3734,25 @@
         <v>215</v>
       </c>
       <c r="D83" s="1">
-        <f t="shared" si="4"/>
+        <f>C83-C83*15/100</f>
         <v>182.75</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H83" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I83" s="13">
+        <v>171</v>
+      </c>
+      <c r="H83" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>177.375</v>
       </c>
-      <c r="J83" s="1"/>
-      <c r="K83" s="1"/>
-    </row>
-    <row r="84" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I83" s="1"/>
+    </row>
+    <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>59</v>
       </c>
@@ -4285,30 +3763,25 @@
         <v>185</v>
       </c>
       <c r="D84" s="1">
-        <f t="shared" si="4"/>
+        <f>C84-C84*15/100</f>
         <v>157.25</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H84" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I84" s="13">
+        <v>171</v>
+      </c>
+      <c r="H84" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>152.625</v>
       </c>
-      <c r="J84" s="1"/>
-      <c r="K84" s="1"/>
-    </row>
-    <row r="85" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>59</v>
       </c>
@@ -4319,30 +3792,25 @@
         <v>190</v>
       </c>
       <c r="D85" s="1">
-        <f t="shared" si="4"/>
+        <f>C85-C85*15/100</f>
         <v>161.5</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H85" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I85" s="13">
+        <v>171</v>
+      </c>
+      <c r="H85" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>156.75</v>
       </c>
-      <c r="J85" s="1"/>
-      <c r="K85" s="1"/>
-    </row>
-    <row r="86" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I85" s="1"/>
+    </row>
+    <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>59</v>
       </c>
@@ -4353,30 +3821,25 @@
         <v>170</v>
       </c>
       <c r="D86" s="1">
-        <f t="shared" si="4"/>
+        <f>C86-C86*15/100</f>
         <v>144.5</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H86" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I86" s="13">
+        <v>171</v>
+      </c>
+      <c r="H86" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>140.25</v>
       </c>
-      <c r="J86" s="1"/>
-      <c r="K86" s="1"/>
-    </row>
-    <row r="87" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I86" s="1"/>
+    </row>
+    <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>59</v>
       </c>
@@ -4390,26 +3853,21 @@
         <v>0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H87" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I87" s="13">
+        <v>171</v>
+      </c>
+      <c r="H87" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>119.625</v>
       </c>
-      <c r="J87" s="1"/>
-      <c r="K87" s="1"/>
-    </row>
-    <row r="88" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I87" s="1"/>
+    </row>
+    <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>59</v>
       </c>
@@ -4420,30 +3878,25 @@
         <v>195</v>
       </c>
       <c r="D88" s="1">
-        <f t="shared" ref="D88:D94" si="5">C88-C88*15/100</f>
+        <f>C88-C88*15/100</f>
         <v>165.75</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H88" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I88" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>159.9</v>
       </c>
-      <c r="J88" s="1"/>
-      <c r="K88" s="1"/>
-    </row>
-    <row r="89" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>59</v>
       </c>
@@ -4454,30 +3907,25 @@
         <v>159</v>
       </c>
       <c r="D89" s="1">
-        <f t="shared" si="5"/>
+        <f>C89-C89*15/100</f>
         <v>135.15</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H89" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I89" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>130.38</v>
       </c>
-      <c r="J89" s="1"/>
-      <c r="K89" s="1"/>
-    </row>
-    <row r="90" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>59</v>
       </c>
@@ -4488,30 +3936,25 @@
         <v>169</v>
       </c>
       <c r="D90" s="1">
-        <f t="shared" si="5"/>
+        <f>C90-C90*15/100</f>
         <v>143.65</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H90" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I90" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>138.58000000000001</v>
       </c>
-      <c r="J90" s="1"/>
-      <c r="K90" s="1"/>
-    </row>
-    <row r="91" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>59</v>
       </c>
@@ -4522,64 +3965,53 @@
         <v>175</v>
       </c>
       <c r="D91" s="1">
-        <f t="shared" si="5"/>
+        <f>C91-C91*15/100</f>
         <v>148.75</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H91" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>143.5</v>
+      </c>
+      <c r="I91" s="1"/>
+    </row>
+    <row r="92" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C92" s="1">
+        <v>199</v>
+      </c>
+      <c r="D92" s="1">
         <v>0</v>
       </c>
-      <c r="I91" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>143.5</v>
-      </c>
-      <c r="J91" s="1"/>
-      <c r="K91" s="1"/>
-    </row>
-    <row r="92" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C92" s="1">
-        <v>179</v>
-      </c>
-      <c r="D92" s="1">
-        <f t="shared" si="5"/>
-        <v>152.15</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H92" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I92" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>146.78</v>
-      </c>
-      <c r="J92" s="1"/>
-      <c r="K92" s="1"/>
-    </row>
-    <row r="93" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
+      <c r="I92" s="1"/>
+    </row>
+    <row r="93" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>59</v>
       </c>
@@ -4590,30 +4022,25 @@
         <v>187</v>
       </c>
       <c r="D93" s="1">
-        <f t="shared" si="5"/>
+        <f>C93-C93*15/100</f>
         <v>158.94999999999999</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H93" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I93" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>149.6</v>
       </c>
-      <c r="J93" s="1"/>
-      <c r="K93" s="1"/>
-    </row>
-    <row r="94" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I93" s="1"/>
+    </row>
+    <row r="94" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>59</v>
       </c>
@@ -4624,30 +4051,25 @@
         <v>155</v>
       </c>
       <c r="D94" s="1">
-        <f t="shared" si="5"/>
+        <f>C94-C94*15/100</f>
         <v>131.75</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H94" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I94" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>127.1</v>
       </c>
-      <c r="J94" s="1"/>
-      <c r="K94" s="1"/>
-    </row>
-    <row r="95" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I94" s="1"/>
+    </row>
+    <row r="95" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>59</v>
       </c>
@@ -4661,26 +4083,21 @@
         <v>0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H95" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I95" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>154.98000000000002</v>
       </c>
-      <c r="J95" s="1"/>
-      <c r="K95" s="1"/>
-    </row>
-    <row r="96" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I95" s="1"/>
+    </row>
+    <row r="96" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>59</v>
       </c>
@@ -4694,26 +4111,21 @@
         <v>0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H96" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I96" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>168.1</v>
       </c>
-      <c r="J96" s="1"/>
-      <c r="K96" s="1"/>
-    </row>
-    <row r="97" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I96" s="1"/>
+    </row>
+    <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>59</v>
       </c>
@@ -4727,31 +4139,26 @@
         <v>0</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H97" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I97" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>241.9</v>
       </c>
-      <c r="J97" s="1"/>
-      <c r="K97" s="1"/>
-    </row>
-    <row r="98" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I97" s="1"/>
+    </row>
+    <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C98" s="1">
         <v>275</v>
@@ -4760,26 +4167,21 @@
         <v>235</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H98" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I98" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>225.5</v>
       </c>
-      <c r="J98" s="1"/>
-      <c r="K98" s="1"/>
-    </row>
-    <row r="99" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I98" s="1"/>
+    </row>
+    <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>60</v>
       </c>
@@ -4794,26 +4196,21 @@
         <v>187</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="H99" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I99" s="13">
+        <v>172</v>
+      </c>
+      <c r="H99" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>181.5</v>
       </c>
-      <c r="J99" s="1"/>
-      <c r="K99" s="1"/>
-    </row>
-    <row r="100" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I99" s="1"/>
+    </row>
+    <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>60</v>
       </c>
@@ -4828,26 +4225,21 @@
         <v>161.5</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="H100" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I100" s="13">
+        <v>172</v>
+      </c>
+      <c r="H100" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>156.75</v>
       </c>
-      <c r="J100" s="1"/>
-      <c r="K100" s="1"/>
-    </row>
-    <row r="101" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I100" s="1"/>
+    </row>
+    <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>60</v>
       </c>
@@ -4862,26 +4254,21 @@
         <v>157.25</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="H101" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I101" s="13">
+        <v>172</v>
+      </c>
+      <c r="H101" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>152.625</v>
       </c>
-      <c r="J101" s="1"/>
-      <c r="K101" s="1"/>
-    </row>
-    <row r="102" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I101" s="1"/>
+    </row>
+    <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>60</v>
       </c>
@@ -4896,26 +4283,21 @@
         <v>144.5</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="H102" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I102" s="13">
+        <v>172</v>
+      </c>
+      <c r="H102" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>140.25</v>
       </c>
-      <c r="J102" s="1"/>
-      <c r="K102" s="1"/>
-    </row>
-    <row r="103" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I102" s="1"/>
+    </row>
+    <row r="103" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,26 +4311,21 @@
         <v>0</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="H103" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I103" s="13">
+        <v>172</v>
+      </c>
+      <c r="H103" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>119.625</v>
       </c>
-      <c r="J103" s="1"/>
-      <c r="K103" s="1"/>
-    </row>
-    <row r="104" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I103" s="1"/>
+    </row>
+    <row r="104" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>60</v>
       </c>
@@ -4959,30 +4336,25 @@
         <v>199</v>
       </c>
       <c r="D104" s="1">
-        <f t="shared" ref="D104:D110" si="6">C104-C104*15/100</f>
+        <f>C104-C104*15/100</f>
         <v>169.15</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H104" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I104" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>163.18</v>
       </c>
-      <c r="J104" s="1"/>
-      <c r="K104" s="1"/>
-    </row>
-    <row r="105" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I104" s="1"/>
+    </row>
+    <row r="105" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>60</v>
       </c>
@@ -4993,30 +4365,25 @@
         <v>169</v>
       </c>
       <c r="D105" s="1">
-        <f t="shared" si="6"/>
+        <f>C105-C105*15/100</f>
         <v>143.65</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H105" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I105" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>138.58000000000001</v>
       </c>
-      <c r="J105" s="1"/>
-      <c r="K105" s="1"/>
-    </row>
-    <row r="106" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I105" s="1"/>
+    </row>
+    <row r="106" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>60</v>
       </c>
@@ -5027,30 +4394,25 @@
         <v>165</v>
       </c>
       <c r="D106" s="1">
-        <f t="shared" si="6"/>
+        <f>C106-C106*15/100</f>
         <v>140.25</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H106" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I106" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>135.30000000000001</v>
       </c>
-      <c r="J106" s="1"/>
-      <c r="K106" s="1"/>
-    </row>
-    <row r="107" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I106" s="1"/>
+    </row>
+    <row r="107" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>60</v>
       </c>
@@ -5061,30 +4423,25 @@
         <v>175</v>
       </c>
       <c r="D107" s="1">
-        <f t="shared" si="6"/>
+        <f>C107-C107*15/100</f>
         <v>148.75</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H107" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I107" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>143.5</v>
       </c>
-      <c r="J107" s="1"/>
-      <c r="K107" s="1"/>
-    </row>
-    <row r="108" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I107" s="1"/>
+    </row>
+    <row r="108" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,30 +4452,25 @@
         <v>179</v>
       </c>
       <c r="D108" s="1">
-        <f t="shared" si="6"/>
+        <f>C108-C108*15/100</f>
         <v>152.15</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H108" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I108" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>146.78</v>
       </c>
-      <c r="J108" s="1"/>
-      <c r="K108" s="1"/>
-    </row>
-    <row r="109" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I108" s="1"/>
+    </row>
+    <row r="109" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>60</v>
       </c>
@@ -5129,30 +4481,25 @@
         <v>195</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" si="6"/>
+        <f>C109-C109*15/100</f>
         <v>165.75</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H109" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I109" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>156</v>
       </c>
-      <c r="J109" s="1"/>
-      <c r="K109" s="1"/>
-    </row>
-    <row r="110" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I109" s="1"/>
+    </row>
+    <row r="110" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>60</v>
       </c>
@@ -5163,30 +4510,25 @@
         <v>155</v>
       </c>
       <c r="D110" s="1">
-        <f t="shared" si="6"/>
+        <f>C110-C110*15/100</f>
         <v>131.75</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H110" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I110" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>127.1</v>
       </c>
-      <c r="J110" s="1"/>
-      <c r="K110" s="1"/>
-    </row>
-    <row r="111" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I110" s="1"/>
+    </row>
+    <row r="111" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>60</v>
       </c>
@@ -5200,26 +4542,21 @@
         <v>0</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H111" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I111" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>154.98000000000002</v>
       </c>
-      <c r="J111" s="1"/>
-      <c r="K111" s="1"/>
-    </row>
-    <row r="112" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I111" s="1"/>
+    </row>
+    <row r="112" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>60</v>
       </c>
@@ -5233,26 +4570,21 @@
         <v>0</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H112" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I112" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>168.1</v>
       </c>
-      <c r="J112" s="1"/>
-      <c r="K112" s="1"/>
-    </row>
-    <row r="113" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I112" s="1"/>
+    </row>
+    <row r="113" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>60</v>
       </c>
@@ -5266,26 +4598,21 @@
         <v>0</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H113" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I113" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>245.18</v>
       </c>
-      <c r="J113" s="1"/>
-      <c r="K113" s="1"/>
-    </row>
-    <row r="114" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I113" s="1"/>
+    </row>
+    <row r="114" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>60</v>
       </c>
@@ -5293,33 +4620,27 @@
         <v>84</v>
       </c>
       <c r="C114" s="1">
+        <v>390</v>
+      </c>
+      <c r="D114" s="1">
         <v>0</v>
       </c>
-      <c r="D114" s="1">
-        <f>C114-C114*15/100</f>
-        <v>0</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H114" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I114" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>0</v>
-      </c>
-      <c r="J114" s="1"/>
-      <c r="K114" s="1"/>
-    </row>
-    <row r="115" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>319.8</v>
+      </c>
+      <c r="I114" s="1"/>
+    </row>
+    <row r="115" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>61</v>
       </c>
@@ -5334,26 +4655,21 @@
         <v>187</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H115" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I115" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>180.4</v>
       </c>
-      <c r="J115" s="1"/>
-      <c r="K115" s="1"/>
-    </row>
-    <row r="116" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I115" s="1"/>
+    </row>
+    <row r="116" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>61</v>
       </c>
@@ -5367,26 +4683,21 @@
         <v>0</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H116" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I116" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>153.34</v>
       </c>
-      <c r="J116" s="1"/>
-      <c r="K116" s="1"/>
-    </row>
-    <row r="117" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I116" s="1"/>
+    </row>
+    <row r="117" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>61</v>
       </c>
@@ -5400,26 +4711,21 @@
         <v>0</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H117" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I117" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>163.18</v>
       </c>
-      <c r="J117" s="1"/>
-      <c r="K117" s="1"/>
-    </row>
-    <row r="118" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I117" s="1"/>
+    </row>
+    <row r="118" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>61</v>
       </c>
@@ -5433,26 +4739,21 @@
         <v>185</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H118" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I118" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>151.69999999999999</v>
       </c>
-      <c r="J118" s="1"/>
-      <c r="K118" s="1"/>
-    </row>
-    <row r="119" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I118" s="1"/>
+    </row>
+    <row r="119" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>61</v>
       </c>
@@ -5466,26 +4767,21 @@
         <v>0</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H119" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I119" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>163.18</v>
       </c>
-      <c r="J119" s="1"/>
-      <c r="K119" s="1"/>
-    </row>
-    <row r="120" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I119" s="1"/>
+    </row>
+    <row r="120" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>61</v>
       </c>
@@ -5499,26 +4795,21 @@
         <v>0</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H120" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I120" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>168.1</v>
       </c>
-      <c r="J120" s="1"/>
-      <c r="K120" s="1"/>
-    </row>
-    <row r="121" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I120" s="1"/>
+    </row>
+    <row r="121" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>61</v>
       </c>
@@ -5532,26 +4823,21 @@
         <v>0</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H121" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I121" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>245.18</v>
       </c>
-      <c r="J121" s="1"/>
-      <c r="K121" s="1"/>
-    </row>
-    <row r="122" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I121" s="1"/>
+    </row>
+    <row r="122" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>61</v>
       </c>
@@ -5562,30 +4848,25 @@
         <v>390</v>
       </c>
       <c r="D122" s="1">
-        <f t="shared" ref="D122:D127" si="7">C122-C122*15/100</f>
+        <f>C122-C122*15/100</f>
         <v>331.5</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H122" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I122" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>319.8</v>
       </c>
-      <c r="J122" s="1"/>
-      <c r="K122" s="1"/>
-    </row>
-    <row r="123" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I122" s="1"/>
+    </row>
+    <row r="123" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>61</v>
       </c>
@@ -5599,26 +4880,21 @@
         <v>0</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H123" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I123" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>163.18</v>
       </c>
-      <c r="J123" s="1"/>
-      <c r="K123" s="1"/>
-    </row>
-    <row r="124" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I123" s="1"/>
+    </row>
+    <row r="124" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>61</v>
       </c>
@@ -5632,26 +4908,21 @@
         <v>0</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H124" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I124" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>151.69999999999999</v>
       </c>
-      <c r="J124" s="1"/>
-      <c r="K124" s="1"/>
-    </row>
-    <row r="125" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I124" s="1"/>
+    </row>
+    <row r="125" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>61</v>
       </c>
@@ -5665,59 +4936,50 @@
         <v>0</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H125" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I125" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>143.5</v>
       </c>
-      <c r="J125" s="1"/>
-      <c r="K125" s="1"/>
-    </row>
-    <row r="126" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I125" s="1"/>
+    </row>
+    <row r="126" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B126" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C126" s="1">
         <v>199</v>
       </c>
       <c r="D126" s="1">
-        <v>0</v>
+        <f>C126-C126*15/100</f>
+        <v>169.15</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H126" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I126" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>163.18</v>
       </c>
-      <c r="J126" s="1"/>
-      <c r="K126" s="1"/>
-    </row>
-    <row r="127" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I126" s="1"/>
+    </row>
+    <row r="127" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>61</v>
       </c>
@@ -5728,30 +4990,25 @@
         <v>150</v>
       </c>
       <c r="D127" s="1">
-        <f t="shared" si="7"/>
+        <f>C127-C127*15/100</f>
         <v>127.5</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H127" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I127" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>123</v>
       </c>
-      <c r="J127" s="1"/>
-      <c r="K127" s="1"/>
-    </row>
-    <row r="128" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I127" s="1"/>
+    </row>
+    <row r="128" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>61</v>
       </c>
@@ -5765,26 +5022,21 @@
         <v>0</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H128" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I128" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>113.98</v>
       </c>
-      <c r="J128" s="1"/>
-      <c r="K128" s="1"/>
-    </row>
-    <row r="129" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I128" s="1"/>
+    </row>
+    <row r="129" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>61</v>
       </c>
@@ -5798,26 +5050,21 @@
         <v>0</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="H129" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I129" s="13">
+        <v>173</v>
+      </c>
+      <c r="H129" s="13">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*17.5%</f>
         <v>119.625</v>
       </c>
-      <c r="J129" s="1"/>
-      <c r="K129" s="1"/>
-    </row>
-    <row r="130" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I129" s="1"/>
+    </row>
+    <row r="130" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>61</v>
       </c>
@@ -5832,94 +5079,79 @@
         <v>148.75</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H130" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I130" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>140</v>
       </c>
-      <c r="J130" s="1"/>
-      <c r="K130" s="1"/>
-    </row>
-    <row r="131" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I130" s="1"/>
+    </row>
+    <row r="131" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="C131" s="1">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="D131" s="1">
-        <f t="shared" ref="D131:D137" si="8">C131-C131*15/100</f>
-        <v>187</v>
+        <f>C131-C131*15/100</f>
+        <v>169.15</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H131" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I131" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>180.4</v>
-      </c>
-      <c r="J131" s="1"/>
-      <c r="K131" s="1"/>
-    </row>
-    <row r="132" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>163.18</v>
+      </c>
+      <c r="I131" s="1"/>
+    </row>
+    <row r="132" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="C132" s="1">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D132" s="1">
-        <f t="shared" si="8"/>
-        <v>160.65</v>
+        <f>C132-C132*15/100</f>
+        <v>182.75</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H132" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I132" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>154.98000000000002</v>
-      </c>
-      <c r="J132" s="1"/>
-      <c r="K132" s="1"/>
-    </row>
-    <row r="133" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>176.3</v>
+      </c>
+      <c r="I132" s="1"/>
+    </row>
+    <row r="133" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>62</v>
       </c>
@@ -5930,64 +5162,54 @@
         <v>189</v>
       </c>
       <c r="D133" s="1">
-        <f t="shared" si="8"/>
+        <f>C133-C133*15/100</f>
         <v>160.65</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H133" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>154.98000000000002</v>
+      </c>
+      <c r="I133" s="1"/>
+    </row>
+    <row r="134" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A134" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I133" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>154.98000000000002</v>
-      </c>
-      <c r="J133" s="1"/>
-      <c r="K133" s="1"/>
-    </row>
-    <row r="134" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A134" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C134" s="1">
-        <v>185</v>
+      <c r="C134">
+        <v>249</v>
       </c>
       <c r="D134" s="1">
-        <f t="shared" si="8"/>
-        <v>157.25</v>
+        <f>C134-C134*15/100</f>
+        <v>211.65</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>177</v>
       </c>
       <c r="H134" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I134" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>151.69999999999999</v>
-      </c>
-      <c r="J134" s="1"/>
-      <c r="K134" s="1"/>
-    </row>
-    <row r="135" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>204.18</v>
+      </c>
+      <c r="I134" s="1"/>
+    </row>
+    <row r="135" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
         <v>62</v>
       </c>
@@ -5998,30 +5220,25 @@
         <v>199</v>
       </c>
       <c r="D135" s="1">
-        <f t="shared" si="8"/>
+        <f>C135-C135*15/100</f>
         <v>169.15</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H135" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I135" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>163.18</v>
       </c>
-      <c r="J135" s="1"/>
-      <c r="K135" s="1"/>
-    </row>
-    <row r="136" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I135" s="1"/>
+    </row>
+    <row r="136" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
         <v>62</v>
       </c>
@@ -6035,26 +5252,21 @@
         <v>0</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H136" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I136" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>168.1</v>
       </c>
-      <c r="J136" s="1"/>
-      <c r="K136" s="1"/>
-    </row>
-    <row r="137" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I136" s="1"/>
+    </row>
+    <row r="137" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>62</v>
       </c>
@@ -6065,30 +5277,25 @@
         <v>0</v>
       </c>
       <c r="D137" s="1">
-        <f t="shared" si="8"/>
+        <f>C137-C137*15/100</f>
         <v>0</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H137" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>0</v>
       </c>
-      <c r="I137" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>0</v>
-      </c>
-      <c r="J137" s="1"/>
-      <c r="K137" s="1"/>
-    </row>
-    <row r="138" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I137" s="1"/>
+    </row>
+    <row r="138" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>62</v>
       </c>
@@ -6102,26 +5309,21 @@
         <v>0</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H138" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I138" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>307.5</v>
       </c>
-      <c r="J138" s="1"/>
-      <c r="K138" s="1"/>
-    </row>
-    <row r="139" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I138" s="1"/>
+    </row>
+    <row r="139" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>62</v>
       </c>
@@ -6135,60 +5337,50 @@
         <v>0</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H139" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I139" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>123</v>
       </c>
-      <c r="J139" s="1"/>
-      <c r="K139" s="1"/>
-    </row>
-    <row r="140" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I139" s="1"/>
+    </row>
+    <row r="140" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C140" s="1">
-        <v>199</v>
+        <v>66</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C140">
+        <v>329</v>
       </c>
       <c r="D140" s="1">
         <f>C140-C140*15/100</f>
-        <v>169.15</v>
+        <v>279.64999999999998</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>177</v>
       </c>
       <c r="H140" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I140" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>163.18</v>
-      </c>
-      <c r="J140" s="1"/>
-      <c r="K140" s="1"/>
-    </row>
-    <row r="141" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>269.77999999999997</v>
+      </c>
+      <c r="I140" s="1"/>
+    </row>
+    <row r="141" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>62</v>
       </c>
@@ -6203,26 +5395,21 @@
         <v>169.15</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H141" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I141" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>163.18</v>
       </c>
-      <c r="J141" s="1"/>
-      <c r="K141" s="1"/>
-    </row>
-    <row r="142" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I141" s="1"/>
+    </row>
+    <row r="142" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>62</v>
       </c>
@@ -6236,26 +5423,21 @@
         <v>0</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H142" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I142" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>122.18</v>
       </c>
-      <c r="J142" s="1"/>
-      <c r="K142" s="1"/>
-    </row>
-    <row r="143" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I142" s="1"/>
+    </row>
+    <row r="143" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
         <v>62</v>
       </c>
@@ -6270,26 +5452,21 @@
         <v>152.15</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H143" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I143" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>146.78</v>
       </c>
-      <c r="J143" s="1"/>
-      <c r="K143" s="1"/>
-    </row>
-    <row r="144" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I143" s="1"/>
+    </row>
+    <row r="144" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
         <v>62</v>
       </c>
@@ -6304,94 +5481,79 @@
         <v>157.25</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H144" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I144" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>151.69999999999999</v>
       </c>
-      <c r="J144" s="1"/>
-      <c r="K144" s="1"/>
-    </row>
-    <row r="145" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I144" s="1"/>
+    </row>
+    <row r="145" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B145" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C145" s="1">
-        <v>175</v>
+        <v>66</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C145">
+        <v>229</v>
       </c>
       <c r="D145" s="1">
-        <f t="shared" ref="D145:D150" si="9">C145-C145*15/100</f>
-        <v>148.75</v>
+        <f>C145-C145*15/100</f>
+        <v>194.65</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>177</v>
       </c>
       <c r="H145" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I145" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
-        <v>140</v>
-      </c>
-      <c r="J145" s="1"/>
-      <c r="K145" s="1"/>
-    </row>
-    <row r="146" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>187.78</v>
+      </c>
+      <c r="I145" s="1"/>
+    </row>
+    <row r="146" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="C146" s="1">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="D146" s="1">
-        <f t="shared" si="9"/>
-        <v>199.75</v>
+        <f>C146-C146*15/100</f>
+        <v>187</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H146" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I146" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>192.7</v>
-      </c>
-      <c r="J146" s="1"/>
-      <c r="K146" s="1"/>
-    </row>
-    <row r="147" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>180.4</v>
+      </c>
+      <c r="I146" s="1"/>
+    </row>
+    <row r="147" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>63</v>
       </c>
@@ -6402,30 +5564,25 @@
         <v>199</v>
       </c>
       <c r="D147" s="1">
-        <f t="shared" si="9"/>
+        <f>C147-C147*15/100</f>
         <v>169.15</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H147" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I147" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>163.18</v>
       </c>
-      <c r="J147" s="1"/>
-      <c r="K147" s="1"/>
-    </row>
-    <row r="148" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I147" s="1"/>
+    </row>
+    <row r="148" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>63</v>
       </c>
@@ -6436,30 +5593,25 @@
         <v>199</v>
       </c>
       <c r="D148" s="1">
-        <f t="shared" si="9"/>
+        <f>C148-C148*15/100</f>
         <v>169.15</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H148" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I148" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>163.18</v>
       </c>
-      <c r="J148" s="1"/>
-      <c r="K148" s="1"/>
-    </row>
-    <row r="149" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I148" s="1"/>
+    </row>
+    <row r="149" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
         <v>63</v>
       </c>
@@ -6470,30 +5622,25 @@
         <v>185</v>
       </c>
       <c r="D149" s="1">
-        <f t="shared" si="9"/>
+        <f>C149-C149*15/100</f>
         <v>157.25</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H149" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I149" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>151.69999999999999</v>
       </c>
-      <c r="J149" s="1"/>
-      <c r="K149" s="1"/>
-    </row>
-    <row r="150" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I149" s="1"/>
+    </row>
+    <row r="150" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
         <v>63</v>
       </c>
@@ -6504,30 +5651,25 @@
         <v>199</v>
       </c>
       <c r="D150" s="1">
-        <f t="shared" si="9"/>
+        <f>C150-C150*15/100</f>
         <v>169.15</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H150" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I150" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>163.18</v>
       </c>
-      <c r="J150" s="1"/>
-      <c r="K150" s="1"/>
-    </row>
-    <row r="151" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I150" s="1"/>
+    </row>
+    <row r="151" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
         <v>63</v>
       </c>
@@ -6541,26 +5683,21 @@
         <v>0</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H151" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I151" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>168.1</v>
       </c>
-      <c r="J151" s="1"/>
-      <c r="K151" s="1"/>
-    </row>
-    <row r="152" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I151" s="1"/>
+    </row>
+    <row r="152" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>63</v>
       </c>
@@ -6575,26 +5712,21 @@
         <v>0</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H152" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>0</v>
       </c>
-      <c r="I152" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>0</v>
-      </c>
-      <c r="J152" s="1"/>
-      <c r="K152" s="1"/>
-    </row>
-    <row r="153" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I152" s="1"/>
+    </row>
+    <row r="153" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
         <v>63</v>
       </c>
@@ -6609,26 +5741,21 @@
         <v>0</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H153" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>0</v>
       </c>
-      <c r="I153" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>0</v>
-      </c>
-      <c r="J153" s="1"/>
-      <c r="K153" s="1"/>
-    </row>
-    <row r="154" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I153" s="1"/>
+    </row>
+    <row r="154" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
         <v>63</v>
       </c>
@@ -6643,94 +5770,79 @@
         <v>127.5</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H154" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I154" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>123</v>
       </c>
-      <c r="J154" s="1"/>
-      <c r="K154" s="1"/>
-    </row>
-    <row r="155" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I154" s="1"/>
+    </row>
+    <row r="155" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>89</v>
+        <v>62</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C155" s="1">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D155" s="1">
         <f>C155-C155*15/100</f>
-        <v>169.15</v>
+        <v>160.65</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H155" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I155" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>163.18</v>
-      </c>
-      <c r="J155" s="1"/>
-      <c r="K155" s="1"/>
-    </row>
-    <row r="156" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>154.98000000000002</v>
+      </c>
+      <c r="I155" s="1"/>
+    </row>
+    <row r="156" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>80</v>
+      <c r="B156" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="C156" s="1">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="D156" s="1">
-        <f t="shared" ref="D156:D162" si="10">C156-C156*15/100</f>
-        <v>182.75</v>
+        <f>C156-C156*15/100</f>
+        <v>199.75</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H156" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I156" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>176.3</v>
-      </c>
-      <c r="J156" s="1"/>
-      <c r="K156" s="1"/>
-    </row>
-    <row r="157" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>192.7</v>
+      </c>
+      <c r="I156" s="1"/>
+    </row>
+    <row r="157" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
         <v>63</v>
       </c>
@@ -6741,30 +5853,25 @@
         <v>189</v>
       </c>
       <c r="D157" s="1">
-        <f t="shared" si="10"/>
+        <f>C157-C157*15/100</f>
         <v>160.65</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H157" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I157" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>154.98000000000002</v>
       </c>
-      <c r="J157" s="1"/>
-      <c r="K157" s="1"/>
-    </row>
-    <row r="158" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I157" s="1"/>
+    </row>
+    <row r="158" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
         <v>63</v>
       </c>
@@ -6775,30 +5882,25 @@
         <v>189</v>
       </c>
       <c r="D158" s="1">
-        <f t="shared" si="10"/>
+        <f>C158-C158*15/100</f>
         <v>160.65</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H158" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I158" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>154.98000000000002</v>
       </c>
-      <c r="J158" s="1"/>
-      <c r="K158" s="1"/>
-    </row>
-    <row r="159" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I158" s="1"/>
+    </row>
+    <row r="159" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
         <v>63</v>
       </c>
@@ -6812,26 +5914,21 @@
         <v>0</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H159" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I159" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>122.18</v>
       </c>
-      <c r="J159" s="1"/>
-      <c r="K159" s="1"/>
-    </row>
-    <row r="160" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I159" s="1"/>
+    </row>
+    <row r="160" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
         <v>63</v>
       </c>
@@ -6842,30 +5939,25 @@
         <v>175</v>
       </c>
       <c r="D160" s="1">
-        <f t="shared" si="10"/>
+        <f>C160-C160*15/100</f>
         <v>148.75</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H160" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I160" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>140</v>
       </c>
-      <c r="J160" s="1"/>
-      <c r="K160" s="1"/>
-    </row>
-    <row r="161" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I160" s="1"/>
+    </row>
+    <row r="161" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>64</v>
       </c>
@@ -6876,30 +5968,25 @@
         <v>180</v>
       </c>
       <c r="D161" s="1">
-        <f t="shared" si="10"/>
+        <f>C161-C161*15/100</f>
         <v>153</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H161" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I161" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>144</v>
       </c>
-      <c r="J161" s="1"/>
-      <c r="K161" s="1"/>
-    </row>
-    <row r="162" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I161" s="1"/>
+    </row>
+    <row r="162" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
         <v>64</v>
       </c>
@@ -6910,30 +5997,25 @@
         <v>285</v>
       </c>
       <c r="D162" s="1">
-        <f t="shared" si="10"/>
+        <f>C162-C162*15/100</f>
         <v>242.25</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H162" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I162" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>233.7</v>
       </c>
-      <c r="J162" s="1"/>
-      <c r="K162" s="1"/>
-    </row>
-    <row r="163" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I162" s="1"/>
+    </row>
+    <row r="163" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
         <v>64</v>
       </c>
@@ -6944,30 +6026,25 @@
         <v>275</v>
       </c>
       <c r="D163" s="1">
-        <f t="shared" ref="D163:D169" si="11">C163-C163*15/100</f>
+        <f>C163-C163*15/100</f>
         <v>233.75</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H163" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I163" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>225.5</v>
       </c>
-      <c r="J163" s="1"/>
-      <c r="K163" s="1"/>
-    </row>
-    <row r="164" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I163" s="1"/>
+    </row>
+    <row r="164" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
         <v>64</v>
       </c>
@@ -6978,30 +6055,25 @@
         <v>239</v>
       </c>
       <c r="D164" s="1">
-        <f t="shared" si="11"/>
+        <f>C164-C164*15/100</f>
         <v>203.15</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H164" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I164" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>195.98000000000002</v>
       </c>
-      <c r="J164" s="1"/>
-      <c r="K164" s="1"/>
-    </row>
-    <row r="165" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I164" s="1"/>
+    </row>
+    <row r="165" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
         <v>64</v>
       </c>
@@ -7012,30 +6084,25 @@
         <v>174</v>
       </c>
       <c r="D165" s="1">
-        <f t="shared" si="11"/>
+        <f>C165-C165*15/100</f>
         <v>147.9</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H165" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I165" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>142.68</v>
       </c>
-      <c r="J165" s="1"/>
-      <c r="K165" s="1"/>
-    </row>
-    <row r="166" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I165" s="1"/>
+    </row>
+    <row r="166" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
         <v>64</v>
       </c>
@@ -7046,30 +6113,25 @@
         <v>185</v>
       </c>
       <c r="D166" s="1">
-        <f t="shared" si="11"/>
+        <f>C166-C166*15/100</f>
         <v>157.25</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H166" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I166" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>151.69999999999999</v>
       </c>
-      <c r="J166" s="1"/>
-      <c r="K166" s="1"/>
-    </row>
-    <row r="167" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I166" s="1"/>
+    </row>
+    <row r="167" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>64</v>
       </c>
@@ -7080,30 +6142,25 @@
         <v>259</v>
       </c>
       <c r="D167" s="1">
-        <f t="shared" si="11"/>
+        <f>C167-C167*15/100</f>
         <v>220.15</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H167" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I167" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>212.38</v>
       </c>
-      <c r="J167" s="1"/>
-      <c r="K167" s="1"/>
-    </row>
-    <row r="168" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I167" s="1"/>
+    </row>
+    <row r="168" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
         <v>64</v>
       </c>
@@ -7114,30 +6171,25 @@
         <v>160</v>
       </c>
       <c r="D168" s="1">
-        <f t="shared" si="11"/>
+        <f>C168-C168*15/100</f>
         <v>136</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H168" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I168" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>128</v>
       </c>
-      <c r="J168" s="1"/>
-      <c r="K168" s="1"/>
-    </row>
-    <row r="169" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I168" s="1"/>
+    </row>
+    <row r="169" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
         <v>65</v>
       </c>
@@ -7148,35 +6200,30 @@
         <v>340</v>
       </c>
       <c r="D169" s="1">
-        <f t="shared" si="11"/>
+        <f>C169-C169*15/100</f>
         <v>289</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H169" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I169" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>278.8</v>
       </c>
-      <c r="J169" s="1"/>
-      <c r="K169" s="1"/>
-    </row>
-    <row r="170" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I169" s="1"/>
+    </row>
+    <row r="170" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C170" s="1">
         <v>299</v>
@@ -7186,26 +6233,21 @@
         <v>254.15</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H170" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I170" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>245.18</v>
       </c>
-      <c r="J170" s="1"/>
-      <c r="K170" s="1"/>
-    </row>
-    <row r="171" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I170" s="1"/>
+    </row>
+    <row r="171" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>66</v>
       </c>
@@ -7216,30 +6258,25 @@
         <v>218</v>
       </c>
       <c r="D171" s="1">
-        <f t="shared" ref="D171:D190" si="12">C171-C171*15/100</f>
+        <f>C171-C171*15/100</f>
         <v>185.3</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H171" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I171" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>178.76</v>
       </c>
-      <c r="J171" s="1"/>
-      <c r="K171" s="1"/>
-    </row>
-    <row r="172" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I171" s="1"/>
+    </row>
+    <row r="172" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
         <v>66</v>
       </c>
@@ -7250,30 +6287,25 @@
         <v>265</v>
       </c>
       <c r="D172" s="1">
-        <f t="shared" si="12"/>
+        <f>C172-C172*15/100</f>
         <v>225.25</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H172" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I172" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>217.3</v>
       </c>
-      <c r="J172" s="1"/>
-      <c r="K172" s="1"/>
-    </row>
-    <row r="173" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I172" s="1"/>
+    </row>
+    <row r="173" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
         <v>66</v>
       </c>
@@ -7288,26 +6320,21 @@
         <v>229.5</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H173" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I173" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>221.4</v>
       </c>
-      <c r="J173" s="1"/>
-      <c r="K173" s="1"/>
-    </row>
-    <row r="174" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I173" s="1"/>
+    </row>
+    <row r="174" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
         <v>66</v>
       </c>
@@ -7322,26 +6349,21 @@
         <v>225.25</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H174" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I174" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>217.3</v>
       </c>
-      <c r="J174" s="1"/>
-      <c r="K174" s="1"/>
-    </row>
-    <row r="175" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I174" s="1"/>
+    </row>
+    <row r="175" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
         <v>66</v>
       </c>
@@ -7352,30 +6374,25 @@
         <v>285</v>
       </c>
       <c r="D175" s="1">
-        <f t="shared" si="12"/>
+        <f>C175-C175*15/100</f>
         <v>242.25</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H175" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I175" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>233.7</v>
       </c>
-      <c r="J175" s="1"/>
-      <c r="K175" s="1"/>
-    </row>
-    <row r="176" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I175" s="1"/>
+    </row>
+    <row r="176" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
         <v>66</v>
       </c>
@@ -7386,30 +6403,25 @@
         <v>340</v>
       </c>
       <c r="D176" s="1">
-        <f t="shared" si="12"/>
+        <f>C176-C176*15/100</f>
         <v>289</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H176" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I176" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>278.8</v>
       </c>
-      <c r="J176" s="1"/>
-      <c r="K176" s="1"/>
-    </row>
-    <row r="177" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I176" s="1"/>
+    </row>
+    <row r="177" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
         <v>66</v>
       </c>
@@ -7420,30 +6432,25 @@
         <v>215</v>
       </c>
       <c r="D177" s="1">
-        <f t="shared" si="12"/>
+        <f>C177-C177*15/100</f>
         <v>182.75</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H177" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I177" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>176.3</v>
       </c>
-      <c r="J177" s="1"/>
-      <c r="K177" s="1"/>
-    </row>
-    <row r="178" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I177" s="1"/>
+    </row>
+    <row r="178" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
         <v>66</v>
       </c>
@@ -7458,26 +6465,21 @@
         <v>254.15</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H178" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I178" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>245.18</v>
       </c>
-      <c r="J178" s="1"/>
-      <c r="K178" s="1"/>
-    </row>
-    <row r="179" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I178" s="1"/>
+    </row>
+    <row r="179" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
         <v>66</v>
       </c>
@@ -7488,30 +6490,25 @@
         <v>230</v>
       </c>
       <c r="D179" s="1">
-        <f t="shared" si="12"/>
+        <f>C179-C179*15/100</f>
         <v>195.5</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H179" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I179" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>188.6</v>
       </c>
-      <c r="J179" s="1"/>
-      <c r="K179" s="1"/>
-    </row>
-    <row r="180" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I179" s="1"/>
+    </row>
+    <row r="180" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
         <v>66</v>
       </c>
@@ -7526,26 +6523,21 @@
         <v>276.25</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H180" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I180" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>266.5</v>
       </c>
-      <c r="J180" s="1"/>
-      <c r="K180" s="1"/>
-    </row>
-    <row r="181" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I180" s="1"/>
+    </row>
+    <row r="181" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
         <v>66</v>
       </c>
@@ -7556,30 +6548,25 @@
         <v>199</v>
       </c>
       <c r="D181" s="1">
-        <f t="shared" si="12"/>
+        <f>C181-C181*15/100</f>
         <v>169.15</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H181" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I181" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>163.18</v>
       </c>
-      <c r="J181" s="1"/>
-      <c r="K181" s="1"/>
-    </row>
-    <row r="182" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I181" s="1"/>
+    </row>
+    <row r="182" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
         <v>66</v>
       </c>
@@ -7590,30 +6577,25 @@
         <v>445</v>
       </c>
       <c r="D182" s="1">
-        <f t="shared" si="12"/>
+        <f>C182-C182*15/100</f>
         <v>378.25</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H182" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I182" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>364.9</v>
       </c>
-      <c r="J182" s="1"/>
-      <c r="K182" s="1"/>
-    </row>
-    <row r="183" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="I182" s="1"/>
+    </row>
+    <row r="183" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
         <v>66</v>
       </c>
@@ -7624,98 +6606,83 @@
         <v>400</v>
       </c>
       <c r="D183" s="1">
-        <f t="shared" si="12"/>
+        <f>C183-C183*15/100</f>
         <v>340</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H183" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I183" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>328</v>
       </c>
-      <c r="J183" s="1"/>
-      <c r="K183" s="1"/>
-    </row>
-    <row r="184" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I183" s="1"/>
+    </row>
+    <row r="184" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C184">
-        <v>285</v>
+        <v>53</v>
+      </c>
+      <c r="C184" s="1">
+        <v>278</v>
       </c>
       <c r="D184" s="1">
         <f>C184-C184*15/100</f>
-        <v>242.25</v>
+        <v>236.3</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>153</v>
+        <v>247</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H184" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I184" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>233.7</v>
-      </c>
-      <c r="J184" s="1"/>
-      <c r="K184" s="1"/>
-    </row>
-    <row r="185" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>227.96</v>
+      </c>
+      <c r="I184" s="1"/>
+    </row>
+    <row r="185" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="C185" s="1">
-        <v>278</v>
+        <v>175</v>
       </c>
       <c r="D185" s="1">
-        <f t="shared" si="12"/>
-        <v>236.3</v>
+        <f>C185-C185*15/100</f>
+        <v>148.75</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H185" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I185" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>227.96</v>
-      </c>
-      <c r="J185" s="1"/>
-      <c r="K185" s="1"/>
-    </row>
-    <row r="186" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>140</v>
+      </c>
+      <c r="I185" s="1"/>
+    </row>
+    <row r="186" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
         <v>66</v>
       </c>
@@ -7726,132 +6693,112 @@
         <v>405</v>
       </c>
       <c r="D186" s="1">
-        <f t="shared" si="12"/>
+        <f>C186-C186*15/100</f>
         <v>344.25</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>154</v>
+        <v>246</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H186" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I186" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>332.1</v>
       </c>
-      <c r="J186" s="1"/>
-      <c r="K186" s="1"/>
-    </row>
-    <row r="187" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I186" s="1"/>
+    </row>
+    <row r="187" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>244</v>
+        <v>148</v>
       </c>
       <c r="C187">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="D187" s="1">
-        <f t="shared" si="12"/>
-        <v>306</v>
+        <f>C187-C187*15/100</f>
+        <v>272</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>149</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H187" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I187" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>256</v>
+      </c>
+      <c r="I187" s="1"/>
+    </row>
+    <row r="188" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C188" s="1">
+        <v>185</v>
+      </c>
+      <c r="D188" s="1">
+        <f>C188-C188*15/100</f>
+        <v>157.25</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H188" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>148</v>
+      </c>
+      <c r="I188" s="1"/>
+    </row>
+    <row r="189" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C189">
+        <v>360</v>
+      </c>
+      <c r="D189" s="1">
+        <f>C189-C189*15/100</f>
+        <v>306</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H189" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>288</v>
       </c>
-      <c r="J187" s="1"/>
-      <c r="K187" s="1"/>
-    </row>
-    <row r="188" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C188">
-        <v>249</v>
-      </c>
-      <c r="D188" s="1">
-        <f t="shared" si="12"/>
-        <v>211.65</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G188" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="H188" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I188" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>204.18</v>
-      </c>
-      <c r="J188" s="1"/>
-      <c r="K188" s="1"/>
-    </row>
-    <row r="189" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C189">
-        <v>329</v>
-      </c>
-      <c r="D189" s="1">
-        <f t="shared" si="12"/>
-        <v>279.64999999999998</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G189" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="H189" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I189" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>269.77999999999997</v>
-      </c>
-      <c r="J189" s="1"/>
-      <c r="K189" s="1"/>
-    </row>
-    <row r="190" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I189" s="1"/>
+    </row>
+    <row r="190" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
         <v>66</v>
       </c>
@@ -7862,64 +6809,54 @@
         <v>275</v>
       </c>
       <c r="D190" s="1">
-        <f t="shared" si="12"/>
+        <f>C190-C190*15/100</f>
         <v>233.75</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H190" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I190" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
         <v>225.5</v>
       </c>
-      <c r="J190" s="1"/>
-      <c r="K190" s="1"/>
-    </row>
-    <row r="191" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I190" s="1"/>
+    </row>
+    <row r="191" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C191">
-        <v>229</v>
+        <v>62</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C191" s="1">
+        <v>185</v>
       </c>
       <c r="D191" s="1">
         <f>C191-C191*15/100</f>
-        <v>194.65</v>
+        <v>157.25</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H191" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I191" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
-        <v>187.78</v>
-      </c>
-      <c r="J191" s="1"/>
-      <c r="K191" s="1"/>
-    </row>
-    <row r="192" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>151.69999999999999</v>
+      </c>
+      <c r="I191" s="1"/>
+    </row>
+    <row r="192" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
         <v>66</v>
       </c>
@@ -7934,80 +6871,128 @@
         <v>272</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H192" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
-        <v>0</v>
-      </c>
-      <c r="I192" s="1">
         <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
         <v>256</v>
       </c>
-      <c r="J192" s="1"/>
-      <c r="K192" s="1"/>
-    </row>
-    <row r="193" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I192" s="1"/>
+    </row>
+    <row r="193" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="C193">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="D193" s="1">
         <f>C193-C193*15/100</f>
-        <v>272</v>
+        <v>242.25</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="G193" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H193" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>233.7</v>
+      </c>
+      <c r="I193" s="1"/>
+    </row>
+    <row r="194" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C194">
+        <v>335</v>
+      </c>
+      <c r="D194" s="1">
+        <f>C194-C194*15/100</f>
+        <v>284.75</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H194" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*18%</f>
+        <v>274.7</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C195">
+        <v>349</v>
+      </c>
+      <c r="D195" s="1">
+        <f>C195-C195*15/100</f>
+        <v>296.64999999999998</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G195" s="1"/>
+      <c r="H195" s="1">
+        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
+        <v>279.2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="H193" s="1">
-        <f>SUM(الجدول1[[#This Row],[فاتورة شراء 2]:[فاتورة شراء 1]])</f>
+      <c r="B196" s="1"/>
+      <c r="D196" s="1"/>
+      <c r="E196" s="1"/>
+      <c r="F196" s="1"/>
+      <c r="G196" s="1"/>
+      <c r="H196" s="1"/>
+      <c r="I196">
+        <f>SUMPRODUCT(الجدول1[فاتورة شراء - 1],الجدول1[سعر الشراء])-(SUMPRODUCT(الجدول1[فاتورة شراء - 1],الجدول1[سعر الشراء])*2%)</f>
         <v>0</v>
       </c>
-      <c r="I193" s="1">
-        <f>الجدول1[[#This Row],[سعر الغلاف]]-الجدول1[[#This Row],[سعر الغلاف]]*20/100</f>
-        <v>256</v>
-      </c>
-      <c r="J193" s="1"/>
-      <c r="K193" s="1"/>
-    </row>
-    <row r="194" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B194" s="1"/>
-      <c r="D194" s="1"/>
-      <c r="E194" s="1"/>
-      <c r="F194" s="1"/>
-      <c r="G194" s="1"/>
-      <c r="H194" s="1"/>
-      <c r="I194" s="1"/>
-      <c r="J194" s="1"/>
-      <c r="K194" s="1">
-        <f>SUBTOTAL(103,الجدول1[فاتورة شراء 1])</f>
-        <v>0</v>
+    </row>
+    <row r="198" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C198">
+        <f>160+150</f>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
